--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -1063,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1646,10 +1646,13 @@
     <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1662,8 +1665,14 @@
     <xf numFmtId="49" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
@@ -2583,7 +2592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" style="141" min="1" max="1"/>
@@ -2595,9 +2604,9 @@
     <col width="27.675" customWidth="1" style="141" min="7" max="7"/>
     <col width="22.6333333333333" customWidth="1" style="184" min="8" max="8"/>
     <col width="44" customWidth="1" style="141" min="9" max="9"/>
-    <col width="46" customWidth="1" style="141" min="10" max="10"/>
+    <col width="14.6" customWidth="1" style="141" min="10" max="10"/>
     <col width="14" customWidth="1" style="141" min="11" max="21"/>
-    <col width="9" customWidth="1" style="141" min="22" max="16383"/>
+    <col width="46" customWidth="1" style="141" min="22" max="16383"/>
   </cols>
   <sheetData>
     <row r="1" ht="49" customHeight="1" s="70">
@@ -2655,11 +2664,7 @@
           <t>往年申报链接</t>
         </is>
       </c>
-      <c r="J2" s="193" t="inlineStr">
-        <is>
-          <t>最新更新（2026-09-28）</t>
-        </is>
-      </c>
+      <c r="J2" s="150" t="n"/>
       <c r="K2" s="151" t="n"/>
       <c r="L2" s="151" t="n"/>
       <c r="M2" s="151" t="n"/>
@@ -2671,6 +2676,11 @@
       <c r="S2" s="151" t="n"/>
       <c r="T2" s="151" t="n"/>
       <c r="U2" s="151" t="n"/>
+      <c r="V2" s="193" t="inlineStr">
+        <is>
+          <t>最新更新（2026-09-28）</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1" s="70">
       <c r="A3" s="190" t="n">
@@ -3420,7 +3430,19 @@
           <t>https://service.most.gov.cn/kjjh_tztg_all/20260828/5864.html</t>
         </is>
       </c>
-      <c r="J18" s="200" t="inlineStr">
+      <c r="J18" s="200" t="n"/>
+      <c r="K18" s="201" t="n"/>
+      <c r="L18" s="201" t="n"/>
+      <c r="M18" s="201" t="n"/>
+      <c r="N18" s="201" t="n"/>
+      <c r="O18" s="201" t="n"/>
+      <c r="P18" s="201" t="n"/>
+      <c r="Q18" s="201" t="n"/>
+      <c r="R18" s="201" t="n"/>
+      <c r="S18" s="201" t="n"/>
+      <c r="T18" s="201" t="n"/>
+      <c r="U18" s="201" t="n"/>
+      <c r="V18" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度联合研发与示范项目指南2026-09-01发布，港澳单位可承担课题，受聘内地单位的港澳科学家可作负责人</t>
         </is>
@@ -3492,12 +3514,12 @@
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F20" s="202" t="inlineStr">
+      <c r="F20" s="203" t="inlineStr">
         <is>
           <t>由广东省科学技术厅和澳门科学技术发展基金联合征集、联合评审、联合资助。支持广东省创新主体联合澳门合作伙伴，在生物医药、新一代信息技术、节能环保、海洋科技、新材料、新能源、智能制造等涉及两地民生发展和前沿科技的领域开展联合技术研发及成果产业化合作。本专题优先支持在横琴、南沙等重大合作平台实施或落地转化的项目。</t>
         </is>
       </c>
-      <c r="G20" s="203" t="inlineStr">
+      <c r="G20" s="204" t="inlineStr">
         <is>
           <t>100万/项</t>
         </is>
@@ -3507,12 +3529,24 @@
           <t>11月-次年1月</t>
         </is>
       </c>
-      <c r="I20" s="204" t="inlineStr">
+      <c r="I20" s="205" t="inlineStr">
         <is>
           <t>https://gdstc.gd.gov.cn/zwgk_n/tzgg/content/post_4806341.html</t>
         </is>
       </c>
-      <c r="J20" s="200" t="inlineStr">
+      <c r="J20" s="200" t="n"/>
+      <c r="K20" s="201" t="n"/>
+      <c r="L20" s="201" t="n"/>
+      <c r="M20" s="201" t="n"/>
+      <c r="N20" s="201" t="n"/>
+      <c r="O20" s="201" t="n"/>
+      <c r="P20" s="201" t="n"/>
+      <c r="Q20" s="201" t="n"/>
+      <c r="R20" s="201" t="n"/>
+      <c r="S20" s="201" t="n"/>
+      <c r="T20" s="201" t="n"/>
+      <c r="U20" s="201" t="n"/>
+      <c r="V20" s="202" t="inlineStr">
         <is>
           <t>● 更新：2027年度申报指南已发布（2026-09-18），网上申报至2026-11-17 17:00，主管部门推荐截止11-24；粤科函资字〔2026〕1587号</t>
         </is>
@@ -3587,7 +3621,7 @@
 重点支持领域（2025）：网络与通信、半导体与集成电路、软件与信息服务、人工智能、高端装备与仪器、低空经济与空天、机器人、高性能材料、生物医药、海洋、合成生物、智能机器人、脑科学与脑机工程等。</t>
         </is>
       </c>
-      <c r="G22" s="203" t="inlineStr">
+      <c r="G22" s="204" t="inlineStr">
         <is>
           <t>资助强度300万</t>
         </is>
@@ -3597,12 +3631,24 @@
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I22" s="205" t="inlineStr">
+      <c r="I22" s="206" t="inlineStr">
         <is>
           <t>https://stic.sz.gov.cn/xxgk/tzgg/content/post_12116696.html?sessionid=</t>
         </is>
       </c>
-      <c r="J22" s="200" t="inlineStr">
+      <c r="J22" s="200" t="n"/>
+      <c r="K22" s="201" t="n"/>
+      <c r="L22" s="201" t="n"/>
+      <c r="M22" s="201" t="n"/>
+      <c r="N22" s="201" t="n"/>
+      <c r="O22" s="201" t="n"/>
+      <c r="P22" s="201" t="n"/>
+      <c r="Q22" s="201" t="n"/>
+      <c r="R22" s="201" t="n"/>
+      <c r="S22" s="201" t="n"/>
+      <c r="T22" s="201" t="n"/>
+      <c r="U22" s="201" t="n"/>
+      <c r="V22" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026-06-05印发《深港澳科技计划项目管理办法》，A类须获香港ITC或澳门FDCT评审通过方可立项</t>
         </is>
@@ -3678,7 +3724,7 @@
           <t>支持省内高校、科研机构及企业与香港特区、澳门特区、台湾地区开展科技创新合作，结合基础研究和应用技术战略性发展需求，开展联合研发。</t>
         </is>
       </c>
-      <c r="G24" s="203" t="inlineStr">
+      <c r="G24" s="204" t="inlineStr">
         <is>
           <t>30万元-100万元</t>
         </is>
@@ -3688,12 +3734,24 @@
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I24" s="205" t="inlineStr">
+      <c r="I24" s="206" t="inlineStr">
         <is>
           <t>https://kjt.sc.gov.cn/kjt/gstz/2025/9/17/1959a2ee35844389a80b43eb99950708.shtml</t>
         </is>
       </c>
-      <c r="J24" s="200" t="inlineStr">
+      <c r="J24" s="200" t="n"/>
+      <c r="K24" s="201" t="n"/>
+      <c r="L24" s="201" t="n"/>
+      <c r="M24" s="201" t="n"/>
+      <c r="N24" s="201" t="n"/>
+      <c r="O24" s="201" t="n"/>
+      <c r="P24" s="201" t="n"/>
+      <c r="Q24" s="201" t="n"/>
+      <c r="R24" s="201" t="n"/>
+      <c r="S24" s="201" t="n"/>
+      <c r="T24" s="201" t="n"/>
+      <c r="U24" s="201" t="n"/>
+      <c r="V24" s="202" t="inlineStr">
         <is>
           <t>● 更新：2027年度需求征集已完成，指南适时发布；2026年度项目2025-09已发布</t>
         </is>
@@ -3735,19 +3793,30 @@
           <t>3-4月</t>
         </is>
       </c>
-      <c r="I25" s="205" t="inlineStr">
+      <c r="I25" s="206" t="inlineStr">
         <is>
           <t>https://kxjst.jiangsu.gov.cn/art/2026/4/1/art_82568_11752538.html</t>
         </is>
       </c>
-      <c r="J25" s="200" t="inlineStr">
+      <c r="J25" s="207" t="n"/>
+      <c r="K25" s="201" t="inlineStr">
+        <is>
+          <t>这个不要了？</t>
+        </is>
+      </c>
+      <c r="L25" s="201" t="n"/>
+      <c r="M25" s="201" t="n"/>
+      <c r="N25" s="201" t="n"/>
+      <c r="O25" s="201" t="n"/>
+      <c r="P25" s="201" t="n"/>
+      <c r="Q25" s="201" t="n"/>
+      <c r="R25" s="201" t="n"/>
+      <c r="S25" s="201" t="n"/>
+      <c r="T25" s="201" t="n"/>
+      <c r="U25" s="201" t="n"/>
+      <c r="V25" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度申报中（苏科资发〔2026〕26号），长三角—新加坡第五轮网上填报截止2026-10-12 17:30</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>这个不要了？</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3941,24 @@
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I28" s="206" t="inlineStr">
+      <c r="I28" s="208" t="inlineStr">
         <is>
           <t>https://kjt.shanxi.gov.cn/xxgk/zfxxgkml/acs_11737/gjyqykjhzc/202608/t20260831_10210987.shtml</t>
         </is>
       </c>
-      <c r="J28" s="200" t="inlineStr">
+      <c r="J28" s="209" t="n"/>
+      <c r="K28" s="201" t="n"/>
+      <c r="L28" s="201" t="n"/>
+      <c r="M28" s="201" t="n"/>
+      <c r="N28" s="201" t="n"/>
+      <c r="O28" s="201" t="n"/>
+      <c r="P28" s="201" t="n"/>
+      <c r="Q28" s="201" t="n"/>
+      <c r="R28" s="201" t="n"/>
+      <c r="S28" s="201" t="n"/>
+      <c r="T28" s="201" t="n"/>
+      <c r="U28" s="201" t="n"/>
+      <c r="V28" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度设「与香港、澳门科技合作交流项目」，港澳方向不超过50万/项，2026年9月申报中</t>
         </is>
@@ -3959,12 +4040,24 @@
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I30" s="207" t="inlineStr">
+      <c r="I30" s="210" t="inlineStr">
         <is>
           <t>https://kjt.zj.gov.cn/col/col1229225203/art/2026/art_e495d70575a44848947646e93ca2948c.html</t>
         </is>
       </c>
-      <c r="J30" s="200" t="inlineStr">
+      <c r="J30" s="209" t="n"/>
+      <c r="K30" s="201" t="n"/>
+      <c r="L30" s="201" t="n"/>
+      <c r="M30" s="201" t="n"/>
+      <c r="N30" s="201" t="n"/>
+      <c r="O30" s="201" t="n"/>
+      <c r="P30" s="201" t="n"/>
+      <c r="Q30" s="201" t="n"/>
+      <c r="R30" s="201" t="n"/>
+      <c r="S30" s="201" t="n"/>
+      <c r="T30" s="201" t="n"/>
+      <c r="U30" s="201" t="n"/>
+      <c r="V30" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度科技合作项目启动申报（2026-09），含国际（含港澳台）科技合作项目</t>
         </is>
@@ -4387,92 +4480,92 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="70">
-      <c r="A41" s="208" t="n">
+      <c r="A41" s="211" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="209" t="inlineStr">
+      <c r="B41" s="212" t="inlineStr">
         <is>
           <t>国家科技部</t>
         </is>
       </c>
-      <c r="C41" s="209" t="inlineStr">
+      <c r="C41" s="212" t="inlineStr">
         <is>
           <t>新一代人工智能国家科技重大专项2026年度公开项目</t>
         </is>
       </c>
-      <c r="D41" s="209" t="inlineStr"/>
-      <c r="E41" s="209" t="inlineStr">
+      <c r="D41" s="212" t="inlineStr"/>
+      <c r="E41" s="212" t="inlineStr">
         <is>
           <t>教授（参与，名单内港澳单位可参与）</t>
         </is>
       </c>
-      <c r="F41" s="209" t="inlineStr">
+      <c r="F41" s="212" t="inlineStr">
         <is>
           <t>申报附件含内地与香港、内地与澳门科技合作委员会协商确定的港澳科研单位名单</t>
         </is>
       </c>
-      <c r="G41" s="209" t="inlineStr">
+      <c r="G41" s="212" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H41" s="209" t="inlineStr">
+      <c r="H41" s="212" t="inlineStr">
         <is>
           <t>2026年度第一批申报中</t>
         </is>
       </c>
-      <c r="I41" s="210" t="inlineStr">
+      <c r="I41" s="213" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/</t>
         </is>
       </c>
-      <c r="J41" s="211" t="inlineStr">
+      <c r="V41" s="214" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度第一批公开项目申报启动，名单内港澳单位可参与</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="208" t="n">
+      <c r="A42" s="211" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="209" t="inlineStr">
+      <c r="B42" s="212" t="inlineStr">
         <is>
           <t>国家自然科学基金</t>
         </is>
       </c>
-      <c r="C42" s="209" t="inlineStr">
+      <c r="C42" s="212" t="inlineStr">
         <is>
           <t>NSFC民营企业创新发展联合基金（术理创新）</t>
         </is>
       </c>
-      <c r="D42" s="209" t="inlineStr"/>
-      <c r="E42" s="209" t="inlineStr">
+      <c r="D42" s="212" t="inlineStr"/>
+      <c r="E42" s="212" t="inlineStr">
         <is>
           <t>教授（主申/参与）</t>
         </is>
       </c>
-      <c r="F42" s="209" t="inlineStr">
+      <c r="F42" s="212" t="inlineStr">
         <is>
           <t>企业出资的NSFC联合基金，按国自然流程申报；脑机接口与神经调控方向</t>
         </is>
       </c>
-      <c r="G42" s="209" t="inlineStr">
+      <c r="G42" s="212" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H42" s="209" t="inlineStr">
+      <c r="H42" s="212" t="inlineStr">
         <is>
           <t>2026-06发布</t>
         </is>
       </c>
-      <c r="I42" s="210" t="inlineStr">
+      <c r="I42" s="213" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="J42" s="211" t="inlineStr">
+      <c r="V42" s="214" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度项目申报中（脑机接口与神经调控方向）</t>
         </is>
@@ -4537,7 +4630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.891666666666669" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" style="70" min="1" max="1"/>
@@ -4548,9 +4641,9 @@
     <col width="37.6083333333333" customWidth="1" style="70" min="6" max="6"/>
     <col width="22.6333333333333" customWidth="1" style="70" min="7" max="7"/>
     <col width="44" customWidth="1" style="70" min="8" max="8"/>
-    <col width="46" customWidth="1" style="70" min="9" max="9"/>
+    <col width="14.6" customWidth="1" style="70" min="9" max="9"/>
     <col width="14" customWidth="1" style="70" min="10" max="20"/>
-    <col width="9" customWidth="1" style="70" min="21" max="16384"/>
+    <col width="46" customWidth="1" style="70" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="49" customHeight="1" s="70">
@@ -4602,7 +4695,8 @@
           <t>往年申报链接</t>
         </is>
       </c>
-      <c r="I2" s="193" t="inlineStr">
+      <c r="I2" s="118" t="n"/>
+      <c r="U2" s="193" t="inlineStr">
         <is>
           <t>最新更新（2026-09-28）</t>
         </is>
@@ -4612,7 +4706,7 @@
       <c r="A3" s="190" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="212" t="inlineStr">
+      <c r="B3" s="215" t="inlineStr">
         <is>
           <t>社科项目</t>
         </is>
@@ -4976,7 +5070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" style="70" min="1" max="1"/>
@@ -4986,9 +5080,9 @@
     <col width="37.625" customWidth="1" style="70" min="5" max="5"/>
     <col width="22.625" customWidth="1" style="70" min="6" max="6"/>
     <col width="44" customWidth="1" style="70" min="7" max="7"/>
-    <col width="46" customWidth="1" style="70" min="8" max="8"/>
+    <col width="14.625" customWidth="1" style="70" min="8" max="8"/>
     <col width="14" customWidth="1" style="70" min="9" max="19"/>
-    <col width="9" customWidth="1" style="141" min="20" max="16383"/>
+    <col width="46" customWidth="1" style="141" min="20" max="16383"/>
   </cols>
   <sheetData>
     <row r="1" ht="48.95" customFormat="1" customHeight="1" s="141">
@@ -5035,7 +5129,8 @@
           <t>往年申报链接</t>
         </is>
       </c>
-      <c r="H2" s="193" t="inlineStr">
+      <c r="H2" s="118" t="n"/>
+      <c r="T2" s="193" t="inlineStr">
         <is>
           <t>最新更新（2026-09-28）</t>
         </is>
@@ -5106,7 +5201,7 @@
           <t>何享健青年科学家项目</t>
         </is>
       </c>
-      <c r="C4" s="213" t="inlineStr">
+      <c r="C4" s="216" t="inlineStr">
         <is>
           <t>研究院全职研究人员</t>
         </is>
@@ -5129,12 +5224,29 @@
           <t>11月-次年2月</t>
         </is>
       </c>
-      <c r="G4" s="205" t="inlineStr">
+      <c r="G4" s="206" t="inlineStr">
         <is>
           <t>https://www.heprize.org/Home</t>
         </is>
       </c>
-      <c r="H4" s="200" t="inlineStr">
+      <c r="H4" s="209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评审流程按照“提名机构提交材料-秘书处形式审查-同行评审专家评审-评审委员会评审-理事会审批-获资助人名单公布”严格执行。
+</t>
+        </is>
+      </c>
+      <c r="I4" s="201" t="n"/>
+      <c r="J4" s="201" t="n"/>
+      <c r="K4" s="201" t="n"/>
+      <c r="L4" s="201" t="n"/>
+      <c r="M4" s="201" t="n"/>
+      <c r="N4" s="201" t="n"/>
+      <c r="O4" s="201" t="n"/>
+      <c r="P4" s="201" t="n"/>
+      <c r="Q4" s="201" t="n"/>
+      <c r="R4" s="201" t="n"/>
+      <c r="S4" s="201" t="n"/>
+      <c r="T4" s="202" t="inlineStr">
         <is>
           <t>● 更新：第二期已启动（2025-11-03正式启动），200万元/3年，研究院全职研究人员可申</t>
         </is>
@@ -6477,7 +6589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T288"/>
+  <dimension ref="A1:U288"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="7" customWidth="1" style="70" min="1" max="1"/>
@@ -6491,8 +6603,9 @@
     <col width="9" customWidth="1" style="70" min="9" max="9"/>
     <col width="12" customWidth="1" style="70" min="10" max="11"/>
     <col width="17" customWidth="1" style="70" min="12" max="12"/>
-    <col width="46" customWidth="1" style="70" min="13" max="13"/>
+    <col width="30" customWidth="1" style="70" min="13" max="13"/>
     <col width="14" customWidth="1" style="70" min="14" max="20"/>
+    <col width="46" customWidth="1" style="70" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="39" customHeight="1" s="70">
@@ -6501,18 +6614,18 @@
           <t>重点实验室开放课题清单</t>
         </is>
       </c>
-      <c r="B1" s="214" t="n"/>
-      <c r="C1" s="214" t="n"/>
-      <c r="D1" s="214" t="n"/>
-      <c r="E1" s="214" t="n"/>
-      <c r="F1" s="214" t="n"/>
-      <c r="G1" s="214" t="n"/>
-      <c r="H1" s="214" t="n"/>
-      <c r="I1" s="214" t="n"/>
-      <c r="J1" s="214" t="n"/>
-      <c r="K1" s="214" t="n"/>
-      <c r="L1" s="214" t="n"/>
-      <c r="M1" s="214" t="n"/>
+      <c r="B1" s="217" t="n"/>
+      <c r="C1" s="217" t="n"/>
+      <c r="D1" s="217" t="n"/>
+      <c r="E1" s="217" t="n"/>
+      <c r="F1" s="217" t="n"/>
+      <c r="G1" s="217" t="n"/>
+      <c r="H1" s="217" t="n"/>
+      <c r="I1" s="217" t="n"/>
+      <c r="J1" s="217" t="n"/>
+      <c r="K1" s="217" t="n"/>
+      <c r="L1" s="217" t="n"/>
+      <c r="M1" s="217" t="n"/>
     </row>
     <row r="2" ht="41.25" customHeight="1" s="70">
       <c r="A2" s="5" t="inlineStr">
@@ -6565,7 +6678,7 @@
           <t>公告月份</t>
         </is>
       </c>
-      <c r="K2" s="215" t="inlineStr">
+      <c r="K2" s="218" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -6575,9 +6688,9 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="M2" s="216" t="inlineStr">
-        <is>
-          <t>最新更新（2026-09-28）</t>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>相关链接</t>
         </is>
       </c>
       <c r="N2" s="10" t="n"/>
@@ -6587,6 +6700,11 @@
       <c r="R2" s="10" t="n"/>
       <c r="S2" s="10" t="n"/>
       <c r="T2" s="10" t="n"/>
+      <c r="U2" s="219" t="inlineStr">
+        <is>
+          <t>最新更新（2026-09-28）</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1" s="70">
       <c r="A3" s="11" t="n">
@@ -6627,84 +6745,84 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="217" t="inlineStr">
+      <c r="I3" s="220" t="inlineStr">
         <is>
           <t>http://sklpre.zju.edu.cn/redir.php?catalog_id=60520&amp;object_id=63561</t>
         </is>
       </c>
       <c r="J3" s="15" t="n"/>
-      <c r="K3" s="218" t="n"/>
+      <c r="K3" s="221" t="n"/>
       <c r="L3" s="17" t="n"/>
       <c r="M3" s="18" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="219" t="n"/>
-      <c r="B4" s="219" t="n"/>
-      <c r="C4" s="219" t="n"/>
+      <c r="A4" s="222" t="n"/>
+      <c r="B4" s="222" t="n"/>
+      <c r="C4" s="222" t="n"/>
       <c r="D4" s="12" t="inlineStr">
         <is>
           <t>天津大学</t>
         </is>
       </c>
-      <c r="E4" s="219" t="n"/>
-      <c r="F4" s="219" t="n"/>
-      <c r="G4" s="219" t="n"/>
+      <c r="E4" s="222" t="n"/>
+      <c r="F4" s="222" t="n"/>
+      <c r="G4" s="222" t="n"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="219" t="n"/>
+      <c r="I4" s="222" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="218" t="n"/>
+      <c r="K4" s="221" t="n"/>
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="219" t="n"/>
-      <c r="B5" s="219" t="n"/>
-      <c r="C5" s="219" t="n"/>
+      <c r="A5" s="222" t="n"/>
+      <c r="B5" s="222" t="n"/>
+      <c r="C5" s="222" t="n"/>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>华东理工大学</t>
         </is>
       </c>
-      <c r="E5" s="219" t="n"/>
-      <c r="F5" s="219" t="n"/>
-      <c r="G5" s="219" t="n"/>
+      <c r="E5" s="222" t="n"/>
+      <c r="F5" s="222" t="n"/>
+      <c r="G5" s="222" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="219" t="n"/>
+      <c r="I5" s="222" t="n"/>
       <c r="J5" s="15" t="n"/>
-      <c r="K5" s="218" t="n"/>
+      <c r="K5" s="221" t="n"/>
       <c r="L5" s="17" t="n"/>
       <c r="M5" s="18" t="n"/>
     </row>
     <row r="6" ht="55.5" customHeight="1" s="70">
-      <c r="A6" s="220" t="n"/>
-      <c r="B6" s="220" t="n"/>
-      <c r="C6" s="220" t="n"/>
+      <c r="A6" s="223" t="n"/>
+      <c r="B6" s="223" t="n"/>
+      <c r="C6" s="223" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E6" s="220" t="n"/>
-      <c r="F6" s="220" t="n"/>
-      <c r="G6" s="220" t="n"/>
+      <c r="E6" s="223" t="n"/>
+      <c r="F6" s="223" t="n"/>
+      <c r="G6" s="223" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I6" s="220" t="n"/>
+      <c r="I6" s="223" t="n"/>
       <c r="J6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="221" t="n">
+      <c r="K6" s="224" t="n">
         <v>44679</v>
       </c>
       <c r="L6" s="17" t="n"/>
@@ -6757,30 +6875,30 @@
       <c r="J7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="222" t="n">
+      <c r="K7" s="225" t="n">
         <v>44677</v>
       </c>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="70">
-      <c r="A8" s="220" t="n"/>
-      <c r="B8" s="220" t="n"/>
-      <c r="C8" s="220" t="n"/>
+      <c r="A8" s="223" t="n"/>
+      <c r="B8" s="223" t="n"/>
+      <c r="C8" s="223" t="n"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>中国石油大学（华东）</t>
         </is>
       </c>
-      <c r="E8" s="220" t="n"/>
-      <c r="F8" s="220" t="n"/>
-      <c r="G8" s="220" t="n"/>
-      <c r="H8" s="220" t="n"/>
-      <c r="I8" s="220" t="n"/>
-      <c r="J8" s="220" t="n"/>
-      <c r="K8" s="220" t="n"/>
-      <c r="L8" s="220" t="n"/>
-      <c r="M8" s="220" t="n"/>
+      <c r="E8" s="223" t="n"/>
+      <c r="F8" s="223" t="n"/>
+      <c r="G8" s="223" t="n"/>
+      <c r="H8" s="223" t="n"/>
+      <c r="I8" s="223" t="n"/>
+      <c r="J8" s="223" t="n"/>
+      <c r="K8" s="223" t="n"/>
+      <c r="L8" s="223" t="n"/>
+      <c r="M8" s="223" t="n"/>
     </row>
     <row r="9" ht="44.25" customHeight="1" s="70">
       <c r="A9" s="11" t="n">
@@ -6827,7 +6945,7 @@
         </is>
       </c>
       <c r="J9" s="15" t="n"/>
-      <c r="K9" s="218" t="n"/>
+      <c r="K9" s="221" t="n"/>
       <c r="L9" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -6880,7 +6998,7 @@
         </is>
       </c>
       <c r="J10" s="15" t="n"/>
-      <c r="K10" s="218" t="n"/>
+      <c r="K10" s="221" t="n"/>
       <c r="L10" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -6939,7 +7057,7 @@
       <c r="J11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="221" t="n">
+      <c r="K11" s="224" t="n">
         <v>44727</v>
       </c>
       <c r="L11" s="26" t="inlineStr">
@@ -6986,7 +7104,7 @@
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="15" t="n"/>
-      <c r="K12" s="218" t="n"/>
+      <c r="K12" s="221" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="29" t="inlineStr">
         <is>
@@ -7039,7 +7157,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n"/>
-      <c r="K13" s="218" t="n"/>
+      <c r="K13" s="221" t="n"/>
       <c r="L13" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7096,7 +7214,7 @@
         </is>
       </c>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="218" t="n"/>
+      <c r="K14" s="221" t="n"/>
       <c r="L14" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7155,7 +7273,7 @@
       <c r="J15" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="221" t="n">
+      <c r="K15" s="224" t="n">
         <v>44774</v>
       </c>
       <c r="L15" s="26" t="inlineStr">
@@ -7212,7 +7330,7 @@
       <c r="J16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="221" t="n">
+      <c r="K16" s="224" t="n">
         <v>44731</v>
       </c>
       <c r="L16" s="26" t="inlineStr">
@@ -7269,7 +7387,7 @@
       <c r="J17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="221" t="n">
+      <c r="K17" s="224" t="n">
         <v>44696</v>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -7318,7 +7436,7 @@
       <c r="J18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="221" t="n">
+      <c r="K18" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L18" s="26" t="inlineStr">
@@ -7379,7 +7497,7 @@
       <c r="J19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K19" s="221" t="n">
+      <c r="K19" s="224" t="n">
         <v>44866</v>
       </c>
       <c r="L19" s="26" t="inlineStr">
@@ -7440,7 +7558,7 @@
       <c r="J20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="221" t="n">
+      <c r="K20" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L20" s="26" t="inlineStr">
@@ -7495,7 +7613,7 @@
       </c>
       <c r="I21" s="34" t="n"/>
       <c r="J21" s="15" t="n"/>
-      <c r="K21" s="218" t="n"/>
+      <c r="K21" s="221" t="n"/>
       <c r="L21" s="26" t="inlineStr">
         <is>
           <t>最近几年未有相关的课题申请消息</t>
@@ -7554,7 +7672,7 @@
       <c r="J22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="223" t="n">
+      <c r="K22" s="226" t="n">
         <v>44694</v>
       </c>
       <c r="L22" s="36" t="n"/>
@@ -7597,7 +7715,7 @@
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="28" t="n"/>
       <c r="J23" s="15" t="n"/>
-      <c r="K23" s="224" t="n"/>
+      <c r="K23" s="227" t="n"/>
       <c r="L23" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7642,7 +7760,7 @@
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="28" t="n"/>
       <c r="J24" s="15" t="n"/>
-      <c r="K24" s="218" t="n"/>
+      <c r="K24" s="221" t="n"/>
       <c r="L24" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7697,7 +7815,7 @@
       <c r="J25" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="221" t="n">
+      <c r="K25" s="224" t="n">
         <v>44822</v>
       </c>
       <c r="L25" s="17" t="n"/>
@@ -7750,7 +7868,7 @@
       <c r="J26" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="221" t="n">
+      <c r="K26" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L26" s="39" t="inlineStr">
@@ -7811,7 +7929,7 @@
       <c r="J27" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="221" t="n">
+      <c r="K27" s="224" t="n">
         <v>44804</v>
       </c>
       <c r="L27" s="40" t="n"/>
@@ -7864,7 +7982,7 @@
       <c r="J28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="221" t="n">
+      <c r="K28" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L28" s="26" t="inlineStr">
@@ -7925,7 +8043,7 @@
       <c r="J29" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="221" t="n">
+      <c r="K29" s="224" t="n">
         <v>44835</v>
       </c>
       <c r="L29" s="17" t="n"/>
@@ -7978,7 +8096,7 @@
       <c r="J30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="221" t="n">
+      <c r="K30" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L30" s="26" t="inlineStr">
@@ -8033,7 +8151,7 @@
         </is>
       </c>
       <c r="J31" s="15" t="n"/>
-      <c r="K31" s="218" t="n"/>
+      <c r="K31" s="221" t="n"/>
       <c r="L31" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关消息</t>
@@ -8088,7 +8206,7 @@
       <c r="J32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="221" t="n">
+      <c r="K32" s="224" t="n">
         <v>44631</v>
       </c>
       <c r="L32" s="17" t="n"/>
@@ -8139,7 +8257,7 @@
       </c>
       <c r="I33" s="28" t="n"/>
       <c r="J33" s="15" t="n"/>
-      <c r="K33" s="218" t="n"/>
+      <c r="K33" s="221" t="n"/>
       <c r="L33" s="17" t="n"/>
       <c r="M33" s="18" t="n"/>
     </row>
@@ -8190,7 +8308,7 @@
       <c r="J34" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="221" t="n">
+      <c r="K34" s="224" t="n">
         <v>44657</v>
       </c>
       <c r="L34" s="17" t="n"/>
@@ -8237,7 +8355,7 @@
       </c>
       <c r="I35" s="28" t="n"/>
       <c r="J35" s="15" t="n"/>
-      <c r="K35" s="218" t="n"/>
+      <c r="K35" s="221" t="n"/>
       <c r="L35" s="17" t="n"/>
       <c r="M35" s="18" t="n"/>
     </row>
@@ -8282,7 +8400,7 @@
       </c>
       <c r="I36" s="28" t="n"/>
       <c r="J36" s="15" t="n"/>
-      <c r="K36" s="218" t="n"/>
+      <c r="K36" s="221" t="n"/>
       <c r="L36" s="17" t="n"/>
       <c r="M36" s="18" t="n"/>
     </row>
@@ -8333,7 +8451,7 @@
       <c r="J37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="221" t="n">
+      <c r="K37" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L37" s="26" t="inlineStr">
@@ -8390,7 +8508,7 @@
       <c r="J38" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="221" t="n">
+      <c r="K38" s="224" t="n">
         <v>44835</v>
       </c>
       <c r="L38" s="26" t="inlineStr">
@@ -8447,7 +8565,7 @@
       <c r="J39" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="221" t="n">
+      <c r="K39" s="224" t="n">
         <v>44690</v>
       </c>
       <c r="L39" s="17" t="n"/>
@@ -8500,30 +8618,30 @@
       <c r="J40" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K40" s="222" t="n">
+      <c r="K40" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L40" s="36" t="n"/>
       <c r="M40" s="18" t="n"/>
     </row>
     <row r="41" ht="24.75" customHeight="1" s="70">
-      <c r="A41" s="220" t="n"/>
-      <c r="B41" s="220" t="n"/>
-      <c r="C41" s="220" t="n"/>
+      <c r="A41" s="223" t="n"/>
+      <c r="B41" s="223" t="n"/>
+      <c r="C41" s="223" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="E41" s="220" t="n"/>
-      <c r="F41" s="220" t="n"/>
-      <c r="G41" s="220" t="n"/>
-      <c r="H41" s="220" t="n"/>
-      <c r="I41" s="220" t="n"/>
-      <c r="J41" s="220" t="n"/>
-      <c r="K41" s="220" t="n"/>
-      <c r="L41" s="225" t="n"/>
-      <c r="M41" s="220" t="n"/>
+      <c r="E41" s="223" t="n"/>
+      <c r="F41" s="223" t="n"/>
+      <c r="G41" s="223" t="n"/>
+      <c r="H41" s="223" t="n"/>
+      <c r="I41" s="223" t="n"/>
+      <c r="J41" s="223" t="n"/>
+      <c r="K41" s="223" t="n"/>
+      <c r="L41" s="228" t="n"/>
+      <c r="M41" s="223" t="n"/>
     </row>
     <row r="42" ht="24.75" customHeight="1" s="70">
       <c r="A42" s="11" t="n">
@@ -8566,7 +8684,7 @@
       </c>
       <c r="I42" s="28" t="n"/>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="218" t="n"/>
+      <c r="K42" s="221" t="n"/>
       <c r="L42" s="17" t="n"/>
       <c r="M42" s="18" t="n"/>
     </row>
@@ -8611,7 +8729,7 @@
       </c>
       <c r="I43" s="28" t="n"/>
       <c r="J43" s="15" t="n"/>
-      <c r="K43" s="218" t="n"/>
+      <c r="K43" s="221" t="n"/>
       <c r="L43" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -8664,7 +8782,7 @@
       </c>
       <c r="I44" s="28" t="n"/>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="218" t="n"/>
+      <c r="K44" s="221" t="n"/>
       <c r="L44" s="17" t="n"/>
       <c r="M44" s="18" t="n"/>
     </row>
@@ -8715,7 +8833,7 @@
       <c r="J45" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="221" t="n">
+      <c r="K45" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L45" s="26" t="inlineStr">
@@ -8776,7 +8894,7 @@
       <c r="J46" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="221" t="n">
+      <c r="K46" s="224" t="n">
         <v>44642</v>
       </c>
       <c r="L46" s="26" t="inlineStr">
@@ -8827,7 +8945,7 @@
       </c>
       <c r="I47" s="28" t="n"/>
       <c r="J47" s="15" t="n"/>
-      <c r="K47" s="218" t="n"/>
+      <c r="K47" s="221" t="n"/>
       <c r="L47" s="17" t="n"/>
       <c r="M47" s="18" t="n"/>
     </row>
@@ -8878,7 +8996,7 @@
       <c r="J48" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K48" s="221" t="n">
+      <c r="K48" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L48" s="17" t="n"/>
@@ -8925,7 +9043,7 @@
       </c>
       <c r="I49" s="28" t="n"/>
       <c r="J49" s="15" t="n"/>
-      <c r="K49" s="218" t="n"/>
+      <c r="K49" s="221" t="n"/>
       <c r="L49" s="26" t="inlineStr">
         <is>
           <t>官网信息不全</t>
@@ -8984,68 +9102,68 @@
       <c r="J50" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="222" t="n">
+      <c r="K50" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L50" s="18" t="n"/>
       <c r="M50" s="18" t="n"/>
     </row>
     <row r="51" ht="24.75" customHeight="1" s="70">
-      <c r="A51" s="219" t="n"/>
-      <c r="B51" s="219" t="n"/>
-      <c r="C51" s="219" t="n"/>
+      <c r="A51" s="222" t="n"/>
+      <c r="B51" s="222" t="n"/>
+      <c r="C51" s="222" t="n"/>
       <c r="D51" s="12" t="inlineStr">
         <is>
           <t>中国科学院生态环境研究中心</t>
         </is>
       </c>
-      <c r="E51" s="219" t="n"/>
-      <c r="F51" s="219" t="n"/>
-      <c r="G51" s="219" t="n"/>
-      <c r="H51" s="219" t="n"/>
-      <c r="I51" s="219" t="n"/>
-      <c r="J51" s="219" t="n"/>
-      <c r="K51" s="219" t="n"/>
-      <c r="L51" s="219" t="n"/>
-      <c r="M51" s="219" t="n"/>
+      <c r="E51" s="222" t="n"/>
+      <c r="F51" s="222" t="n"/>
+      <c r="G51" s="222" t="n"/>
+      <c r="H51" s="222" t="n"/>
+      <c r="I51" s="222" t="n"/>
+      <c r="J51" s="222" t="n"/>
+      <c r="K51" s="222" t="n"/>
+      <c r="L51" s="222" t="n"/>
+      <c r="M51" s="222" t="n"/>
     </row>
     <row r="52" ht="24.75" customHeight="1" s="70">
-      <c r="A52" s="219" t="n"/>
-      <c r="B52" s="219" t="n"/>
-      <c r="C52" s="219" t="n"/>
+      <c r="A52" s="222" t="n"/>
+      <c r="B52" s="222" t="n"/>
+      <c r="C52" s="222" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E52" s="219" t="n"/>
-      <c r="F52" s="219" t="n"/>
-      <c r="G52" s="219" t="n"/>
-      <c r="H52" s="219" t="n"/>
-      <c r="I52" s="219" t="n"/>
-      <c r="J52" s="219" t="n"/>
-      <c r="K52" s="219" t="n"/>
-      <c r="L52" s="219" t="n"/>
-      <c r="M52" s="219" t="n"/>
+      <c r="E52" s="222" t="n"/>
+      <c r="F52" s="222" t="n"/>
+      <c r="G52" s="222" t="n"/>
+      <c r="H52" s="222" t="n"/>
+      <c r="I52" s="222" t="n"/>
+      <c r="J52" s="222" t="n"/>
+      <c r="K52" s="222" t="n"/>
+      <c r="L52" s="222" t="n"/>
+      <c r="M52" s="222" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="70">
-      <c r="A53" s="220" t="n"/>
-      <c r="B53" s="220" t="n"/>
-      <c r="C53" s="220" t="n"/>
+      <c r="A53" s="223" t="n"/>
+      <c r="B53" s="223" t="n"/>
+      <c r="C53" s="223" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E53" s="220" t="n"/>
-      <c r="F53" s="220" t="n"/>
-      <c r="G53" s="220" t="n"/>
-      <c r="H53" s="220" t="n"/>
-      <c r="I53" s="220" t="n"/>
-      <c r="J53" s="220" t="n"/>
-      <c r="K53" s="220" t="n"/>
-      <c r="L53" s="220" t="n"/>
-      <c r="M53" s="220" t="n"/>
+      <c r="E53" s="223" t="n"/>
+      <c r="F53" s="223" t="n"/>
+      <c r="G53" s="223" t="n"/>
+      <c r="H53" s="223" t="n"/>
+      <c r="I53" s="223" t="n"/>
+      <c r="J53" s="223" t="n"/>
+      <c r="K53" s="223" t="n"/>
+      <c r="L53" s="223" t="n"/>
+      <c r="M53" s="223" t="n"/>
     </row>
     <row r="54" ht="24.75" customHeight="1" s="70">
       <c r="A54" s="11" t="n">
@@ -9088,7 +9206,7 @@
       </c>
       <c r="I54" s="28" t="n"/>
       <c r="J54" s="15" t="n"/>
-      <c r="K54" s="218" t="n"/>
+      <c r="K54" s="221" t="n"/>
       <c r="L54" s="17" t="n"/>
       <c r="M54" s="18" t="n"/>
     </row>
@@ -9139,30 +9257,30 @@
       <c r="J55" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="222" t="n">
+      <c r="K55" s="225" t="n">
         <v>44599</v>
       </c>
       <c r="L55" s="18" t="n"/>
       <c r="M55" s="18" t="n"/>
     </row>
     <row r="56" ht="24.75" customHeight="1" s="70">
-      <c r="A56" s="220" t="n"/>
-      <c r="B56" s="220" t="n"/>
-      <c r="C56" s="220" t="n"/>
+      <c r="A56" s="223" t="n"/>
+      <c r="B56" s="223" t="n"/>
+      <c r="C56" s="223" t="n"/>
       <c r="D56" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E56" s="220" t="n"/>
-      <c r="F56" s="220" t="n"/>
-      <c r="G56" s="220" t="n"/>
-      <c r="H56" s="220" t="n"/>
-      <c r="I56" s="220" t="n"/>
-      <c r="J56" s="220" t="n"/>
-      <c r="K56" s="220" t="n"/>
-      <c r="L56" s="220" t="n"/>
-      <c r="M56" s="220" t="n"/>
+      <c r="E56" s="223" t="n"/>
+      <c r="F56" s="223" t="n"/>
+      <c r="G56" s="223" t="n"/>
+      <c r="H56" s="223" t="n"/>
+      <c r="I56" s="223" t="n"/>
+      <c r="J56" s="223" t="n"/>
+      <c r="K56" s="223" t="n"/>
+      <c r="L56" s="223" t="n"/>
+      <c r="M56" s="223" t="n"/>
     </row>
     <row r="57" ht="24.75" customHeight="1" s="70">
       <c r="A57" s="11" t="n">
@@ -9211,7 +9329,7 @@
       <c r="J57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="221" t="n">
+      <c r="K57" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L57" s="26" t="inlineStr">
@@ -9268,7 +9386,7 @@
       <c r="J58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="221" t="n">
+      <c r="K58" s="224" t="n">
         <v>44658</v>
       </c>
       <c r="L58" s="26" t="inlineStr">
@@ -9325,7 +9443,7 @@
       <c r="J59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="226" t="n">
+      <c r="K59" s="229" t="n">
         <v>44615</v>
       </c>
       <c r="L59" s="36" t="n"/>
@@ -9378,7 +9496,7 @@
       <c r="J60" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K60" s="227" t="n">
+      <c r="K60" s="230" t="n">
         <v>44667</v>
       </c>
       <c r="L60" s="17" t="n"/>
@@ -9431,7 +9549,7 @@
       <c r="J61" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K61" s="221" t="n">
+      <c r="K61" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L61" s="17" t="n"/>
@@ -9484,30 +9602,30 @@
       <c r="J62" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K62" s="222" t="n">
+      <c r="K62" s="225" t="n">
         <v>44877</v>
       </c>
       <c r="L62" s="18" t="n"/>
       <c r="M62" s="18" t="n"/>
     </row>
     <row r="63" ht="24.75" customHeight="1" s="70">
-      <c r="A63" s="220" t="n"/>
-      <c r="B63" s="220" t="n"/>
-      <c r="C63" s="220" t="n"/>
+      <c r="A63" s="223" t="n"/>
+      <c r="B63" s="223" t="n"/>
+      <c r="C63" s="223" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学</t>
         </is>
       </c>
-      <c r="E63" s="220" t="n"/>
-      <c r="F63" s="220" t="n"/>
-      <c r="G63" s="220" t="n"/>
-      <c r="H63" s="220" t="n"/>
-      <c r="I63" s="220" t="n"/>
-      <c r="J63" s="220" t="n"/>
-      <c r="K63" s="220" t="n"/>
-      <c r="L63" s="220" t="n"/>
-      <c r="M63" s="220" t="n"/>
+      <c r="E63" s="223" t="n"/>
+      <c r="F63" s="223" t="n"/>
+      <c r="G63" s="223" t="n"/>
+      <c r="H63" s="223" t="n"/>
+      <c r="I63" s="223" t="n"/>
+      <c r="J63" s="223" t="n"/>
+      <c r="K63" s="223" t="n"/>
+      <c r="L63" s="223" t="n"/>
+      <c r="M63" s="223" t="n"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" s="70">
       <c r="A64" s="11" t="n">
@@ -9556,7 +9674,7 @@
       <c r="J64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="221" t="n">
+      <c r="K64" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L64" s="26" t="inlineStr">
@@ -9611,7 +9729,7 @@
       </c>
       <c r="I65" s="28" t="n"/>
       <c r="J65" s="15" t="n"/>
-      <c r="K65" s="218" t="n"/>
+      <c r="K65" s="221" t="n"/>
       <c r="L65" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -9666,7 +9784,7 @@
       <c r="J66" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K66" s="221" t="n">
+      <c r="K66" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L66" s="26" t="inlineStr">
@@ -9721,7 +9839,7 @@
       </c>
       <c r="I67" s="28" t="n"/>
       <c r="J67" s="15" t="n"/>
-      <c r="K67" s="218" t="n"/>
+      <c r="K67" s="221" t="n"/>
       <c r="L67" s="26" t="inlineStr">
         <is>
           <t>未找到往年信息</t>
@@ -9774,7 +9892,7 @@
       </c>
       <c r="I68" s="28" t="n"/>
       <c r="J68" s="15" t="n"/>
-      <c r="K68" s="218" t="n"/>
+      <c r="K68" s="221" t="n"/>
       <c r="L68" s="17" t="n"/>
       <c r="M68" s="18" t="n"/>
     </row>
@@ -9825,7 +9943,7 @@
       <c r="J69" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K69" s="221" t="n">
+      <c r="K69" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L69" s="26" t="inlineStr">
@@ -9882,7 +10000,7 @@
       <c r="J70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="221" t="n">
+      <c r="K70" s="224" t="n">
         <v>44565</v>
       </c>
       <c r="L70" s="26" t="inlineStr">
@@ -9939,30 +10057,30 @@
       <c r="J71" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K71" s="222" t="n">
+      <c r="K71" s="225" t="n">
         <v>44882</v>
       </c>
       <c r="L71" s="36" t="n"/>
       <c r="M71" s="18" t="n"/>
     </row>
     <row r="72" ht="24.75" customHeight="1" s="70">
-      <c r="A72" s="220" t="n"/>
-      <c r="B72" s="220" t="n"/>
-      <c r="C72" s="220" t="n"/>
+      <c r="A72" s="223" t="n"/>
+      <c r="B72" s="223" t="n"/>
+      <c r="C72" s="223" t="n"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
           <t>南京大学</t>
         </is>
       </c>
-      <c r="E72" s="220" t="n"/>
-      <c r="F72" s="220" t="n"/>
-      <c r="G72" s="220" t="n"/>
-      <c r="H72" s="220" t="n"/>
-      <c r="I72" s="220" t="n"/>
-      <c r="J72" s="220" t="n"/>
-      <c r="K72" s="220" t="n"/>
-      <c r="L72" s="225" t="n"/>
-      <c r="M72" s="220" t="n"/>
+      <c r="E72" s="223" t="n"/>
+      <c r="F72" s="223" t="n"/>
+      <c r="G72" s="223" t="n"/>
+      <c r="H72" s="223" t="n"/>
+      <c r="I72" s="223" t="n"/>
+      <c r="J72" s="223" t="n"/>
+      <c r="K72" s="223" t="n"/>
+      <c r="L72" s="228" t="n"/>
+      <c r="M72" s="223" t="n"/>
     </row>
     <row r="73" ht="24.75" customHeight="1" s="70">
       <c r="A73" s="11" t="n">
@@ -10011,7 +10129,7 @@
       <c r="J73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K73" s="221" t="n">
+      <c r="K73" s="224" t="n">
         <v>44670</v>
       </c>
       <c r="L73" s="26" t="inlineStr">
@@ -10068,7 +10186,7 @@
       <c r="J74" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K74" s="221" t="n">
+      <c r="K74" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L74" s="26" t="inlineStr">
@@ -10125,7 +10243,7 @@
       <c r="J75" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="221" t="n">
+      <c r="K75" s="224" t="n">
         <v>44588</v>
       </c>
       <c r="L75" s="26" t="inlineStr">
@@ -10182,7 +10300,7 @@
       <c r="J76" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="221" t="n">
+      <c r="K76" s="224" t="n">
         <v>44667</v>
       </c>
       <c r="L76" s="26" t="inlineStr">
@@ -10239,7 +10357,7 @@
       <c r="J77" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="221" t="n">
+      <c r="K77" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L77" s="26" t="inlineStr">
@@ -10296,7 +10414,7 @@
       <c r="J78" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K78" s="221" t="n">
+      <c r="K78" s="224" t="n">
         <v>44741</v>
       </c>
       <c r="L78" s="26" t="inlineStr">
@@ -10353,7 +10471,7 @@
       <c r="J79" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K79" s="221" t="n">
+      <c r="K79" s="224" t="n">
         <v>44825</v>
       </c>
       <c r="L79" s="17" t="n"/>
@@ -10406,7 +10524,7 @@
       <c r="J80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="228" t="n">
+      <c r="K80" s="231" t="n">
         <v>44709</v>
       </c>
       <c r="L80" s="36" t="n"/>
@@ -10459,7 +10577,7 @@
       <c r="J81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K81" s="229" t="n">
+      <c r="K81" s="232" t="n">
         <v>44670</v>
       </c>
       <c r="L81" s="17" t="n"/>
@@ -10502,7 +10620,7 @@
       <c r="H82" s="31" t="n"/>
       <c r="I82" s="48" t="n"/>
       <c r="J82" s="31" t="n"/>
-      <c r="K82" s="230" t="n"/>
+      <c r="K82" s="233" t="n"/>
       <c r="L82" s="29" t="inlineStr">
         <is>
           <t>不是专用连接，进不了官网</t>
@@ -10511,23 +10629,23 @@
       <c r="M82" s="18" t="n"/>
     </row>
     <row r="83" ht="24.75" customHeight="1" s="70">
-      <c r="A83" s="220" t="n"/>
-      <c r="B83" s="220" t="n"/>
-      <c r="C83" s="220" t="n"/>
+      <c r="A83" s="223" t="n"/>
+      <c r="B83" s="223" t="n"/>
+      <c r="C83" s="223" t="n"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
           <t>中国地质大学（北京）</t>
         </is>
       </c>
-      <c r="E83" s="220" t="n"/>
-      <c r="F83" s="220" t="n"/>
-      <c r="G83" s="220" t="n"/>
-      <c r="H83" s="220" t="n"/>
-      <c r="I83" s="220" t="n"/>
-      <c r="J83" s="220" t="n"/>
-      <c r="K83" s="220" t="n"/>
-      <c r="L83" s="220" t="n"/>
-      <c r="M83" s="220" t="n"/>
+      <c r="E83" s="223" t="n"/>
+      <c r="F83" s="223" t="n"/>
+      <c r="G83" s="223" t="n"/>
+      <c r="H83" s="223" t="n"/>
+      <c r="I83" s="223" t="n"/>
+      <c r="J83" s="223" t="n"/>
+      <c r="K83" s="223" t="n"/>
+      <c r="L83" s="223" t="n"/>
+      <c r="M83" s="223" t="n"/>
     </row>
     <row r="84" ht="24.75" customHeight="1" s="70">
       <c r="A84" s="11" t="n">
@@ -10576,7 +10694,7 @@
       <c r="J84" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K84" s="221" t="n">
+      <c r="K84" s="224" t="n">
         <v>44813</v>
       </c>
       <c r="L84" s="17" t="n"/>
@@ -10629,7 +10747,7 @@
       <c r="J85" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K85" s="221" t="n">
+      <c r="K85" s="224" t="n">
         <v>44881</v>
       </c>
       <c r="L85" s="26" t="inlineStr">
@@ -10686,7 +10804,7 @@
       <c r="J86" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="221" t="n">
+      <c r="K86" s="224" t="n">
         <v>44635</v>
       </c>
       <c r="L86" s="26" t="inlineStr">
@@ -10743,7 +10861,7 @@
       <c r="J87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K87" s="221" t="n">
+      <c r="K87" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L87" s="26" t="inlineStr">
@@ -10804,7 +10922,7 @@
       <c r="J88" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K88" s="221" t="n">
+      <c r="K88" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L88" s="26" t="inlineStr">
@@ -10861,7 +10979,7 @@
       <c r="J89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="221" t="n">
+      <c r="K89" s="224" t="n">
         <v>44592</v>
       </c>
       <c r="L89" s="26" t="inlineStr">
@@ -10872,17 +10990,17 @@
       <c r="M89" s="18" t="n"/>
     </row>
     <row r="90" ht="24.75" customHeight="1" s="70">
-      <c r="A90" s="220" t="n"/>
-      <c r="B90" s="220" t="n"/>
-      <c r="C90" s="220" t="n"/>
+      <c r="A90" s="223" t="n"/>
+      <c r="B90" s="223" t="n"/>
+      <c r="C90" s="223" t="n"/>
       <c r="D90" s="12" t="inlineStr">
         <is>
           <t>成都理工大学</t>
         </is>
       </c>
-      <c r="E90" s="220" t="n"/>
-      <c r="F90" s="220" t="n"/>
-      <c r="G90" s="220" t="n"/>
+      <c r="E90" s="223" t="n"/>
+      <c r="F90" s="223" t="n"/>
+      <c r="G90" s="223" t="n"/>
       <c r="H90" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -10896,7 +11014,7 @@
       <c r="J90" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K90" s="221" t="n">
+      <c r="K90" s="224" t="n">
         <v>44871</v>
       </c>
       <c r="L90" s="26" t="inlineStr">
@@ -10953,7 +11071,7 @@
       <c r="J91" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K91" s="221" t="n">
+      <c r="K91" s="224" t="n">
         <v>44806</v>
       </c>
       <c r="L91" s="26" t="inlineStr">
@@ -11010,7 +11128,7 @@
       <c r="J92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="221" t="n">
+      <c r="K92" s="224" t="n">
         <v>44576</v>
       </c>
       <c r="L92" s="26" t="inlineStr">
@@ -11061,7 +11179,7 @@
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="50" t="n"/>
-      <c r="K93" s="231" t="n"/>
+      <c r="K93" s="234" t="n"/>
       <c r="L93" s="17" t="n"/>
       <c r="M93" s="18" t="n"/>
     </row>
@@ -11112,7 +11230,7 @@
       <c r="J94" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K94" s="221" t="n">
+      <c r="K94" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L94" s="17" t="n"/>
@@ -11165,7 +11283,7 @@
       <c r="J95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K95" s="221" t="n">
+      <c r="K95" s="224" t="n">
         <v>44679</v>
       </c>
       <c r="L95" s="17" t="n"/>
@@ -11218,7 +11336,7 @@
       <c r="J96" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K96" s="221" t="n">
+      <c r="K96" s="224" t="n">
         <v>44840</v>
       </c>
       <c r="L96" s="17" t="n"/>
@@ -11271,7 +11389,7 @@
       <c r="J97" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K97" s="221" t="n">
+      <c r="K97" s="224" t="n">
         <v>44848</v>
       </c>
       <c r="L97" s="17" t="n"/>
@@ -11324,7 +11442,7 @@
       <c r="J98" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K98" s="221" t="n">
+      <c r="K98" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L98" s="17" t="n"/>
@@ -11377,7 +11495,7 @@
       <c r="J99" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="221" t="n">
+      <c r="K99" s="224" t="n">
         <v>44644</v>
       </c>
       <c r="L99" s="17" t="n"/>
@@ -11430,7 +11548,7 @@
       <c r="J100" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K100" s="221" t="n">
+      <c r="K100" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L100" s="26" t="inlineStr">
@@ -11491,7 +11609,7 @@
       <c r="J101" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K101" s="221" t="n">
+      <c r="K101" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L101" s="26" t="inlineStr">
@@ -11548,7 +11666,7 @@
       <c r="J102" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K102" s="221" t="n">
+      <c r="K102" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L102" s="26" t="inlineStr">
@@ -11599,22 +11717,22 @@
       </c>
       <c r="I103" s="28" t="n"/>
       <c r="J103" s="15" t="n"/>
-      <c r="K103" s="218" t="n"/>
+      <c r="K103" s="221" t="n"/>
       <c r="L103" s="17" t="n"/>
       <c r="M103" s="18" t="n"/>
     </row>
     <row r="104" ht="24.75" customHeight="1" s="70">
-      <c r="A104" s="219" t="n"/>
-      <c r="B104" s="219" t="n"/>
-      <c r="C104" s="219" t="n"/>
+      <c r="A104" s="222" t="n"/>
+      <c r="B104" s="222" t="n"/>
+      <c r="C104" s="222" t="n"/>
       <c r="D104" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E104" s="219" t="n"/>
-      <c r="F104" s="219" t="n"/>
-      <c r="G104" s="219" t="n"/>
+      <c r="E104" s="222" t="n"/>
+      <c r="F104" s="222" t="n"/>
+      <c r="G104" s="222" t="n"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11628,7 +11746,7 @@
       <c r="J104" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K104" s="221" t="n">
+      <c r="K104" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L104" s="26" t="inlineStr">
@@ -11639,17 +11757,17 @@
       <c r="M104" s="18" t="n"/>
     </row>
     <row r="105" ht="24.75" customHeight="1" s="70">
-      <c r="A105" s="220" t="n"/>
-      <c r="B105" s="220" t="n"/>
-      <c r="C105" s="220" t="n"/>
+      <c r="A105" s="223" t="n"/>
+      <c r="B105" s="223" t="n"/>
+      <c r="C105" s="223" t="n"/>
       <c r="D105" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E105" s="220" t="n"/>
-      <c r="F105" s="220" t="n"/>
-      <c r="G105" s="220" t="n"/>
+      <c r="E105" s="223" t="n"/>
+      <c r="F105" s="223" t="n"/>
+      <c r="G105" s="223" t="n"/>
       <c r="H105" s="52" t="inlineStr">
         <is>
           <t>否</t>
@@ -11708,7 +11826,7 @@
       <c r="J106" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="K106" s="229" t="n">
+      <c r="K106" s="232" t="n">
         <v>44814</v>
       </c>
       <c r="L106" s="40" t="n"/>
@@ -11755,7 +11873,7 @@
       </c>
       <c r="I107" s="56" t="n"/>
       <c r="J107" s="15" t="n"/>
-      <c r="K107" s="218" t="n"/>
+      <c r="K107" s="221" t="n"/>
       <c r="L107" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11812,7 +11930,7 @@
         </is>
       </c>
       <c r="J108" s="15" t="n"/>
-      <c r="K108" s="218" t="n"/>
+      <c r="K108" s="221" t="n"/>
       <c r="L108" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11861,7 +11979,7 @@
       </c>
       <c r="I109" s="28" t="n"/>
       <c r="J109" s="15" t="n"/>
-      <c r="K109" s="218" t="n"/>
+      <c r="K109" s="221" t="n"/>
       <c r="L109" s="26" t="inlineStr">
         <is>
           <t>网址打不开</t>
@@ -11914,7 +12032,7 @@
         </is>
       </c>
       <c r="J110" s="15" t="n"/>
-      <c r="K110" s="218" t="n"/>
+      <c r="K110" s="221" t="n"/>
       <c r="L110" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -11923,17 +12041,17 @@
       <c r="M110" s="18" t="n"/>
     </row>
     <row r="111" ht="24.75" customHeight="1" s="70">
-      <c r="A111" s="220" t="n"/>
-      <c r="B111" s="220" t="n"/>
-      <c r="C111" s="220" t="n"/>
+      <c r="A111" s="223" t="n"/>
+      <c r="B111" s="223" t="n"/>
+      <c r="C111" s="223" t="n"/>
       <c r="D111" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E111" s="220" t="n"/>
-      <c r="F111" s="220" t="n"/>
-      <c r="G111" s="220" t="n"/>
+      <c r="E111" s="223" t="n"/>
+      <c r="F111" s="223" t="n"/>
+      <c r="G111" s="223" t="n"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
           <t>否</t>
@@ -11941,7 +12059,7 @@
       </c>
       <c r="I111" s="28" t="n"/>
       <c r="J111" s="15" t="n"/>
-      <c r="K111" s="218" t="n"/>
+      <c r="K111" s="221" t="n"/>
       <c r="L111" s="17" t="n"/>
       <c r="M111" s="18" t="n"/>
     </row>
@@ -11990,7 +12108,7 @@
         </is>
       </c>
       <c r="J112" s="31" t="n"/>
-      <c r="K112" s="230" t="n"/>
+      <c r="K112" s="233" t="n"/>
       <c r="L112" s="29" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -11999,23 +12117,23 @@
       <c r="M112" s="18" t="n"/>
     </row>
     <row r="113" ht="24.75" customHeight="1" s="70">
-      <c r="A113" s="220" t="n"/>
-      <c r="B113" s="220" t="n"/>
-      <c r="C113" s="220" t="n"/>
+      <c r="A113" s="223" t="n"/>
+      <c r="B113" s="223" t="n"/>
+      <c r="C113" s="223" t="n"/>
       <c r="D113" s="12" t="inlineStr">
         <is>
           <t>中国科学院微生物研究所</t>
         </is>
       </c>
-      <c r="E113" s="220" t="n"/>
-      <c r="F113" s="220" t="n"/>
-      <c r="G113" s="220" t="n"/>
-      <c r="H113" s="220" t="n"/>
-      <c r="I113" s="220" t="n"/>
-      <c r="J113" s="220" t="n"/>
-      <c r="K113" s="220" t="n"/>
-      <c r="L113" s="220" t="n"/>
-      <c r="M113" s="220" t="n"/>
+      <c r="E113" s="223" t="n"/>
+      <c r="F113" s="223" t="n"/>
+      <c r="G113" s="223" t="n"/>
+      <c r="H113" s="223" t="n"/>
+      <c r="I113" s="223" t="n"/>
+      <c r="J113" s="223" t="n"/>
+      <c r="K113" s="223" t="n"/>
+      <c r="L113" s="223" t="n"/>
+      <c r="M113" s="223" t="n"/>
     </row>
     <row r="114" ht="24.75" customHeight="1" s="70">
       <c r="A114" s="11" t="n">
@@ -12058,7 +12176,7 @@
       </c>
       <c r="I114" s="28" t="n"/>
       <c r="J114" s="15" t="n"/>
-      <c r="K114" s="218" t="n"/>
+      <c r="K114" s="221" t="n"/>
       <c r="L114" s="17" t="n"/>
       <c r="M114" s="18" t="n"/>
     </row>
@@ -12109,7 +12227,7 @@
       <c r="J115" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K115" s="222" t="n">
+      <c r="K115" s="225" t="n">
         <v>44690</v>
       </c>
       <c r="L115" s="27" t="inlineStr">
@@ -12120,23 +12238,23 @@
       <c r="M115" s="18" t="n"/>
     </row>
     <row r="116" ht="24.75" customHeight="1" s="70">
-      <c r="A116" s="220" t="n"/>
-      <c r="B116" s="220" t="n"/>
-      <c r="C116" s="220" t="n"/>
+      <c r="A116" s="223" t="n"/>
+      <c r="B116" s="223" t="n"/>
+      <c r="C116" s="223" t="n"/>
       <c r="D116" s="12" t="inlineStr">
         <is>
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="E116" s="220" t="n"/>
-      <c r="F116" s="220" t="n"/>
-      <c r="G116" s="220" t="n"/>
-      <c r="H116" s="220" t="n"/>
-      <c r="I116" s="220" t="n"/>
-      <c r="J116" s="220" t="n"/>
-      <c r="K116" s="220" t="n"/>
-      <c r="L116" s="220" t="n"/>
-      <c r="M116" s="220" t="n"/>
+      <c r="E116" s="223" t="n"/>
+      <c r="F116" s="223" t="n"/>
+      <c r="G116" s="223" t="n"/>
+      <c r="H116" s="223" t="n"/>
+      <c r="I116" s="223" t="n"/>
+      <c r="J116" s="223" t="n"/>
+      <c r="K116" s="223" t="n"/>
+      <c r="L116" s="223" t="n"/>
+      <c r="M116" s="223" t="n"/>
     </row>
     <row r="117" ht="24.75" customHeight="1" s="70">
       <c r="A117" s="11" t="n">
@@ -12185,16 +12303,16 @@
       <c r="J117" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K117" s="221" t="n">
+      <c r="K117" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L117" s="17" t="n"/>
       <c r="M117" s="18" t="n"/>
     </row>
     <row r="118" ht="24.75" customHeight="1" s="70">
-      <c r="A118" s="220" t="n"/>
-      <c r="B118" s="220" t="n"/>
-      <c r="C118" s="220" t="n"/>
+      <c r="A118" s="223" t="n"/>
+      <c r="B118" s="223" t="n"/>
+      <c r="C118" s="223" t="n"/>
       <c r="D118" s="12" t="inlineStr">
         <is>
           <t>东北林业大学</t>
@@ -12205,8 +12323,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F118" s="220" t="n"/>
-      <c r="G118" s="220" t="n"/>
+      <c r="F118" s="223" t="n"/>
+      <c r="G118" s="223" t="n"/>
       <c r="H118" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12220,7 +12338,7 @@
       <c r="J118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K118" s="221" t="n">
+      <c r="K118" s="224" t="n">
         <v>44834</v>
       </c>
       <c r="L118" s="17" t="n"/>
@@ -12271,7 +12389,7 @@
         </is>
       </c>
       <c r="J119" s="15" t="n"/>
-      <c r="K119" s="218" t="n"/>
+      <c r="K119" s="221" t="n"/>
       <c r="L119" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知页</t>
@@ -12324,7 +12442,7 @@
       </c>
       <c r="I120" s="28" t="n"/>
       <c r="J120" s="15" t="n"/>
-      <c r="K120" s="218" t="n"/>
+      <c r="K120" s="221" t="n"/>
       <c r="L120" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -12379,7 +12497,7 @@
       <c r="J121" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="221" t="n">
+      <c r="K121" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L121" s="17" t="n"/>
@@ -12432,7 +12550,7 @@
       <c r="J122" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K122" s="221" t="n">
+      <c r="K122" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L122" s="17" t="n"/>
@@ -12479,7 +12597,7 @@
       </c>
       <c r="I123" s="28" t="n"/>
       <c r="J123" s="15" t="n"/>
-      <c r="K123" s="218" t="n"/>
+      <c r="K123" s="221" t="n"/>
       <c r="L123" s="17" t="n"/>
       <c r="M123" s="18" t="n"/>
     </row>
@@ -12530,7 +12648,7 @@
       <c r="J124" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K124" s="221" t="n">
+      <c r="K124" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -12583,7 +12701,7 @@
       <c r="J125" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K125" s="221" t="n">
+      <c r="K125" s="224" t="n">
         <v>44809</v>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -12630,7 +12748,7 @@
       </c>
       <c r="I126" s="28" t="n"/>
       <c r="J126" s="15" t="n"/>
-      <c r="K126" s="218" t="n"/>
+      <c r="K126" s="221" t="n"/>
       <c r="L126" s="26" t="inlineStr">
         <is>
           <t>未找到相应的官网</t>
@@ -12685,7 +12803,7 @@
       <c r="J127" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K127" s="221" t="n">
+      <c r="K127" s="224" t="n">
         <v>44589</v>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -12738,7 +12856,7 @@
       <c r="J128" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K128" s="221" t="n">
+      <c r="K128" s="224" t="n">
         <v>44917</v>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -12791,24 +12909,24 @@
       <c r="J129" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K129" s="221" t="n">
+      <c r="K129" s="224" t="n">
         <v>44586</v>
       </c>
       <c r="L129" s="17" t="n"/>
       <c r="M129" s="18" t="n"/>
     </row>
     <row r="130" ht="24.75" customHeight="1" s="70">
-      <c r="A130" s="220" t="n"/>
-      <c r="B130" s="220" t="n"/>
-      <c r="C130" s="220" t="n"/>
+      <c r="A130" s="223" t="n"/>
+      <c r="B130" s="223" t="n"/>
+      <c r="C130" s="223" t="n"/>
       <c r="D130" s="12" t="inlineStr">
         <is>
           <t>南昌大学</t>
         </is>
       </c>
-      <c r="E130" s="220" t="n"/>
-      <c r="F130" s="220" t="n"/>
-      <c r="G130" s="220" t="n"/>
+      <c r="E130" s="223" t="n"/>
+      <c r="F130" s="223" t="n"/>
+      <c r="G130" s="223" t="n"/>
       <c r="H130" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12822,7 +12940,7 @@
       <c r="J130" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K130" s="221" t="n">
+      <c r="K130" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L130" s="26" t="inlineStr">
@@ -12873,26 +12991,26 @@
       </c>
       <c r="I131" s="28" t="n"/>
       <c r="J131" s="15" t="n"/>
-      <c r="K131" s="218" t="n"/>
+      <c r="K131" s="221" t="n"/>
       <c r="L131" s="17" t="n"/>
       <c r="M131" s="18" t="n"/>
     </row>
     <row r="132" ht="24.75" customHeight="1" s="70">
-      <c r="A132" s="220" t="n"/>
-      <c r="B132" s="220" t="n"/>
-      <c r="C132" s="220" t="n"/>
+      <c r="A132" s="223" t="n"/>
+      <c r="B132" s="223" t="n"/>
+      <c r="C132" s="223" t="n"/>
       <c r="D132" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E132" s="220" t="n"/>
-      <c r="F132" s="220" t="n"/>
-      <c r="G132" s="220" t="n"/>
-      <c r="H132" s="220" t="n"/>
+      <c r="E132" s="223" t="n"/>
+      <c r="F132" s="223" t="n"/>
+      <c r="G132" s="223" t="n"/>
+      <c r="H132" s="223" t="n"/>
       <c r="I132" s="28" t="n"/>
       <c r="J132" s="15" t="n"/>
-      <c r="K132" s="218" t="n"/>
+      <c r="K132" s="221" t="n"/>
       <c r="L132" s="17" t="n"/>
       <c r="M132" s="18" t="n"/>
     </row>
@@ -12943,7 +13061,7 @@
       <c r="J133" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K133" s="221" t="n">
+      <c r="K133" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -12990,7 +13108,7 @@
       </c>
       <c r="I134" s="28" t="n"/>
       <c r="J134" s="15" t="n"/>
-      <c r="K134" s="218" t="n"/>
+      <c r="K134" s="221" t="n"/>
       <c r="L134" s="26" t="inlineStr">
         <is>
           <t>开放课题基金的申请每年受理一次，申请截止日期为每年的3月15日。</t>
@@ -13049,16 +13167,16 @@
       <c r="J135" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K135" s="222" t="n">
+      <c r="K135" s="225" t="n">
         <v>44878</v>
       </c>
       <c r="L135" s="18" t="n"/>
       <c r="M135" s="58" t="n"/>
     </row>
     <row r="136" ht="24.75" customHeight="1" s="70">
-      <c r="A136" s="220" t="n"/>
-      <c r="B136" s="220" t="n"/>
-      <c r="C136" s="220" t="n"/>
+      <c r="A136" s="223" t="n"/>
+      <c r="B136" s="223" t="n"/>
+      <c r="C136" s="223" t="n"/>
       <c r="D136" s="12" t="inlineStr">
         <is>
           <t>河南大学</t>
@@ -13069,13 +13187,13 @@
           <t>河南省科技厅</t>
         </is>
       </c>
-      <c r="F136" s="220" t="n"/>
-      <c r="G136" s="220" t="n"/>
-      <c r="H136" s="220" t="n"/>
-      <c r="I136" s="220" t="n"/>
-      <c r="J136" s="220" t="n"/>
-      <c r="K136" s="220" t="n"/>
-      <c r="L136" s="220" t="n"/>
+      <c r="F136" s="223" t="n"/>
+      <c r="G136" s="223" t="n"/>
+      <c r="H136" s="223" t="n"/>
+      <c r="I136" s="223" t="n"/>
+      <c r="J136" s="223" t="n"/>
+      <c r="K136" s="223" t="n"/>
+      <c r="L136" s="223" t="n"/>
       <c r="M136" s="58" t="n"/>
     </row>
     <row r="137" ht="24.75" customHeight="1" s="70">
@@ -13125,7 +13243,7 @@
       <c r="J137" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K137" s="221" t="n">
+      <c r="K137" s="224" t="n">
         <v>44624</v>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -13178,7 +13296,7 @@
       <c r="J138" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K138" s="221" t="n">
+      <c r="K138" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L138" s="26" t="inlineStr">
@@ -13235,7 +13353,7 @@
       <c r="J139" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K139" s="221" t="n">
+      <c r="K139" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -13282,26 +13400,26 @@
       </c>
       <c r="I140" s="48" t="n"/>
       <c r="J140" s="31" t="n"/>
-      <c r="K140" s="230" t="n"/>
+      <c r="K140" s="233" t="n"/>
       <c r="L140" s="17" t="n"/>
       <c r="M140" s="18" t="n"/>
     </row>
     <row r="141" ht="24.75" customHeight="1" s="70">
-      <c r="A141" s="220" t="n"/>
-      <c r="B141" s="220" t="n"/>
-      <c r="C141" s="220" t="n"/>
+      <c r="A141" s="223" t="n"/>
+      <c r="B141" s="223" t="n"/>
+      <c r="C141" s="223" t="n"/>
       <c r="D141" s="12" t="inlineStr">
         <is>
           <t>中国科学院武汉病毒研究所</t>
         </is>
       </c>
-      <c r="E141" s="220" t="n"/>
-      <c r="F141" s="220" t="n"/>
-      <c r="G141" s="220" t="n"/>
-      <c r="H141" s="220" t="n"/>
-      <c r="I141" s="220" t="n"/>
-      <c r="J141" s="220" t="n"/>
-      <c r="K141" s="220" t="n"/>
+      <c r="E141" s="223" t="n"/>
+      <c r="F141" s="223" t="n"/>
+      <c r="G141" s="223" t="n"/>
+      <c r="H141" s="223" t="n"/>
+      <c r="I141" s="223" t="n"/>
+      <c r="J141" s="223" t="n"/>
+      <c r="K141" s="223" t="n"/>
       <c r="L141" s="17" t="n"/>
       <c r="M141" s="18" t="n"/>
     </row>
@@ -13352,16 +13470,16 @@
       <c r="J142" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K142" s="221" t="n">
+      <c r="K142" s="224" t="n">
         <v>44745</v>
       </c>
       <c r="L142" s="17" t="n"/>
       <c r="M142" s="18" t="n"/>
     </row>
     <row r="143" ht="24.75" customHeight="1" s="70">
-      <c r="A143" s="220" t="n"/>
-      <c r="B143" s="220" t="n"/>
-      <c r="C143" s="220" t="n"/>
+      <c r="A143" s="223" t="n"/>
+      <c r="B143" s="223" t="n"/>
+      <c r="C143" s="223" t="n"/>
       <c r="D143" s="12" t="inlineStr">
         <is>
           <t>武汉大学</t>
@@ -13372,8 +13490,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F143" s="220" t="n"/>
-      <c r="G143" s="220" t="n"/>
+      <c r="F143" s="223" t="n"/>
+      <c r="G143" s="223" t="n"/>
       <c r="H143" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13387,7 +13505,7 @@
       <c r="J143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K143" s="221" t="n">
+      <c r="K143" s="224" t="n">
         <v>44675</v>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -13440,7 +13558,7 @@
       <c r="J144" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K144" s="221" t="n">
+      <c r="K144" s="224" t="n">
         <v>44826</v>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -13493,16 +13611,16 @@
       <c r="J145" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K145" s="221" t="n">
+      <c r="K145" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L145" s="17" t="n"/>
       <c r="M145" s="18" t="n"/>
     </row>
     <row r="146" ht="24.75" customHeight="1" s="70">
-      <c r="A146" s="220" t="n"/>
-      <c r="B146" s="220" t="n"/>
-      <c r="C146" s="220" t="n"/>
+      <c r="A146" s="223" t="n"/>
+      <c r="B146" s="223" t="n"/>
+      <c r="C146" s="223" t="n"/>
       <c r="D146" s="12" t="inlineStr">
         <is>
           <t>华南农业大学</t>
@@ -13513,8 +13631,8 @@
           <t>广东省科技厅</t>
         </is>
       </c>
-      <c r="F146" s="220" t="n"/>
-      <c r="G146" s="220" t="n"/>
+      <c r="F146" s="223" t="n"/>
+      <c r="G146" s="223" t="n"/>
       <c r="H146" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13528,7 +13646,7 @@
       <c r="J146" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K146" s="221" t="n">
+      <c r="K146" s="224" t="n">
         <v>44876</v>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -13581,7 +13699,7 @@
       <c r="J147" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K147" s="221" t="n">
+      <c r="K147" s="224" t="n">
         <v>44870</v>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -13634,7 +13752,7 @@
       <c r="J148" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K148" s="221" t="n">
+      <c r="K148" s="224" t="n">
         <v>44653</v>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -13687,7 +13805,7 @@
       <c r="J149" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K149" s="221" t="n">
+      <c r="K149" s="224" t="n">
         <v>44844</v>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -13740,7 +13858,7 @@
       <c r="J150" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K150" s="221" t="n">
+      <c r="K150" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L150" s="17" t="n"/>
@@ -13793,7 +13911,7 @@
       <c r="J151" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K151" s="221" t="n">
+      <c r="K151" s="224" t="n">
         <v>44737</v>
       </c>
       <c r="L151" s="17" t="n"/>
@@ -13846,7 +13964,7 @@
       <c r="J152" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K152" s="221" t="n">
+      <c r="K152" s="224" t="n">
         <v>44761</v>
       </c>
       <c r="L152" s="17" t="n"/>
@@ -13899,7 +14017,7 @@
       <c r="J153" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K153" s="221" t="n">
+      <c r="K153" s="224" t="n">
         <v>44590</v>
       </c>
       <c r="L153" s="17" t="n"/>
@@ -13952,7 +14070,7 @@
       <c r="J154" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K154" s="221" t="n">
+      <c r="K154" s="224" t="n">
         <v>44597</v>
       </c>
       <c r="L154" s="17" t="n"/>
@@ -14007,7 +14125,7 @@
           <t>4、5</t>
         </is>
       </c>
-      <c r="K155" s="221" t="n">
+      <c r="K155" s="224" t="n">
         <v>44701</v>
       </c>
       <c r="L155" s="17" t="n"/>
@@ -14060,7 +14178,7 @@
       <c r="J156" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K156" s="221" t="n">
+      <c r="K156" s="224" t="n">
         <v>44924</v>
       </c>
       <c r="L156" s="17" t="n"/>
@@ -14113,7 +14231,7 @@
       <c r="J157" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K157" s="221" t="n">
+      <c r="K157" s="224" t="n">
         <v>44657</v>
       </c>
       <c r="L157" s="17" t="n"/>
@@ -14166,7 +14284,7 @@
       <c r="J158" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K158" s="221" t="n">
+      <c r="K158" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L158" s="17" t="n"/>
@@ -14219,7 +14337,7 @@
       <c r="J159" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K159" s="221" t="n">
+      <c r="K159" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L159" s="59" t="n"/>
@@ -14272,7 +14390,7 @@
       <c r="J160" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K160" s="221" t="n">
+      <c r="K160" s="224" t="n">
         <v>44649</v>
       </c>
       <c r="L160" s="17" t="n"/>
@@ -14325,24 +14443,24 @@
       <c r="J161" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K161" s="221" t="n">
+      <c r="K161" s="224" t="n">
         <v>44789</v>
       </c>
       <c r="L161" s="17" t="n"/>
       <c r="M161" s="18" t="n"/>
     </row>
     <row r="162" ht="24.75" customHeight="1" s="70">
-      <c r="A162" s="220" t="n"/>
-      <c r="B162" s="220" t="n"/>
-      <c r="C162" s="220" t="n"/>
+      <c r="A162" s="223" t="n"/>
+      <c r="B162" s="223" t="n"/>
+      <c r="C162" s="223" t="n"/>
       <c r="D162" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E162" s="220" t="n"/>
-      <c r="F162" s="220" t="n"/>
-      <c r="G162" s="220" t="n"/>
+      <c r="E162" s="223" t="n"/>
+      <c r="F162" s="223" t="n"/>
+      <c r="G162" s="223" t="n"/>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -14350,7 +14468,7 @@
       </c>
       <c r="I162" s="28" t="n"/>
       <c r="J162" s="15" t="n"/>
-      <c r="K162" s="218" t="n"/>
+      <c r="K162" s="221" t="n"/>
       <c r="L162" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知</t>
@@ -14399,7 +14517,7 @@
       </c>
       <c r="I163" s="28" t="n"/>
       <c r="J163" s="15" t="n"/>
-      <c r="K163" s="218" t="n"/>
+      <c r="K163" s="221" t="n"/>
       <c r="L163" s="17" t="n"/>
       <c r="M163" s="18" t="n"/>
     </row>
@@ -14450,7 +14568,7 @@
       <c r="J164" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="221" t="n">
+      <c r="K164" s="224" t="n">
         <v>44668</v>
       </c>
       <c r="L164" s="17" t="n"/>
@@ -14499,7 +14617,7 @@
       <c r="J165" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K165" s="221" t="n">
+      <c r="K165" s="224" t="n">
         <v>44660</v>
       </c>
       <c r="L165" s="60" t="inlineStr">
@@ -14560,7 +14678,7 @@
       <c r="J166" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K166" s="221" t="n">
+      <c r="K166" s="224" t="n">
         <v>44649</v>
       </c>
       <c r="L166" s="40" t="n"/>
@@ -14613,28 +14731,28 @@
       <c r="J167" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K167" s="222" t="n">
+      <c r="K167" s="225" t="n">
         <v>44709</v>
       </c>
       <c r="L167" s="17" t="n"/>
       <c r="M167" s="18" t="n"/>
     </row>
     <row r="168" ht="24.75" customHeight="1" s="70">
-      <c r="A168" s="220" t="n"/>
-      <c r="B168" s="220" t="n"/>
-      <c r="C168" s="220" t="n"/>
+      <c r="A168" s="223" t="n"/>
+      <c r="B168" s="223" t="n"/>
+      <c r="C168" s="223" t="n"/>
       <c r="D168" s="12" t="inlineStr">
         <is>
           <t>中国科学院半导体研究所</t>
         </is>
       </c>
-      <c r="E168" s="220" t="n"/>
-      <c r="F168" s="220" t="n"/>
-      <c r="G168" s="220" t="n"/>
-      <c r="H168" s="220" t="n"/>
-      <c r="I168" s="220" t="n"/>
-      <c r="J168" s="220" t="n"/>
-      <c r="K168" s="220" t="n"/>
+      <c r="E168" s="223" t="n"/>
+      <c r="F168" s="223" t="n"/>
+      <c r="G168" s="223" t="n"/>
+      <c r="H168" s="223" t="n"/>
+      <c r="I168" s="223" t="n"/>
+      <c r="J168" s="223" t="n"/>
+      <c r="K168" s="223" t="n"/>
       <c r="L168" s="17" t="n"/>
       <c r="M168" s="18" t="n"/>
     </row>
@@ -14685,7 +14803,7 @@
       <c r="J169" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K169" s="221" t="n">
+      <c r="K169" s="224" t="n">
         <v>44821</v>
       </c>
       <c r="L169" s="17" t="n"/>
@@ -14738,28 +14856,28 @@
       <c r="J170" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K170" s="222" t="n">
+      <c r="K170" s="225" t="n">
         <v>44819</v>
       </c>
       <c r="L170" s="17" t="n"/>
       <c r="M170" s="18" t="n"/>
     </row>
     <row r="171" ht="24.75" customHeight="1" s="70">
-      <c r="A171" s="220" t="n"/>
-      <c r="B171" s="220" t="n"/>
-      <c r="C171" s="220" t="n"/>
+      <c r="A171" s="223" t="n"/>
+      <c r="B171" s="223" t="n"/>
+      <c r="C171" s="223" t="n"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
           <t>中国科学院电子学研究所</t>
         </is>
       </c>
-      <c r="E171" s="220" t="n"/>
-      <c r="F171" s="220" t="n"/>
-      <c r="G171" s="220" t="n"/>
-      <c r="H171" s="220" t="n"/>
-      <c r="I171" s="220" t="n"/>
-      <c r="J171" s="220" t="n"/>
-      <c r="K171" s="220" t="n"/>
+      <c r="E171" s="223" t="n"/>
+      <c r="F171" s="223" t="n"/>
+      <c r="G171" s="223" t="n"/>
+      <c r="H171" s="223" t="n"/>
+      <c r="I171" s="223" t="n"/>
+      <c r="J171" s="223" t="n"/>
+      <c r="K171" s="223" t="n"/>
       <c r="L171" s="17" t="n"/>
       <c r="M171" s="18" t="n"/>
     </row>
@@ -14808,7 +14926,7 @@
         </is>
       </c>
       <c r="J172" s="15" t="n"/>
-      <c r="K172" s="218" t="n"/>
+      <c r="K172" s="221" t="n"/>
       <c r="L172" s="26" t="inlineStr">
         <is>
           <t>网站时常故障</t>
@@ -14863,28 +14981,28 @@
       <c r="J173" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K173" s="222" t="n">
+      <c r="K173" s="225" t="n">
         <v>44881</v>
       </c>
       <c r="L173" s="17" t="n"/>
       <c r="M173" s="18" t="n"/>
     </row>
     <row r="174" ht="24.75" customHeight="1" s="70">
-      <c r="A174" s="220" t="n"/>
-      <c r="B174" s="220" t="n"/>
-      <c r="C174" s="220" t="n"/>
+      <c r="A174" s="223" t="n"/>
+      <c r="B174" s="223" t="n"/>
+      <c r="C174" s="223" t="n"/>
       <c r="D174" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E174" s="220" t="n"/>
-      <c r="F174" s="220" t="n"/>
-      <c r="G174" s="220" t="n"/>
-      <c r="H174" s="220" t="n"/>
-      <c r="I174" s="220" t="n"/>
-      <c r="J174" s="220" t="n"/>
-      <c r="K174" s="220" t="n"/>
+      <c r="E174" s="223" t="n"/>
+      <c r="F174" s="223" t="n"/>
+      <c r="G174" s="223" t="n"/>
+      <c r="H174" s="223" t="n"/>
+      <c r="I174" s="223" t="n"/>
+      <c r="J174" s="223" t="n"/>
+      <c r="K174" s="223" t="n"/>
       <c r="L174" s="17" t="n"/>
       <c r="M174" s="18" t="n"/>
     </row>
@@ -14935,7 +15053,7 @@
       <c r="J175" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K175" s="221" t="n">
+      <c r="K175" s="224" t="n">
         <v>44666</v>
       </c>
       <c r="L175" s="26" t="inlineStr">
@@ -14992,7 +15110,7 @@
       <c r="J176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K176" s="221" t="n">
+      <c r="K176" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L176" s="26" t="inlineStr">
@@ -15049,7 +15167,7 @@
       <c r="J177" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K177" s="221" t="n">
+      <c r="K177" s="224" t="n">
         <v>44671</v>
       </c>
       <c r="L177" s="17" t="n"/>
@@ -15102,7 +15220,7 @@
       <c r="J178" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K178" s="221" t="n">
+      <c r="K178" s="224" t="n">
         <v>44648</v>
       </c>
       <c r="L178" s="17" t="n"/>
@@ -15155,7 +15273,7 @@
       <c r="J179" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K179" s="221" t="n">
+      <c r="K179" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L179" s="17" t="n"/>
@@ -15208,7 +15326,7 @@
       <c r="J180" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K180" s="221" t="n">
+      <c r="K180" s="224" t="n">
         <v>44831</v>
       </c>
       <c r="L180" s="17" t="n"/>
@@ -15261,7 +15379,7 @@
       <c r="J181" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K181" s="221" t="n">
+      <c r="K181" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L181" s="17" t="n"/>
@@ -15314,7 +15432,7 @@
       <c r="J182" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K182" s="221" t="n">
+      <c r="K182" s="224" t="n">
         <v>44926</v>
       </c>
       <c r="L182" s="17" t="n"/>
@@ -15361,7 +15479,7 @@
       </c>
       <c r="I183" s="28" t="n"/>
       <c r="J183" s="15" t="n"/>
-      <c r="K183" s="218" t="n"/>
+      <c r="K183" s="221" t="n"/>
       <c r="L183" s="17" t="n"/>
       <c r="M183" s="18" t="n"/>
     </row>
@@ -15412,7 +15530,7 @@
       <c r="J184" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K184" s="221" t="n">
+      <c r="K184" s="224" t="n">
         <v>44718</v>
       </c>
       <c r="L184" s="17" t="n"/>
@@ -15465,7 +15583,7 @@
       <c r="J185" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K185" s="221" t="n">
+      <c r="K185" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L185" s="17" t="n"/>
@@ -15518,7 +15636,7 @@
       <c r="J186" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K186" s="221" t="n">
+      <c r="K186" s="224" t="n">
         <v>44800</v>
       </c>
       <c r="L186" s="17" t="n"/>
@@ -15571,7 +15689,7 @@
       <c r="J187" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K187" s="221" t="n">
+      <c r="K187" s="224" t="n">
         <v>44737</v>
       </c>
       <c r="L187" s="17" t="n"/>
@@ -15624,7 +15742,7 @@
       <c r="J188" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="221" t="n">
+      <c r="K188" s="224" t="n">
         <v>44573</v>
       </c>
       <c r="L188" s="17" t="n"/>
@@ -15677,7 +15795,7 @@
       <c r="J189" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K189" s="221" t="n">
+      <c r="K189" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L189" s="17" t="n"/>
@@ -15724,7 +15842,7 @@
       </c>
       <c r="I190" s="28" t="n"/>
       <c r="J190" s="15" t="n"/>
-      <c r="K190" s="218" t="n"/>
+      <c r="K190" s="221" t="n"/>
       <c r="L190" s="17" t="n"/>
       <c r="M190" s="18" t="n"/>
     </row>
@@ -15775,7 +15893,7 @@
       <c r="J191" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K191" s="221" t="n">
+      <c r="K191" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L191" s="63" t="inlineStr">
@@ -15826,7 +15944,7 @@
       </c>
       <c r="I192" s="28" t="n"/>
       <c r="J192" s="15" t="n"/>
-      <c r="K192" s="218" t="n"/>
+      <c r="K192" s="221" t="n"/>
       <c r="L192" s="40" t="n"/>
       <c r="M192" s="18" t="n"/>
     </row>
@@ -15877,7 +15995,7 @@
       <c r="J193" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K193" s="221" t="n">
+      <c r="K193" s="224" t="n">
         <v>44694</v>
       </c>
       <c r="L193" s="17" t="n"/>
@@ -15930,7 +16048,7 @@
       <c r="J194" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K194" s="221" t="n">
+      <c r="K194" s="224" t="n">
         <v>44904</v>
       </c>
       <c r="L194" s="17" t="n"/>
@@ -15977,7 +16095,7 @@
       </c>
       <c r="I195" s="28" t="n"/>
       <c r="J195" s="15" t="n"/>
-      <c r="K195" s="218" t="n"/>
+      <c r="K195" s="221" t="n"/>
       <c r="L195" s="17" t="n"/>
       <c r="M195" s="18" t="n"/>
     </row>
@@ -16028,7 +16146,7 @@
       <c r="J196" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K196" s="221" t="n">
+      <c r="K196" s="224" t="n">
         <v>44632</v>
       </c>
       <c r="L196" s="17" t="n"/>
@@ -16081,7 +16199,7 @@
       <c r="J197" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K197" s="221" t="n">
+      <c r="K197" s="224" t="n">
         <v>44764</v>
       </c>
       <c r="L197" s="17" t="n"/>
@@ -16134,7 +16252,7 @@
       <c r="J198" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K198" s="221" t="n">
+      <c r="K198" s="224" t="n">
         <v>44813</v>
       </c>
       <c r="L198" s="17" t="n"/>
@@ -16187,7 +16305,7 @@
       <c r="J199" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K199" s="221" t="n">
+      <c r="K199" s="224" t="n">
         <v>44856</v>
       </c>
       <c r="L199" s="17" t="n"/>
@@ -16240,7 +16358,7 @@
       <c r="J200" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K200" s="221" t="n">
+      <c r="K200" s="224" t="n">
         <v>44730</v>
       </c>
       <c r="L200" s="17" t="n"/>
@@ -16287,7 +16405,7 @@
       </c>
       <c r="I201" s="28" t="n"/>
       <c r="J201" s="15" t="n"/>
-      <c r="K201" s="218" t="n"/>
+      <c r="K201" s="221" t="n"/>
       <c r="L201" s="17" t="n"/>
       <c r="M201" s="18" t="n"/>
     </row>
@@ -16338,7 +16456,7 @@
       <c r="J202" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K202" s="221" t="n">
+      <c r="K202" s="224" t="n">
         <v>44872</v>
       </c>
       <c r="L202" s="17" t="n"/>
@@ -16391,7 +16509,7 @@
       <c r="J203" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K203" s="221" t="n">
+      <c r="K203" s="224" t="n">
         <v>44845</v>
       </c>
       <c r="L203" s="17" t="n"/>
@@ -16444,7 +16562,7 @@
       <c r="J204" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K204" s="221" t="n">
+      <c r="K204" s="224" t="n">
         <v>44688</v>
       </c>
       <c r="L204" s="17" t="n"/>
@@ -16497,7 +16615,7 @@
       <c r="J205" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K205" s="221" t="n">
+      <c r="K205" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L205" s="17" t="n"/>
@@ -16550,7 +16668,7 @@
       <c r="J206" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K206" s="221" t="n">
+      <c r="K206" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L206" s="17" t="n"/>
@@ -16597,7 +16715,7 @@
       </c>
       <c r="I207" s="28" t="n"/>
       <c r="J207" s="15" t="n"/>
-      <c r="K207" s="218" t="n"/>
+      <c r="K207" s="221" t="n"/>
       <c r="L207" s="26" t="inlineStr">
         <is>
           <t>未找到往年申请通知</t>
@@ -16656,7 +16774,7 @@
       <c r="J208" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K208" s="221" t="n">
+      <c r="K208" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L208" s="26" t="inlineStr">
@@ -16707,7 +16825,7 @@
       </c>
       <c r="I209" s="28" t="n"/>
       <c r="J209" s="15" t="n"/>
-      <c r="K209" s="218" t="n"/>
+      <c r="K209" s="221" t="n"/>
       <c r="L209" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -16762,7 +16880,7 @@
       <c r="J210" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K210" s="221" t="n">
+      <c r="K210" s="224" t="n">
         <v>44831</v>
       </c>
       <c r="L210" s="17" t="n"/>
@@ -16815,7 +16933,7 @@
       <c r="J211" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K211" s="221" t="n">
+      <c r="K211" s="224" t="n">
         <v>44815</v>
       </c>
       <c r="L211" s="17" t="n"/>
@@ -16868,7 +16986,7 @@
       <c r="J212" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K212" s="221" t="n">
+      <c r="K212" s="224" t="n">
         <v>44850</v>
       </c>
       <c r="L212" s="17" t="n"/>
@@ -16921,7 +17039,7 @@
       <c r="J213" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K213" s="221" t="n">
+      <c r="K213" s="224" t="n">
         <v>44845</v>
       </c>
       <c r="L213" s="17" t="n"/>
@@ -16974,7 +17092,7 @@
       <c r="J214" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K214" s="221" t="n">
+      <c r="K214" s="224" t="n">
         <v>44772</v>
       </c>
       <c r="L214" s="26" t="inlineStr">
@@ -17031,7 +17149,7 @@
       <c r="J215" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K215" s="221" t="n">
+      <c r="K215" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L215" s="17" t="n"/>
@@ -17084,7 +17202,7 @@
       <c r="J216" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K216" s="221" t="n">
+      <c r="K216" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L216" s="17" t="n"/>
@@ -17131,7 +17249,7 @@
       </c>
       <c r="I217" s="34" t="n"/>
       <c r="J217" s="15" t="n"/>
-      <c r="K217" s="218" t="n"/>
+      <c r="K217" s="221" t="n"/>
       <c r="L217" s="17" t="n"/>
       <c r="M217" s="18" t="n"/>
     </row>
@@ -17182,7 +17300,7 @@
       <c r="J218" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K218" s="221" t="n">
+      <c r="K218" s="224" t="n">
         <v>44843</v>
       </c>
       <c r="L218" s="17" t="n"/>
@@ -17235,7 +17353,7 @@
       <c r="J219" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K219" s="221" t="n">
+      <c r="K219" s="224" t="n">
         <v>44680</v>
       </c>
       <c r="L219" s="17" t="n"/>
@@ -17288,7 +17406,7 @@
       <c r="J220" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K220" s="221" t="n">
+      <c r="K220" s="224" t="n">
         <v>44722</v>
       </c>
       <c r="L220" s="17" t="n"/>
@@ -17341,7 +17459,7 @@
       <c r="J221" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K221" s="221" t="n">
+      <c r="K221" s="224" t="n">
         <v>44646</v>
       </c>
       <c r="L221" s="17" t="n"/>
@@ -17394,7 +17512,7 @@
       <c r="J222" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K222" s="221" t="n">
+      <c r="K222" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L222" s="17" t="n"/>
@@ -17447,7 +17565,7 @@
       <c r="J223" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K223" s="221" t="n">
+      <c r="K223" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L223" s="17" t="n"/>
@@ -17500,7 +17618,7 @@
       <c r="J224" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K224" s="221" t="n">
+      <c r="K224" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L224" s="17" t="n"/>
@@ -17553,7 +17671,7 @@
       <c r="J225" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K225" s="221" t="n">
+      <c r="K225" s="224" t="n">
         <v>44811</v>
       </c>
       <c r="L225" s="17" t="n"/>
@@ -17606,7 +17724,7 @@
       <c r="J226" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K226" s="221" t="n">
+      <c r="K226" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L226" s="17" t="n"/>
@@ -17659,28 +17777,28 @@
       <c r="J227" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K227" s="222" t="n">
+      <c r="K227" s="225" t="n">
         <v>44808</v>
       </c>
       <c r="L227" s="17" t="n"/>
       <c r="M227" s="18" t="n"/>
     </row>
     <row r="228" ht="24.75" customHeight="1" s="70">
-      <c r="A228" s="220" t="n"/>
-      <c r="B228" s="220" t="n"/>
-      <c r="C228" s="220" t="n"/>
+      <c r="A228" s="223" t="n"/>
+      <c r="B228" s="223" t="n"/>
+      <c r="C228" s="223" t="n"/>
       <c r="D228" s="12" t="inlineStr">
         <is>
           <t>南京水利科学研究院</t>
         </is>
       </c>
-      <c r="E228" s="220" t="n"/>
-      <c r="F228" s="220" t="n"/>
-      <c r="G228" s="220" t="n"/>
-      <c r="H228" s="220" t="n"/>
-      <c r="I228" s="220" t="n"/>
-      <c r="J228" s="220" t="n"/>
-      <c r="K228" s="220" t="n"/>
+      <c r="E228" s="223" t="n"/>
+      <c r="F228" s="223" t="n"/>
+      <c r="G228" s="223" t="n"/>
+      <c r="H228" s="223" t="n"/>
+      <c r="I228" s="223" t="n"/>
+      <c r="J228" s="223" t="n"/>
+      <c r="K228" s="223" t="n"/>
       <c r="L228" s="17" t="n"/>
       <c r="M228" s="18" t="n"/>
     </row>
@@ -17731,7 +17849,7 @@
       <c r="J229" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K229" s="221" t="n">
+      <c r="K229" s="224" t="n">
         <v>44846</v>
       </c>
       <c r="L229" s="17" t="n"/>
@@ -17771,7 +17889,7 @@
           <t>2008DA105277</t>
         </is>
       </c>
-      <c r="H230" s="232" t="inlineStr">
+      <c r="H230" s="235" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17784,28 +17902,28 @@
       <c r="J230" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K230" s="222" t="n">
+      <c r="K230" s="225" t="n">
         <v>44724</v>
       </c>
       <c r="L230" s="17" t="n"/>
       <c r="M230" s="18" t="n"/>
     </row>
     <row r="231" ht="24.75" customHeight="1" s="70">
-      <c r="A231" s="220" t="n"/>
-      <c r="B231" s="220" t="n"/>
-      <c r="C231" s="220" t="n"/>
+      <c r="A231" s="223" t="n"/>
+      <c r="B231" s="223" t="n"/>
+      <c r="C231" s="223" t="n"/>
       <c r="D231" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学（北京）</t>
         </is>
       </c>
-      <c r="E231" s="220" t="n"/>
-      <c r="F231" s="220" t="n"/>
-      <c r="G231" s="220" t="n"/>
-      <c r="H231" s="220" t="n"/>
-      <c r="I231" s="220" t="n"/>
-      <c r="J231" s="220" t="n"/>
-      <c r="K231" s="220" t="n"/>
+      <c r="E231" s="223" t="n"/>
+      <c r="F231" s="223" t="n"/>
+      <c r="G231" s="223" t="n"/>
+      <c r="H231" s="223" t="n"/>
+      <c r="I231" s="223" t="n"/>
+      <c r="J231" s="223" t="n"/>
+      <c r="K231" s="223" t="n"/>
       <c r="L231" s="17" t="n"/>
       <c r="M231" s="18" t="n"/>
     </row>
@@ -17856,7 +17974,7 @@
       <c r="J232" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K232" s="221" t="n">
+      <c r="K232" s="224" t="n">
         <v>44828</v>
       </c>
       <c r="L232" s="17" t="n"/>
@@ -17909,7 +18027,7 @@
       <c r="J233" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K233" s="221" t="n">
+      <c r="K233" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L233" s="17" t="n"/>
@@ -17956,7 +18074,7 @@
       </c>
       <c r="I234" s="34" t="n"/>
       <c r="J234" s="15" t="n"/>
-      <c r="K234" s="218" t="n"/>
+      <c r="K234" s="221" t="n"/>
       <c r="L234" s="17" t="n"/>
       <c r="M234" s="18" t="n"/>
     </row>
@@ -18007,7 +18125,7 @@
       <c r="J235" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K235" s="221" t="n">
+      <c r="K235" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L235" s="26" t="inlineStr">
@@ -18064,7 +18182,7 @@
       <c r="J236" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K236" s="221" t="n">
+      <c r="K236" s="224" t="n">
         <v>44622</v>
       </c>
       <c r="L236" s="17" t="n"/>
@@ -18117,7 +18235,7 @@
       <c r="J237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K237" s="221" t="n">
+      <c r="K237" s="224" t="n">
         <v>44689</v>
       </c>
       <c r="L237" s="17" t="n"/>
@@ -18170,7 +18288,7 @@
       <c r="J238" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K238" s="221" t="n">
+      <c r="K238" s="224" t="n">
         <v>44861</v>
       </c>
       <c r="L238" s="17" t="n"/>
@@ -18223,7 +18341,7 @@
       <c r="J239" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K239" s="221" t="n">
+      <c r="K239" s="224" t="n">
         <v>44826</v>
       </c>
       <c r="L239" s="17" t="n"/>
@@ -18270,7 +18388,7 @@
       </c>
       <c r="I240" s="28" t="n"/>
       <c r="J240" s="15" t="n"/>
-      <c r="K240" s="218" t="n"/>
+      <c r="K240" s="221" t="n"/>
       <c r="L240" s="26" t="inlineStr">
         <is>
           <t>未找到相关往年通知</t>
@@ -18329,7 +18447,7 @@
       <c r="J241" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K241" s="221" t="n">
+      <c r="K241" s="224" t="n">
         <v>44848</v>
       </c>
       <c r="L241" s="17" t="n"/>
@@ -18382,7 +18500,7 @@
       <c r="J242" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K242" s="221" t="n">
+      <c r="K242" s="224" t="n">
         <v>44820</v>
       </c>
       <c r="L242" s="17" t="n"/>
@@ -18435,7 +18553,7 @@
       <c r="J243" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K243" s="221" t="n">
+      <c r="K243" s="224" t="n">
         <v>44699</v>
       </c>
       <c r="L243" s="17" t="n"/>
@@ -18488,7 +18606,7 @@
       <c r="J244" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="221" t="n">
+      <c r="K244" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L244" s="26" t="inlineStr">
@@ -18545,7 +18663,7 @@
       <c r="J245" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K245" s="221" t="n">
+      <c r="K245" s="224" t="n">
         <v>44741</v>
       </c>
       <c r="L245" s="17" t="n"/>
@@ -18598,7 +18716,7 @@
       <c r="J246" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K246" s="221" t="n">
+      <c r="K246" s="224" t="n">
         <v>44771</v>
       </c>
       <c r="L246" s="17" t="n"/>
@@ -18651,7 +18769,7 @@
       <c r="J247" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K247" s="221" t="n">
+      <c r="K247" s="224" t="n">
         <v>44859</v>
       </c>
       <c r="L247" s="17" t="n"/>
@@ -18704,7 +18822,7 @@
       <c r="J248" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K248" s="221" t="n">
+      <c r="K248" s="224" t="n">
         <v>44815</v>
       </c>
       <c r="L248" s="17" t="n"/>
@@ -18757,7 +18875,7 @@
       <c r="J249" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K249" s="221" t="n">
+      <c r="K249" s="224" t="n">
         <v>44742</v>
       </c>
       <c r="L249" s="26" t="inlineStr">
@@ -18808,7 +18926,7 @@
       </c>
       <c r="I250" s="28" t="n"/>
       <c r="J250" s="15" t="n"/>
-      <c r="K250" s="218" t="n"/>
+      <c r="K250" s="221" t="n"/>
       <c r="L250" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -18863,7 +18981,7 @@
       <c r="J251" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K251" s="221" t="n">
+      <c r="K251" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L251" s="26" t="inlineStr">
@@ -18918,7 +19036,7 @@
       </c>
       <c r="I252" s="28" t="n"/>
       <c r="J252" s="15" t="n"/>
-      <c r="K252" s="218" t="n"/>
+      <c r="K252" s="221" t="n"/>
       <c r="L252" s="17" t="n"/>
       <c r="M252" s="18" t="n"/>
     </row>
@@ -18969,7 +19087,7 @@
       <c r="J253" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K253" s="221" t="n">
+      <c r="K253" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L253" s="17" t="n"/>
@@ -19016,7 +19134,7 @@
       </c>
       <c r="I254" s="28" t="n"/>
       <c r="J254" s="15" t="n"/>
-      <c r="K254" s="218" t="n"/>
+      <c r="K254" s="221" t="n"/>
       <c r="L254" s="17" t="n"/>
       <c r="M254" s="18" t="n"/>
     </row>
@@ -19061,7 +19179,7 @@
       </c>
       <c r="I255" s="28" t="n"/>
       <c r="J255" s="15" t="n"/>
-      <c r="K255" s="218" t="n"/>
+      <c r="K255" s="221" t="n"/>
       <c r="L255" s="17" t="n"/>
       <c r="M255" s="18" t="n"/>
     </row>
@@ -19106,7 +19224,7 @@
       </c>
       <c r="I256" s="28" t="n"/>
       <c r="J256" s="15" t="n"/>
-      <c r="K256" s="218" t="n"/>
+      <c r="K256" s="221" t="n"/>
       <c r="L256" s="17" t="n"/>
       <c r="M256" s="18" t="n"/>
     </row>
@@ -19157,7 +19275,7 @@
       <c r="J257" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K257" s="221" t="n">
+      <c r="K257" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L257" s="17" t="n"/>
@@ -19210,7 +19328,7 @@
       <c r="J258" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K258" s="221" t="n">
+      <c r="K258" s="224" t="n">
         <v>44665</v>
       </c>
       <c r="L258" s="17" t="n"/>
@@ -19263,7 +19381,7 @@
       <c r="J259" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K259" s="221" t="n">
+      <c r="K259" s="224" t="n">
         <v>44882</v>
       </c>
       <c r="L259" s="17" t="n"/>
@@ -19310,7 +19428,7 @@
       </c>
       <c r="I260" s="28" t="n"/>
       <c r="J260" s="15" t="n"/>
-      <c r="K260" s="218" t="n"/>
+      <c r="K260" s="221" t="n"/>
       <c r="L260" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -19359,7 +19477,7 @@
       </c>
       <c r="I261" s="34" t="n"/>
       <c r="J261" s="15" t="n"/>
-      <c r="K261" s="218" t="n"/>
+      <c r="K261" s="221" t="n"/>
       <c r="L261" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -19408,7 +19526,7 @@
       </c>
       <c r="I262" s="28" t="n"/>
       <c r="J262" s="15" t="n"/>
-      <c r="K262" s="218" t="n"/>
+      <c r="K262" s="221" t="n"/>
       <c r="L262" s="17" t="n"/>
       <c r="M262" s="18" t="n"/>
     </row>
@@ -19453,7 +19571,7 @@
       </c>
       <c r="I263" s="28" t="n"/>
       <c r="J263" s="15" t="n"/>
-      <c r="K263" s="218" t="n"/>
+      <c r="K263" s="221" t="n"/>
       <c r="L263" s="17" t="n"/>
       <c r="M263" s="18" t="n"/>
     </row>
@@ -19504,7 +19622,7 @@
       <c r="J264" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K264" s="221" t="n">
+      <c r="K264" s="224" t="n">
         <v>44667</v>
       </c>
       <c r="L264" s="26" t="n">
@@ -19559,7 +19677,7 @@
       <c r="J265" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K265" s="221" t="n">
+      <c r="K265" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L265" s="17" t="n"/>
@@ -19610,7 +19728,7 @@
         </is>
       </c>
       <c r="J266" s="15" t="n"/>
-      <c r="K266" s="218" t="n"/>
+      <c r="K266" s="221" t="n"/>
       <c r="L266" s="26" t="inlineStr">
         <is>
           <t>相关通知最近的是2014年的</t>
@@ -19665,7 +19783,7 @@
       <c r="J267" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K267" s="221" t="n">
+      <c r="K267" s="224" t="n">
         <v>44731</v>
       </c>
       <c r="L267" s="17" t="n"/>
@@ -19712,7 +19830,7 @@
       </c>
       <c r="I268" s="28" t="n"/>
       <c r="J268" s="15" t="n"/>
-      <c r="K268" s="218" t="n"/>
+      <c r="K268" s="221" t="n"/>
       <c r="L268" s="17" t="n"/>
       <c r="M268" s="18" t="n"/>
     </row>
@@ -19763,7 +19881,7 @@
       <c r="J269" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K269" s="221" t="n">
+      <c r="K269" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L269" s="17" t="n"/>
@@ -19816,7 +19934,7 @@
       <c r="J270" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K270" s="221" t="n">
+      <c r="K270" s="224" t="n">
         <v>44721</v>
       </c>
       <c r="L270" s="26" t="inlineStr">
@@ -19867,7 +19985,7 @@
       </c>
       <c r="I271" s="28" t="n"/>
       <c r="J271" s="15" t="n"/>
-      <c r="K271" s="218" t="n"/>
+      <c r="K271" s="221" t="n"/>
       <c r="L271" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -19916,7 +20034,7 @@
       </c>
       <c r="I272" s="28" t="n"/>
       <c r="J272" s="15" t="n"/>
-      <c r="K272" s="218" t="n"/>
+      <c r="K272" s="221" t="n"/>
       <c r="L272" s="17" t="n"/>
       <c r="M272" s="18" t="n"/>
     </row>
@@ -19961,7 +20079,7 @@
       </c>
       <c r="I273" s="28" t="n"/>
       <c r="J273" s="15" t="n"/>
-      <c r="K273" s="218" t="n"/>
+      <c r="K273" s="221" t="n"/>
       <c r="L273" s="17" t="n"/>
       <c r="M273" s="18" t="n"/>
     </row>
@@ -20006,7 +20124,7 @@
       </c>
       <c r="I274" s="28" t="n"/>
       <c r="J274" s="15" t="n"/>
-      <c r="K274" s="218" t="n"/>
+      <c r="K274" s="221" t="n"/>
       <c r="L274" s="17" t="n"/>
       <c r="M274" s="18" t="n"/>
     </row>
@@ -20057,7 +20175,7 @@
       <c r="J275" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K275" s="221" t="n">
+      <c r="K275" s="224" t="n">
         <v>44746</v>
       </c>
       <c r="L275" s="26" t="inlineStr">
@@ -20114,7 +20232,7 @@
       <c r="J276" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K276" s="221" t="n">
+      <c r="K276" s="224" t="n">
         <v>44866</v>
       </c>
       <c r="L276" s="17" t="n"/>
@@ -20161,7 +20279,7 @@
       </c>
       <c r="I277" s="28" t="n"/>
       <c r="J277" s="15" t="n"/>
-      <c r="K277" s="218" t="n"/>
+      <c r="K277" s="221" t="n"/>
       <c r="L277" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20216,7 +20334,7 @@
       <c r="J278" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K278" s="221" t="n">
+      <c r="K278" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L278" s="17" t="n"/>
@@ -20265,7 +20383,7 @@
       <c r="J279" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K279" s="221" t="n">
+      <c r="K279" s="224" t="n">
         <v>44599</v>
       </c>
       <c r="L279" s="26" t="inlineStr">
@@ -20320,7 +20438,7 @@
       </c>
       <c r="I280" s="34" t="n"/>
       <c r="J280" s="15" t="n"/>
-      <c r="K280" s="218" t="n"/>
+      <c r="K280" s="221" t="n"/>
       <c r="L280" s="17" t="n"/>
       <c r="M280" s="18" t="n"/>
     </row>
@@ -20371,7 +20489,7 @@
       <c r="J281" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K281" s="221" t="n">
+      <c r="K281" s="224" t="n">
         <v>44855</v>
       </c>
       <c r="L281" s="17" t="n"/>
@@ -20424,7 +20542,7 @@
       <c r="J282" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K282" s="221" t="n">
+      <c r="K282" s="224" t="n">
         <v>44569</v>
       </c>
       <c r="L282" s="26" t="inlineStr">
@@ -20475,7 +20593,7 @@
       </c>
       <c r="I283" s="28" t="n"/>
       <c r="J283" s="15" t="n"/>
-      <c r="K283" s="218" t="n"/>
+      <c r="K283" s="221" t="n"/>
       <c r="L283" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -20530,7 +20648,7 @@
       <c r="J284" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K284" s="221" t="n">
+      <c r="K284" s="224" t="n">
         <v>44581</v>
       </c>
       <c r="L284" s="17" t="n"/>
@@ -20577,7 +20695,7 @@
       </c>
       <c r="I285" s="28" t="n"/>
       <c r="J285" s="15" t="n"/>
-      <c r="K285" s="218" t="n"/>
+      <c r="K285" s="221" t="n"/>
       <c r="L285" s="17" t="n"/>
       <c r="M285" s="18" t="n"/>
     </row>
@@ -20622,7 +20740,7 @@
       </c>
       <c r="I286" s="28" t="n"/>
       <c r="J286" s="15" t="n"/>
-      <c r="K286" s="218" t="n"/>
+      <c r="K286" s="221" t="n"/>
       <c r="L286" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20673,7 +20791,7 @@
       <c r="J287" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K287" s="221" t="n">
+      <c r="K287" s="224" t="n">
         <v>44923</v>
       </c>
       <c r="L287" s="58" t="n"/>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2678,7 +2678,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-28）</t>
+          <t>最新更新（2026-09-29）</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-28）</t>
+          <t>最新更新（2026-09-29）</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-28）</t>
+          <t>最新更新（2026-09-29）</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="219" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-28）</t>
+          <t>最新更新（2026-09-29）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2678,7 +2678,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-29）</t>
+          <t>最新更新（2026-09-30）</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-29）</t>
+          <t>最新更新（2026-09-30）</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-29）</t>
+          <t>最新更新（2026-09-30）</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="219" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-29）</t>
+          <t>最新更新（2026-09-30）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -1063,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1630,27 +1630,30 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2678,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-30）</t>
+          <t>最新更新（2026-10-08）</t>
         </is>
       </c>
     </row>
@@ -2731,50 +2734,67 @@
       <c r="J3" s="148" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="190" t="n">
+      <c r="A4" s="194" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="189" t="inlineStr">
+      <c r="B4" s="195" t="n"/>
+      <c r="C4" s="196" t="inlineStr">
         <is>
           <t>国自然面上项目</t>
         </is>
       </c>
-      <c r="D4" s="175" t="inlineStr">
+      <c r="D4" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E4" s="152" t="inlineStr">
+      <c r="E4" s="198" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（主申/参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F4" s="189" t="inlineStr">
+      <c r="F4" s="196" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为4年</t>
         </is>
       </c>
-      <c r="G4" s="189" t="inlineStr">
+      <c r="G4" s="196" t="inlineStr">
         <is>
           <t>平均资助强度
 约50万</t>
         </is>
       </c>
-      <c r="H4" s="190" t="inlineStr">
+      <c r="H4" s="194" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I4" s="155" t="inlineStr">
+      <c r="I4" s="199" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3976/msxm22.html</t>
         </is>
       </c>
-      <c r="J4" s="148" t="n"/>
+      <c r="J4" s="200" t="n"/>
+      <c r="K4" s="195" t="n"/>
+      <c r="L4" s="195" t="n"/>
+      <c r="M4" s="195" t="n"/>
+      <c r="N4" s="195" t="n"/>
+      <c r="O4" s="195" t="n"/>
+      <c r="P4" s="195" t="n"/>
+      <c r="Q4" s="195" t="n"/>
+      <c r="R4" s="195" t="n"/>
+      <c r="S4" s="195" t="n"/>
+      <c r="T4" s="195" t="n"/>
+      <c r="U4" s="195" t="n"/>
+      <c r="V4" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：关于发布2026年度国家自然科学基金“面向低空经济前沿的基础研究”专项项目申请指南...（2026-09-30）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
       <c r="A5" s="190" t="n">
@@ -2966,7 +2986,7 @@
       <c r="A9" s="190" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="194" t="n"/>
+      <c r="B9" s="202" t="n"/>
       <c r="C9" s="161" t="inlineStr">
         <is>
           <t>国家科技部重大研发计划</t>
@@ -3391,16 +3411,16 @@
       <c r="J17" s="148" t="n"/>
     </row>
     <row r="18" ht="66" customHeight="1" s="70">
-      <c r="A18" s="195" t="n">
+      <c r="A18" s="194" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="196" t="n"/>
-      <c r="C18" s="197" t="inlineStr">
+      <c r="B18" s="197" t="n"/>
+      <c r="C18" s="196" t="inlineStr">
         <is>
           <t>国家重点研发计划“战略性科技创新合作”重点专项</t>
         </is>
       </c>
-      <c r="D18" s="196" t="inlineStr">
+      <c r="D18" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3410,39 +3430,39 @@
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F18" s="197" t="inlineStr">
+      <c r="F18" s="196" t="inlineStr">
         <is>
           <t>国家重点研发计划、国家科技重大专项、国家自然科学基金委有关类型项目实施联合限项，按照要求，对项目（课题）负责人等人员进行联合审查，科研人员同期申请和承担的项目（课题）数原则上不得超过2项。</t>
         </is>
       </c>
-      <c r="G18" s="197" t="inlineStr">
+      <c r="G18" s="196" t="inlineStr">
         <is>
           <t>200万元—400万元</t>
         </is>
       </c>
-      <c r="H18" s="196" t="inlineStr">
+      <c r="H18" s="197" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I18" s="199" t="inlineStr">
+      <c r="I18" s="203" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/20260828/5864.html</t>
         </is>
       </c>
       <c r="J18" s="200" t="n"/>
-      <c r="K18" s="201" t="n"/>
-      <c r="L18" s="201" t="n"/>
-      <c r="M18" s="201" t="n"/>
-      <c r="N18" s="201" t="n"/>
-      <c r="O18" s="201" t="n"/>
-      <c r="P18" s="201" t="n"/>
-      <c r="Q18" s="201" t="n"/>
-      <c r="R18" s="201" t="n"/>
-      <c r="S18" s="201" t="n"/>
-      <c r="T18" s="201" t="n"/>
-      <c r="U18" s="201" t="n"/>
-      <c r="V18" s="202" t="inlineStr">
+      <c r="K18" s="195" t="n"/>
+      <c r="L18" s="195" t="n"/>
+      <c r="M18" s="195" t="n"/>
+      <c r="N18" s="195" t="n"/>
+      <c r="O18" s="195" t="n"/>
+      <c r="P18" s="195" t="n"/>
+      <c r="Q18" s="195" t="n"/>
+      <c r="R18" s="195" t="n"/>
+      <c r="S18" s="195" t="n"/>
+      <c r="T18" s="195" t="n"/>
+      <c r="U18" s="195" t="n"/>
+      <c r="V18" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度联合研发与示范项目指南2026-09-01发布，港澳单位可承担课题，受聘内地单位的港澳科学家可作负责人</t>
         </is>
@@ -3495,58 +3515,58 @@
       <c r="J19" s="148" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1" s="70">
-      <c r="A20" s="195" t="n">
+      <c r="A20" s="194" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="201" t="n"/>
-      <c r="C20" s="197" t="inlineStr">
+      <c r="B20" s="195" t="n"/>
+      <c r="C20" s="196" t="inlineStr">
         <is>
           <t>粤澳科技创新联合资助专题-粤澳联合资助项目</t>
         </is>
       </c>
-      <c r="D20" s="196" t="inlineStr">
+      <c r="D20" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E20" s="196" t="inlineStr">
+      <c r="E20" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F20" s="203" t="inlineStr">
+      <c r="F20" s="204" t="inlineStr">
         <is>
           <t>由广东省科学技术厅和澳门科学技术发展基金联合征集、联合评审、联合资助。支持广东省创新主体联合澳门合作伙伴，在生物医药、新一代信息技术、节能环保、海洋科技、新材料、新能源、智能制造等涉及两地民生发展和前沿科技的领域开展联合技术研发及成果产业化合作。本专题优先支持在横琴、南沙等重大合作平台实施或落地转化的项目。</t>
         </is>
       </c>
-      <c r="G20" s="204" t="inlineStr">
+      <c r="G20" s="205" t="inlineStr">
         <is>
           <t>100万/项</t>
         </is>
       </c>
-      <c r="H20" s="195" t="inlineStr">
+      <c r="H20" s="194" t="inlineStr">
         <is>
           <t>11月-次年1月</t>
         </is>
       </c>
-      <c r="I20" s="205" t="inlineStr">
+      <c r="I20" s="206" t="inlineStr">
         <is>
           <t>https://gdstc.gd.gov.cn/zwgk_n/tzgg/content/post_4806341.html</t>
         </is>
       </c>
       <c r="J20" s="200" t="n"/>
-      <c r="K20" s="201" t="n"/>
-      <c r="L20" s="201" t="n"/>
-      <c r="M20" s="201" t="n"/>
-      <c r="N20" s="201" t="n"/>
-      <c r="O20" s="201" t="n"/>
-      <c r="P20" s="201" t="n"/>
-      <c r="Q20" s="201" t="n"/>
-      <c r="R20" s="201" t="n"/>
-      <c r="S20" s="201" t="n"/>
-      <c r="T20" s="201" t="n"/>
-      <c r="U20" s="201" t="n"/>
-      <c r="V20" s="202" t="inlineStr">
+      <c r="K20" s="195" t="n"/>
+      <c r="L20" s="195" t="n"/>
+      <c r="M20" s="195" t="n"/>
+      <c r="N20" s="195" t="n"/>
+      <c r="O20" s="195" t="n"/>
+      <c r="P20" s="195" t="n"/>
+      <c r="Q20" s="195" t="n"/>
+      <c r="R20" s="195" t="n"/>
+      <c r="S20" s="195" t="n"/>
+      <c r="T20" s="195" t="n"/>
+      <c r="U20" s="195" t="n"/>
+      <c r="V20" s="201" t="inlineStr">
         <is>
           <t>● 更新：2027年度申报指南已发布（2026-09-18），网上申报至2026-11-17 17:00，主管部门推荐截止11-24；粤科函资字〔2026〕1587号</t>
         </is>
@@ -3596,59 +3616,59 @@
       <c r="J21" s="148" t="n"/>
     </row>
     <row r="22" ht="148" customHeight="1" s="70">
-      <c r="A22" s="195" t="n">
+      <c r="A22" s="194" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="201" t="n"/>
-      <c r="C22" s="197" t="inlineStr">
+      <c r="B22" s="195" t="n"/>
+      <c r="C22" s="196" t="inlineStr">
         <is>
           <t>深圳市深港澳科技计划项目（C类项目）</t>
         </is>
       </c>
-      <c r="D22" s="196" t="inlineStr">
+      <c r="D22" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E22" s="196" t="inlineStr">
+      <c r="E22" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F22" s="197" t="inlineStr">
+      <c r="F22" s="196" t="inlineStr">
         <is>
           <t>深港澳科技计划C类项目由香港、澳门申请单位提出申请，深圳市科技创新局进行评审和资助，深圳市财政资助资金直接拨付至香港、澳门申请单位账户。
 重点支持领域（2025）：网络与通信、半导体与集成电路、软件与信息服务、人工智能、高端装备与仪器、低空经济与空天、机器人、高性能材料、生物医药、海洋、合成生物、智能机器人、脑科学与脑机工程等。</t>
         </is>
       </c>
-      <c r="G22" s="204" t="inlineStr">
+      <c r="G22" s="205" t="inlineStr">
         <is>
           <t>资助强度300万</t>
         </is>
       </c>
-      <c r="H22" s="195" t="inlineStr">
+      <c r="H22" s="194" t="inlineStr">
         <is>
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I22" s="206" t="inlineStr">
+      <c r="I22" s="207" t="inlineStr">
         <is>
           <t>https://stic.sz.gov.cn/xxgk/tzgg/content/post_12116696.html?sessionid=</t>
         </is>
       </c>
       <c r="J22" s="200" t="n"/>
-      <c r="K22" s="201" t="n"/>
-      <c r="L22" s="201" t="n"/>
-      <c r="M22" s="201" t="n"/>
-      <c r="N22" s="201" t="n"/>
-      <c r="O22" s="201" t="n"/>
-      <c r="P22" s="201" t="n"/>
-      <c r="Q22" s="201" t="n"/>
-      <c r="R22" s="201" t="n"/>
-      <c r="S22" s="201" t="n"/>
-      <c r="T22" s="201" t="n"/>
-      <c r="U22" s="201" t="n"/>
-      <c r="V22" s="202" t="inlineStr">
+      <c r="K22" s="195" t="n"/>
+      <c r="L22" s="195" t="n"/>
+      <c r="M22" s="195" t="n"/>
+      <c r="N22" s="195" t="n"/>
+      <c r="O22" s="195" t="n"/>
+      <c r="P22" s="195" t="n"/>
+      <c r="Q22" s="195" t="n"/>
+      <c r="R22" s="195" t="n"/>
+      <c r="S22" s="195" t="n"/>
+      <c r="T22" s="195" t="n"/>
+      <c r="U22" s="195" t="n"/>
+      <c r="V22" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026-06-05印发《深港澳科技计划项目管理办法》，A类须获香港ITC或澳门FDCT评审通过方可立项</t>
         </is>
@@ -3700,121 +3720,121 @@
       </c>
     </row>
     <row r="24" ht="70.5" customHeight="1" s="70">
-      <c r="A24" s="195" t="n">
+      <c r="A24" s="194" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="201" t="n"/>
-      <c r="C24" s="197" t="inlineStr">
+      <c r="B24" s="195" t="n"/>
+      <c r="C24" s="196" t="inlineStr">
         <is>
           <t>四川省国际科技创新/港澳台科技创新合作项目</t>
         </is>
       </c>
-      <c r="D24" s="196" t="inlineStr">
+      <c r="D24" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E24" s="196" t="inlineStr">
+      <c r="E24" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F24" s="197" t="inlineStr">
+      <c r="F24" s="196" t="inlineStr">
         <is>
           <t>支持省内高校、科研机构及企业与香港特区、澳门特区、台湾地区开展科技创新合作，结合基础研究和应用技术战略性发展需求，开展联合研发。</t>
         </is>
       </c>
-      <c r="G24" s="204" t="inlineStr">
+      <c r="G24" s="205" t="inlineStr">
         <is>
           <t>30万元-100万元</t>
         </is>
       </c>
-      <c r="H24" s="195" t="inlineStr">
+      <c r="H24" s="194" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I24" s="206" t="inlineStr">
+      <c r="I24" s="207" t="inlineStr">
         <is>
           <t>https://kjt.sc.gov.cn/kjt/gstz/2025/9/17/1959a2ee35844389a80b43eb99950708.shtml</t>
         </is>
       </c>
       <c r="J24" s="200" t="n"/>
-      <c r="K24" s="201" t="n"/>
-      <c r="L24" s="201" t="n"/>
-      <c r="M24" s="201" t="n"/>
-      <c r="N24" s="201" t="n"/>
-      <c r="O24" s="201" t="n"/>
-      <c r="P24" s="201" t="n"/>
-      <c r="Q24" s="201" t="n"/>
-      <c r="R24" s="201" t="n"/>
-      <c r="S24" s="201" t="n"/>
-      <c r="T24" s="201" t="n"/>
-      <c r="U24" s="201" t="n"/>
-      <c r="V24" s="202" t="inlineStr">
+      <c r="K24" s="195" t="n"/>
+      <c r="L24" s="195" t="n"/>
+      <c r="M24" s="195" t="n"/>
+      <c r="N24" s="195" t="n"/>
+      <c r="O24" s="195" t="n"/>
+      <c r="P24" s="195" t="n"/>
+      <c r="Q24" s="195" t="n"/>
+      <c r="R24" s="195" t="n"/>
+      <c r="S24" s="195" t="n"/>
+      <c r="T24" s="195" t="n"/>
+      <c r="U24" s="195" t="n"/>
+      <c r="V24" s="201" t="inlineStr">
         <is>
           <t>● 更新：2027年度需求征集已完成，指南适时发布；2026年度项目2025-09已发布</t>
         </is>
       </c>
     </row>
     <row r="25" ht="63.75" customHeight="1" s="70">
-      <c r="A25" s="195" t="n">
+      <c r="A25" s="194" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="201" t="n"/>
-      <c r="C25" s="197" t="inlineStr">
+      <c r="B25" s="195" t="n"/>
+      <c r="C25" s="196" t="inlineStr">
         <is>
           <t>江苏省国际科技合作/ 港澳台科技合作计划项目</t>
         </is>
       </c>
-      <c r="D25" s="196" t="inlineStr">
+      <c r="D25" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E25" s="196" t="inlineStr">
+      <c r="E25" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F25" s="197" t="inlineStr">
+      <c r="F25" s="196" t="inlineStr">
         <is>
           <t>专题五：港澳台科技合作项目
 重点支持的技术领域：生命健康、人工智能、先进材料等。</t>
         </is>
       </c>
-      <c r="G25" s="197" t="inlineStr">
+      <c r="G25" s="196" t="inlineStr">
         <is>
           <t>省资助经费每项原则上不超过80万元，且不超过项目江苏方总预算的50%。</t>
         </is>
       </c>
-      <c r="H25" s="195" t="inlineStr">
+      <c r="H25" s="194" t="inlineStr">
         <is>
           <t>3-4月</t>
         </is>
       </c>
-      <c r="I25" s="206" t="inlineStr">
+      <c r="I25" s="207" t="inlineStr">
         <is>
           <t>https://kxjst.jiangsu.gov.cn/art/2026/4/1/art_82568_11752538.html</t>
         </is>
       </c>
-      <c r="J25" s="207" t="n"/>
-      <c r="K25" s="201" t="inlineStr">
+      <c r="J25" s="208" t="n"/>
+      <c r="K25" s="195" t="inlineStr">
         <is>
           <t>这个不要了？</t>
         </is>
       </c>
-      <c r="L25" s="201" t="n"/>
-      <c r="M25" s="201" t="n"/>
-      <c r="N25" s="201" t="n"/>
-      <c r="O25" s="201" t="n"/>
-      <c r="P25" s="201" t="n"/>
-      <c r="Q25" s="201" t="n"/>
-      <c r="R25" s="201" t="n"/>
-      <c r="S25" s="201" t="n"/>
-      <c r="T25" s="201" t="n"/>
-      <c r="U25" s="201" t="n"/>
-      <c r="V25" s="202" t="inlineStr">
+      <c r="L25" s="195" t="n"/>
+      <c r="M25" s="195" t="n"/>
+      <c r="N25" s="195" t="n"/>
+      <c r="O25" s="195" t="n"/>
+      <c r="P25" s="195" t="n"/>
+      <c r="Q25" s="195" t="n"/>
+      <c r="R25" s="195" t="n"/>
+      <c r="S25" s="195" t="n"/>
+      <c r="T25" s="195" t="n"/>
+      <c r="U25" s="195" t="n"/>
+      <c r="V25" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度申报中（苏科资发〔2026〕26号），长三角—新加坡第五轮网上填报截止2026-10-12 17:30</t>
         </is>
@@ -3907,21 +3927,21 @@
       <c r="J27" s="85" t="n"/>
     </row>
     <row r="28" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A28" s="195" t="n">
+      <c r="A28" s="194" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="201" t="n"/>
-      <c r="C28" s="197" t="inlineStr">
+      <c r="B28" s="195" t="n"/>
+      <c r="C28" s="196" t="inlineStr">
         <is>
           <t>山西省科技合作交流专项项目</t>
         </is>
       </c>
-      <c r="D28" s="196" t="inlineStr">
+      <c r="D28" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E28" s="196" t="inlineStr">
+      <c r="E28" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -3931,34 +3951,34 @@
           <t>与香港、澳门科技合作交流项目</t>
         </is>
       </c>
-      <c r="G28" s="197" t="inlineStr">
+      <c r="G28" s="196" t="inlineStr">
         <is>
           <t>30万</t>
         </is>
       </c>
-      <c r="H28" s="195" t="inlineStr">
+      <c r="H28" s="194" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I28" s="208" t="inlineStr">
+      <c r="I28" s="209" t="inlineStr">
         <is>
           <t>https://kjt.shanxi.gov.cn/xxgk/zfxxgkml/acs_11737/gjyqykjhzc/202608/t20260831_10210987.shtml</t>
         </is>
       </c>
-      <c r="J28" s="209" t="n"/>
-      <c r="K28" s="201" t="n"/>
-      <c r="L28" s="201" t="n"/>
-      <c r="M28" s="201" t="n"/>
-      <c r="N28" s="201" t="n"/>
-      <c r="O28" s="201" t="n"/>
-      <c r="P28" s="201" t="n"/>
-      <c r="Q28" s="201" t="n"/>
-      <c r="R28" s="201" t="n"/>
-      <c r="S28" s="201" t="n"/>
-      <c r="T28" s="201" t="n"/>
-      <c r="U28" s="201" t="n"/>
-      <c r="V28" s="202" t="inlineStr">
+      <c r="J28" s="210" t="n"/>
+      <c r="K28" s="195" t="n"/>
+      <c r="L28" s="195" t="n"/>
+      <c r="M28" s="195" t="n"/>
+      <c r="N28" s="195" t="n"/>
+      <c r="O28" s="195" t="n"/>
+      <c r="P28" s="195" t="n"/>
+      <c r="Q28" s="195" t="n"/>
+      <c r="R28" s="195" t="n"/>
+      <c r="S28" s="195" t="n"/>
+      <c r="T28" s="195" t="n"/>
+      <c r="U28" s="195" t="n"/>
+      <c r="V28" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度设「与香港、澳门科技合作交流项目」，港澳方向不超过50万/项，2026年9月申报中</t>
         </is>
@@ -4006,21 +4026,21 @@
       <c r="J29" s="85" t="n"/>
     </row>
     <row r="30" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A30" s="195" t="n">
+      <c r="A30" s="194" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="201" t="n"/>
-      <c r="C30" s="197" t="inlineStr">
+      <c r="B30" s="195" t="n"/>
+      <c r="C30" s="196" t="inlineStr">
         <is>
           <t>浙江省“尖兵”“领雁”科技计划科技合作项目</t>
         </is>
       </c>
-      <c r="D30" s="196" t="inlineStr">
+      <c r="D30" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E30" s="196" t="inlineStr">
+      <c r="E30" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -4030,34 +4050,34 @@
           <t>国际（含港澳台）科技合作项目。围绕支持元首外交合作平台、“一带一路”联合实验室、深化拓展政府间合作网络以及支撑撬动培育国际大科学计划、国际科技组织等重点任务，部署重点国家（地区）和关键领域合作项目。中国澳门：优先支持生物医药（中医药）、电子信息、空间科学、人工智能、海洋科技等领域。</t>
         </is>
       </c>
-      <c r="G30" s="197" t="inlineStr">
+      <c r="G30" s="196" t="inlineStr">
         <is>
           <t>120万元以内</t>
         </is>
       </c>
-      <c r="H30" s="195" t="inlineStr">
+      <c r="H30" s="194" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I30" s="210" t="inlineStr">
+      <c r="I30" s="211" t="inlineStr">
         <is>
           <t>https://kjt.zj.gov.cn/col/col1229225203/art/2026/art_e495d70575a44848947646e93ca2948c.html</t>
         </is>
       </c>
-      <c r="J30" s="209" t="n"/>
-      <c r="K30" s="201" t="n"/>
-      <c r="L30" s="201" t="n"/>
-      <c r="M30" s="201" t="n"/>
-      <c r="N30" s="201" t="n"/>
-      <c r="O30" s="201" t="n"/>
-      <c r="P30" s="201" t="n"/>
-      <c r="Q30" s="201" t="n"/>
-      <c r="R30" s="201" t="n"/>
-      <c r="S30" s="201" t="n"/>
-      <c r="T30" s="201" t="n"/>
-      <c r="U30" s="201" t="n"/>
-      <c r="V30" s="202" t="inlineStr">
+      <c r="J30" s="210" t="n"/>
+      <c r="K30" s="195" t="n"/>
+      <c r="L30" s="195" t="n"/>
+      <c r="M30" s="195" t="n"/>
+      <c r="N30" s="195" t="n"/>
+      <c r="O30" s="195" t="n"/>
+      <c r="P30" s="195" t="n"/>
+      <c r="Q30" s="195" t="n"/>
+      <c r="R30" s="195" t="n"/>
+      <c r="S30" s="195" t="n"/>
+      <c r="T30" s="195" t="n"/>
+      <c r="U30" s="195" t="n"/>
+      <c r="V30" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度科技合作项目启动申报（2026-09），含国际（含港澳台）科技合作项目</t>
         </is>
@@ -4480,92 +4500,92 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="70">
-      <c r="A41" s="211" t="n">
+      <c r="A41" s="212" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="212" t="inlineStr">
+      <c r="B41" s="213" t="inlineStr">
         <is>
           <t>国家科技部</t>
         </is>
       </c>
-      <c r="C41" s="212" t="inlineStr">
+      <c r="C41" s="213" t="inlineStr">
         <is>
           <t>新一代人工智能国家科技重大专项2026年度公开项目</t>
         </is>
       </c>
-      <c r="D41" s="212" t="inlineStr"/>
-      <c r="E41" s="212" t="inlineStr">
+      <c r="D41" s="213" t="inlineStr"/>
+      <c r="E41" s="213" t="inlineStr">
         <is>
           <t>教授（参与，名单内港澳单位可参与）</t>
         </is>
       </c>
-      <c r="F41" s="212" t="inlineStr">
+      <c r="F41" s="213" t="inlineStr">
         <is>
           <t>申报附件含内地与香港、内地与澳门科技合作委员会协商确定的港澳科研单位名单</t>
         </is>
       </c>
-      <c r="G41" s="212" t="inlineStr">
+      <c r="G41" s="213" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H41" s="212" t="inlineStr">
+      <c r="H41" s="213" t="inlineStr">
         <is>
           <t>2026年度第一批申报中</t>
         </is>
       </c>
-      <c r="I41" s="213" t="inlineStr">
+      <c r="I41" s="214" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/</t>
         </is>
       </c>
-      <c r="V41" s="214" t="inlineStr">
+      <c r="V41" s="215" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度第一批公开项目申报启动，名单内港澳单位可参与</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="211" t="n">
+      <c r="A42" s="212" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="212" t="inlineStr">
+      <c r="B42" s="213" t="inlineStr">
         <is>
           <t>国家自然科学基金</t>
         </is>
       </c>
-      <c r="C42" s="212" t="inlineStr">
+      <c r="C42" s="213" t="inlineStr">
         <is>
           <t>NSFC民营企业创新发展联合基金（术理创新）</t>
         </is>
       </c>
-      <c r="D42" s="212" t="inlineStr"/>
-      <c r="E42" s="212" t="inlineStr">
+      <c r="D42" s="213" t="inlineStr"/>
+      <c r="E42" s="213" t="inlineStr">
         <is>
           <t>教授（主申/参与）</t>
         </is>
       </c>
-      <c r="F42" s="212" t="inlineStr">
+      <c r="F42" s="213" t="inlineStr">
         <is>
           <t>企业出资的NSFC联合基金，按国自然流程申报；脑机接口与神经调控方向</t>
         </is>
       </c>
-      <c r="G42" s="212" t="inlineStr">
+      <c r="G42" s="213" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H42" s="212" t="inlineStr">
+      <c r="H42" s="213" t="inlineStr">
         <is>
           <t>2026-06发布</t>
         </is>
       </c>
-      <c r="I42" s="213" t="inlineStr">
+      <c r="I42" s="214" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="V42" s="214" t="inlineStr">
+      <c r="V42" s="215" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度项目申报中（脑机接口与神经调控方向）</t>
         </is>
@@ -4698,7 +4718,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-30）</t>
+          <t>最新更新（2026-10-08）</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4726,7 @@
       <c r="A3" s="190" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="215" t="inlineStr">
+      <c r="B3" s="216" t="inlineStr">
         <is>
           <t>社科项目</t>
         </is>
@@ -5010,7 +5030,7 @@
       <c r="A11" s="190" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="194" t="n"/>
+      <c r="B11" s="202" t="n"/>
       <c r="C11" s="134" t="inlineStr">
         <is>
           <t>珠海市哲学社会科学规划年度课题</t>
@@ -5132,7 +5152,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-09-30）</t>
+          <t>最新更新（2026-10-08）</t>
         </is>
       </c>
     </row>
@@ -5193,20 +5213,20 @@
       <c r="S3" s="82" t="n"/>
     </row>
     <row r="4" ht="148.5" customFormat="1" customHeight="1" s="141">
-      <c r="A4" s="195" t="n">
+      <c r="A4" s="194" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="197" t="inlineStr">
+      <c r="B4" s="196" t="inlineStr">
         <is>
           <t>何享健青年科学家项目</t>
         </is>
       </c>
-      <c r="C4" s="216" t="inlineStr">
+      <c r="C4" s="217" t="inlineStr">
         <is>
           <t>研究院全职研究人员</t>
         </is>
       </c>
-      <c r="D4" s="197" t="inlineStr">
+      <c r="D4" s="196" t="inlineStr">
         <is>
           <t>面向医学与生命科学、能源环境与气候变化领域，每年评选总数不超过20人。
 学位要求：已取得博士学位。
@@ -5214,39 +5234,39 @@
 年龄要求：被提名当年，参评人年龄在35周岁及以下，女性候选人放宽至38周岁。临床医学专业背景的被提名人统一放宽至40周岁，女性候选人放宽至43周岁。</t>
         </is>
       </c>
-      <c r="E4" s="197" t="inlineStr">
+      <c r="E4" s="196" t="inlineStr">
         <is>
           <t>200万元/3年</t>
         </is>
       </c>
-      <c r="F4" s="195" t="inlineStr">
+      <c r="F4" s="194" t="inlineStr">
         <is>
           <t>11月-次年2月</t>
         </is>
       </c>
-      <c r="G4" s="206" t="inlineStr">
+      <c r="G4" s="207" t="inlineStr">
         <is>
           <t>https://www.heprize.org/Home</t>
         </is>
       </c>
-      <c r="H4" s="209" t="inlineStr">
+      <c r="H4" s="210" t="inlineStr">
         <is>
           <t xml:space="preserve">评审流程按照“提名机构提交材料-秘书处形式审查-同行评审专家评审-评审委员会评审-理事会审批-获资助人名单公布”严格执行。
 </t>
         </is>
       </c>
-      <c r="I4" s="201" t="n"/>
-      <c r="J4" s="201" t="n"/>
-      <c r="K4" s="201" t="n"/>
-      <c r="L4" s="201" t="n"/>
-      <c r="M4" s="201" t="n"/>
-      <c r="N4" s="201" t="n"/>
-      <c r="O4" s="201" t="n"/>
-      <c r="P4" s="201" t="n"/>
-      <c r="Q4" s="201" t="n"/>
-      <c r="R4" s="201" t="n"/>
-      <c r="S4" s="201" t="n"/>
-      <c r="T4" s="202" t="inlineStr">
+      <c r="I4" s="195" t="n"/>
+      <c r="J4" s="195" t="n"/>
+      <c r="K4" s="195" t="n"/>
+      <c r="L4" s="195" t="n"/>
+      <c r="M4" s="195" t="n"/>
+      <c r="N4" s="195" t="n"/>
+      <c r="O4" s="195" t="n"/>
+      <c r="P4" s="195" t="n"/>
+      <c r="Q4" s="195" t="n"/>
+      <c r="R4" s="195" t="n"/>
+      <c r="S4" s="195" t="n"/>
+      <c r="T4" s="201" t="inlineStr">
         <is>
           <t>● 更新：第二期已启动（2025-11-03正式启动），200万元/3年，研究院全职研究人员可申</t>
         </is>
@@ -6614,18 +6634,18 @@
           <t>重点实验室开放课题清单</t>
         </is>
       </c>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="217" t="n"/>
-      <c r="L1" s="217" t="n"/>
-      <c r="M1" s="217" t="n"/>
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
     </row>
     <row r="2" ht="41.25" customHeight="1" s="70">
       <c r="A2" s="5" t="inlineStr">
@@ -6678,7 +6698,7 @@
           <t>公告月份</t>
         </is>
       </c>
-      <c r="K2" s="218" t="inlineStr">
+      <c r="K2" s="219" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -6700,9 +6720,9 @@
       <c r="R2" s="10" t="n"/>
       <c r="S2" s="10" t="n"/>
       <c r="T2" s="10" t="n"/>
-      <c r="U2" s="219" t="inlineStr">
-        <is>
-          <t>最新更新（2026-09-30）</t>
+      <c r="U2" s="220" t="inlineStr">
+        <is>
+          <t>最新更新（2026-10-08）</t>
         </is>
       </c>
     </row>
@@ -6745,84 +6765,84 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="220" t="inlineStr">
+      <c r="I3" s="221" t="inlineStr">
         <is>
           <t>http://sklpre.zju.edu.cn/redir.php?catalog_id=60520&amp;object_id=63561</t>
         </is>
       </c>
       <c r="J3" s="15" t="n"/>
-      <c r="K3" s="221" t="n"/>
+      <c r="K3" s="222" t="n"/>
       <c r="L3" s="17" t="n"/>
       <c r="M3" s="18" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="222" t="n"/>
-      <c r="B4" s="222" t="n"/>
-      <c r="C4" s="222" t="n"/>
+      <c r="A4" s="223" t="n"/>
+      <c r="B4" s="223" t="n"/>
+      <c r="C4" s="223" t="n"/>
       <c r="D4" s="12" t="inlineStr">
         <is>
           <t>天津大学</t>
         </is>
       </c>
-      <c r="E4" s="222" t="n"/>
-      <c r="F4" s="222" t="n"/>
-      <c r="G4" s="222" t="n"/>
+      <c r="E4" s="223" t="n"/>
+      <c r="F4" s="223" t="n"/>
+      <c r="G4" s="223" t="n"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="222" t="n"/>
+      <c r="I4" s="223" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="221" t="n"/>
+      <c r="K4" s="222" t="n"/>
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="222" t="n"/>
-      <c r="B5" s="222" t="n"/>
-      <c r="C5" s="222" t="n"/>
+      <c r="A5" s="223" t="n"/>
+      <c r="B5" s="223" t="n"/>
+      <c r="C5" s="223" t="n"/>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>华东理工大学</t>
         </is>
       </c>
-      <c r="E5" s="222" t="n"/>
-      <c r="F5" s="222" t="n"/>
-      <c r="G5" s="222" t="n"/>
+      <c r="E5" s="223" t="n"/>
+      <c r="F5" s="223" t="n"/>
+      <c r="G5" s="223" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="222" t="n"/>
+      <c r="I5" s="223" t="n"/>
       <c r="J5" s="15" t="n"/>
-      <c r="K5" s="221" t="n"/>
+      <c r="K5" s="222" t="n"/>
       <c r="L5" s="17" t="n"/>
       <c r="M5" s="18" t="n"/>
     </row>
     <row r="6" ht="55.5" customHeight="1" s="70">
-      <c r="A6" s="223" t="n"/>
-      <c r="B6" s="223" t="n"/>
-      <c r="C6" s="223" t="n"/>
+      <c r="A6" s="224" t="n"/>
+      <c r="B6" s="224" t="n"/>
+      <c r="C6" s="224" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E6" s="223" t="n"/>
-      <c r="F6" s="223" t="n"/>
-      <c r="G6" s="223" t="n"/>
+      <c r="E6" s="224" t="n"/>
+      <c r="F6" s="224" t="n"/>
+      <c r="G6" s="224" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I6" s="223" t="n"/>
+      <c r="I6" s="224" t="n"/>
       <c r="J6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="224" t="n">
+      <c r="K6" s="225" t="n">
         <v>44679</v>
       </c>
       <c r="L6" s="17" t="n"/>
@@ -6875,30 +6895,30 @@
       <c r="J7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="225" t="n">
+      <c r="K7" s="226" t="n">
         <v>44677</v>
       </c>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="70">
-      <c r="A8" s="223" t="n"/>
-      <c r="B8" s="223" t="n"/>
-      <c r="C8" s="223" t="n"/>
+      <c r="A8" s="224" t="n"/>
+      <c r="B8" s="224" t="n"/>
+      <c r="C8" s="224" t="n"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>中国石油大学（华东）</t>
         </is>
       </c>
-      <c r="E8" s="223" t="n"/>
-      <c r="F8" s="223" t="n"/>
-      <c r="G8" s="223" t="n"/>
-      <c r="H8" s="223" t="n"/>
-      <c r="I8" s="223" t="n"/>
-      <c r="J8" s="223" t="n"/>
-      <c r="K8" s="223" t="n"/>
-      <c r="L8" s="223" t="n"/>
-      <c r="M8" s="223" t="n"/>
+      <c r="E8" s="224" t="n"/>
+      <c r="F8" s="224" t="n"/>
+      <c r="G8" s="224" t="n"/>
+      <c r="H8" s="224" t="n"/>
+      <c r="I8" s="224" t="n"/>
+      <c r="J8" s="224" t="n"/>
+      <c r="K8" s="224" t="n"/>
+      <c r="L8" s="224" t="n"/>
+      <c r="M8" s="224" t="n"/>
     </row>
     <row r="9" ht="44.25" customHeight="1" s="70">
       <c r="A9" s="11" t="n">
@@ -6945,7 +6965,7 @@
         </is>
       </c>
       <c r="J9" s="15" t="n"/>
-      <c r="K9" s="221" t="n"/>
+      <c r="K9" s="222" t="n"/>
       <c r="L9" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -6998,7 +7018,7 @@
         </is>
       </c>
       <c r="J10" s="15" t="n"/>
-      <c r="K10" s="221" t="n"/>
+      <c r="K10" s="222" t="n"/>
       <c r="L10" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7057,7 +7077,7 @@
       <c r="J11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="224" t="n">
+      <c r="K11" s="225" t="n">
         <v>44727</v>
       </c>
       <c r="L11" s="26" t="inlineStr">
@@ -7104,7 +7124,7 @@
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="15" t="n"/>
-      <c r="K12" s="221" t="n"/>
+      <c r="K12" s="222" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="29" t="inlineStr">
         <is>
@@ -7157,7 +7177,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n"/>
-      <c r="K13" s="221" t="n"/>
+      <c r="K13" s="222" t="n"/>
       <c r="L13" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7214,7 +7234,7 @@
         </is>
       </c>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="221" t="n"/>
+      <c r="K14" s="222" t="n"/>
       <c r="L14" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7273,7 +7293,7 @@
       <c r="J15" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="224" t="n">
+      <c r="K15" s="225" t="n">
         <v>44774</v>
       </c>
       <c r="L15" s="26" t="inlineStr">
@@ -7330,7 +7350,7 @@
       <c r="J16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="224" t="n">
+      <c r="K16" s="225" t="n">
         <v>44731</v>
       </c>
       <c r="L16" s="26" t="inlineStr">
@@ -7387,7 +7407,7 @@
       <c r="J17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="224" t="n">
+      <c r="K17" s="225" t="n">
         <v>44696</v>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -7436,7 +7456,7 @@
       <c r="J18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="224" t="n">
+      <c r="K18" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L18" s="26" t="inlineStr">
@@ -7497,7 +7517,7 @@
       <c r="J19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K19" s="224" t="n">
+      <c r="K19" s="225" t="n">
         <v>44866</v>
       </c>
       <c r="L19" s="26" t="inlineStr">
@@ -7558,7 +7578,7 @@
       <c r="J20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="224" t="n">
+      <c r="K20" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L20" s="26" t="inlineStr">
@@ -7613,7 +7633,7 @@
       </c>
       <c r="I21" s="34" t="n"/>
       <c r="J21" s="15" t="n"/>
-      <c r="K21" s="221" t="n"/>
+      <c r="K21" s="222" t="n"/>
       <c r="L21" s="26" t="inlineStr">
         <is>
           <t>最近几年未有相关的课题申请消息</t>
@@ -7672,7 +7692,7 @@
       <c r="J22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="226" t="n">
+      <c r="K22" s="227" t="n">
         <v>44694</v>
       </c>
       <c r="L22" s="36" t="n"/>
@@ -7715,7 +7735,7 @@
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="28" t="n"/>
       <c r="J23" s="15" t="n"/>
-      <c r="K23" s="227" t="n"/>
+      <c r="K23" s="228" t="n"/>
       <c r="L23" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7760,7 +7780,7 @@
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="28" t="n"/>
       <c r="J24" s="15" t="n"/>
-      <c r="K24" s="221" t="n"/>
+      <c r="K24" s="222" t="n"/>
       <c r="L24" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7815,7 +7835,7 @@
       <c r="J25" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="224" t="n">
+      <c r="K25" s="225" t="n">
         <v>44822</v>
       </c>
       <c r="L25" s="17" t="n"/>
@@ -7868,7 +7888,7 @@
       <c r="J26" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="224" t="n">
+      <c r="K26" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L26" s="39" t="inlineStr">
@@ -7929,7 +7949,7 @@
       <c r="J27" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="224" t="n">
+      <c r="K27" s="225" t="n">
         <v>44804</v>
       </c>
       <c r="L27" s="40" t="n"/>
@@ -7982,7 +8002,7 @@
       <c r="J28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="224" t="n">
+      <c r="K28" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L28" s="26" t="inlineStr">
@@ -8043,7 +8063,7 @@
       <c r="J29" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="224" t="n">
+      <c r="K29" s="225" t="n">
         <v>44835</v>
       </c>
       <c r="L29" s="17" t="n"/>
@@ -8096,7 +8116,7 @@
       <c r="J30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="224" t="n">
+      <c r="K30" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L30" s="26" t="inlineStr">
@@ -8151,7 +8171,7 @@
         </is>
       </c>
       <c r="J31" s="15" t="n"/>
-      <c r="K31" s="221" t="n"/>
+      <c r="K31" s="222" t="n"/>
       <c r="L31" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关消息</t>
@@ -8206,7 +8226,7 @@
       <c r="J32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="224" t="n">
+      <c r="K32" s="225" t="n">
         <v>44631</v>
       </c>
       <c r="L32" s="17" t="n"/>
@@ -8257,7 +8277,7 @@
       </c>
       <c r="I33" s="28" t="n"/>
       <c r="J33" s="15" t="n"/>
-      <c r="K33" s="221" t="n"/>
+      <c r="K33" s="222" t="n"/>
       <c r="L33" s="17" t="n"/>
       <c r="M33" s="18" t="n"/>
     </row>
@@ -8308,7 +8328,7 @@
       <c r="J34" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="224" t="n">
+      <c r="K34" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L34" s="17" t="n"/>
@@ -8355,7 +8375,7 @@
       </c>
       <c r="I35" s="28" t="n"/>
       <c r="J35" s="15" t="n"/>
-      <c r="K35" s="221" t="n"/>
+      <c r="K35" s="222" t="n"/>
       <c r="L35" s="17" t="n"/>
       <c r="M35" s="18" t="n"/>
     </row>
@@ -8400,7 +8420,7 @@
       </c>
       <c r="I36" s="28" t="n"/>
       <c r="J36" s="15" t="n"/>
-      <c r="K36" s="221" t="n"/>
+      <c r="K36" s="222" t="n"/>
       <c r="L36" s="17" t="n"/>
       <c r="M36" s="18" t="n"/>
     </row>
@@ -8451,7 +8471,7 @@
       <c r="J37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="224" t="n">
+      <c r="K37" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L37" s="26" t="inlineStr">
@@ -8508,7 +8528,7 @@
       <c r="J38" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="224" t="n">
+      <c r="K38" s="225" t="n">
         <v>44835</v>
       </c>
       <c r="L38" s="26" t="inlineStr">
@@ -8565,7 +8585,7 @@
       <c r="J39" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="224" t="n">
+      <c r="K39" s="225" t="n">
         <v>44690</v>
       </c>
       <c r="L39" s="17" t="n"/>
@@ -8618,30 +8638,30 @@
       <c r="J40" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K40" s="225" t="n">
+      <c r="K40" s="226" t="n">
         <v>44657</v>
       </c>
       <c r="L40" s="36" t="n"/>
       <c r="M40" s="18" t="n"/>
     </row>
     <row r="41" ht="24.75" customHeight="1" s="70">
-      <c r="A41" s="223" t="n"/>
-      <c r="B41" s="223" t="n"/>
-      <c r="C41" s="223" t="n"/>
+      <c r="A41" s="224" t="n"/>
+      <c r="B41" s="224" t="n"/>
+      <c r="C41" s="224" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="E41" s="223" t="n"/>
-      <c r="F41" s="223" t="n"/>
-      <c r="G41" s="223" t="n"/>
-      <c r="H41" s="223" t="n"/>
-      <c r="I41" s="223" t="n"/>
-      <c r="J41" s="223" t="n"/>
-      <c r="K41" s="223" t="n"/>
-      <c r="L41" s="228" t="n"/>
-      <c r="M41" s="223" t="n"/>
+      <c r="E41" s="224" t="n"/>
+      <c r="F41" s="224" t="n"/>
+      <c r="G41" s="224" t="n"/>
+      <c r="H41" s="224" t="n"/>
+      <c r="I41" s="224" t="n"/>
+      <c r="J41" s="224" t="n"/>
+      <c r="K41" s="224" t="n"/>
+      <c r="L41" s="229" t="n"/>
+      <c r="M41" s="224" t="n"/>
     </row>
     <row r="42" ht="24.75" customHeight="1" s="70">
       <c r="A42" s="11" t="n">
@@ -8684,7 +8704,7 @@
       </c>
       <c r="I42" s="28" t="n"/>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="221" t="n"/>
+      <c r="K42" s="222" t="n"/>
       <c r="L42" s="17" t="n"/>
       <c r="M42" s="18" t="n"/>
     </row>
@@ -8729,7 +8749,7 @@
       </c>
       <c r="I43" s="28" t="n"/>
       <c r="J43" s="15" t="n"/>
-      <c r="K43" s="221" t="n"/>
+      <c r="K43" s="222" t="n"/>
       <c r="L43" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -8782,7 +8802,7 @@
       </c>
       <c r="I44" s="28" t="n"/>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="221" t="n"/>
+      <c r="K44" s="222" t="n"/>
       <c r="L44" s="17" t="n"/>
       <c r="M44" s="18" t="n"/>
     </row>
@@ -8833,7 +8853,7 @@
       <c r="J45" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="224" t="n">
+      <c r="K45" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L45" s="26" t="inlineStr">
@@ -8894,7 +8914,7 @@
       <c r="J46" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="224" t="n">
+      <c r="K46" s="225" t="n">
         <v>44642</v>
       </c>
       <c r="L46" s="26" t="inlineStr">
@@ -8945,7 +8965,7 @@
       </c>
       <c r="I47" s="28" t="n"/>
       <c r="J47" s="15" t="n"/>
-      <c r="K47" s="221" t="n"/>
+      <c r="K47" s="222" t="n"/>
       <c r="L47" s="17" t="n"/>
       <c r="M47" s="18" t="n"/>
     </row>
@@ -8996,7 +9016,7 @@
       <c r="J48" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K48" s="224" t="n">
+      <c r="K48" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L48" s="17" t="n"/>
@@ -9043,7 +9063,7 @@
       </c>
       <c r="I49" s="28" t="n"/>
       <c r="J49" s="15" t="n"/>
-      <c r="K49" s="221" t="n"/>
+      <c r="K49" s="222" t="n"/>
       <c r="L49" s="26" t="inlineStr">
         <is>
           <t>官网信息不全</t>
@@ -9102,68 +9122,68 @@
       <c r="J50" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="225" t="n">
+      <c r="K50" s="226" t="n">
         <v>44652</v>
       </c>
       <c r="L50" s="18" t="n"/>
       <c r="M50" s="18" t="n"/>
     </row>
     <row r="51" ht="24.75" customHeight="1" s="70">
-      <c r="A51" s="222" t="n"/>
-      <c r="B51" s="222" t="n"/>
-      <c r="C51" s="222" t="n"/>
+      <c r="A51" s="223" t="n"/>
+      <c r="B51" s="223" t="n"/>
+      <c r="C51" s="223" t="n"/>
       <c r="D51" s="12" t="inlineStr">
         <is>
           <t>中国科学院生态环境研究中心</t>
         </is>
       </c>
-      <c r="E51" s="222" t="n"/>
-      <c r="F51" s="222" t="n"/>
-      <c r="G51" s="222" t="n"/>
-      <c r="H51" s="222" t="n"/>
-      <c r="I51" s="222" t="n"/>
-      <c r="J51" s="222" t="n"/>
-      <c r="K51" s="222" t="n"/>
-      <c r="L51" s="222" t="n"/>
-      <c r="M51" s="222" t="n"/>
+      <c r="E51" s="223" t="n"/>
+      <c r="F51" s="223" t="n"/>
+      <c r="G51" s="223" t="n"/>
+      <c r="H51" s="223" t="n"/>
+      <c r="I51" s="223" t="n"/>
+      <c r="J51" s="223" t="n"/>
+      <c r="K51" s="223" t="n"/>
+      <c r="L51" s="223" t="n"/>
+      <c r="M51" s="223" t="n"/>
     </row>
     <row r="52" ht="24.75" customHeight="1" s="70">
-      <c r="A52" s="222" t="n"/>
-      <c r="B52" s="222" t="n"/>
-      <c r="C52" s="222" t="n"/>
+      <c r="A52" s="223" t="n"/>
+      <c r="B52" s="223" t="n"/>
+      <c r="C52" s="223" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E52" s="222" t="n"/>
-      <c r="F52" s="222" t="n"/>
-      <c r="G52" s="222" t="n"/>
-      <c r="H52" s="222" t="n"/>
-      <c r="I52" s="222" t="n"/>
-      <c r="J52" s="222" t="n"/>
-      <c r="K52" s="222" t="n"/>
-      <c r="L52" s="222" t="n"/>
-      <c r="M52" s="222" t="n"/>
+      <c r="E52" s="223" t="n"/>
+      <c r="F52" s="223" t="n"/>
+      <c r="G52" s="223" t="n"/>
+      <c r="H52" s="223" t="n"/>
+      <c r="I52" s="223" t="n"/>
+      <c r="J52" s="223" t="n"/>
+      <c r="K52" s="223" t="n"/>
+      <c r="L52" s="223" t="n"/>
+      <c r="M52" s="223" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="70">
-      <c r="A53" s="223" t="n"/>
-      <c r="B53" s="223" t="n"/>
-      <c r="C53" s="223" t="n"/>
+      <c r="A53" s="224" t="n"/>
+      <c r="B53" s="224" t="n"/>
+      <c r="C53" s="224" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E53" s="223" t="n"/>
-      <c r="F53" s="223" t="n"/>
-      <c r="G53" s="223" t="n"/>
-      <c r="H53" s="223" t="n"/>
-      <c r="I53" s="223" t="n"/>
-      <c r="J53" s="223" t="n"/>
-      <c r="K53" s="223" t="n"/>
-      <c r="L53" s="223" t="n"/>
-      <c r="M53" s="223" t="n"/>
+      <c r="E53" s="224" t="n"/>
+      <c r="F53" s="224" t="n"/>
+      <c r="G53" s="224" t="n"/>
+      <c r="H53" s="224" t="n"/>
+      <c r="I53" s="224" t="n"/>
+      <c r="J53" s="224" t="n"/>
+      <c r="K53" s="224" t="n"/>
+      <c r="L53" s="224" t="n"/>
+      <c r="M53" s="224" t="n"/>
     </row>
     <row r="54" ht="24.75" customHeight="1" s="70">
       <c r="A54" s="11" t="n">
@@ -9206,7 +9226,7 @@
       </c>
       <c r="I54" s="28" t="n"/>
       <c r="J54" s="15" t="n"/>
-      <c r="K54" s="221" t="n"/>
+      <c r="K54" s="222" t="n"/>
       <c r="L54" s="17" t="n"/>
       <c r="M54" s="18" t="n"/>
     </row>
@@ -9257,30 +9277,30 @@
       <c r="J55" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="225" t="n">
+      <c r="K55" s="226" t="n">
         <v>44599</v>
       </c>
       <c r="L55" s="18" t="n"/>
       <c r="M55" s="18" t="n"/>
     </row>
     <row r="56" ht="24.75" customHeight="1" s="70">
-      <c r="A56" s="223" t="n"/>
-      <c r="B56" s="223" t="n"/>
-      <c r="C56" s="223" t="n"/>
+      <c r="A56" s="224" t="n"/>
+      <c r="B56" s="224" t="n"/>
+      <c r="C56" s="224" t="n"/>
       <c r="D56" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E56" s="223" t="n"/>
-      <c r="F56" s="223" t="n"/>
-      <c r="G56" s="223" t="n"/>
-      <c r="H56" s="223" t="n"/>
-      <c r="I56" s="223" t="n"/>
-      <c r="J56" s="223" t="n"/>
-      <c r="K56" s="223" t="n"/>
-      <c r="L56" s="223" t="n"/>
-      <c r="M56" s="223" t="n"/>
+      <c r="E56" s="224" t="n"/>
+      <c r="F56" s="224" t="n"/>
+      <c r="G56" s="224" t="n"/>
+      <c r="H56" s="224" t="n"/>
+      <c r="I56" s="224" t="n"/>
+      <c r="J56" s="224" t="n"/>
+      <c r="K56" s="224" t="n"/>
+      <c r="L56" s="224" t="n"/>
+      <c r="M56" s="224" t="n"/>
     </row>
     <row r="57" ht="24.75" customHeight="1" s="70">
       <c r="A57" s="11" t="n">
@@ -9329,7 +9349,7 @@
       <c r="J57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="224" t="n">
+      <c r="K57" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L57" s="26" t="inlineStr">
@@ -9386,7 +9406,7 @@
       <c r="J58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="224" t="n">
+      <c r="K58" s="225" t="n">
         <v>44658</v>
       </c>
       <c r="L58" s="26" t="inlineStr">
@@ -9443,7 +9463,7 @@
       <c r="J59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="229" t="n">
+      <c r="K59" s="230" t="n">
         <v>44615</v>
       </c>
       <c r="L59" s="36" t="n"/>
@@ -9496,7 +9516,7 @@
       <c r="J60" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K60" s="230" t="n">
+      <c r="K60" s="231" t="n">
         <v>44667</v>
       </c>
       <c r="L60" s="17" t="n"/>
@@ -9549,7 +9569,7 @@
       <c r="J61" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K61" s="224" t="n">
+      <c r="K61" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L61" s="17" t="n"/>
@@ -9602,30 +9622,30 @@
       <c r="J62" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K62" s="225" t="n">
+      <c r="K62" s="226" t="n">
         <v>44877</v>
       </c>
       <c r="L62" s="18" t="n"/>
       <c r="M62" s="18" t="n"/>
     </row>
     <row r="63" ht="24.75" customHeight="1" s="70">
-      <c r="A63" s="223" t="n"/>
-      <c r="B63" s="223" t="n"/>
-      <c r="C63" s="223" t="n"/>
+      <c r="A63" s="224" t="n"/>
+      <c r="B63" s="224" t="n"/>
+      <c r="C63" s="224" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学</t>
         </is>
       </c>
-      <c r="E63" s="223" t="n"/>
-      <c r="F63" s="223" t="n"/>
-      <c r="G63" s="223" t="n"/>
-      <c r="H63" s="223" t="n"/>
-      <c r="I63" s="223" t="n"/>
-      <c r="J63" s="223" t="n"/>
-      <c r="K63" s="223" t="n"/>
-      <c r="L63" s="223" t="n"/>
-      <c r="M63" s="223" t="n"/>
+      <c r="E63" s="224" t="n"/>
+      <c r="F63" s="224" t="n"/>
+      <c r="G63" s="224" t="n"/>
+      <c r="H63" s="224" t="n"/>
+      <c r="I63" s="224" t="n"/>
+      <c r="J63" s="224" t="n"/>
+      <c r="K63" s="224" t="n"/>
+      <c r="L63" s="224" t="n"/>
+      <c r="M63" s="224" t="n"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" s="70">
       <c r="A64" s="11" t="n">
@@ -9674,7 +9694,7 @@
       <c r="J64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="224" t="n">
+      <c r="K64" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L64" s="26" t="inlineStr">
@@ -9729,7 +9749,7 @@
       </c>
       <c r="I65" s="28" t="n"/>
       <c r="J65" s="15" t="n"/>
-      <c r="K65" s="221" t="n"/>
+      <c r="K65" s="222" t="n"/>
       <c r="L65" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -9784,7 +9804,7 @@
       <c r="J66" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K66" s="224" t="n">
+      <c r="K66" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L66" s="26" t="inlineStr">
@@ -9839,7 +9859,7 @@
       </c>
       <c r="I67" s="28" t="n"/>
       <c r="J67" s="15" t="n"/>
-      <c r="K67" s="221" t="n"/>
+      <c r="K67" s="222" t="n"/>
       <c r="L67" s="26" t="inlineStr">
         <is>
           <t>未找到往年信息</t>
@@ -9892,7 +9912,7 @@
       </c>
       <c r="I68" s="28" t="n"/>
       <c r="J68" s="15" t="n"/>
-      <c r="K68" s="221" t="n"/>
+      <c r="K68" s="222" t="n"/>
       <c r="L68" s="17" t="n"/>
       <c r="M68" s="18" t="n"/>
     </row>
@@ -9943,7 +9963,7 @@
       <c r="J69" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K69" s="224" t="n">
+      <c r="K69" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L69" s="26" t="inlineStr">
@@ -10000,7 +10020,7 @@
       <c r="J70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="224" t="n">
+      <c r="K70" s="225" t="n">
         <v>44565</v>
       </c>
       <c r="L70" s="26" t="inlineStr">
@@ -10057,30 +10077,30 @@
       <c r="J71" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K71" s="225" t="n">
+      <c r="K71" s="226" t="n">
         <v>44882</v>
       </c>
       <c r="L71" s="36" t="n"/>
       <c r="M71" s="18" t="n"/>
     </row>
     <row r="72" ht="24.75" customHeight="1" s="70">
-      <c r="A72" s="223" t="n"/>
-      <c r="B72" s="223" t="n"/>
-      <c r="C72" s="223" t="n"/>
+      <c r="A72" s="224" t="n"/>
+      <c r="B72" s="224" t="n"/>
+      <c r="C72" s="224" t="n"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
           <t>南京大学</t>
         </is>
       </c>
-      <c r="E72" s="223" t="n"/>
-      <c r="F72" s="223" t="n"/>
-      <c r="G72" s="223" t="n"/>
-      <c r="H72" s="223" t="n"/>
-      <c r="I72" s="223" t="n"/>
-      <c r="J72" s="223" t="n"/>
-      <c r="K72" s="223" t="n"/>
-      <c r="L72" s="228" t="n"/>
-      <c r="M72" s="223" t="n"/>
+      <c r="E72" s="224" t="n"/>
+      <c r="F72" s="224" t="n"/>
+      <c r="G72" s="224" t="n"/>
+      <c r="H72" s="224" t="n"/>
+      <c r="I72" s="224" t="n"/>
+      <c r="J72" s="224" t="n"/>
+      <c r="K72" s="224" t="n"/>
+      <c r="L72" s="229" t="n"/>
+      <c r="M72" s="224" t="n"/>
     </row>
     <row r="73" ht="24.75" customHeight="1" s="70">
       <c r="A73" s="11" t="n">
@@ -10129,7 +10149,7 @@
       <c r="J73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K73" s="224" t="n">
+      <c r="K73" s="225" t="n">
         <v>44670</v>
       </c>
       <c r="L73" s="26" t="inlineStr">
@@ -10186,7 +10206,7 @@
       <c r="J74" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K74" s="224" t="n">
+      <c r="K74" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L74" s="26" t="inlineStr">
@@ -10243,7 +10263,7 @@
       <c r="J75" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="224" t="n">
+      <c r="K75" s="225" t="n">
         <v>44588</v>
       </c>
       <c r="L75" s="26" t="inlineStr">
@@ -10300,7 +10320,7 @@
       <c r="J76" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="224" t="n">
+      <c r="K76" s="225" t="n">
         <v>44667</v>
       </c>
       <c r="L76" s="26" t="inlineStr">
@@ -10357,7 +10377,7 @@
       <c r="J77" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="224" t="n">
+      <c r="K77" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L77" s="26" t="inlineStr">
@@ -10414,7 +10434,7 @@
       <c r="J78" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K78" s="224" t="n">
+      <c r="K78" s="225" t="n">
         <v>44741</v>
       </c>
       <c r="L78" s="26" t="inlineStr">
@@ -10471,7 +10491,7 @@
       <c r="J79" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K79" s="224" t="n">
+      <c r="K79" s="225" t="n">
         <v>44825</v>
       </c>
       <c r="L79" s="17" t="n"/>
@@ -10524,7 +10544,7 @@
       <c r="J80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="231" t="n">
+      <c r="K80" s="232" t="n">
         <v>44709</v>
       </c>
       <c r="L80" s="36" t="n"/>
@@ -10577,7 +10597,7 @@
       <c r="J81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K81" s="232" t="n">
+      <c r="K81" s="233" t="n">
         <v>44670</v>
       </c>
       <c r="L81" s="17" t="n"/>
@@ -10620,7 +10640,7 @@
       <c r="H82" s="31" t="n"/>
       <c r="I82" s="48" t="n"/>
       <c r="J82" s="31" t="n"/>
-      <c r="K82" s="233" t="n"/>
+      <c r="K82" s="234" t="n"/>
       <c r="L82" s="29" t="inlineStr">
         <is>
           <t>不是专用连接，进不了官网</t>
@@ -10629,23 +10649,23 @@
       <c r="M82" s="18" t="n"/>
     </row>
     <row r="83" ht="24.75" customHeight="1" s="70">
-      <c r="A83" s="223" t="n"/>
-      <c r="B83" s="223" t="n"/>
-      <c r="C83" s="223" t="n"/>
+      <c r="A83" s="224" t="n"/>
+      <c r="B83" s="224" t="n"/>
+      <c r="C83" s="224" t="n"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
           <t>中国地质大学（北京）</t>
         </is>
       </c>
-      <c r="E83" s="223" t="n"/>
-      <c r="F83" s="223" t="n"/>
-      <c r="G83" s="223" t="n"/>
-      <c r="H83" s="223" t="n"/>
-      <c r="I83" s="223" t="n"/>
-      <c r="J83" s="223" t="n"/>
-      <c r="K83" s="223" t="n"/>
-      <c r="L83" s="223" t="n"/>
-      <c r="M83" s="223" t="n"/>
+      <c r="E83" s="224" t="n"/>
+      <c r="F83" s="224" t="n"/>
+      <c r="G83" s="224" t="n"/>
+      <c r="H83" s="224" t="n"/>
+      <c r="I83" s="224" t="n"/>
+      <c r="J83" s="224" t="n"/>
+      <c r="K83" s="224" t="n"/>
+      <c r="L83" s="224" t="n"/>
+      <c r="M83" s="224" t="n"/>
     </row>
     <row r="84" ht="24.75" customHeight="1" s="70">
       <c r="A84" s="11" t="n">
@@ -10694,7 +10714,7 @@
       <c r="J84" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K84" s="224" t="n">
+      <c r="K84" s="225" t="n">
         <v>44813</v>
       </c>
       <c r="L84" s="17" t="n"/>
@@ -10747,7 +10767,7 @@
       <c r="J85" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K85" s="224" t="n">
+      <c r="K85" s="225" t="n">
         <v>44881</v>
       </c>
       <c r="L85" s="26" t="inlineStr">
@@ -10804,7 +10824,7 @@
       <c r="J86" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="224" t="n">
+      <c r="K86" s="225" t="n">
         <v>44635</v>
       </c>
       <c r="L86" s="26" t="inlineStr">
@@ -10861,7 +10881,7 @@
       <c r="J87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K87" s="224" t="n">
+      <c r="K87" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L87" s="26" t="inlineStr">
@@ -10922,7 +10942,7 @@
       <c r="J88" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K88" s="224" t="n">
+      <c r="K88" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L88" s="26" t="inlineStr">
@@ -10979,7 +10999,7 @@
       <c r="J89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="224" t="n">
+      <c r="K89" s="225" t="n">
         <v>44592</v>
       </c>
       <c r="L89" s="26" t="inlineStr">
@@ -10990,17 +11010,17 @@
       <c r="M89" s="18" t="n"/>
     </row>
     <row r="90" ht="24.75" customHeight="1" s="70">
-      <c r="A90" s="223" t="n"/>
-      <c r="B90" s="223" t="n"/>
-      <c r="C90" s="223" t="n"/>
+      <c r="A90" s="224" t="n"/>
+      <c r="B90" s="224" t="n"/>
+      <c r="C90" s="224" t="n"/>
       <c r="D90" s="12" t="inlineStr">
         <is>
           <t>成都理工大学</t>
         </is>
       </c>
-      <c r="E90" s="223" t="n"/>
-      <c r="F90" s="223" t="n"/>
-      <c r="G90" s="223" t="n"/>
+      <c r="E90" s="224" t="n"/>
+      <c r="F90" s="224" t="n"/>
+      <c r="G90" s="224" t="n"/>
       <c r="H90" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11014,7 +11034,7 @@
       <c r="J90" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K90" s="224" t="n">
+      <c r="K90" s="225" t="n">
         <v>44871</v>
       </c>
       <c r="L90" s="26" t="inlineStr">
@@ -11071,7 +11091,7 @@
       <c r="J91" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K91" s="224" t="n">
+      <c r="K91" s="225" t="n">
         <v>44806</v>
       </c>
       <c r="L91" s="26" t="inlineStr">
@@ -11128,7 +11148,7 @@
       <c r="J92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="224" t="n">
+      <c r="K92" s="225" t="n">
         <v>44576</v>
       </c>
       <c r="L92" s="26" t="inlineStr">
@@ -11179,7 +11199,7 @@
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="50" t="n"/>
-      <c r="K93" s="234" t="n"/>
+      <c r="K93" s="235" t="n"/>
       <c r="L93" s="17" t="n"/>
       <c r="M93" s="18" t="n"/>
     </row>
@@ -11230,7 +11250,7 @@
       <c r="J94" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K94" s="224" t="n">
+      <c r="K94" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L94" s="17" t="n"/>
@@ -11283,7 +11303,7 @@
       <c r="J95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K95" s="224" t="n">
+      <c r="K95" s="225" t="n">
         <v>44679</v>
       </c>
       <c r="L95" s="17" t="n"/>
@@ -11336,7 +11356,7 @@
       <c r="J96" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K96" s="224" t="n">
+      <c r="K96" s="225" t="n">
         <v>44840</v>
       </c>
       <c r="L96" s="17" t="n"/>
@@ -11389,7 +11409,7 @@
       <c r="J97" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K97" s="224" t="n">
+      <c r="K97" s="225" t="n">
         <v>44848</v>
       </c>
       <c r="L97" s="17" t="n"/>
@@ -11442,7 +11462,7 @@
       <c r="J98" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K98" s="224" t="n">
+      <c r="K98" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L98" s="17" t="n"/>
@@ -11495,7 +11515,7 @@
       <c r="J99" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="224" t="n">
+      <c r="K99" s="225" t="n">
         <v>44644</v>
       </c>
       <c r="L99" s="17" t="n"/>
@@ -11548,7 +11568,7 @@
       <c r="J100" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K100" s="224" t="n">
+      <c r="K100" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L100" s="26" t="inlineStr">
@@ -11609,7 +11629,7 @@
       <c r="J101" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K101" s="224" t="n">
+      <c r="K101" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L101" s="26" t="inlineStr">
@@ -11666,7 +11686,7 @@
       <c r="J102" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K102" s="224" t="n">
+      <c r="K102" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L102" s="26" t="inlineStr">
@@ -11717,22 +11737,22 @@
       </c>
       <c r="I103" s="28" t="n"/>
       <c r="J103" s="15" t="n"/>
-      <c r="K103" s="221" t="n"/>
+      <c r="K103" s="222" t="n"/>
       <c r="L103" s="17" t="n"/>
       <c r="M103" s="18" t="n"/>
     </row>
     <row r="104" ht="24.75" customHeight="1" s="70">
-      <c r="A104" s="222" t="n"/>
-      <c r="B104" s="222" t="n"/>
-      <c r="C104" s="222" t="n"/>
+      <c r="A104" s="223" t="n"/>
+      <c r="B104" s="223" t="n"/>
+      <c r="C104" s="223" t="n"/>
       <c r="D104" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E104" s="222" t="n"/>
-      <c r="F104" s="222" t="n"/>
-      <c r="G104" s="222" t="n"/>
+      <c r="E104" s="223" t="n"/>
+      <c r="F104" s="223" t="n"/>
+      <c r="G104" s="223" t="n"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11746,7 +11766,7 @@
       <c r="J104" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K104" s="224" t="n">
+      <c r="K104" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L104" s="26" t="inlineStr">
@@ -11757,17 +11777,17 @@
       <c r="M104" s="18" t="n"/>
     </row>
     <row r="105" ht="24.75" customHeight="1" s="70">
-      <c r="A105" s="223" t="n"/>
-      <c r="B105" s="223" t="n"/>
-      <c r="C105" s="223" t="n"/>
+      <c r="A105" s="224" t="n"/>
+      <c r="B105" s="224" t="n"/>
+      <c r="C105" s="224" t="n"/>
       <c r="D105" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E105" s="223" t="n"/>
-      <c r="F105" s="223" t="n"/>
-      <c r="G105" s="223" t="n"/>
+      <c r="E105" s="224" t="n"/>
+      <c r="F105" s="224" t="n"/>
+      <c r="G105" s="224" t="n"/>
       <c r="H105" s="52" t="inlineStr">
         <is>
           <t>否</t>
@@ -11826,7 +11846,7 @@
       <c r="J106" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="K106" s="232" t="n">
+      <c r="K106" s="233" t="n">
         <v>44814</v>
       </c>
       <c r="L106" s="40" t="n"/>
@@ -11873,7 +11893,7 @@
       </c>
       <c r="I107" s="56" t="n"/>
       <c r="J107" s="15" t="n"/>
-      <c r="K107" s="221" t="n"/>
+      <c r="K107" s="222" t="n"/>
       <c r="L107" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11930,7 +11950,7 @@
         </is>
       </c>
       <c r="J108" s="15" t="n"/>
-      <c r="K108" s="221" t="n"/>
+      <c r="K108" s="222" t="n"/>
       <c r="L108" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11979,7 +11999,7 @@
       </c>
       <c r="I109" s="28" t="n"/>
       <c r="J109" s="15" t="n"/>
-      <c r="K109" s="221" t="n"/>
+      <c r="K109" s="222" t="n"/>
       <c r="L109" s="26" t="inlineStr">
         <is>
           <t>网址打不开</t>
@@ -12032,7 +12052,7 @@
         </is>
       </c>
       <c r="J110" s="15" t="n"/>
-      <c r="K110" s="221" t="n"/>
+      <c r="K110" s="222" t="n"/>
       <c r="L110" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -12041,17 +12061,17 @@
       <c r="M110" s="18" t="n"/>
     </row>
     <row r="111" ht="24.75" customHeight="1" s="70">
-      <c r="A111" s="223" t="n"/>
-      <c r="B111" s="223" t="n"/>
-      <c r="C111" s="223" t="n"/>
+      <c r="A111" s="224" t="n"/>
+      <c r="B111" s="224" t="n"/>
+      <c r="C111" s="224" t="n"/>
       <c r="D111" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E111" s="223" t="n"/>
-      <c r="F111" s="223" t="n"/>
-      <c r="G111" s="223" t="n"/>
+      <c r="E111" s="224" t="n"/>
+      <c r="F111" s="224" t="n"/>
+      <c r="G111" s="224" t="n"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
           <t>否</t>
@@ -12059,7 +12079,7 @@
       </c>
       <c r="I111" s="28" t="n"/>
       <c r="J111" s="15" t="n"/>
-      <c r="K111" s="221" t="n"/>
+      <c r="K111" s="222" t="n"/>
       <c r="L111" s="17" t="n"/>
       <c r="M111" s="18" t="n"/>
     </row>
@@ -12108,7 +12128,7 @@
         </is>
       </c>
       <c r="J112" s="31" t="n"/>
-      <c r="K112" s="233" t="n"/>
+      <c r="K112" s="234" t="n"/>
       <c r="L112" s="29" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -12117,23 +12137,23 @@
       <c r="M112" s="18" t="n"/>
     </row>
     <row r="113" ht="24.75" customHeight="1" s="70">
-      <c r="A113" s="223" t="n"/>
-      <c r="B113" s="223" t="n"/>
-      <c r="C113" s="223" t="n"/>
+      <c r="A113" s="224" t="n"/>
+      <c r="B113" s="224" t="n"/>
+      <c r="C113" s="224" t="n"/>
       <c r="D113" s="12" t="inlineStr">
         <is>
           <t>中国科学院微生物研究所</t>
         </is>
       </c>
-      <c r="E113" s="223" t="n"/>
-      <c r="F113" s="223" t="n"/>
-      <c r="G113" s="223" t="n"/>
-      <c r="H113" s="223" t="n"/>
-      <c r="I113" s="223" t="n"/>
-      <c r="J113" s="223" t="n"/>
-      <c r="K113" s="223" t="n"/>
-      <c r="L113" s="223" t="n"/>
-      <c r="M113" s="223" t="n"/>
+      <c r="E113" s="224" t="n"/>
+      <c r="F113" s="224" t="n"/>
+      <c r="G113" s="224" t="n"/>
+      <c r="H113" s="224" t="n"/>
+      <c r="I113" s="224" t="n"/>
+      <c r="J113" s="224" t="n"/>
+      <c r="K113" s="224" t="n"/>
+      <c r="L113" s="224" t="n"/>
+      <c r="M113" s="224" t="n"/>
     </row>
     <row r="114" ht="24.75" customHeight="1" s="70">
       <c r="A114" s="11" t="n">
@@ -12176,7 +12196,7 @@
       </c>
       <c r="I114" s="28" t="n"/>
       <c r="J114" s="15" t="n"/>
-      <c r="K114" s="221" t="n"/>
+      <c r="K114" s="222" t="n"/>
       <c r="L114" s="17" t="n"/>
       <c r="M114" s="18" t="n"/>
     </row>
@@ -12227,7 +12247,7 @@
       <c r="J115" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K115" s="225" t="n">
+      <c r="K115" s="226" t="n">
         <v>44690</v>
       </c>
       <c r="L115" s="27" t="inlineStr">
@@ -12238,23 +12258,23 @@
       <c r="M115" s="18" t="n"/>
     </row>
     <row r="116" ht="24.75" customHeight="1" s="70">
-      <c r="A116" s="223" t="n"/>
-      <c r="B116" s="223" t="n"/>
-      <c r="C116" s="223" t="n"/>
+      <c r="A116" s="224" t="n"/>
+      <c r="B116" s="224" t="n"/>
+      <c r="C116" s="224" t="n"/>
       <c r="D116" s="12" t="inlineStr">
         <is>
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="E116" s="223" t="n"/>
-      <c r="F116" s="223" t="n"/>
-      <c r="G116" s="223" t="n"/>
-      <c r="H116" s="223" t="n"/>
-      <c r="I116" s="223" t="n"/>
-      <c r="J116" s="223" t="n"/>
-      <c r="K116" s="223" t="n"/>
-      <c r="L116" s="223" t="n"/>
-      <c r="M116" s="223" t="n"/>
+      <c r="E116" s="224" t="n"/>
+      <c r="F116" s="224" t="n"/>
+      <c r="G116" s="224" t="n"/>
+      <c r="H116" s="224" t="n"/>
+      <c r="I116" s="224" t="n"/>
+      <c r="J116" s="224" t="n"/>
+      <c r="K116" s="224" t="n"/>
+      <c r="L116" s="224" t="n"/>
+      <c r="M116" s="224" t="n"/>
     </row>
     <row r="117" ht="24.75" customHeight="1" s="70">
       <c r="A117" s="11" t="n">
@@ -12303,16 +12323,16 @@
       <c r="J117" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K117" s="224" t="n">
+      <c r="K117" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L117" s="17" t="n"/>
       <c r="M117" s="18" t="n"/>
     </row>
     <row r="118" ht="24.75" customHeight="1" s="70">
-      <c r="A118" s="223" t="n"/>
-      <c r="B118" s="223" t="n"/>
-      <c r="C118" s="223" t="n"/>
+      <c r="A118" s="224" t="n"/>
+      <c r="B118" s="224" t="n"/>
+      <c r="C118" s="224" t="n"/>
       <c r="D118" s="12" t="inlineStr">
         <is>
           <t>东北林业大学</t>
@@ -12323,8 +12343,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F118" s="223" t="n"/>
-      <c r="G118" s="223" t="n"/>
+      <c r="F118" s="224" t="n"/>
+      <c r="G118" s="224" t="n"/>
       <c r="H118" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12338,7 +12358,7 @@
       <c r="J118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K118" s="224" t="n">
+      <c r="K118" s="225" t="n">
         <v>44834</v>
       </c>
       <c r="L118" s="17" t="n"/>
@@ -12389,7 +12409,7 @@
         </is>
       </c>
       <c r="J119" s="15" t="n"/>
-      <c r="K119" s="221" t="n"/>
+      <c r="K119" s="222" t="n"/>
       <c r="L119" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知页</t>
@@ -12442,7 +12462,7 @@
       </c>
       <c r="I120" s="28" t="n"/>
       <c r="J120" s="15" t="n"/>
-      <c r="K120" s="221" t="n"/>
+      <c r="K120" s="222" t="n"/>
       <c r="L120" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -12497,7 +12517,7 @@
       <c r="J121" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="224" t="n">
+      <c r="K121" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L121" s="17" t="n"/>
@@ -12550,7 +12570,7 @@
       <c r="J122" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K122" s="224" t="n">
+      <c r="K122" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L122" s="17" t="n"/>
@@ -12597,7 +12617,7 @@
       </c>
       <c r="I123" s="28" t="n"/>
       <c r="J123" s="15" t="n"/>
-      <c r="K123" s="221" t="n"/>
+      <c r="K123" s="222" t="n"/>
       <c r="L123" s="17" t="n"/>
       <c r="M123" s="18" t="n"/>
     </row>
@@ -12648,7 +12668,7 @@
       <c r="J124" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K124" s="224" t="n">
+      <c r="K124" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -12701,7 +12721,7 @@
       <c r="J125" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K125" s="224" t="n">
+      <c r="K125" s="225" t="n">
         <v>44809</v>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -12748,7 +12768,7 @@
       </c>
       <c r="I126" s="28" t="n"/>
       <c r="J126" s="15" t="n"/>
-      <c r="K126" s="221" t="n"/>
+      <c r="K126" s="222" t="n"/>
       <c r="L126" s="26" t="inlineStr">
         <is>
           <t>未找到相应的官网</t>
@@ -12803,7 +12823,7 @@
       <c r="J127" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K127" s="224" t="n">
+      <c r="K127" s="225" t="n">
         <v>44589</v>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -12856,7 +12876,7 @@
       <c r="J128" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K128" s="224" t="n">
+      <c r="K128" s="225" t="n">
         <v>44917</v>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -12909,24 +12929,24 @@
       <c r="J129" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K129" s="224" t="n">
+      <c r="K129" s="225" t="n">
         <v>44586</v>
       </c>
       <c r="L129" s="17" t="n"/>
       <c r="M129" s="18" t="n"/>
     </row>
     <row r="130" ht="24.75" customHeight="1" s="70">
-      <c r="A130" s="223" t="n"/>
-      <c r="B130" s="223" t="n"/>
-      <c r="C130" s="223" t="n"/>
+      <c r="A130" s="224" t="n"/>
+      <c r="B130" s="224" t="n"/>
+      <c r="C130" s="224" t="n"/>
       <c r="D130" s="12" t="inlineStr">
         <is>
           <t>南昌大学</t>
         </is>
       </c>
-      <c r="E130" s="223" t="n"/>
-      <c r="F130" s="223" t="n"/>
-      <c r="G130" s="223" t="n"/>
+      <c r="E130" s="224" t="n"/>
+      <c r="F130" s="224" t="n"/>
+      <c r="G130" s="224" t="n"/>
       <c r="H130" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12940,7 +12960,7 @@
       <c r="J130" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K130" s="224" t="n">
+      <c r="K130" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L130" s="26" t="inlineStr">
@@ -12991,26 +13011,26 @@
       </c>
       <c r="I131" s="28" t="n"/>
       <c r="J131" s="15" t="n"/>
-      <c r="K131" s="221" t="n"/>
+      <c r="K131" s="222" t="n"/>
       <c r="L131" s="17" t="n"/>
       <c r="M131" s="18" t="n"/>
     </row>
     <row r="132" ht="24.75" customHeight="1" s="70">
-      <c r="A132" s="223" t="n"/>
-      <c r="B132" s="223" t="n"/>
-      <c r="C132" s="223" t="n"/>
+      <c r="A132" s="224" t="n"/>
+      <c r="B132" s="224" t="n"/>
+      <c r="C132" s="224" t="n"/>
       <c r="D132" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E132" s="223" t="n"/>
-      <c r="F132" s="223" t="n"/>
-      <c r="G132" s="223" t="n"/>
-      <c r="H132" s="223" t="n"/>
+      <c r="E132" s="224" t="n"/>
+      <c r="F132" s="224" t="n"/>
+      <c r="G132" s="224" t="n"/>
+      <c r="H132" s="224" t="n"/>
       <c r="I132" s="28" t="n"/>
       <c r="J132" s="15" t="n"/>
-      <c r="K132" s="221" t="n"/>
+      <c r="K132" s="222" t="n"/>
       <c r="L132" s="17" t="n"/>
       <c r="M132" s="18" t="n"/>
     </row>
@@ -13061,7 +13081,7 @@
       <c r="J133" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K133" s="224" t="n">
+      <c r="K133" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -13108,7 +13128,7 @@
       </c>
       <c r="I134" s="28" t="n"/>
       <c r="J134" s="15" t="n"/>
-      <c r="K134" s="221" t="n"/>
+      <c r="K134" s="222" t="n"/>
       <c r="L134" s="26" t="inlineStr">
         <is>
           <t>开放课题基金的申请每年受理一次，申请截止日期为每年的3月15日。</t>
@@ -13167,16 +13187,16 @@
       <c r="J135" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K135" s="225" t="n">
+      <c r="K135" s="226" t="n">
         <v>44878</v>
       </c>
       <c r="L135" s="18" t="n"/>
       <c r="M135" s="58" t="n"/>
     </row>
     <row r="136" ht="24.75" customHeight="1" s="70">
-      <c r="A136" s="223" t="n"/>
-      <c r="B136" s="223" t="n"/>
-      <c r="C136" s="223" t="n"/>
+      <c r="A136" s="224" t="n"/>
+      <c r="B136" s="224" t="n"/>
+      <c r="C136" s="224" t="n"/>
       <c r="D136" s="12" t="inlineStr">
         <is>
           <t>河南大学</t>
@@ -13187,13 +13207,13 @@
           <t>河南省科技厅</t>
         </is>
       </c>
-      <c r="F136" s="223" t="n"/>
-      <c r="G136" s="223" t="n"/>
-      <c r="H136" s="223" t="n"/>
-      <c r="I136" s="223" t="n"/>
-      <c r="J136" s="223" t="n"/>
-      <c r="K136" s="223" t="n"/>
-      <c r="L136" s="223" t="n"/>
+      <c r="F136" s="224" t="n"/>
+      <c r="G136" s="224" t="n"/>
+      <c r="H136" s="224" t="n"/>
+      <c r="I136" s="224" t="n"/>
+      <c r="J136" s="224" t="n"/>
+      <c r="K136" s="224" t="n"/>
+      <c r="L136" s="224" t="n"/>
       <c r="M136" s="58" t="n"/>
     </row>
     <row r="137" ht="24.75" customHeight="1" s="70">
@@ -13243,7 +13263,7 @@
       <c r="J137" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K137" s="224" t="n">
+      <c r="K137" s="225" t="n">
         <v>44624</v>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -13296,7 +13316,7 @@
       <c r="J138" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K138" s="224" t="n">
+      <c r="K138" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L138" s="26" t="inlineStr">
@@ -13353,7 +13373,7 @@
       <c r="J139" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K139" s="224" t="n">
+      <c r="K139" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -13400,26 +13420,26 @@
       </c>
       <c r="I140" s="48" t="n"/>
       <c r="J140" s="31" t="n"/>
-      <c r="K140" s="233" t="n"/>
+      <c r="K140" s="234" t="n"/>
       <c r="L140" s="17" t="n"/>
       <c r="M140" s="18" t="n"/>
     </row>
     <row r="141" ht="24.75" customHeight="1" s="70">
-      <c r="A141" s="223" t="n"/>
-      <c r="B141" s="223" t="n"/>
-      <c r="C141" s="223" t="n"/>
+      <c r="A141" s="224" t="n"/>
+      <c r="B141" s="224" t="n"/>
+      <c r="C141" s="224" t="n"/>
       <c r="D141" s="12" t="inlineStr">
         <is>
           <t>中国科学院武汉病毒研究所</t>
         </is>
       </c>
-      <c r="E141" s="223" t="n"/>
-      <c r="F141" s="223" t="n"/>
-      <c r="G141" s="223" t="n"/>
-      <c r="H141" s="223" t="n"/>
-      <c r="I141" s="223" t="n"/>
-      <c r="J141" s="223" t="n"/>
-      <c r="K141" s="223" t="n"/>
+      <c r="E141" s="224" t="n"/>
+      <c r="F141" s="224" t="n"/>
+      <c r="G141" s="224" t="n"/>
+      <c r="H141" s="224" t="n"/>
+      <c r="I141" s="224" t="n"/>
+      <c r="J141" s="224" t="n"/>
+      <c r="K141" s="224" t="n"/>
       <c r="L141" s="17" t="n"/>
       <c r="M141" s="18" t="n"/>
     </row>
@@ -13470,16 +13490,16 @@
       <c r="J142" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K142" s="224" t="n">
+      <c r="K142" s="225" t="n">
         <v>44745</v>
       </c>
       <c r="L142" s="17" t="n"/>
       <c r="M142" s="18" t="n"/>
     </row>
     <row r="143" ht="24.75" customHeight="1" s="70">
-      <c r="A143" s="223" t="n"/>
-      <c r="B143" s="223" t="n"/>
-      <c r="C143" s="223" t="n"/>
+      <c r="A143" s="224" t="n"/>
+      <c r="B143" s="224" t="n"/>
+      <c r="C143" s="224" t="n"/>
       <c r="D143" s="12" t="inlineStr">
         <is>
           <t>武汉大学</t>
@@ -13490,8 +13510,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F143" s="223" t="n"/>
-      <c r="G143" s="223" t="n"/>
+      <c r="F143" s="224" t="n"/>
+      <c r="G143" s="224" t="n"/>
       <c r="H143" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13505,7 +13525,7 @@
       <c r="J143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K143" s="224" t="n">
+      <c r="K143" s="225" t="n">
         <v>44675</v>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -13558,7 +13578,7 @@
       <c r="J144" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K144" s="224" t="n">
+      <c r="K144" s="225" t="n">
         <v>44826</v>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -13611,16 +13631,16 @@
       <c r="J145" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K145" s="224" t="n">
+      <c r="K145" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L145" s="17" t="n"/>
       <c r="M145" s="18" t="n"/>
     </row>
     <row r="146" ht="24.75" customHeight="1" s="70">
-      <c r="A146" s="223" t="n"/>
-      <c r="B146" s="223" t="n"/>
-      <c r="C146" s="223" t="n"/>
+      <c r="A146" s="224" t="n"/>
+      <c r="B146" s="224" t="n"/>
+      <c r="C146" s="224" t="n"/>
       <c r="D146" s="12" t="inlineStr">
         <is>
           <t>华南农业大学</t>
@@ -13631,8 +13651,8 @@
           <t>广东省科技厅</t>
         </is>
       </c>
-      <c r="F146" s="223" t="n"/>
-      <c r="G146" s="223" t="n"/>
+      <c r="F146" s="224" t="n"/>
+      <c r="G146" s="224" t="n"/>
       <c r="H146" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13646,7 +13666,7 @@
       <c r="J146" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K146" s="224" t="n">
+      <c r="K146" s="225" t="n">
         <v>44876</v>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -13699,7 +13719,7 @@
       <c r="J147" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K147" s="224" t="n">
+      <c r="K147" s="225" t="n">
         <v>44870</v>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -13752,7 +13772,7 @@
       <c r="J148" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K148" s="224" t="n">
+      <c r="K148" s="225" t="n">
         <v>44653</v>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -13805,7 +13825,7 @@
       <c r="J149" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K149" s="224" t="n">
+      <c r="K149" s="225" t="n">
         <v>44844</v>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -13858,7 +13878,7 @@
       <c r="J150" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K150" s="224" t="n">
+      <c r="K150" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L150" s="17" t="n"/>
@@ -13911,7 +13931,7 @@
       <c r="J151" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K151" s="224" t="n">
+      <c r="K151" s="225" t="n">
         <v>44737</v>
       </c>
       <c r="L151" s="17" t="n"/>
@@ -13964,7 +13984,7 @@
       <c r="J152" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K152" s="224" t="n">
+      <c r="K152" s="225" t="n">
         <v>44761</v>
       </c>
       <c r="L152" s="17" t="n"/>
@@ -14017,7 +14037,7 @@
       <c r="J153" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K153" s="224" t="n">
+      <c r="K153" s="225" t="n">
         <v>44590</v>
       </c>
       <c r="L153" s="17" t="n"/>
@@ -14070,7 +14090,7 @@
       <c r="J154" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K154" s="224" t="n">
+      <c r="K154" s="225" t="n">
         <v>44597</v>
       </c>
       <c r="L154" s="17" t="n"/>
@@ -14125,7 +14145,7 @@
           <t>4、5</t>
         </is>
       </c>
-      <c r="K155" s="224" t="n">
+      <c r="K155" s="225" t="n">
         <v>44701</v>
       </c>
       <c r="L155" s="17" t="n"/>
@@ -14178,7 +14198,7 @@
       <c r="J156" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K156" s="224" t="n">
+      <c r="K156" s="225" t="n">
         <v>44924</v>
       </c>
       <c r="L156" s="17" t="n"/>
@@ -14231,7 +14251,7 @@
       <c r="J157" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K157" s="224" t="n">
+      <c r="K157" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L157" s="17" t="n"/>
@@ -14284,7 +14304,7 @@
       <c r="J158" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K158" s="224" t="n">
+      <c r="K158" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L158" s="17" t="n"/>
@@ -14337,7 +14357,7 @@
       <c r="J159" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K159" s="224" t="n">
+      <c r="K159" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L159" s="59" t="n"/>
@@ -14390,7 +14410,7 @@
       <c r="J160" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K160" s="224" t="n">
+      <c r="K160" s="225" t="n">
         <v>44649</v>
       </c>
       <c r="L160" s="17" t="n"/>
@@ -14443,24 +14463,24 @@
       <c r="J161" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K161" s="224" t="n">
+      <c r="K161" s="225" t="n">
         <v>44789</v>
       </c>
       <c r="L161" s="17" t="n"/>
       <c r="M161" s="18" t="n"/>
     </row>
     <row r="162" ht="24.75" customHeight="1" s="70">
-      <c r="A162" s="223" t="n"/>
-      <c r="B162" s="223" t="n"/>
-      <c r="C162" s="223" t="n"/>
+      <c r="A162" s="224" t="n"/>
+      <c r="B162" s="224" t="n"/>
+      <c r="C162" s="224" t="n"/>
       <c r="D162" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E162" s="223" t="n"/>
-      <c r="F162" s="223" t="n"/>
-      <c r="G162" s="223" t="n"/>
+      <c r="E162" s="224" t="n"/>
+      <c r="F162" s="224" t="n"/>
+      <c r="G162" s="224" t="n"/>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -14468,7 +14488,7 @@
       </c>
       <c r="I162" s="28" t="n"/>
       <c r="J162" s="15" t="n"/>
-      <c r="K162" s="221" t="n"/>
+      <c r="K162" s="222" t="n"/>
       <c r="L162" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知</t>
@@ -14517,7 +14537,7 @@
       </c>
       <c r="I163" s="28" t="n"/>
       <c r="J163" s="15" t="n"/>
-      <c r="K163" s="221" t="n"/>
+      <c r="K163" s="222" t="n"/>
       <c r="L163" s="17" t="n"/>
       <c r="M163" s="18" t="n"/>
     </row>
@@ -14568,7 +14588,7 @@
       <c r="J164" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="224" t="n">
+      <c r="K164" s="225" t="n">
         <v>44668</v>
       </c>
       <c r="L164" s="17" t="n"/>
@@ -14617,7 +14637,7 @@
       <c r="J165" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K165" s="224" t="n">
+      <c r="K165" s="225" t="n">
         <v>44660</v>
       </c>
       <c r="L165" s="60" t="inlineStr">
@@ -14678,7 +14698,7 @@
       <c r="J166" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K166" s="224" t="n">
+      <c r="K166" s="225" t="n">
         <v>44649</v>
       </c>
       <c r="L166" s="40" t="n"/>
@@ -14731,28 +14751,28 @@
       <c r="J167" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K167" s="225" t="n">
+      <c r="K167" s="226" t="n">
         <v>44709</v>
       </c>
       <c r="L167" s="17" t="n"/>
       <c r="M167" s="18" t="n"/>
     </row>
     <row r="168" ht="24.75" customHeight="1" s="70">
-      <c r="A168" s="223" t="n"/>
-      <c r="B168" s="223" t="n"/>
-      <c r="C168" s="223" t="n"/>
+      <c r="A168" s="224" t="n"/>
+      <c r="B168" s="224" t="n"/>
+      <c r="C168" s="224" t="n"/>
       <c r="D168" s="12" t="inlineStr">
         <is>
           <t>中国科学院半导体研究所</t>
         </is>
       </c>
-      <c r="E168" s="223" t="n"/>
-      <c r="F168" s="223" t="n"/>
-      <c r="G168" s="223" t="n"/>
-      <c r="H168" s="223" t="n"/>
-      <c r="I168" s="223" t="n"/>
-      <c r="J168" s="223" t="n"/>
-      <c r="K168" s="223" t="n"/>
+      <c r="E168" s="224" t="n"/>
+      <c r="F168" s="224" t="n"/>
+      <c r="G168" s="224" t="n"/>
+      <c r="H168" s="224" t="n"/>
+      <c r="I168" s="224" t="n"/>
+      <c r="J168" s="224" t="n"/>
+      <c r="K168" s="224" t="n"/>
       <c r="L168" s="17" t="n"/>
       <c r="M168" s="18" t="n"/>
     </row>
@@ -14803,7 +14823,7 @@
       <c r="J169" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K169" s="224" t="n">
+      <c r="K169" s="225" t="n">
         <v>44821</v>
       </c>
       <c r="L169" s="17" t="n"/>
@@ -14856,28 +14876,28 @@
       <c r="J170" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K170" s="225" t="n">
+      <c r="K170" s="226" t="n">
         <v>44819</v>
       </c>
       <c r="L170" s="17" t="n"/>
       <c r="M170" s="18" t="n"/>
     </row>
     <row r="171" ht="24.75" customHeight="1" s="70">
-      <c r="A171" s="223" t="n"/>
-      <c r="B171" s="223" t="n"/>
-      <c r="C171" s="223" t="n"/>
+      <c r="A171" s="224" t="n"/>
+      <c r="B171" s="224" t="n"/>
+      <c r="C171" s="224" t="n"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
           <t>中国科学院电子学研究所</t>
         </is>
       </c>
-      <c r="E171" s="223" t="n"/>
-      <c r="F171" s="223" t="n"/>
-      <c r="G171" s="223" t="n"/>
-      <c r="H171" s="223" t="n"/>
-      <c r="I171" s="223" t="n"/>
-      <c r="J171" s="223" t="n"/>
-      <c r="K171" s="223" t="n"/>
+      <c r="E171" s="224" t="n"/>
+      <c r="F171" s="224" t="n"/>
+      <c r="G171" s="224" t="n"/>
+      <c r="H171" s="224" t="n"/>
+      <c r="I171" s="224" t="n"/>
+      <c r="J171" s="224" t="n"/>
+      <c r="K171" s="224" t="n"/>
       <c r="L171" s="17" t="n"/>
       <c r="M171" s="18" t="n"/>
     </row>
@@ -14926,7 +14946,7 @@
         </is>
       </c>
       <c r="J172" s="15" t="n"/>
-      <c r="K172" s="221" t="n"/>
+      <c r="K172" s="222" t="n"/>
       <c r="L172" s="26" t="inlineStr">
         <is>
           <t>网站时常故障</t>
@@ -14981,28 +15001,28 @@
       <c r="J173" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K173" s="225" t="n">
+      <c r="K173" s="226" t="n">
         <v>44881</v>
       </c>
       <c r="L173" s="17" t="n"/>
       <c r="M173" s="18" t="n"/>
     </row>
     <row r="174" ht="24.75" customHeight="1" s="70">
-      <c r="A174" s="223" t="n"/>
-      <c r="B174" s="223" t="n"/>
-      <c r="C174" s="223" t="n"/>
+      <c r="A174" s="224" t="n"/>
+      <c r="B174" s="224" t="n"/>
+      <c r="C174" s="224" t="n"/>
       <c r="D174" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E174" s="223" t="n"/>
-      <c r="F174" s="223" t="n"/>
-      <c r="G174" s="223" t="n"/>
-      <c r="H174" s="223" t="n"/>
-      <c r="I174" s="223" t="n"/>
-      <c r="J174" s="223" t="n"/>
-      <c r="K174" s="223" t="n"/>
+      <c r="E174" s="224" t="n"/>
+      <c r="F174" s="224" t="n"/>
+      <c r="G174" s="224" t="n"/>
+      <c r="H174" s="224" t="n"/>
+      <c r="I174" s="224" t="n"/>
+      <c r="J174" s="224" t="n"/>
+      <c r="K174" s="224" t="n"/>
       <c r="L174" s="17" t="n"/>
       <c r="M174" s="18" t="n"/>
     </row>
@@ -15053,7 +15073,7 @@
       <c r="J175" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K175" s="224" t="n">
+      <c r="K175" s="225" t="n">
         <v>44666</v>
       </c>
       <c r="L175" s="26" t="inlineStr">
@@ -15110,7 +15130,7 @@
       <c r="J176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K176" s="224" t="n">
+      <c r="K176" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L176" s="26" t="inlineStr">
@@ -15167,7 +15187,7 @@
       <c r="J177" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K177" s="224" t="n">
+      <c r="K177" s="225" t="n">
         <v>44671</v>
       </c>
       <c r="L177" s="17" t="n"/>
@@ -15220,7 +15240,7 @@
       <c r="J178" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K178" s="224" t="n">
+      <c r="K178" s="225" t="n">
         <v>44648</v>
       </c>
       <c r="L178" s="17" t="n"/>
@@ -15273,7 +15293,7 @@
       <c r="J179" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K179" s="224" t="n">
+      <c r="K179" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L179" s="17" t="n"/>
@@ -15326,7 +15346,7 @@
       <c r="J180" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K180" s="224" t="n">
+      <c r="K180" s="225" t="n">
         <v>44831</v>
       </c>
       <c r="L180" s="17" t="n"/>
@@ -15379,7 +15399,7 @@
       <c r="J181" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K181" s="224" t="n">
+      <c r="K181" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L181" s="17" t="n"/>
@@ -15432,7 +15452,7 @@
       <c r="J182" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K182" s="224" t="n">
+      <c r="K182" s="225" t="n">
         <v>44926</v>
       </c>
       <c r="L182" s="17" t="n"/>
@@ -15479,7 +15499,7 @@
       </c>
       <c r="I183" s="28" t="n"/>
       <c r="J183" s="15" t="n"/>
-      <c r="K183" s="221" t="n"/>
+      <c r="K183" s="222" t="n"/>
       <c r="L183" s="17" t="n"/>
       <c r="M183" s="18" t="n"/>
     </row>
@@ -15530,7 +15550,7 @@
       <c r="J184" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K184" s="224" t="n">
+      <c r="K184" s="225" t="n">
         <v>44718</v>
       </c>
       <c r="L184" s="17" t="n"/>
@@ -15583,7 +15603,7 @@
       <c r="J185" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K185" s="224" t="n">
+      <c r="K185" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L185" s="17" t="n"/>
@@ -15636,7 +15656,7 @@
       <c r="J186" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K186" s="224" t="n">
+      <c r="K186" s="225" t="n">
         <v>44800</v>
       </c>
       <c r="L186" s="17" t="n"/>
@@ -15689,7 +15709,7 @@
       <c r="J187" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K187" s="224" t="n">
+      <c r="K187" s="225" t="n">
         <v>44737</v>
       </c>
       <c r="L187" s="17" t="n"/>
@@ -15742,7 +15762,7 @@
       <c r="J188" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="224" t="n">
+      <c r="K188" s="225" t="n">
         <v>44573</v>
       </c>
       <c r="L188" s="17" t="n"/>
@@ -15795,7 +15815,7 @@
       <c r="J189" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K189" s="224" t="n">
+      <c r="K189" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L189" s="17" t="n"/>
@@ -15842,7 +15862,7 @@
       </c>
       <c r="I190" s="28" t="n"/>
       <c r="J190" s="15" t="n"/>
-      <c r="K190" s="221" t="n"/>
+      <c r="K190" s="222" t="n"/>
       <c r="L190" s="17" t="n"/>
       <c r="M190" s="18" t="n"/>
     </row>
@@ -15893,7 +15913,7 @@
       <c r="J191" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K191" s="224" t="n">
+      <c r="K191" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L191" s="63" t="inlineStr">
@@ -15944,7 +15964,7 @@
       </c>
       <c r="I192" s="28" t="n"/>
       <c r="J192" s="15" t="n"/>
-      <c r="K192" s="221" t="n"/>
+      <c r="K192" s="222" t="n"/>
       <c r="L192" s="40" t="n"/>
       <c r="M192" s="18" t="n"/>
     </row>
@@ -15995,7 +16015,7 @@
       <c r="J193" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K193" s="224" t="n">
+      <c r="K193" s="225" t="n">
         <v>44694</v>
       </c>
       <c r="L193" s="17" t="n"/>
@@ -16048,7 +16068,7 @@
       <c r="J194" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K194" s="224" t="n">
+      <c r="K194" s="225" t="n">
         <v>44904</v>
       </c>
       <c r="L194" s="17" t="n"/>
@@ -16095,7 +16115,7 @@
       </c>
       <c r="I195" s="28" t="n"/>
       <c r="J195" s="15" t="n"/>
-      <c r="K195" s="221" t="n"/>
+      <c r="K195" s="222" t="n"/>
       <c r="L195" s="17" t="n"/>
       <c r="M195" s="18" t="n"/>
     </row>
@@ -16146,7 +16166,7 @@
       <c r="J196" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K196" s="224" t="n">
+      <c r="K196" s="225" t="n">
         <v>44632</v>
       </c>
       <c r="L196" s="17" t="n"/>
@@ -16199,7 +16219,7 @@
       <c r="J197" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K197" s="224" t="n">
+      <c r="K197" s="225" t="n">
         <v>44764</v>
       </c>
       <c r="L197" s="17" t="n"/>
@@ -16252,7 +16272,7 @@
       <c r="J198" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K198" s="224" t="n">
+      <c r="K198" s="225" t="n">
         <v>44813</v>
       </c>
       <c r="L198" s="17" t="n"/>
@@ -16305,7 +16325,7 @@
       <c r="J199" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K199" s="224" t="n">
+      <c r="K199" s="225" t="n">
         <v>44856</v>
       </c>
       <c r="L199" s="17" t="n"/>
@@ -16358,7 +16378,7 @@
       <c r="J200" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K200" s="224" t="n">
+      <c r="K200" s="225" t="n">
         <v>44730</v>
       </c>
       <c r="L200" s="17" t="n"/>
@@ -16405,7 +16425,7 @@
       </c>
       <c r="I201" s="28" t="n"/>
       <c r="J201" s="15" t="n"/>
-      <c r="K201" s="221" t="n"/>
+      <c r="K201" s="222" t="n"/>
       <c r="L201" s="17" t="n"/>
       <c r="M201" s="18" t="n"/>
     </row>
@@ -16456,7 +16476,7 @@
       <c r="J202" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K202" s="224" t="n">
+      <c r="K202" s="225" t="n">
         <v>44872</v>
       </c>
       <c r="L202" s="17" t="n"/>
@@ -16509,7 +16529,7 @@
       <c r="J203" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K203" s="224" t="n">
+      <c r="K203" s="225" t="n">
         <v>44845</v>
       </c>
       <c r="L203" s="17" t="n"/>
@@ -16562,7 +16582,7 @@
       <c r="J204" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K204" s="224" t="n">
+      <c r="K204" s="225" t="n">
         <v>44688</v>
       </c>
       <c r="L204" s="17" t="n"/>
@@ -16615,7 +16635,7 @@
       <c r="J205" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K205" s="224" t="n">
+      <c r="K205" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L205" s="17" t="n"/>
@@ -16668,7 +16688,7 @@
       <c r="J206" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K206" s="224" t="n">
+      <c r="K206" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L206" s="17" t="n"/>
@@ -16715,7 +16735,7 @@
       </c>
       <c r="I207" s="28" t="n"/>
       <c r="J207" s="15" t="n"/>
-      <c r="K207" s="221" t="n"/>
+      <c r="K207" s="222" t="n"/>
       <c r="L207" s="26" t="inlineStr">
         <is>
           <t>未找到往年申请通知</t>
@@ -16774,7 +16794,7 @@
       <c r="J208" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K208" s="224" t="n">
+      <c r="K208" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L208" s="26" t="inlineStr">
@@ -16825,7 +16845,7 @@
       </c>
       <c r="I209" s="28" t="n"/>
       <c r="J209" s="15" t="n"/>
-      <c r="K209" s="221" t="n"/>
+      <c r="K209" s="222" t="n"/>
       <c r="L209" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -16880,7 +16900,7 @@
       <c r="J210" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K210" s="224" t="n">
+      <c r="K210" s="225" t="n">
         <v>44831</v>
       </c>
       <c r="L210" s="17" t="n"/>
@@ -16933,7 +16953,7 @@
       <c r="J211" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K211" s="224" t="n">
+      <c r="K211" s="225" t="n">
         <v>44815</v>
       </c>
       <c r="L211" s="17" t="n"/>
@@ -16986,7 +17006,7 @@
       <c r="J212" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K212" s="224" t="n">
+      <c r="K212" s="225" t="n">
         <v>44850</v>
       </c>
       <c r="L212" s="17" t="n"/>
@@ -17039,7 +17059,7 @@
       <c r="J213" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K213" s="224" t="n">
+      <c r="K213" s="225" t="n">
         <v>44845</v>
       </c>
       <c r="L213" s="17" t="n"/>
@@ -17092,7 +17112,7 @@
       <c r="J214" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K214" s="224" t="n">
+      <c r="K214" s="225" t="n">
         <v>44772</v>
       </c>
       <c r="L214" s="26" t="inlineStr">
@@ -17149,7 +17169,7 @@
       <c r="J215" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K215" s="224" t="n">
+      <c r="K215" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L215" s="17" t="n"/>
@@ -17202,7 +17222,7 @@
       <c r="J216" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K216" s="224" t="n">
+      <c r="K216" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L216" s="17" t="n"/>
@@ -17249,7 +17269,7 @@
       </c>
       <c r="I217" s="34" t="n"/>
       <c r="J217" s="15" t="n"/>
-      <c r="K217" s="221" t="n"/>
+      <c r="K217" s="222" t="n"/>
       <c r="L217" s="17" t="n"/>
       <c r="M217" s="18" t="n"/>
     </row>
@@ -17300,7 +17320,7 @@
       <c r="J218" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K218" s="224" t="n">
+      <c r="K218" s="225" t="n">
         <v>44843</v>
       </c>
       <c r="L218" s="17" t="n"/>
@@ -17353,7 +17373,7 @@
       <c r="J219" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K219" s="224" t="n">
+      <c r="K219" s="225" t="n">
         <v>44680</v>
       </c>
       <c r="L219" s="17" t="n"/>
@@ -17406,7 +17426,7 @@
       <c r="J220" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K220" s="224" t="n">
+      <c r="K220" s="225" t="n">
         <v>44722</v>
       </c>
       <c r="L220" s="17" t="n"/>
@@ -17459,7 +17479,7 @@
       <c r="J221" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K221" s="224" t="n">
+      <c r="K221" s="225" t="n">
         <v>44646</v>
       </c>
       <c r="L221" s="17" t="n"/>
@@ -17512,7 +17532,7 @@
       <c r="J222" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K222" s="224" t="n">
+      <c r="K222" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L222" s="17" t="n"/>
@@ -17565,7 +17585,7 @@
       <c r="J223" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K223" s="224" t="n">
+      <c r="K223" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L223" s="17" t="n"/>
@@ -17618,7 +17638,7 @@
       <c r="J224" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K224" s="224" t="n">
+      <c r="K224" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L224" s="17" t="n"/>
@@ -17671,7 +17691,7 @@
       <c r="J225" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K225" s="224" t="n">
+      <c r="K225" s="225" t="n">
         <v>44811</v>
       </c>
       <c r="L225" s="17" t="n"/>
@@ -17724,7 +17744,7 @@
       <c r="J226" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K226" s="224" t="n">
+      <c r="K226" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L226" s="17" t="n"/>
@@ -17777,28 +17797,28 @@
       <c r="J227" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K227" s="225" t="n">
+      <c r="K227" s="226" t="n">
         <v>44808</v>
       </c>
       <c r="L227" s="17" t="n"/>
       <c r="M227" s="18" t="n"/>
     </row>
     <row r="228" ht="24.75" customHeight="1" s="70">
-      <c r="A228" s="223" t="n"/>
-      <c r="B228" s="223" t="n"/>
-      <c r="C228" s="223" t="n"/>
+      <c r="A228" s="224" t="n"/>
+      <c r="B228" s="224" t="n"/>
+      <c r="C228" s="224" t="n"/>
       <c r="D228" s="12" t="inlineStr">
         <is>
           <t>南京水利科学研究院</t>
         </is>
       </c>
-      <c r="E228" s="223" t="n"/>
-      <c r="F228" s="223" t="n"/>
-      <c r="G228" s="223" t="n"/>
-      <c r="H228" s="223" t="n"/>
-      <c r="I228" s="223" t="n"/>
-      <c r="J228" s="223" t="n"/>
-      <c r="K228" s="223" t="n"/>
+      <c r="E228" s="224" t="n"/>
+      <c r="F228" s="224" t="n"/>
+      <c r="G228" s="224" t="n"/>
+      <c r="H228" s="224" t="n"/>
+      <c r="I228" s="224" t="n"/>
+      <c r="J228" s="224" t="n"/>
+      <c r="K228" s="224" t="n"/>
       <c r="L228" s="17" t="n"/>
       <c r="M228" s="18" t="n"/>
     </row>
@@ -17849,7 +17869,7 @@
       <c r="J229" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K229" s="224" t="n">
+      <c r="K229" s="225" t="n">
         <v>44846</v>
       </c>
       <c r="L229" s="17" t="n"/>
@@ -17889,7 +17909,7 @@
           <t>2008DA105277</t>
         </is>
       </c>
-      <c r="H230" s="235" t="inlineStr">
+      <c r="H230" s="236" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17902,28 +17922,28 @@
       <c r="J230" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K230" s="225" t="n">
+      <c r="K230" s="226" t="n">
         <v>44724</v>
       </c>
       <c r="L230" s="17" t="n"/>
       <c r="M230" s="18" t="n"/>
     </row>
     <row r="231" ht="24.75" customHeight="1" s="70">
-      <c r="A231" s="223" t="n"/>
-      <c r="B231" s="223" t="n"/>
-      <c r="C231" s="223" t="n"/>
+      <c r="A231" s="224" t="n"/>
+      <c r="B231" s="224" t="n"/>
+      <c r="C231" s="224" t="n"/>
       <c r="D231" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学（北京）</t>
         </is>
       </c>
-      <c r="E231" s="223" t="n"/>
-      <c r="F231" s="223" t="n"/>
-      <c r="G231" s="223" t="n"/>
-      <c r="H231" s="223" t="n"/>
-      <c r="I231" s="223" t="n"/>
-      <c r="J231" s="223" t="n"/>
-      <c r="K231" s="223" t="n"/>
+      <c r="E231" s="224" t="n"/>
+      <c r="F231" s="224" t="n"/>
+      <c r="G231" s="224" t="n"/>
+      <c r="H231" s="224" t="n"/>
+      <c r="I231" s="224" t="n"/>
+      <c r="J231" s="224" t="n"/>
+      <c r="K231" s="224" t="n"/>
       <c r="L231" s="17" t="n"/>
       <c r="M231" s="18" t="n"/>
     </row>
@@ -17974,7 +17994,7 @@
       <c r="J232" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K232" s="224" t="n">
+      <c r="K232" s="225" t="n">
         <v>44828</v>
       </c>
       <c r="L232" s="17" t="n"/>
@@ -18027,7 +18047,7 @@
       <c r="J233" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K233" s="224" t="n">
+      <c r="K233" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L233" s="17" t="n"/>
@@ -18074,7 +18094,7 @@
       </c>
       <c r="I234" s="34" t="n"/>
       <c r="J234" s="15" t="n"/>
-      <c r="K234" s="221" t="n"/>
+      <c r="K234" s="222" t="n"/>
       <c r="L234" s="17" t="n"/>
       <c r="M234" s="18" t="n"/>
     </row>
@@ -18125,7 +18145,7 @@
       <c r="J235" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K235" s="224" t="n">
+      <c r="K235" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L235" s="26" t="inlineStr">
@@ -18182,7 +18202,7 @@
       <c r="J236" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K236" s="224" t="n">
+      <c r="K236" s="225" t="n">
         <v>44622</v>
       </c>
       <c r="L236" s="17" t="n"/>
@@ -18235,7 +18255,7 @@
       <c r="J237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K237" s="224" t="n">
+      <c r="K237" s="225" t="n">
         <v>44689</v>
       </c>
       <c r="L237" s="17" t="n"/>
@@ -18288,7 +18308,7 @@
       <c r="J238" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K238" s="224" t="n">
+      <c r="K238" s="225" t="n">
         <v>44861</v>
       </c>
       <c r="L238" s="17" t="n"/>
@@ -18341,7 +18361,7 @@
       <c r="J239" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K239" s="224" t="n">
+      <c r="K239" s="225" t="n">
         <v>44826</v>
       </c>
       <c r="L239" s="17" t="n"/>
@@ -18388,7 +18408,7 @@
       </c>
       <c r="I240" s="28" t="n"/>
       <c r="J240" s="15" t="n"/>
-      <c r="K240" s="221" t="n"/>
+      <c r="K240" s="222" t="n"/>
       <c r="L240" s="26" t="inlineStr">
         <is>
           <t>未找到相关往年通知</t>
@@ -18447,7 +18467,7 @@
       <c r="J241" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K241" s="224" t="n">
+      <c r="K241" s="225" t="n">
         <v>44848</v>
       </c>
       <c r="L241" s="17" t="n"/>
@@ -18500,7 +18520,7 @@
       <c r="J242" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K242" s="224" t="n">
+      <c r="K242" s="225" t="n">
         <v>44820</v>
       </c>
       <c r="L242" s="17" t="n"/>
@@ -18553,7 +18573,7 @@
       <c r="J243" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K243" s="224" t="n">
+      <c r="K243" s="225" t="n">
         <v>44699</v>
       </c>
       <c r="L243" s="17" t="n"/>
@@ -18606,7 +18626,7 @@
       <c r="J244" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="224" t="n">
+      <c r="K244" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L244" s="26" t="inlineStr">
@@ -18663,7 +18683,7 @@
       <c r="J245" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K245" s="224" t="n">
+      <c r="K245" s="225" t="n">
         <v>44741</v>
       </c>
       <c r="L245" s="17" t="n"/>
@@ -18716,7 +18736,7 @@
       <c r="J246" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K246" s="224" t="n">
+      <c r="K246" s="225" t="n">
         <v>44771</v>
       </c>
       <c r="L246" s="17" t="n"/>
@@ -18769,7 +18789,7 @@
       <c r="J247" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K247" s="224" t="n">
+      <c r="K247" s="225" t="n">
         <v>44859</v>
       </c>
       <c r="L247" s="17" t="n"/>
@@ -18822,7 +18842,7 @@
       <c r="J248" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K248" s="224" t="n">
+      <c r="K248" s="225" t="n">
         <v>44815</v>
       </c>
       <c r="L248" s="17" t="n"/>
@@ -18875,7 +18895,7 @@
       <c r="J249" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K249" s="224" t="n">
+      <c r="K249" s="225" t="n">
         <v>44742</v>
       </c>
       <c r="L249" s="26" t="inlineStr">
@@ -18926,7 +18946,7 @@
       </c>
       <c r="I250" s="28" t="n"/>
       <c r="J250" s="15" t="n"/>
-      <c r="K250" s="221" t="n"/>
+      <c r="K250" s="222" t="n"/>
       <c r="L250" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -18981,7 +19001,7 @@
       <c r="J251" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K251" s="224" t="n">
+      <c r="K251" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L251" s="26" t="inlineStr">
@@ -19036,7 +19056,7 @@
       </c>
       <c r="I252" s="28" t="n"/>
       <c r="J252" s="15" t="n"/>
-      <c r="K252" s="221" t="n"/>
+      <c r="K252" s="222" t="n"/>
       <c r="L252" s="17" t="n"/>
       <c r="M252" s="18" t="n"/>
     </row>
@@ -19087,7 +19107,7 @@
       <c r="J253" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K253" s="224" t="n">
+      <c r="K253" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L253" s="17" t="n"/>
@@ -19134,7 +19154,7 @@
       </c>
       <c r="I254" s="28" t="n"/>
       <c r="J254" s="15" t="n"/>
-      <c r="K254" s="221" t="n"/>
+      <c r="K254" s="222" t="n"/>
       <c r="L254" s="17" t="n"/>
       <c r="M254" s="18" t="n"/>
     </row>
@@ -19179,7 +19199,7 @@
       </c>
       <c r="I255" s="28" t="n"/>
       <c r="J255" s="15" t="n"/>
-      <c r="K255" s="221" t="n"/>
+      <c r="K255" s="222" t="n"/>
       <c r="L255" s="17" t="n"/>
       <c r="M255" s="18" t="n"/>
     </row>
@@ -19224,7 +19244,7 @@
       </c>
       <c r="I256" s="28" t="n"/>
       <c r="J256" s="15" t="n"/>
-      <c r="K256" s="221" t="n"/>
+      <c r="K256" s="222" t="n"/>
       <c r="L256" s="17" t="n"/>
       <c r="M256" s="18" t="n"/>
     </row>
@@ -19275,7 +19295,7 @@
       <c r="J257" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K257" s="224" t="n">
+      <c r="K257" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L257" s="17" t="n"/>
@@ -19328,7 +19348,7 @@
       <c r="J258" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K258" s="224" t="n">
+      <c r="K258" s="225" t="n">
         <v>44665</v>
       </c>
       <c r="L258" s="17" t="n"/>
@@ -19381,7 +19401,7 @@
       <c r="J259" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K259" s="224" t="n">
+      <c r="K259" s="225" t="n">
         <v>44882</v>
       </c>
       <c r="L259" s="17" t="n"/>
@@ -19428,7 +19448,7 @@
       </c>
       <c r="I260" s="28" t="n"/>
       <c r="J260" s="15" t="n"/>
-      <c r="K260" s="221" t="n"/>
+      <c r="K260" s="222" t="n"/>
       <c r="L260" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -19477,7 +19497,7 @@
       </c>
       <c r="I261" s="34" t="n"/>
       <c r="J261" s="15" t="n"/>
-      <c r="K261" s="221" t="n"/>
+      <c r="K261" s="222" t="n"/>
       <c r="L261" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -19526,7 +19546,7 @@
       </c>
       <c r="I262" s="28" t="n"/>
       <c r="J262" s="15" t="n"/>
-      <c r="K262" s="221" t="n"/>
+      <c r="K262" s="222" t="n"/>
       <c r="L262" s="17" t="n"/>
       <c r="M262" s="18" t="n"/>
     </row>
@@ -19571,7 +19591,7 @@
       </c>
       <c r="I263" s="28" t="n"/>
       <c r="J263" s="15" t="n"/>
-      <c r="K263" s="221" t="n"/>
+      <c r="K263" s="222" t="n"/>
       <c r="L263" s="17" t="n"/>
       <c r="M263" s="18" t="n"/>
     </row>
@@ -19622,7 +19642,7 @@
       <c r="J264" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K264" s="224" t="n">
+      <c r="K264" s="225" t="n">
         <v>44667</v>
       </c>
       <c r="L264" s="26" t="n">
@@ -19677,7 +19697,7 @@
       <c r="J265" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K265" s="224" t="n">
+      <c r="K265" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L265" s="17" t="n"/>
@@ -19728,7 +19748,7 @@
         </is>
       </c>
       <c r="J266" s="15" t="n"/>
-      <c r="K266" s="221" t="n"/>
+      <c r="K266" s="222" t="n"/>
       <c r="L266" s="26" t="inlineStr">
         <is>
           <t>相关通知最近的是2014年的</t>
@@ -19783,7 +19803,7 @@
       <c r="J267" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K267" s="224" t="n">
+      <c r="K267" s="225" t="n">
         <v>44731</v>
       </c>
       <c r="L267" s="17" t="n"/>
@@ -19830,7 +19850,7 @@
       </c>
       <c r="I268" s="28" t="n"/>
       <c r="J268" s="15" t="n"/>
-      <c r="K268" s="221" t="n"/>
+      <c r="K268" s="222" t="n"/>
       <c r="L268" s="17" t="n"/>
       <c r="M268" s="18" t="n"/>
     </row>
@@ -19881,7 +19901,7 @@
       <c r="J269" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K269" s="224" t="n">
+      <c r="K269" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L269" s="17" t="n"/>
@@ -19934,7 +19954,7 @@
       <c r="J270" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K270" s="224" t="n">
+      <c r="K270" s="225" t="n">
         <v>44721</v>
       </c>
       <c r="L270" s="26" t="inlineStr">
@@ -19985,7 +20005,7 @@
       </c>
       <c r="I271" s="28" t="n"/>
       <c r="J271" s="15" t="n"/>
-      <c r="K271" s="221" t="n"/>
+      <c r="K271" s="222" t="n"/>
       <c r="L271" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20034,7 +20054,7 @@
       </c>
       <c r="I272" s="28" t="n"/>
       <c r="J272" s="15" t="n"/>
-      <c r="K272" s="221" t="n"/>
+      <c r="K272" s="222" t="n"/>
       <c r="L272" s="17" t="n"/>
       <c r="M272" s="18" t="n"/>
     </row>
@@ -20079,7 +20099,7 @@
       </c>
       <c r="I273" s="28" t="n"/>
       <c r="J273" s="15" t="n"/>
-      <c r="K273" s="221" t="n"/>
+      <c r="K273" s="222" t="n"/>
       <c r="L273" s="17" t="n"/>
       <c r="M273" s="18" t="n"/>
     </row>
@@ -20124,7 +20144,7 @@
       </c>
       <c r="I274" s="28" t="n"/>
       <c r="J274" s="15" t="n"/>
-      <c r="K274" s="221" t="n"/>
+      <c r="K274" s="222" t="n"/>
       <c r="L274" s="17" t="n"/>
       <c r="M274" s="18" t="n"/>
     </row>
@@ -20175,7 +20195,7 @@
       <c r="J275" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K275" s="224" t="n">
+      <c r="K275" s="225" t="n">
         <v>44746</v>
       </c>
       <c r="L275" s="26" t="inlineStr">
@@ -20232,7 +20252,7 @@
       <c r="J276" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K276" s="224" t="n">
+      <c r="K276" s="225" t="n">
         <v>44866</v>
       </c>
       <c r="L276" s="17" t="n"/>
@@ -20279,7 +20299,7 @@
       </c>
       <c r="I277" s="28" t="n"/>
       <c r="J277" s="15" t="n"/>
-      <c r="K277" s="221" t="n"/>
+      <c r="K277" s="222" t="n"/>
       <c r="L277" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20334,7 +20354,7 @@
       <c r="J278" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K278" s="224" t="n">
+      <c r="K278" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L278" s="17" t="n"/>
@@ -20383,7 +20403,7 @@
       <c r="J279" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K279" s="224" t="n">
+      <c r="K279" s="225" t="n">
         <v>44599</v>
       </c>
       <c r="L279" s="26" t="inlineStr">
@@ -20438,7 +20458,7 @@
       </c>
       <c r="I280" s="34" t="n"/>
       <c r="J280" s="15" t="n"/>
-      <c r="K280" s="221" t="n"/>
+      <c r="K280" s="222" t="n"/>
       <c r="L280" s="17" t="n"/>
       <c r="M280" s="18" t="n"/>
     </row>
@@ -20489,7 +20509,7 @@
       <c r="J281" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K281" s="224" t="n">
+      <c r="K281" s="225" t="n">
         <v>44855</v>
       </c>
       <c r="L281" s="17" t="n"/>
@@ -20542,7 +20562,7 @@
       <c r="J282" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K282" s="224" t="n">
+      <c r="K282" s="225" t="n">
         <v>44569</v>
       </c>
       <c r="L282" s="26" t="inlineStr">
@@ -20593,7 +20613,7 @@
       </c>
       <c r="I283" s="28" t="n"/>
       <c r="J283" s="15" t="n"/>
-      <c r="K283" s="221" t="n"/>
+      <c r="K283" s="222" t="n"/>
       <c r="L283" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -20648,7 +20668,7 @@
       <c r="J284" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K284" s="224" t="n">
+      <c r="K284" s="225" t="n">
         <v>44581</v>
       </c>
       <c r="L284" s="17" t="n"/>
@@ -20695,7 +20715,7 @@
       </c>
       <c r="I285" s="28" t="n"/>
       <c r="J285" s="15" t="n"/>
-      <c r="K285" s="221" t="n"/>
+      <c r="K285" s="222" t="n"/>
       <c r="L285" s="17" t="n"/>
       <c r="M285" s="18" t="n"/>
     </row>
@@ -20740,7 +20760,7 @@
       </c>
       <c r="I286" s="28" t="n"/>
       <c r="J286" s="15" t="n"/>
-      <c r="K286" s="221" t="n"/>
+      <c r="K286" s="222" t="n"/>
       <c r="L286" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20791,7 +20811,7 @@
       <c r="J287" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K287" s="224" t="n">
+      <c r="K287" s="225" t="n">
         <v>44923</v>
       </c>
       <c r="L287" s="58" t="n"/>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-08）</t>
+          <t>最新更新（2026-10-09）</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-08）</t>
+          <t>最新更新（2026-10-09）</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-08）</t>
+          <t>最新更新（2026-10-09）</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-08）</t>
+          <t>最新更新（2026-10-09）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-09）</t>
+          <t>最新更新（2026-10-10）</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-09）</t>
+          <t>最新更新（2026-10-10）</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-09）</t>
+          <t>最新更新（2026-10-10）</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-09）</t>
+          <t>最新更新（2026-10-10）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-10）</t>
+          <t>最新更新（2026-10-12）</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-10）</t>
+          <t>最新更新（2026-10-12）</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-10）</t>
+          <t>最新更新（2026-10-12）</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-10）</t>
+          <t>最新更新（2026-10-12）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-12）</t>
+          <t>最新更新（2026-10-13）</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-12）</t>
+          <t>最新更新（2026-10-13）</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-12）</t>
+          <t>最新更新（2026-10-13）</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-12）</t>
+          <t>最新更新（2026-10-13）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -1063,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1630,30 +1630,27 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2681,7 +2678,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-13）</t>
+          <t>最新更新（2026-10-17）</t>
         </is>
       </c>
     </row>
@@ -2734,67 +2731,50 @@
       <c r="J3" s="148" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="194" t="n">
+      <c r="A4" s="190" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="195" t="n"/>
-      <c r="C4" s="196" t="inlineStr">
+      <c r="C4" s="189" t="inlineStr">
         <is>
           <t>国自然面上项目</t>
         </is>
       </c>
-      <c r="D4" s="197" t="inlineStr">
+      <c r="D4" s="175" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E4" s="198" t="inlineStr">
+      <c r="E4" s="152" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（主申/参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F4" s="196" t="inlineStr">
+      <c r="F4" s="189" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为4年</t>
         </is>
       </c>
-      <c r="G4" s="196" t="inlineStr">
+      <c r="G4" s="189" t="inlineStr">
         <is>
           <t>平均资助强度
 约50万</t>
         </is>
       </c>
-      <c r="H4" s="194" t="inlineStr">
+      <c r="H4" s="190" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I4" s="199" t="inlineStr">
+      <c r="I4" s="155" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3976/msxm22.html</t>
         </is>
       </c>
-      <c r="J4" s="200" t="n"/>
-      <c r="K4" s="195" t="n"/>
-      <c r="L4" s="195" t="n"/>
-      <c r="M4" s="195" t="n"/>
-      <c r="N4" s="195" t="n"/>
-      <c r="O4" s="195" t="n"/>
-      <c r="P4" s="195" t="n"/>
-      <c r="Q4" s="195" t="n"/>
-      <c r="R4" s="195" t="n"/>
-      <c r="S4" s="195" t="n"/>
-      <c r="T4" s="195" t="n"/>
-      <c r="U4" s="195" t="n"/>
-      <c r="V4" s="201" t="inlineStr">
-        <is>
-          <t>● 更新：关于发布2026年度国家自然科学基金“面向低空经济前沿的基础研究”专项项目申请指南...（2026-09-30）</t>
-        </is>
-      </c>
+      <c r="J4" s="148" t="n"/>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
       <c r="A5" s="190" t="n">
@@ -2986,7 +2966,7 @@
       <c r="A9" s="190" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="202" t="n"/>
+      <c r="B9" s="194" t="n"/>
       <c r="C9" s="161" t="inlineStr">
         <is>
           <t>国家科技部重大研发计划</t>
@@ -3411,16 +3391,16 @@
       <c r="J17" s="148" t="n"/>
     </row>
     <row r="18" ht="66" customHeight="1" s="70">
-      <c r="A18" s="194" t="n">
+      <c r="A18" s="195" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="197" t="n"/>
-      <c r="C18" s="196" t="inlineStr">
+      <c r="B18" s="196" t="n"/>
+      <c r="C18" s="197" t="inlineStr">
         <is>
           <t>国家重点研发计划“战略性科技创新合作”重点专项</t>
         </is>
       </c>
-      <c r="D18" s="197" t="inlineStr">
+      <c r="D18" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3430,39 +3410,39 @@
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F18" s="196" t="inlineStr">
+      <c r="F18" s="197" t="inlineStr">
         <is>
           <t>国家重点研发计划、国家科技重大专项、国家自然科学基金委有关类型项目实施联合限项，按照要求，对项目（课题）负责人等人员进行联合审查，科研人员同期申请和承担的项目（课题）数原则上不得超过2项。</t>
         </is>
       </c>
-      <c r="G18" s="196" t="inlineStr">
+      <c r="G18" s="197" t="inlineStr">
         <is>
           <t>200万元—400万元</t>
         </is>
       </c>
-      <c r="H18" s="197" t="inlineStr">
+      <c r="H18" s="196" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I18" s="203" t="inlineStr">
+      <c r="I18" s="199" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/20260828/5864.html</t>
         </is>
       </c>
       <c r="J18" s="200" t="n"/>
-      <c r="K18" s="195" t="n"/>
-      <c r="L18" s="195" t="n"/>
-      <c r="M18" s="195" t="n"/>
-      <c r="N18" s="195" t="n"/>
-      <c r="O18" s="195" t="n"/>
-      <c r="P18" s="195" t="n"/>
-      <c r="Q18" s="195" t="n"/>
-      <c r="R18" s="195" t="n"/>
-      <c r="S18" s="195" t="n"/>
-      <c r="T18" s="195" t="n"/>
-      <c r="U18" s="195" t="n"/>
-      <c r="V18" s="201" t="inlineStr">
+      <c r="K18" s="201" t="n"/>
+      <c r="L18" s="201" t="n"/>
+      <c r="M18" s="201" t="n"/>
+      <c r="N18" s="201" t="n"/>
+      <c r="O18" s="201" t="n"/>
+      <c r="P18" s="201" t="n"/>
+      <c r="Q18" s="201" t="n"/>
+      <c r="R18" s="201" t="n"/>
+      <c r="S18" s="201" t="n"/>
+      <c r="T18" s="201" t="n"/>
+      <c r="U18" s="201" t="n"/>
+      <c r="V18" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度联合研发与示范项目指南2026-09-01发布，港澳单位可承担课题，受聘内地单位的港澳科学家可作负责人</t>
         </is>
@@ -3515,58 +3495,58 @@
       <c r="J19" s="148" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1" s="70">
-      <c r="A20" s="194" t="n">
+      <c r="A20" s="195" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="195" t="n"/>
-      <c r="C20" s="196" t="inlineStr">
+      <c r="B20" s="201" t="n"/>
+      <c r="C20" s="197" t="inlineStr">
         <is>
           <t>粤澳科技创新联合资助专题-粤澳联合资助项目</t>
         </is>
       </c>
-      <c r="D20" s="197" t="inlineStr">
+      <c r="D20" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E20" s="197" t="inlineStr">
+      <c r="E20" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F20" s="204" t="inlineStr">
+      <c r="F20" s="203" t="inlineStr">
         <is>
           <t>由广东省科学技术厅和澳门科学技术发展基金联合征集、联合评审、联合资助。支持广东省创新主体联合澳门合作伙伴，在生物医药、新一代信息技术、节能环保、海洋科技、新材料、新能源、智能制造等涉及两地民生发展和前沿科技的领域开展联合技术研发及成果产业化合作。本专题优先支持在横琴、南沙等重大合作平台实施或落地转化的项目。</t>
         </is>
       </c>
-      <c r="G20" s="205" t="inlineStr">
+      <c r="G20" s="204" t="inlineStr">
         <is>
           <t>100万/项</t>
         </is>
       </c>
-      <c r="H20" s="194" t="inlineStr">
+      <c r="H20" s="195" t="inlineStr">
         <is>
           <t>11月-次年1月</t>
         </is>
       </c>
-      <c r="I20" s="206" t="inlineStr">
+      <c r="I20" s="205" t="inlineStr">
         <is>
           <t>https://gdstc.gd.gov.cn/zwgk_n/tzgg/content/post_4806341.html</t>
         </is>
       </c>
       <c r="J20" s="200" t="n"/>
-      <c r="K20" s="195" t="n"/>
-      <c r="L20" s="195" t="n"/>
-      <c r="M20" s="195" t="n"/>
-      <c r="N20" s="195" t="n"/>
-      <c r="O20" s="195" t="n"/>
-      <c r="P20" s="195" t="n"/>
-      <c r="Q20" s="195" t="n"/>
-      <c r="R20" s="195" t="n"/>
-      <c r="S20" s="195" t="n"/>
-      <c r="T20" s="195" t="n"/>
-      <c r="U20" s="195" t="n"/>
-      <c r="V20" s="201" t="inlineStr">
+      <c r="K20" s="201" t="n"/>
+      <c r="L20" s="201" t="n"/>
+      <c r="M20" s="201" t="n"/>
+      <c r="N20" s="201" t="n"/>
+      <c r="O20" s="201" t="n"/>
+      <c r="P20" s="201" t="n"/>
+      <c r="Q20" s="201" t="n"/>
+      <c r="R20" s="201" t="n"/>
+      <c r="S20" s="201" t="n"/>
+      <c r="T20" s="201" t="n"/>
+      <c r="U20" s="201" t="n"/>
+      <c r="V20" s="202" t="inlineStr">
         <is>
           <t>● 更新：2027年度申报指南已发布（2026-09-18），网上申报至2026-11-17 17:00，主管部门推荐截止11-24；粤科函资字〔2026〕1587号</t>
         </is>
@@ -3616,59 +3596,59 @@
       <c r="J21" s="148" t="n"/>
     </row>
     <row r="22" ht="148" customHeight="1" s="70">
-      <c r="A22" s="194" t="n">
+      <c r="A22" s="195" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="195" t="n"/>
-      <c r="C22" s="196" t="inlineStr">
+      <c r="B22" s="201" t="n"/>
+      <c r="C22" s="197" t="inlineStr">
         <is>
           <t>深圳市深港澳科技计划项目（C类项目）</t>
         </is>
       </c>
-      <c r="D22" s="197" t="inlineStr">
+      <c r="D22" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E22" s="197" t="inlineStr">
+      <c r="E22" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F22" s="196" t="inlineStr">
+      <c r="F22" s="197" t="inlineStr">
         <is>
           <t>深港澳科技计划C类项目由香港、澳门申请单位提出申请，深圳市科技创新局进行评审和资助，深圳市财政资助资金直接拨付至香港、澳门申请单位账户。
 重点支持领域（2025）：网络与通信、半导体与集成电路、软件与信息服务、人工智能、高端装备与仪器、低空经济与空天、机器人、高性能材料、生物医药、海洋、合成生物、智能机器人、脑科学与脑机工程等。</t>
         </is>
       </c>
-      <c r="G22" s="205" t="inlineStr">
+      <c r="G22" s="204" t="inlineStr">
         <is>
           <t>资助强度300万</t>
         </is>
       </c>
-      <c r="H22" s="194" t="inlineStr">
+      <c r="H22" s="195" t="inlineStr">
         <is>
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I22" s="207" t="inlineStr">
+      <c r="I22" s="206" t="inlineStr">
         <is>
           <t>https://stic.sz.gov.cn/xxgk/tzgg/content/post_12116696.html?sessionid=</t>
         </is>
       </c>
       <c r="J22" s="200" t="n"/>
-      <c r="K22" s="195" t="n"/>
-      <c r="L22" s="195" t="n"/>
-      <c r="M22" s="195" t="n"/>
-      <c r="N22" s="195" t="n"/>
-      <c r="O22" s="195" t="n"/>
-      <c r="P22" s="195" t="n"/>
-      <c r="Q22" s="195" t="n"/>
-      <c r="R22" s="195" t="n"/>
-      <c r="S22" s="195" t="n"/>
-      <c r="T22" s="195" t="n"/>
-      <c r="U22" s="195" t="n"/>
-      <c r="V22" s="201" t="inlineStr">
+      <c r="K22" s="201" t="n"/>
+      <c r="L22" s="201" t="n"/>
+      <c r="M22" s="201" t="n"/>
+      <c r="N22" s="201" t="n"/>
+      <c r="O22" s="201" t="n"/>
+      <c r="P22" s="201" t="n"/>
+      <c r="Q22" s="201" t="n"/>
+      <c r="R22" s="201" t="n"/>
+      <c r="S22" s="201" t="n"/>
+      <c r="T22" s="201" t="n"/>
+      <c r="U22" s="201" t="n"/>
+      <c r="V22" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026-06-05印发《深港澳科技计划项目管理办法》，A类须获香港ITC或澳门FDCT评审通过方可立项</t>
         </is>
@@ -3720,121 +3700,121 @@
       </c>
     </row>
     <row r="24" ht="70.5" customHeight="1" s="70">
-      <c r="A24" s="194" t="n">
+      <c r="A24" s="195" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="195" t="n"/>
-      <c r="C24" s="196" t="inlineStr">
+      <c r="B24" s="201" t="n"/>
+      <c r="C24" s="197" t="inlineStr">
         <is>
           <t>四川省国际科技创新/港澳台科技创新合作项目</t>
         </is>
       </c>
-      <c r="D24" s="197" t="inlineStr">
+      <c r="D24" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E24" s="197" t="inlineStr">
+      <c r="E24" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F24" s="196" t="inlineStr">
+      <c r="F24" s="197" t="inlineStr">
         <is>
           <t>支持省内高校、科研机构及企业与香港特区、澳门特区、台湾地区开展科技创新合作，结合基础研究和应用技术战略性发展需求，开展联合研发。</t>
         </is>
       </c>
-      <c r="G24" s="205" t="inlineStr">
+      <c r="G24" s="204" t="inlineStr">
         <is>
           <t>30万元-100万元</t>
         </is>
       </c>
-      <c r="H24" s="194" t="inlineStr">
+      <c r="H24" s="195" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I24" s="207" t="inlineStr">
+      <c r="I24" s="206" t="inlineStr">
         <is>
           <t>https://kjt.sc.gov.cn/kjt/gstz/2025/9/17/1959a2ee35844389a80b43eb99950708.shtml</t>
         </is>
       </c>
       <c r="J24" s="200" t="n"/>
-      <c r="K24" s="195" t="n"/>
-      <c r="L24" s="195" t="n"/>
-      <c r="M24" s="195" t="n"/>
-      <c r="N24" s="195" t="n"/>
-      <c r="O24" s="195" t="n"/>
-      <c r="P24" s="195" t="n"/>
-      <c r="Q24" s="195" t="n"/>
-      <c r="R24" s="195" t="n"/>
-      <c r="S24" s="195" t="n"/>
-      <c r="T24" s="195" t="n"/>
-      <c r="U24" s="195" t="n"/>
-      <c r="V24" s="201" t="inlineStr">
+      <c r="K24" s="201" t="n"/>
+      <c r="L24" s="201" t="n"/>
+      <c r="M24" s="201" t="n"/>
+      <c r="N24" s="201" t="n"/>
+      <c r="O24" s="201" t="n"/>
+      <c r="P24" s="201" t="n"/>
+      <c r="Q24" s="201" t="n"/>
+      <c r="R24" s="201" t="n"/>
+      <c r="S24" s="201" t="n"/>
+      <c r="T24" s="201" t="n"/>
+      <c r="U24" s="201" t="n"/>
+      <c r="V24" s="202" t="inlineStr">
         <is>
           <t>● 更新：2027年度需求征集已完成，指南适时发布；2026年度项目2025-09已发布</t>
         </is>
       </c>
     </row>
     <row r="25" ht="63.75" customHeight="1" s="70">
-      <c r="A25" s="194" t="n">
+      <c r="A25" s="195" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="195" t="n"/>
-      <c r="C25" s="196" t="inlineStr">
+      <c r="B25" s="201" t="n"/>
+      <c r="C25" s="197" t="inlineStr">
         <is>
           <t>江苏省国际科技合作/ 港澳台科技合作计划项目</t>
         </is>
       </c>
-      <c r="D25" s="197" t="inlineStr">
+      <c r="D25" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E25" s="197" t="inlineStr">
+      <c r="E25" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F25" s="196" t="inlineStr">
+      <c r="F25" s="197" t="inlineStr">
         <is>
           <t>专题五：港澳台科技合作项目
 重点支持的技术领域：生命健康、人工智能、先进材料等。</t>
         </is>
       </c>
-      <c r="G25" s="196" t="inlineStr">
+      <c r="G25" s="197" t="inlineStr">
         <is>
           <t>省资助经费每项原则上不超过80万元，且不超过项目江苏方总预算的50%。</t>
         </is>
       </c>
-      <c r="H25" s="194" t="inlineStr">
+      <c r="H25" s="195" t="inlineStr">
         <is>
           <t>3-4月</t>
         </is>
       </c>
-      <c r="I25" s="207" t="inlineStr">
+      <c r="I25" s="206" t="inlineStr">
         <is>
           <t>https://kxjst.jiangsu.gov.cn/art/2026/4/1/art_82568_11752538.html</t>
         </is>
       </c>
-      <c r="J25" s="208" t="n"/>
-      <c r="K25" s="195" t="inlineStr">
+      <c r="J25" s="207" t="n"/>
+      <c r="K25" s="201" t="inlineStr">
         <is>
           <t>这个不要了？</t>
         </is>
       </c>
-      <c r="L25" s="195" t="n"/>
-      <c r="M25" s="195" t="n"/>
-      <c r="N25" s="195" t="n"/>
-      <c r="O25" s="195" t="n"/>
-      <c r="P25" s="195" t="n"/>
-      <c r="Q25" s="195" t="n"/>
-      <c r="R25" s="195" t="n"/>
-      <c r="S25" s="195" t="n"/>
-      <c r="T25" s="195" t="n"/>
-      <c r="U25" s="195" t="n"/>
-      <c r="V25" s="201" t="inlineStr">
+      <c r="L25" s="201" t="n"/>
+      <c r="M25" s="201" t="n"/>
+      <c r="N25" s="201" t="n"/>
+      <c r="O25" s="201" t="n"/>
+      <c r="P25" s="201" t="n"/>
+      <c r="Q25" s="201" t="n"/>
+      <c r="R25" s="201" t="n"/>
+      <c r="S25" s="201" t="n"/>
+      <c r="T25" s="201" t="n"/>
+      <c r="U25" s="201" t="n"/>
+      <c r="V25" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度申报中（苏科资发〔2026〕26号），长三角—新加坡第五轮网上填报截止2026-10-12 17:30</t>
         </is>
@@ -3927,21 +3907,21 @@
       <c r="J27" s="85" t="n"/>
     </row>
     <row r="28" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A28" s="194" t="n">
+      <c r="A28" s="195" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="195" t="n"/>
-      <c r="C28" s="196" t="inlineStr">
+      <c r="B28" s="201" t="n"/>
+      <c r="C28" s="197" t="inlineStr">
         <is>
           <t>山西省科技合作交流专项项目</t>
         </is>
       </c>
-      <c r="D28" s="197" t="inlineStr">
+      <c r="D28" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E28" s="197" t="inlineStr">
+      <c r="E28" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -3951,34 +3931,34 @@
           <t>与香港、澳门科技合作交流项目</t>
         </is>
       </c>
-      <c r="G28" s="196" t="inlineStr">
+      <c r="G28" s="197" t="inlineStr">
         <is>
           <t>30万</t>
         </is>
       </c>
-      <c r="H28" s="194" t="inlineStr">
+      <c r="H28" s="195" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I28" s="209" t="inlineStr">
+      <c r="I28" s="208" t="inlineStr">
         <is>
           <t>https://kjt.shanxi.gov.cn/xxgk/zfxxgkml/acs_11737/gjyqykjhzc/202608/t20260831_10210987.shtml</t>
         </is>
       </c>
-      <c r="J28" s="210" t="n"/>
-      <c r="K28" s="195" t="n"/>
-      <c r="L28" s="195" t="n"/>
-      <c r="M28" s="195" t="n"/>
-      <c r="N28" s="195" t="n"/>
-      <c r="O28" s="195" t="n"/>
-      <c r="P28" s="195" t="n"/>
-      <c r="Q28" s="195" t="n"/>
-      <c r="R28" s="195" t="n"/>
-      <c r="S28" s="195" t="n"/>
-      <c r="T28" s="195" t="n"/>
-      <c r="U28" s="195" t="n"/>
-      <c r="V28" s="201" t="inlineStr">
+      <c r="J28" s="209" t="n"/>
+      <c r="K28" s="201" t="n"/>
+      <c r="L28" s="201" t="n"/>
+      <c r="M28" s="201" t="n"/>
+      <c r="N28" s="201" t="n"/>
+      <c r="O28" s="201" t="n"/>
+      <c r="P28" s="201" t="n"/>
+      <c r="Q28" s="201" t="n"/>
+      <c r="R28" s="201" t="n"/>
+      <c r="S28" s="201" t="n"/>
+      <c r="T28" s="201" t="n"/>
+      <c r="U28" s="201" t="n"/>
+      <c r="V28" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度设「与香港、澳门科技合作交流项目」，港澳方向不超过50万/项，2026年9月申报中</t>
         </is>
@@ -4026,21 +4006,21 @@
       <c r="J29" s="85" t="n"/>
     </row>
     <row r="30" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A30" s="194" t="n">
+      <c r="A30" s="195" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="195" t="n"/>
-      <c r="C30" s="196" t="inlineStr">
+      <c r="B30" s="201" t="n"/>
+      <c r="C30" s="197" t="inlineStr">
         <is>
           <t>浙江省“尖兵”“领雁”科技计划科技合作项目</t>
         </is>
       </c>
-      <c r="D30" s="197" t="inlineStr">
+      <c r="D30" s="196" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E30" s="197" t="inlineStr">
+      <c r="E30" s="196" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -4050,34 +4030,34 @@
           <t>国际（含港澳台）科技合作项目。围绕支持元首外交合作平台、“一带一路”联合实验室、深化拓展政府间合作网络以及支撑撬动培育国际大科学计划、国际科技组织等重点任务，部署重点国家（地区）和关键领域合作项目。中国澳门：优先支持生物医药（中医药）、电子信息、空间科学、人工智能、海洋科技等领域。</t>
         </is>
       </c>
-      <c r="G30" s="196" t="inlineStr">
+      <c r="G30" s="197" t="inlineStr">
         <is>
           <t>120万元以内</t>
         </is>
       </c>
-      <c r="H30" s="194" t="inlineStr">
+      <c r="H30" s="195" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I30" s="211" t="inlineStr">
+      <c r="I30" s="210" t="inlineStr">
         <is>
           <t>https://kjt.zj.gov.cn/col/col1229225203/art/2026/art_e495d70575a44848947646e93ca2948c.html</t>
         </is>
       </c>
-      <c r="J30" s="210" t="n"/>
-      <c r="K30" s="195" t="n"/>
-      <c r="L30" s="195" t="n"/>
-      <c r="M30" s="195" t="n"/>
-      <c r="N30" s="195" t="n"/>
-      <c r="O30" s="195" t="n"/>
-      <c r="P30" s="195" t="n"/>
-      <c r="Q30" s="195" t="n"/>
-      <c r="R30" s="195" t="n"/>
-      <c r="S30" s="195" t="n"/>
-      <c r="T30" s="195" t="n"/>
-      <c r="U30" s="195" t="n"/>
-      <c r="V30" s="201" t="inlineStr">
+      <c r="J30" s="209" t="n"/>
+      <c r="K30" s="201" t="n"/>
+      <c r="L30" s="201" t="n"/>
+      <c r="M30" s="201" t="n"/>
+      <c r="N30" s="201" t="n"/>
+      <c r="O30" s="201" t="n"/>
+      <c r="P30" s="201" t="n"/>
+      <c r="Q30" s="201" t="n"/>
+      <c r="R30" s="201" t="n"/>
+      <c r="S30" s="201" t="n"/>
+      <c r="T30" s="201" t="n"/>
+      <c r="U30" s="201" t="n"/>
+      <c r="V30" s="202" t="inlineStr">
         <is>
           <t>● 更新：2026年度科技合作项目启动申报（2026-09），含国际（含港澳台）科技合作项目</t>
         </is>
@@ -4500,92 +4480,92 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="70">
-      <c r="A41" s="212" t="n">
+      <c r="A41" s="211" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="213" t="inlineStr">
+      <c r="B41" s="212" t="inlineStr">
         <is>
           <t>国家科技部</t>
         </is>
       </c>
-      <c r="C41" s="213" t="inlineStr">
+      <c r="C41" s="212" t="inlineStr">
         <is>
           <t>新一代人工智能国家科技重大专项2026年度公开项目</t>
         </is>
       </c>
-      <c r="D41" s="213" t="inlineStr"/>
-      <c r="E41" s="213" t="inlineStr">
+      <c r="D41" s="212" t="inlineStr"/>
+      <c r="E41" s="212" t="inlineStr">
         <is>
           <t>教授（参与，名单内港澳单位可参与）</t>
         </is>
       </c>
-      <c r="F41" s="213" t="inlineStr">
+      <c r="F41" s="212" t="inlineStr">
         <is>
           <t>申报附件含内地与香港、内地与澳门科技合作委员会协商确定的港澳科研单位名单</t>
         </is>
       </c>
-      <c r="G41" s="213" t="inlineStr">
+      <c r="G41" s="212" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H41" s="213" t="inlineStr">
+      <c r="H41" s="212" t="inlineStr">
         <is>
           <t>2026年度第一批申报中</t>
         </is>
       </c>
-      <c r="I41" s="214" t="inlineStr">
+      <c r="I41" s="213" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/</t>
         </is>
       </c>
-      <c r="V41" s="215" t="inlineStr">
+      <c r="V41" s="214" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度第一批公开项目申报启动，名单内港澳单位可参与</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="212" t="n">
+      <c r="A42" s="211" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="213" t="inlineStr">
+      <c r="B42" s="212" t="inlineStr">
         <is>
           <t>国家自然科学基金</t>
         </is>
       </c>
-      <c r="C42" s="213" t="inlineStr">
+      <c r="C42" s="212" t="inlineStr">
         <is>
           <t>NSFC民营企业创新发展联合基金（术理创新）</t>
         </is>
       </c>
-      <c r="D42" s="213" t="inlineStr"/>
-      <c r="E42" s="213" t="inlineStr">
+      <c r="D42" s="212" t="inlineStr"/>
+      <c r="E42" s="212" t="inlineStr">
         <is>
           <t>教授（主申/参与）</t>
         </is>
       </c>
-      <c r="F42" s="213" t="inlineStr">
+      <c r="F42" s="212" t="inlineStr">
         <is>
           <t>企业出资的NSFC联合基金，按国自然流程申报；脑机接口与神经调控方向</t>
         </is>
       </c>
-      <c r="G42" s="213" t="inlineStr">
+      <c r="G42" s="212" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H42" s="213" t="inlineStr">
+      <c r="H42" s="212" t="inlineStr">
         <is>
           <t>2026-06发布</t>
         </is>
       </c>
-      <c r="I42" s="214" t="inlineStr">
+      <c r="I42" s="213" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="V42" s="215" t="inlineStr">
+      <c r="V42" s="214" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度项目申报中（脑机接口与神经调控方向）</t>
         </is>
@@ -4718,7 +4698,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-13）</t>
+          <t>最新更新（2026-10-17）</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4706,7 @@
       <c r="A3" s="190" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="216" t="inlineStr">
+      <c r="B3" s="215" t="inlineStr">
         <is>
           <t>社科项目</t>
         </is>
@@ -5030,7 +5010,7 @@
       <c r="A11" s="190" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="202" t="n"/>
+      <c r="B11" s="194" t="n"/>
       <c r="C11" s="134" t="inlineStr">
         <is>
           <t>珠海市哲学社会科学规划年度课题</t>
@@ -5152,7 +5132,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-13）</t>
+          <t>最新更新（2026-10-17）</t>
         </is>
       </c>
     </row>
@@ -5213,20 +5193,20 @@
       <c r="S3" s="82" t="n"/>
     </row>
     <row r="4" ht="148.5" customFormat="1" customHeight="1" s="141">
-      <c r="A4" s="194" t="n">
+      <c r="A4" s="195" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="196" t="inlineStr">
+      <c r="B4" s="197" t="inlineStr">
         <is>
           <t>何享健青年科学家项目</t>
         </is>
       </c>
-      <c r="C4" s="217" t="inlineStr">
+      <c r="C4" s="216" t="inlineStr">
         <is>
           <t>研究院全职研究人员</t>
         </is>
       </c>
-      <c r="D4" s="196" t="inlineStr">
+      <c r="D4" s="197" t="inlineStr">
         <is>
           <t>面向医学与生命科学、能源环境与气候变化领域，每年评选总数不超过20人。
 学位要求：已取得博士学位。
@@ -5234,39 +5214,39 @@
 年龄要求：被提名当年，参评人年龄在35周岁及以下，女性候选人放宽至38周岁。临床医学专业背景的被提名人统一放宽至40周岁，女性候选人放宽至43周岁。</t>
         </is>
       </c>
-      <c r="E4" s="196" t="inlineStr">
+      <c r="E4" s="197" t="inlineStr">
         <is>
           <t>200万元/3年</t>
         </is>
       </c>
-      <c r="F4" s="194" t="inlineStr">
+      <c r="F4" s="195" t="inlineStr">
         <is>
           <t>11月-次年2月</t>
         </is>
       </c>
-      <c r="G4" s="207" t="inlineStr">
+      <c r="G4" s="206" t="inlineStr">
         <is>
           <t>https://www.heprize.org/Home</t>
         </is>
       </c>
-      <c r="H4" s="210" t="inlineStr">
+      <c r="H4" s="209" t="inlineStr">
         <is>
           <t xml:space="preserve">评审流程按照“提名机构提交材料-秘书处形式审查-同行评审专家评审-评审委员会评审-理事会审批-获资助人名单公布”严格执行。
 </t>
         </is>
       </c>
-      <c r="I4" s="195" t="n"/>
-      <c r="J4" s="195" t="n"/>
-      <c r="K4" s="195" t="n"/>
-      <c r="L4" s="195" t="n"/>
-      <c r="M4" s="195" t="n"/>
-      <c r="N4" s="195" t="n"/>
-      <c r="O4" s="195" t="n"/>
-      <c r="P4" s="195" t="n"/>
-      <c r="Q4" s="195" t="n"/>
-      <c r="R4" s="195" t="n"/>
-      <c r="S4" s="195" t="n"/>
-      <c r="T4" s="201" t="inlineStr">
+      <c r="I4" s="201" t="n"/>
+      <c r="J4" s="201" t="n"/>
+      <c r="K4" s="201" t="n"/>
+      <c r="L4" s="201" t="n"/>
+      <c r="M4" s="201" t="n"/>
+      <c r="N4" s="201" t="n"/>
+      <c r="O4" s="201" t="n"/>
+      <c r="P4" s="201" t="n"/>
+      <c r="Q4" s="201" t="n"/>
+      <c r="R4" s="201" t="n"/>
+      <c r="S4" s="201" t="n"/>
+      <c r="T4" s="202" t="inlineStr">
         <is>
           <t>● 更新：第二期已启动（2025-11-03正式启动），200万元/3年，研究院全职研究人员可申</t>
         </is>
@@ -6634,18 +6614,18 @@
           <t>重点实验室开放课题清单</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
+      <c r="B1" s="217" t="n"/>
+      <c r="C1" s="217" t="n"/>
+      <c r="D1" s="217" t="n"/>
+      <c r="E1" s="217" t="n"/>
+      <c r="F1" s="217" t="n"/>
+      <c r="G1" s="217" t="n"/>
+      <c r="H1" s="217" t="n"/>
+      <c r="I1" s="217" t="n"/>
+      <c r="J1" s="217" t="n"/>
+      <c r="K1" s="217" t="n"/>
+      <c r="L1" s="217" t="n"/>
+      <c r="M1" s="217" t="n"/>
     </row>
     <row r="2" ht="41.25" customHeight="1" s="70">
       <c r="A2" s="5" t="inlineStr">
@@ -6698,7 +6678,7 @@
           <t>公告月份</t>
         </is>
       </c>
-      <c r="K2" s="219" t="inlineStr">
+      <c r="K2" s="218" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -6720,9 +6700,9 @@
       <c r="R2" s="10" t="n"/>
       <c r="S2" s="10" t="n"/>
       <c r="T2" s="10" t="n"/>
-      <c r="U2" s="220" t="inlineStr">
-        <is>
-          <t>最新更新（2026-10-13）</t>
+      <c r="U2" s="219" t="inlineStr">
+        <is>
+          <t>最新更新（2026-10-17）</t>
         </is>
       </c>
     </row>
@@ -6765,84 +6745,84 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="221" t="inlineStr">
+      <c r="I3" s="220" t="inlineStr">
         <is>
           <t>http://sklpre.zju.edu.cn/redir.php?catalog_id=60520&amp;object_id=63561</t>
         </is>
       </c>
       <c r="J3" s="15" t="n"/>
-      <c r="K3" s="222" t="n"/>
+      <c r="K3" s="221" t="n"/>
       <c r="L3" s="17" t="n"/>
       <c r="M3" s="18" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="223" t="n"/>
-      <c r="B4" s="223" t="n"/>
-      <c r="C4" s="223" t="n"/>
+      <c r="A4" s="222" t="n"/>
+      <c r="B4" s="222" t="n"/>
+      <c r="C4" s="222" t="n"/>
       <c r="D4" s="12" t="inlineStr">
         <is>
           <t>天津大学</t>
         </is>
       </c>
-      <c r="E4" s="223" t="n"/>
-      <c r="F4" s="223" t="n"/>
-      <c r="G4" s="223" t="n"/>
+      <c r="E4" s="222" t="n"/>
+      <c r="F4" s="222" t="n"/>
+      <c r="G4" s="222" t="n"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="223" t="n"/>
+      <c r="I4" s="222" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="222" t="n"/>
+      <c r="K4" s="221" t="n"/>
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="223" t="n"/>
-      <c r="B5" s="223" t="n"/>
-      <c r="C5" s="223" t="n"/>
+      <c r="A5" s="222" t="n"/>
+      <c r="B5" s="222" t="n"/>
+      <c r="C5" s="222" t="n"/>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>华东理工大学</t>
         </is>
       </c>
-      <c r="E5" s="223" t="n"/>
-      <c r="F5" s="223" t="n"/>
-      <c r="G5" s="223" t="n"/>
+      <c r="E5" s="222" t="n"/>
+      <c r="F5" s="222" t="n"/>
+      <c r="G5" s="222" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="223" t="n"/>
+      <c r="I5" s="222" t="n"/>
       <c r="J5" s="15" t="n"/>
-      <c r="K5" s="222" t="n"/>
+      <c r="K5" s="221" t="n"/>
       <c r="L5" s="17" t="n"/>
       <c r="M5" s="18" t="n"/>
     </row>
     <row r="6" ht="55.5" customHeight="1" s="70">
-      <c r="A6" s="224" t="n"/>
-      <c r="B6" s="224" t="n"/>
-      <c r="C6" s="224" t="n"/>
+      <c r="A6" s="223" t="n"/>
+      <c r="B6" s="223" t="n"/>
+      <c r="C6" s="223" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E6" s="224" t="n"/>
-      <c r="F6" s="224" t="n"/>
-      <c r="G6" s="224" t="n"/>
+      <c r="E6" s="223" t="n"/>
+      <c r="F6" s="223" t="n"/>
+      <c r="G6" s="223" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I6" s="224" t="n"/>
+      <c r="I6" s="223" t="n"/>
       <c r="J6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="225" t="n">
+      <c r="K6" s="224" t="n">
         <v>44679</v>
       </c>
       <c r="L6" s="17" t="n"/>
@@ -6895,30 +6875,30 @@
       <c r="J7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="226" t="n">
+      <c r="K7" s="225" t="n">
         <v>44677</v>
       </c>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="70">
-      <c r="A8" s="224" t="n"/>
-      <c r="B8" s="224" t="n"/>
-      <c r="C8" s="224" t="n"/>
+      <c r="A8" s="223" t="n"/>
+      <c r="B8" s="223" t="n"/>
+      <c r="C8" s="223" t="n"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>中国石油大学（华东）</t>
         </is>
       </c>
-      <c r="E8" s="224" t="n"/>
-      <c r="F8" s="224" t="n"/>
-      <c r="G8" s="224" t="n"/>
-      <c r="H8" s="224" t="n"/>
-      <c r="I8" s="224" t="n"/>
-      <c r="J8" s="224" t="n"/>
-      <c r="K8" s="224" t="n"/>
-      <c r="L8" s="224" t="n"/>
-      <c r="M8" s="224" t="n"/>
+      <c r="E8" s="223" t="n"/>
+      <c r="F8" s="223" t="n"/>
+      <c r="G8" s="223" t="n"/>
+      <c r="H8" s="223" t="n"/>
+      <c r="I8" s="223" t="n"/>
+      <c r="J8" s="223" t="n"/>
+      <c r="K8" s="223" t="n"/>
+      <c r="L8" s="223" t="n"/>
+      <c r="M8" s="223" t="n"/>
     </row>
     <row r="9" ht="44.25" customHeight="1" s="70">
       <c r="A9" s="11" t="n">
@@ -6965,7 +6945,7 @@
         </is>
       </c>
       <c r="J9" s="15" t="n"/>
-      <c r="K9" s="222" t="n"/>
+      <c r="K9" s="221" t="n"/>
       <c r="L9" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7018,7 +6998,7 @@
         </is>
       </c>
       <c r="J10" s="15" t="n"/>
-      <c r="K10" s="222" t="n"/>
+      <c r="K10" s="221" t="n"/>
       <c r="L10" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7077,7 +7057,7 @@
       <c r="J11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="225" t="n">
+      <c r="K11" s="224" t="n">
         <v>44727</v>
       </c>
       <c r="L11" s="26" t="inlineStr">
@@ -7124,7 +7104,7 @@
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="15" t="n"/>
-      <c r="K12" s="222" t="n"/>
+      <c r="K12" s="221" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="29" t="inlineStr">
         <is>
@@ -7177,7 +7157,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n"/>
-      <c r="K13" s="222" t="n"/>
+      <c r="K13" s="221" t="n"/>
       <c r="L13" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7234,7 +7214,7 @@
         </is>
       </c>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="222" t="n"/>
+      <c r="K14" s="221" t="n"/>
       <c r="L14" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7293,7 +7273,7 @@
       <c r="J15" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="225" t="n">
+      <c r="K15" s="224" t="n">
         <v>44774</v>
       </c>
       <c r="L15" s="26" t="inlineStr">
@@ -7350,7 +7330,7 @@
       <c r="J16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="225" t="n">
+      <c r="K16" s="224" t="n">
         <v>44731</v>
       </c>
       <c r="L16" s="26" t="inlineStr">
@@ -7407,7 +7387,7 @@
       <c r="J17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="225" t="n">
+      <c r="K17" s="224" t="n">
         <v>44696</v>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -7456,7 +7436,7 @@
       <c r="J18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="225" t="n">
+      <c r="K18" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L18" s="26" t="inlineStr">
@@ -7517,7 +7497,7 @@
       <c r="J19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K19" s="225" t="n">
+      <c r="K19" s="224" t="n">
         <v>44866</v>
       </c>
       <c r="L19" s="26" t="inlineStr">
@@ -7578,7 +7558,7 @@
       <c r="J20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="225" t="n">
+      <c r="K20" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L20" s="26" t="inlineStr">
@@ -7633,7 +7613,7 @@
       </c>
       <c r="I21" s="34" t="n"/>
       <c r="J21" s="15" t="n"/>
-      <c r="K21" s="222" t="n"/>
+      <c r="K21" s="221" t="n"/>
       <c r="L21" s="26" t="inlineStr">
         <is>
           <t>最近几年未有相关的课题申请消息</t>
@@ -7692,7 +7672,7 @@
       <c r="J22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="227" t="n">
+      <c r="K22" s="226" t="n">
         <v>44694</v>
       </c>
       <c r="L22" s="36" t="n"/>
@@ -7735,7 +7715,7 @@
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="28" t="n"/>
       <c r="J23" s="15" t="n"/>
-      <c r="K23" s="228" t="n"/>
+      <c r="K23" s="227" t="n"/>
       <c r="L23" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7780,7 +7760,7 @@
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="28" t="n"/>
       <c r="J24" s="15" t="n"/>
-      <c r="K24" s="222" t="n"/>
+      <c r="K24" s="221" t="n"/>
       <c r="L24" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7835,7 +7815,7 @@
       <c r="J25" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="225" t="n">
+      <c r="K25" s="224" t="n">
         <v>44822</v>
       </c>
       <c r="L25" s="17" t="n"/>
@@ -7888,7 +7868,7 @@
       <c r="J26" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="225" t="n">
+      <c r="K26" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L26" s="39" t="inlineStr">
@@ -7949,7 +7929,7 @@
       <c r="J27" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="225" t="n">
+      <c r="K27" s="224" t="n">
         <v>44804</v>
       </c>
       <c r="L27" s="40" t="n"/>
@@ -8002,7 +7982,7 @@
       <c r="J28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="225" t="n">
+      <c r="K28" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L28" s="26" t="inlineStr">
@@ -8063,7 +8043,7 @@
       <c r="J29" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="225" t="n">
+      <c r="K29" s="224" t="n">
         <v>44835</v>
       </c>
       <c r="L29" s="17" t="n"/>
@@ -8116,7 +8096,7 @@
       <c r="J30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="225" t="n">
+      <c r="K30" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L30" s="26" t="inlineStr">
@@ -8171,7 +8151,7 @@
         </is>
       </c>
       <c r="J31" s="15" t="n"/>
-      <c r="K31" s="222" t="n"/>
+      <c r="K31" s="221" t="n"/>
       <c r="L31" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关消息</t>
@@ -8226,7 +8206,7 @@
       <c r="J32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="225" t="n">
+      <c r="K32" s="224" t="n">
         <v>44631</v>
       </c>
       <c r="L32" s="17" t="n"/>
@@ -8277,7 +8257,7 @@
       </c>
       <c r="I33" s="28" t="n"/>
       <c r="J33" s="15" t="n"/>
-      <c r="K33" s="222" t="n"/>
+      <c r="K33" s="221" t="n"/>
       <c r="L33" s="17" t="n"/>
       <c r="M33" s="18" t="n"/>
     </row>
@@ -8328,7 +8308,7 @@
       <c r="J34" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="225" t="n">
+      <c r="K34" s="224" t="n">
         <v>44657</v>
       </c>
       <c r="L34" s="17" t="n"/>
@@ -8375,7 +8355,7 @@
       </c>
       <c r="I35" s="28" t="n"/>
       <c r="J35" s="15" t="n"/>
-      <c r="K35" s="222" t="n"/>
+      <c r="K35" s="221" t="n"/>
       <c r="L35" s="17" t="n"/>
       <c r="M35" s="18" t="n"/>
     </row>
@@ -8420,7 +8400,7 @@
       </c>
       <c r="I36" s="28" t="n"/>
       <c r="J36" s="15" t="n"/>
-      <c r="K36" s="222" t="n"/>
+      <c r="K36" s="221" t="n"/>
       <c r="L36" s="17" t="n"/>
       <c r="M36" s="18" t="n"/>
     </row>
@@ -8471,7 +8451,7 @@
       <c r="J37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="225" t="n">
+      <c r="K37" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L37" s="26" t="inlineStr">
@@ -8528,7 +8508,7 @@
       <c r="J38" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="225" t="n">
+      <c r="K38" s="224" t="n">
         <v>44835</v>
       </c>
       <c r="L38" s="26" t="inlineStr">
@@ -8585,7 +8565,7 @@
       <c r="J39" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="225" t="n">
+      <c r="K39" s="224" t="n">
         <v>44690</v>
       </c>
       <c r="L39" s="17" t="n"/>
@@ -8638,30 +8618,30 @@
       <c r="J40" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K40" s="226" t="n">
+      <c r="K40" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L40" s="36" t="n"/>
       <c r="M40" s="18" t="n"/>
     </row>
     <row r="41" ht="24.75" customHeight="1" s="70">
-      <c r="A41" s="224" t="n"/>
-      <c r="B41" s="224" t="n"/>
-      <c r="C41" s="224" t="n"/>
+      <c r="A41" s="223" t="n"/>
+      <c r="B41" s="223" t="n"/>
+      <c r="C41" s="223" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="E41" s="224" t="n"/>
-      <c r="F41" s="224" t="n"/>
-      <c r="G41" s="224" t="n"/>
-      <c r="H41" s="224" t="n"/>
-      <c r="I41" s="224" t="n"/>
-      <c r="J41" s="224" t="n"/>
-      <c r="K41" s="224" t="n"/>
-      <c r="L41" s="229" t="n"/>
-      <c r="M41" s="224" t="n"/>
+      <c r="E41" s="223" t="n"/>
+      <c r="F41" s="223" t="n"/>
+      <c r="G41" s="223" t="n"/>
+      <c r="H41" s="223" t="n"/>
+      <c r="I41" s="223" t="n"/>
+      <c r="J41" s="223" t="n"/>
+      <c r="K41" s="223" t="n"/>
+      <c r="L41" s="228" t="n"/>
+      <c r="M41" s="223" t="n"/>
     </row>
     <row r="42" ht="24.75" customHeight="1" s="70">
       <c r="A42" s="11" t="n">
@@ -8704,7 +8684,7 @@
       </c>
       <c r="I42" s="28" t="n"/>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="222" t="n"/>
+      <c r="K42" s="221" t="n"/>
       <c r="L42" s="17" t="n"/>
       <c r="M42" s="18" t="n"/>
     </row>
@@ -8749,7 +8729,7 @@
       </c>
       <c r="I43" s="28" t="n"/>
       <c r="J43" s="15" t="n"/>
-      <c r="K43" s="222" t="n"/>
+      <c r="K43" s="221" t="n"/>
       <c r="L43" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -8802,7 +8782,7 @@
       </c>
       <c r="I44" s="28" t="n"/>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="222" t="n"/>
+      <c r="K44" s="221" t="n"/>
       <c r="L44" s="17" t="n"/>
       <c r="M44" s="18" t="n"/>
     </row>
@@ -8853,7 +8833,7 @@
       <c r="J45" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="225" t="n">
+      <c r="K45" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L45" s="26" t="inlineStr">
@@ -8914,7 +8894,7 @@
       <c r="J46" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="225" t="n">
+      <c r="K46" s="224" t="n">
         <v>44642</v>
       </c>
       <c r="L46" s="26" t="inlineStr">
@@ -8965,7 +8945,7 @@
       </c>
       <c r="I47" s="28" t="n"/>
       <c r="J47" s="15" t="n"/>
-      <c r="K47" s="222" t="n"/>
+      <c r="K47" s="221" t="n"/>
       <c r="L47" s="17" t="n"/>
       <c r="M47" s="18" t="n"/>
     </row>
@@ -9016,7 +8996,7 @@
       <c r="J48" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K48" s="225" t="n">
+      <c r="K48" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L48" s="17" t="n"/>
@@ -9063,7 +9043,7 @@
       </c>
       <c r="I49" s="28" t="n"/>
       <c r="J49" s="15" t="n"/>
-      <c r="K49" s="222" t="n"/>
+      <c r="K49" s="221" t="n"/>
       <c r="L49" s="26" t="inlineStr">
         <is>
           <t>官网信息不全</t>
@@ -9122,68 +9102,68 @@
       <c r="J50" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="226" t="n">
+      <c r="K50" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L50" s="18" t="n"/>
       <c r="M50" s="18" t="n"/>
     </row>
     <row r="51" ht="24.75" customHeight="1" s="70">
-      <c r="A51" s="223" t="n"/>
-      <c r="B51" s="223" t="n"/>
-      <c r="C51" s="223" t="n"/>
+      <c r="A51" s="222" t="n"/>
+      <c r="B51" s="222" t="n"/>
+      <c r="C51" s="222" t="n"/>
       <c r="D51" s="12" t="inlineStr">
         <is>
           <t>中国科学院生态环境研究中心</t>
         </is>
       </c>
-      <c r="E51" s="223" t="n"/>
-      <c r="F51" s="223" t="n"/>
-      <c r="G51" s="223" t="n"/>
-      <c r="H51" s="223" t="n"/>
-      <c r="I51" s="223" t="n"/>
-      <c r="J51" s="223" t="n"/>
-      <c r="K51" s="223" t="n"/>
-      <c r="L51" s="223" t="n"/>
-      <c r="M51" s="223" t="n"/>
+      <c r="E51" s="222" t="n"/>
+      <c r="F51" s="222" t="n"/>
+      <c r="G51" s="222" t="n"/>
+      <c r="H51" s="222" t="n"/>
+      <c r="I51" s="222" t="n"/>
+      <c r="J51" s="222" t="n"/>
+      <c r="K51" s="222" t="n"/>
+      <c r="L51" s="222" t="n"/>
+      <c r="M51" s="222" t="n"/>
     </row>
     <row r="52" ht="24.75" customHeight="1" s="70">
-      <c r="A52" s="223" t="n"/>
-      <c r="B52" s="223" t="n"/>
-      <c r="C52" s="223" t="n"/>
+      <c r="A52" s="222" t="n"/>
+      <c r="B52" s="222" t="n"/>
+      <c r="C52" s="222" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E52" s="223" t="n"/>
-      <c r="F52" s="223" t="n"/>
-      <c r="G52" s="223" t="n"/>
-      <c r="H52" s="223" t="n"/>
-      <c r="I52" s="223" t="n"/>
-      <c r="J52" s="223" t="n"/>
-      <c r="K52" s="223" t="n"/>
-      <c r="L52" s="223" t="n"/>
-      <c r="M52" s="223" t="n"/>
+      <c r="E52" s="222" t="n"/>
+      <c r="F52" s="222" t="n"/>
+      <c r="G52" s="222" t="n"/>
+      <c r="H52" s="222" t="n"/>
+      <c r="I52" s="222" t="n"/>
+      <c r="J52" s="222" t="n"/>
+      <c r="K52" s="222" t="n"/>
+      <c r="L52" s="222" t="n"/>
+      <c r="M52" s="222" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="70">
-      <c r="A53" s="224" t="n"/>
-      <c r="B53" s="224" t="n"/>
-      <c r="C53" s="224" t="n"/>
+      <c r="A53" s="223" t="n"/>
+      <c r="B53" s="223" t="n"/>
+      <c r="C53" s="223" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E53" s="224" t="n"/>
-      <c r="F53" s="224" t="n"/>
-      <c r="G53" s="224" t="n"/>
-      <c r="H53" s="224" t="n"/>
-      <c r="I53" s="224" t="n"/>
-      <c r="J53" s="224" t="n"/>
-      <c r="K53" s="224" t="n"/>
-      <c r="L53" s="224" t="n"/>
-      <c r="M53" s="224" t="n"/>
+      <c r="E53" s="223" t="n"/>
+      <c r="F53" s="223" t="n"/>
+      <c r="G53" s="223" t="n"/>
+      <c r="H53" s="223" t="n"/>
+      <c r="I53" s="223" t="n"/>
+      <c r="J53" s="223" t="n"/>
+      <c r="K53" s="223" t="n"/>
+      <c r="L53" s="223" t="n"/>
+      <c r="M53" s="223" t="n"/>
     </row>
     <row r="54" ht="24.75" customHeight="1" s="70">
       <c r="A54" s="11" t="n">
@@ -9226,7 +9206,7 @@
       </c>
       <c r="I54" s="28" t="n"/>
       <c r="J54" s="15" t="n"/>
-      <c r="K54" s="222" t="n"/>
+      <c r="K54" s="221" t="n"/>
       <c r="L54" s="17" t="n"/>
       <c r="M54" s="18" t="n"/>
     </row>
@@ -9277,30 +9257,30 @@
       <c r="J55" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="226" t="n">
+      <c r="K55" s="225" t="n">
         <v>44599</v>
       </c>
       <c r="L55" s="18" t="n"/>
       <c r="M55" s="18" t="n"/>
     </row>
     <row r="56" ht="24.75" customHeight="1" s="70">
-      <c r="A56" s="224" t="n"/>
-      <c r="B56" s="224" t="n"/>
-      <c r="C56" s="224" t="n"/>
+      <c r="A56" s="223" t="n"/>
+      <c r="B56" s="223" t="n"/>
+      <c r="C56" s="223" t="n"/>
       <c r="D56" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E56" s="224" t="n"/>
-      <c r="F56" s="224" t="n"/>
-      <c r="G56" s="224" t="n"/>
-      <c r="H56" s="224" t="n"/>
-      <c r="I56" s="224" t="n"/>
-      <c r="J56" s="224" t="n"/>
-      <c r="K56" s="224" t="n"/>
-      <c r="L56" s="224" t="n"/>
-      <c r="M56" s="224" t="n"/>
+      <c r="E56" s="223" t="n"/>
+      <c r="F56" s="223" t="n"/>
+      <c r="G56" s="223" t="n"/>
+      <c r="H56" s="223" t="n"/>
+      <c r="I56" s="223" t="n"/>
+      <c r="J56" s="223" t="n"/>
+      <c r="K56" s="223" t="n"/>
+      <c r="L56" s="223" t="n"/>
+      <c r="M56" s="223" t="n"/>
     </row>
     <row r="57" ht="24.75" customHeight="1" s="70">
       <c r="A57" s="11" t="n">
@@ -9349,7 +9329,7 @@
       <c r="J57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="225" t="n">
+      <c r="K57" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L57" s="26" t="inlineStr">
@@ -9406,7 +9386,7 @@
       <c r="J58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="225" t="n">
+      <c r="K58" s="224" t="n">
         <v>44658</v>
       </c>
       <c r="L58" s="26" t="inlineStr">
@@ -9463,7 +9443,7 @@
       <c r="J59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="230" t="n">
+      <c r="K59" s="229" t="n">
         <v>44615</v>
       </c>
       <c r="L59" s="36" t="n"/>
@@ -9516,7 +9496,7 @@
       <c r="J60" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K60" s="231" t="n">
+      <c r="K60" s="230" t="n">
         <v>44667</v>
       </c>
       <c r="L60" s="17" t="n"/>
@@ -9569,7 +9549,7 @@
       <c r="J61" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K61" s="225" t="n">
+      <c r="K61" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L61" s="17" t="n"/>
@@ -9622,30 +9602,30 @@
       <c r="J62" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K62" s="226" t="n">
+      <c r="K62" s="225" t="n">
         <v>44877</v>
       </c>
       <c r="L62" s="18" t="n"/>
       <c r="M62" s="18" t="n"/>
     </row>
     <row r="63" ht="24.75" customHeight="1" s="70">
-      <c r="A63" s="224" t="n"/>
-      <c r="B63" s="224" t="n"/>
-      <c r="C63" s="224" t="n"/>
+      <c r="A63" s="223" t="n"/>
+      <c r="B63" s="223" t="n"/>
+      <c r="C63" s="223" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学</t>
         </is>
       </c>
-      <c r="E63" s="224" t="n"/>
-      <c r="F63" s="224" t="n"/>
-      <c r="G63" s="224" t="n"/>
-      <c r="H63" s="224" t="n"/>
-      <c r="I63" s="224" t="n"/>
-      <c r="J63" s="224" t="n"/>
-      <c r="K63" s="224" t="n"/>
-      <c r="L63" s="224" t="n"/>
-      <c r="M63" s="224" t="n"/>
+      <c r="E63" s="223" t="n"/>
+      <c r="F63" s="223" t="n"/>
+      <c r="G63" s="223" t="n"/>
+      <c r="H63" s="223" t="n"/>
+      <c r="I63" s="223" t="n"/>
+      <c r="J63" s="223" t="n"/>
+      <c r="K63" s="223" t="n"/>
+      <c r="L63" s="223" t="n"/>
+      <c r="M63" s="223" t="n"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" s="70">
       <c r="A64" s="11" t="n">
@@ -9694,7 +9674,7 @@
       <c r="J64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="225" t="n">
+      <c r="K64" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L64" s="26" t="inlineStr">
@@ -9749,7 +9729,7 @@
       </c>
       <c r="I65" s="28" t="n"/>
       <c r="J65" s="15" t="n"/>
-      <c r="K65" s="222" t="n"/>
+      <c r="K65" s="221" t="n"/>
       <c r="L65" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -9804,7 +9784,7 @@
       <c r="J66" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K66" s="225" t="n">
+      <c r="K66" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L66" s="26" t="inlineStr">
@@ -9859,7 +9839,7 @@
       </c>
       <c r="I67" s="28" t="n"/>
       <c r="J67" s="15" t="n"/>
-      <c r="K67" s="222" t="n"/>
+      <c r="K67" s="221" t="n"/>
       <c r="L67" s="26" t="inlineStr">
         <is>
           <t>未找到往年信息</t>
@@ -9912,7 +9892,7 @@
       </c>
       <c r="I68" s="28" t="n"/>
       <c r="J68" s="15" t="n"/>
-      <c r="K68" s="222" t="n"/>
+      <c r="K68" s="221" t="n"/>
       <c r="L68" s="17" t="n"/>
       <c r="M68" s="18" t="n"/>
     </row>
@@ -9963,7 +9943,7 @@
       <c r="J69" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K69" s="225" t="n">
+      <c r="K69" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L69" s="26" t="inlineStr">
@@ -10020,7 +10000,7 @@
       <c r="J70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="225" t="n">
+      <c r="K70" s="224" t="n">
         <v>44565</v>
       </c>
       <c r="L70" s="26" t="inlineStr">
@@ -10077,30 +10057,30 @@
       <c r="J71" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K71" s="226" t="n">
+      <c r="K71" s="225" t="n">
         <v>44882</v>
       </c>
       <c r="L71" s="36" t="n"/>
       <c r="M71" s="18" t="n"/>
     </row>
     <row r="72" ht="24.75" customHeight="1" s="70">
-      <c r="A72" s="224" t="n"/>
-      <c r="B72" s="224" t="n"/>
-      <c r="C72" s="224" t="n"/>
+      <c r="A72" s="223" t="n"/>
+      <c r="B72" s="223" t="n"/>
+      <c r="C72" s="223" t="n"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
           <t>南京大学</t>
         </is>
       </c>
-      <c r="E72" s="224" t="n"/>
-      <c r="F72" s="224" t="n"/>
-      <c r="G72" s="224" t="n"/>
-      <c r="H72" s="224" t="n"/>
-      <c r="I72" s="224" t="n"/>
-      <c r="J72" s="224" t="n"/>
-      <c r="K72" s="224" t="n"/>
-      <c r="L72" s="229" t="n"/>
-      <c r="M72" s="224" t="n"/>
+      <c r="E72" s="223" t="n"/>
+      <c r="F72" s="223" t="n"/>
+      <c r="G72" s="223" t="n"/>
+      <c r="H72" s="223" t="n"/>
+      <c r="I72" s="223" t="n"/>
+      <c r="J72" s="223" t="n"/>
+      <c r="K72" s="223" t="n"/>
+      <c r="L72" s="228" t="n"/>
+      <c r="M72" s="223" t="n"/>
     </row>
     <row r="73" ht="24.75" customHeight="1" s="70">
       <c r="A73" s="11" t="n">
@@ -10149,7 +10129,7 @@
       <c r="J73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K73" s="225" t="n">
+      <c r="K73" s="224" t="n">
         <v>44670</v>
       </c>
       <c r="L73" s="26" t="inlineStr">
@@ -10206,7 +10186,7 @@
       <c r="J74" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K74" s="225" t="n">
+      <c r="K74" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L74" s="26" t="inlineStr">
@@ -10263,7 +10243,7 @@
       <c r="J75" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="225" t="n">
+      <c r="K75" s="224" t="n">
         <v>44588</v>
       </c>
       <c r="L75" s="26" t="inlineStr">
@@ -10320,7 +10300,7 @@
       <c r="J76" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="225" t="n">
+      <c r="K76" s="224" t="n">
         <v>44667</v>
       </c>
       <c r="L76" s="26" t="inlineStr">
@@ -10377,7 +10357,7 @@
       <c r="J77" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="225" t="n">
+      <c r="K77" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L77" s="26" t="inlineStr">
@@ -10434,7 +10414,7 @@
       <c r="J78" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K78" s="225" t="n">
+      <c r="K78" s="224" t="n">
         <v>44741</v>
       </c>
       <c r="L78" s="26" t="inlineStr">
@@ -10491,7 +10471,7 @@
       <c r="J79" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K79" s="225" t="n">
+      <c r="K79" s="224" t="n">
         <v>44825</v>
       </c>
       <c r="L79" s="17" t="n"/>
@@ -10544,7 +10524,7 @@
       <c r="J80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="232" t="n">
+      <c r="K80" s="231" t="n">
         <v>44709</v>
       </c>
       <c r="L80" s="36" t="n"/>
@@ -10597,7 +10577,7 @@
       <c r="J81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K81" s="233" t="n">
+      <c r="K81" s="232" t="n">
         <v>44670</v>
       </c>
       <c r="L81" s="17" t="n"/>
@@ -10640,7 +10620,7 @@
       <c r="H82" s="31" t="n"/>
       <c r="I82" s="48" t="n"/>
       <c r="J82" s="31" t="n"/>
-      <c r="K82" s="234" t="n"/>
+      <c r="K82" s="233" t="n"/>
       <c r="L82" s="29" t="inlineStr">
         <is>
           <t>不是专用连接，进不了官网</t>
@@ -10649,23 +10629,23 @@
       <c r="M82" s="18" t="n"/>
     </row>
     <row r="83" ht="24.75" customHeight="1" s="70">
-      <c r="A83" s="224" t="n"/>
-      <c r="B83" s="224" t="n"/>
-      <c r="C83" s="224" t="n"/>
+      <c r="A83" s="223" t="n"/>
+      <c r="B83" s="223" t="n"/>
+      <c r="C83" s="223" t="n"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
           <t>中国地质大学（北京）</t>
         </is>
       </c>
-      <c r="E83" s="224" t="n"/>
-      <c r="F83" s="224" t="n"/>
-      <c r="G83" s="224" t="n"/>
-      <c r="H83" s="224" t="n"/>
-      <c r="I83" s="224" t="n"/>
-      <c r="J83" s="224" t="n"/>
-      <c r="K83" s="224" t="n"/>
-      <c r="L83" s="224" t="n"/>
-      <c r="M83" s="224" t="n"/>
+      <c r="E83" s="223" t="n"/>
+      <c r="F83" s="223" t="n"/>
+      <c r="G83" s="223" t="n"/>
+      <c r="H83" s="223" t="n"/>
+      <c r="I83" s="223" t="n"/>
+      <c r="J83" s="223" t="n"/>
+      <c r="K83" s="223" t="n"/>
+      <c r="L83" s="223" t="n"/>
+      <c r="M83" s="223" t="n"/>
     </row>
     <row r="84" ht="24.75" customHeight="1" s="70">
       <c r="A84" s="11" t="n">
@@ -10714,7 +10694,7 @@
       <c r="J84" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K84" s="225" t="n">
+      <c r="K84" s="224" t="n">
         <v>44813</v>
       </c>
       <c r="L84" s="17" t="n"/>
@@ -10767,7 +10747,7 @@
       <c r="J85" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K85" s="225" t="n">
+      <c r="K85" s="224" t="n">
         <v>44881</v>
       </c>
       <c r="L85" s="26" t="inlineStr">
@@ -10824,7 +10804,7 @@
       <c r="J86" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="225" t="n">
+      <c r="K86" s="224" t="n">
         <v>44635</v>
       </c>
       <c r="L86" s="26" t="inlineStr">
@@ -10881,7 +10861,7 @@
       <c r="J87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K87" s="225" t="n">
+      <c r="K87" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L87" s="26" t="inlineStr">
@@ -10942,7 +10922,7 @@
       <c r="J88" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K88" s="225" t="n">
+      <c r="K88" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L88" s="26" t="inlineStr">
@@ -10999,7 +10979,7 @@
       <c r="J89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="225" t="n">
+      <c r="K89" s="224" t="n">
         <v>44592</v>
       </c>
       <c r="L89" s="26" t="inlineStr">
@@ -11010,17 +10990,17 @@
       <c r="M89" s="18" t="n"/>
     </row>
     <row r="90" ht="24.75" customHeight="1" s="70">
-      <c r="A90" s="224" t="n"/>
-      <c r="B90" s="224" t="n"/>
-      <c r="C90" s="224" t="n"/>
+      <c r="A90" s="223" t="n"/>
+      <c r="B90" s="223" t="n"/>
+      <c r="C90" s="223" t="n"/>
       <c r="D90" s="12" t="inlineStr">
         <is>
           <t>成都理工大学</t>
         </is>
       </c>
-      <c r="E90" s="224" t="n"/>
-      <c r="F90" s="224" t="n"/>
-      <c r="G90" s="224" t="n"/>
+      <c r="E90" s="223" t="n"/>
+      <c r="F90" s="223" t="n"/>
+      <c r="G90" s="223" t="n"/>
       <c r="H90" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11034,7 +11014,7 @@
       <c r="J90" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K90" s="225" t="n">
+      <c r="K90" s="224" t="n">
         <v>44871</v>
       </c>
       <c r="L90" s="26" t="inlineStr">
@@ -11091,7 +11071,7 @@
       <c r="J91" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K91" s="225" t="n">
+      <c r="K91" s="224" t="n">
         <v>44806</v>
       </c>
       <c r="L91" s="26" t="inlineStr">
@@ -11148,7 +11128,7 @@
       <c r="J92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="225" t="n">
+      <c r="K92" s="224" t="n">
         <v>44576</v>
       </c>
       <c r="L92" s="26" t="inlineStr">
@@ -11199,7 +11179,7 @@
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="50" t="n"/>
-      <c r="K93" s="235" t="n"/>
+      <c r="K93" s="234" t="n"/>
       <c r="L93" s="17" t="n"/>
       <c r="M93" s="18" t="n"/>
     </row>
@@ -11250,7 +11230,7 @@
       <c r="J94" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K94" s="225" t="n">
+      <c r="K94" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L94" s="17" t="n"/>
@@ -11303,7 +11283,7 @@
       <c r="J95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K95" s="225" t="n">
+      <c r="K95" s="224" t="n">
         <v>44679</v>
       </c>
       <c r="L95" s="17" t="n"/>
@@ -11356,7 +11336,7 @@
       <c r="J96" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K96" s="225" t="n">
+      <c r="K96" s="224" t="n">
         <v>44840</v>
       </c>
       <c r="L96" s="17" t="n"/>
@@ -11409,7 +11389,7 @@
       <c r="J97" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K97" s="225" t="n">
+      <c r="K97" s="224" t="n">
         <v>44848</v>
       </c>
       <c r="L97" s="17" t="n"/>
@@ -11462,7 +11442,7 @@
       <c r="J98" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K98" s="225" t="n">
+      <c r="K98" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L98" s="17" t="n"/>
@@ -11515,7 +11495,7 @@
       <c r="J99" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="225" t="n">
+      <c r="K99" s="224" t="n">
         <v>44644</v>
       </c>
       <c r="L99" s="17" t="n"/>
@@ -11568,7 +11548,7 @@
       <c r="J100" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K100" s="225" t="n">
+      <c r="K100" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L100" s="26" t="inlineStr">
@@ -11629,7 +11609,7 @@
       <c r="J101" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K101" s="225" t="n">
+      <c r="K101" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L101" s="26" t="inlineStr">
@@ -11686,7 +11666,7 @@
       <c r="J102" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K102" s="225" t="n">
+      <c r="K102" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L102" s="26" t="inlineStr">
@@ -11737,22 +11717,22 @@
       </c>
       <c r="I103" s="28" t="n"/>
       <c r="J103" s="15" t="n"/>
-      <c r="K103" s="222" t="n"/>
+      <c r="K103" s="221" t="n"/>
       <c r="L103" s="17" t="n"/>
       <c r="M103" s="18" t="n"/>
     </row>
     <row r="104" ht="24.75" customHeight="1" s="70">
-      <c r="A104" s="223" t="n"/>
-      <c r="B104" s="223" t="n"/>
-      <c r="C104" s="223" t="n"/>
+      <c r="A104" s="222" t="n"/>
+      <c r="B104" s="222" t="n"/>
+      <c r="C104" s="222" t="n"/>
       <c r="D104" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E104" s="223" t="n"/>
-      <c r="F104" s="223" t="n"/>
-      <c r="G104" s="223" t="n"/>
+      <c r="E104" s="222" t="n"/>
+      <c r="F104" s="222" t="n"/>
+      <c r="G104" s="222" t="n"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11766,7 +11746,7 @@
       <c r="J104" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K104" s="225" t="n">
+      <c r="K104" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L104" s="26" t="inlineStr">
@@ -11777,17 +11757,17 @@
       <c r="M104" s="18" t="n"/>
     </row>
     <row r="105" ht="24.75" customHeight="1" s="70">
-      <c r="A105" s="224" t="n"/>
-      <c r="B105" s="224" t="n"/>
-      <c r="C105" s="224" t="n"/>
+      <c r="A105" s="223" t="n"/>
+      <c r="B105" s="223" t="n"/>
+      <c r="C105" s="223" t="n"/>
       <c r="D105" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E105" s="224" t="n"/>
-      <c r="F105" s="224" t="n"/>
-      <c r="G105" s="224" t="n"/>
+      <c r="E105" s="223" t="n"/>
+      <c r="F105" s="223" t="n"/>
+      <c r="G105" s="223" t="n"/>
       <c r="H105" s="52" t="inlineStr">
         <is>
           <t>否</t>
@@ -11846,7 +11826,7 @@
       <c r="J106" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="K106" s="233" t="n">
+      <c r="K106" s="232" t="n">
         <v>44814</v>
       </c>
       <c r="L106" s="40" t="n"/>
@@ -11893,7 +11873,7 @@
       </c>
       <c r="I107" s="56" t="n"/>
       <c r="J107" s="15" t="n"/>
-      <c r="K107" s="222" t="n"/>
+      <c r="K107" s="221" t="n"/>
       <c r="L107" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11950,7 +11930,7 @@
         </is>
       </c>
       <c r="J108" s="15" t="n"/>
-      <c r="K108" s="222" t="n"/>
+      <c r="K108" s="221" t="n"/>
       <c r="L108" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11999,7 +11979,7 @@
       </c>
       <c r="I109" s="28" t="n"/>
       <c r="J109" s="15" t="n"/>
-      <c r="K109" s="222" t="n"/>
+      <c r="K109" s="221" t="n"/>
       <c r="L109" s="26" t="inlineStr">
         <is>
           <t>网址打不开</t>
@@ -12052,7 +12032,7 @@
         </is>
       </c>
       <c r="J110" s="15" t="n"/>
-      <c r="K110" s="222" t="n"/>
+      <c r="K110" s="221" t="n"/>
       <c r="L110" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -12061,17 +12041,17 @@
       <c r="M110" s="18" t="n"/>
     </row>
     <row r="111" ht="24.75" customHeight="1" s="70">
-      <c r="A111" s="224" t="n"/>
-      <c r="B111" s="224" t="n"/>
-      <c r="C111" s="224" t="n"/>
+      <c r="A111" s="223" t="n"/>
+      <c r="B111" s="223" t="n"/>
+      <c r="C111" s="223" t="n"/>
       <c r="D111" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E111" s="224" t="n"/>
-      <c r="F111" s="224" t="n"/>
-      <c r="G111" s="224" t="n"/>
+      <c r="E111" s="223" t="n"/>
+      <c r="F111" s="223" t="n"/>
+      <c r="G111" s="223" t="n"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
           <t>否</t>
@@ -12079,7 +12059,7 @@
       </c>
       <c r="I111" s="28" t="n"/>
       <c r="J111" s="15" t="n"/>
-      <c r="K111" s="222" t="n"/>
+      <c r="K111" s="221" t="n"/>
       <c r="L111" s="17" t="n"/>
       <c r="M111" s="18" t="n"/>
     </row>
@@ -12128,7 +12108,7 @@
         </is>
       </c>
       <c r="J112" s="31" t="n"/>
-      <c r="K112" s="234" t="n"/>
+      <c r="K112" s="233" t="n"/>
       <c r="L112" s="29" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -12137,23 +12117,23 @@
       <c r="M112" s="18" t="n"/>
     </row>
     <row r="113" ht="24.75" customHeight="1" s="70">
-      <c r="A113" s="224" t="n"/>
-      <c r="B113" s="224" t="n"/>
-      <c r="C113" s="224" t="n"/>
+      <c r="A113" s="223" t="n"/>
+      <c r="B113" s="223" t="n"/>
+      <c r="C113" s="223" t="n"/>
       <c r="D113" s="12" t="inlineStr">
         <is>
           <t>中国科学院微生物研究所</t>
         </is>
       </c>
-      <c r="E113" s="224" t="n"/>
-      <c r="F113" s="224" t="n"/>
-      <c r="G113" s="224" t="n"/>
-      <c r="H113" s="224" t="n"/>
-      <c r="I113" s="224" t="n"/>
-      <c r="J113" s="224" t="n"/>
-      <c r="K113" s="224" t="n"/>
-      <c r="L113" s="224" t="n"/>
-      <c r="M113" s="224" t="n"/>
+      <c r="E113" s="223" t="n"/>
+      <c r="F113" s="223" t="n"/>
+      <c r="G113" s="223" t="n"/>
+      <c r="H113" s="223" t="n"/>
+      <c r="I113" s="223" t="n"/>
+      <c r="J113" s="223" t="n"/>
+      <c r="K113" s="223" t="n"/>
+      <c r="L113" s="223" t="n"/>
+      <c r="M113" s="223" t="n"/>
     </row>
     <row r="114" ht="24.75" customHeight="1" s="70">
       <c r="A114" s="11" t="n">
@@ -12196,7 +12176,7 @@
       </c>
       <c r="I114" s="28" t="n"/>
       <c r="J114" s="15" t="n"/>
-      <c r="K114" s="222" t="n"/>
+      <c r="K114" s="221" t="n"/>
       <c r="L114" s="17" t="n"/>
       <c r="M114" s="18" t="n"/>
     </row>
@@ -12247,7 +12227,7 @@
       <c r="J115" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K115" s="226" t="n">
+      <c r="K115" s="225" t="n">
         <v>44690</v>
       </c>
       <c r="L115" s="27" t="inlineStr">
@@ -12258,23 +12238,23 @@
       <c r="M115" s="18" t="n"/>
     </row>
     <row r="116" ht="24.75" customHeight="1" s="70">
-      <c r="A116" s="224" t="n"/>
-      <c r="B116" s="224" t="n"/>
-      <c r="C116" s="224" t="n"/>
+      <c r="A116" s="223" t="n"/>
+      <c r="B116" s="223" t="n"/>
+      <c r="C116" s="223" t="n"/>
       <c r="D116" s="12" t="inlineStr">
         <is>
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="E116" s="224" t="n"/>
-      <c r="F116" s="224" t="n"/>
-      <c r="G116" s="224" t="n"/>
-      <c r="H116" s="224" t="n"/>
-      <c r="I116" s="224" t="n"/>
-      <c r="J116" s="224" t="n"/>
-      <c r="K116" s="224" t="n"/>
-      <c r="L116" s="224" t="n"/>
-      <c r="M116" s="224" t="n"/>
+      <c r="E116" s="223" t="n"/>
+      <c r="F116" s="223" t="n"/>
+      <c r="G116" s="223" t="n"/>
+      <c r="H116" s="223" t="n"/>
+      <c r="I116" s="223" t="n"/>
+      <c r="J116" s="223" t="n"/>
+      <c r="K116" s="223" t="n"/>
+      <c r="L116" s="223" t="n"/>
+      <c r="M116" s="223" t="n"/>
     </row>
     <row r="117" ht="24.75" customHeight="1" s="70">
       <c r="A117" s="11" t="n">
@@ -12323,16 +12303,16 @@
       <c r="J117" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K117" s="225" t="n">
+      <c r="K117" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L117" s="17" t="n"/>
       <c r="M117" s="18" t="n"/>
     </row>
     <row r="118" ht="24.75" customHeight="1" s="70">
-      <c r="A118" s="224" t="n"/>
-      <c r="B118" s="224" t="n"/>
-      <c r="C118" s="224" t="n"/>
+      <c r="A118" s="223" t="n"/>
+      <c r="B118" s="223" t="n"/>
+      <c r="C118" s="223" t="n"/>
       <c r="D118" s="12" t="inlineStr">
         <is>
           <t>东北林业大学</t>
@@ -12343,8 +12323,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F118" s="224" t="n"/>
-      <c r="G118" s="224" t="n"/>
+      <c r="F118" s="223" t="n"/>
+      <c r="G118" s="223" t="n"/>
       <c r="H118" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12358,7 +12338,7 @@
       <c r="J118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K118" s="225" t="n">
+      <c r="K118" s="224" t="n">
         <v>44834</v>
       </c>
       <c r="L118" s="17" t="n"/>
@@ -12409,7 +12389,7 @@
         </is>
       </c>
       <c r="J119" s="15" t="n"/>
-      <c r="K119" s="222" t="n"/>
+      <c r="K119" s="221" t="n"/>
       <c r="L119" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知页</t>
@@ -12462,7 +12442,7 @@
       </c>
       <c r="I120" s="28" t="n"/>
       <c r="J120" s="15" t="n"/>
-      <c r="K120" s="222" t="n"/>
+      <c r="K120" s="221" t="n"/>
       <c r="L120" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -12517,7 +12497,7 @@
       <c r="J121" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="225" t="n">
+      <c r="K121" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L121" s="17" t="n"/>
@@ -12570,7 +12550,7 @@
       <c r="J122" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K122" s="225" t="n">
+      <c r="K122" s="224" t="n">
         <v>44621</v>
       </c>
       <c r="L122" s="17" t="n"/>
@@ -12617,7 +12597,7 @@
       </c>
       <c r="I123" s="28" t="n"/>
       <c r="J123" s="15" t="n"/>
-      <c r="K123" s="222" t="n"/>
+      <c r="K123" s="221" t="n"/>
       <c r="L123" s="17" t="n"/>
       <c r="M123" s="18" t="n"/>
     </row>
@@ -12668,7 +12648,7 @@
       <c r="J124" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K124" s="225" t="n">
+      <c r="K124" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -12721,7 +12701,7 @@
       <c r="J125" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K125" s="225" t="n">
+      <c r="K125" s="224" t="n">
         <v>44809</v>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -12768,7 +12748,7 @@
       </c>
       <c r="I126" s="28" t="n"/>
       <c r="J126" s="15" t="n"/>
-      <c r="K126" s="222" t="n"/>
+      <c r="K126" s="221" t="n"/>
       <c r="L126" s="26" t="inlineStr">
         <is>
           <t>未找到相应的官网</t>
@@ -12823,7 +12803,7 @@
       <c r="J127" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K127" s="225" t="n">
+      <c r="K127" s="224" t="n">
         <v>44589</v>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -12876,7 +12856,7 @@
       <c r="J128" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K128" s="225" t="n">
+      <c r="K128" s="224" t="n">
         <v>44917</v>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -12929,24 +12909,24 @@
       <c r="J129" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K129" s="225" t="n">
+      <c r="K129" s="224" t="n">
         <v>44586</v>
       </c>
       <c r="L129" s="17" t="n"/>
       <c r="M129" s="18" t="n"/>
     </row>
     <row r="130" ht="24.75" customHeight="1" s="70">
-      <c r="A130" s="224" t="n"/>
-      <c r="B130" s="224" t="n"/>
-      <c r="C130" s="224" t="n"/>
+      <c r="A130" s="223" t="n"/>
+      <c r="B130" s="223" t="n"/>
+      <c r="C130" s="223" t="n"/>
       <c r="D130" s="12" t="inlineStr">
         <is>
           <t>南昌大学</t>
         </is>
       </c>
-      <c r="E130" s="224" t="n"/>
-      <c r="F130" s="224" t="n"/>
-      <c r="G130" s="224" t="n"/>
+      <c r="E130" s="223" t="n"/>
+      <c r="F130" s="223" t="n"/>
+      <c r="G130" s="223" t="n"/>
       <c r="H130" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12960,7 +12940,7 @@
       <c r="J130" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K130" s="225" t="n">
+      <c r="K130" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L130" s="26" t="inlineStr">
@@ -13011,26 +12991,26 @@
       </c>
       <c r="I131" s="28" t="n"/>
       <c r="J131" s="15" t="n"/>
-      <c r="K131" s="222" t="n"/>
+      <c r="K131" s="221" t="n"/>
       <c r="L131" s="17" t="n"/>
       <c r="M131" s="18" t="n"/>
     </row>
     <row r="132" ht="24.75" customHeight="1" s="70">
-      <c r="A132" s="224" t="n"/>
-      <c r="B132" s="224" t="n"/>
-      <c r="C132" s="224" t="n"/>
+      <c r="A132" s="223" t="n"/>
+      <c r="B132" s="223" t="n"/>
+      <c r="C132" s="223" t="n"/>
       <c r="D132" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E132" s="224" t="n"/>
-      <c r="F132" s="224" t="n"/>
-      <c r="G132" s="224" t="n"/>
-      <c r="H132" s="224" t="n"/>
+      <c r="E132" s="223" t="n"/>
+      <c r="F132" s="223" t="n"/>
+      <c r="G132" s="223" t="n"/>
+      <c r="H132" s="223" t="n"/>
       <c r="I132" s="28" t="n"/>
       <c r="J132" s="15" t="n"/>
-      <c r="K132" s="222" t="n"/>
+      <c r="K132" s="221" t="n"/>
       <c r="L132" s="17" t="n"/>
       <c r="M132" s="18" t="n"/>
     </row>
@@ -13081,7 +13061,7 @@
       <c r="J133" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K133" s="225" t="n">
+      <c r="K133" s="224" t="n">
         <v>44713</v>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -13128,7 +13108,7 @@
       </c>
       <c r="I134" s="28" t="n"/>
       <c r="J134" s="15" t="n"/>
-      <c r="K134" s="222" t="n"/>
+      <c r="K134" s="221" t="n"/>
       <c r="L134" s="26" t="inlineStr">
         <is>
           <t>开放课题基金的申请每年受理一次，申请截止日期为每年的3月15日。</t>
@@ -13187,16 +13167,16 @@
       <c r="J135" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K135" s="226" t="n">
+      <c r="K135" s="225" t="n">
         <v>44878</v>
       </c>
       <c r="L135" s="18" t="n"/>
       <c r="M135" s="58" t="n"/>
     </row>
     <row r="136" ht="24.75" customHeight="1" s="70">
-      <c r="A136" s="224" t="n"/>
-      <c r="B136" s="224" t="n"/>
-      <c r="C136" s="224" t="n"/>
+      <c r="A136" s="223" t="n"/>
+      <c r="B136" s="223" t="n"/>
+      <c r="C136" s="223" t="n"/>
       <c r="D136" s="12" t="inlineStr">
         <is>
           <t>河南大学</t>
@@ -13207,13 +13187,13 @@
           <t>河南省科技厅</t>
         </is>
       </c>
-      <c r="F136" s="224" t="n"/>
-      <c r="G136" s="224" t="n"/>
-      <c r="H136" s="224" t="n"/>
-      <c r="I136" s="224" t="n"/>
-      <c r="J136" s="224" t="n"/>
-      <c r="K136" s="224" t="n"/>
-      <c r="L136" s="224" t="n"/>
+      <c r="F136" s="223" t="n"/>
+      <c r="G136" s="223" t="n"/>
+      <c r="H136" s="223" t="n"/>
+      <c r="I136" s="223" t="n"/>
+      <c r="J136" s="223" t="n"/>
+      <c r="K136" s="223" t="n"/>
+      <c r="L136" s="223" t="n"/>
       <c r="M136" s="58" t="n"/>
     </row>
     <row r="137" ht="24.75" customHeight="1" s="70">
@@ -13263,7 +13243,7 @@
       <c r="J137" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K137" s="225" t="n">
+      <c r="K137" s="224" t="n">
         <v>44624</v>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -13316,7 +13296,7 @@
       <c r="J138" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K138" s="225" t="n">
+      <c r="K138" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L138" s="26" t="inlineStr">
@@ -13373,7 +13353,7 @@
       <c r="J139" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K139" s="225" t="n">
+      <c r="K139" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -13420,26 +13400,26 @@
       </c>
       <c r="I140" s="48" t="n"/>
       <c r="J140" s="31" t="n"/>
-      <c r="K140" s="234" t="n"/>
+      <c r="K140" s="233" t="n"/>
       <c r="L140" s="17" t="n"/>
       <c r="M140" s="18" t="n"/>
     </row>
     <row r="141" ht="24.75" customHeight="1" s="70">
-      <c r="A141" s="224" t="n"/>
-      <c r="B141" s="224" t="n"/>
-      <c r="C141" s="224" t="n"/>
+      <c r="A141" s="223" t="n"/>
+      <c r="B141" s="223" t="n"/>
+      <c r="C141" s="223" t="n"/>
       <c r="D141" s="12" t="inlineStr">
         <is>
           <t>中国科学院武汉病毒研究所</t>
         </is>
       </c>
-      <c r="E141" s="224" t="n"/>
-      <c r="F141" s="224" t="n"/>
-      <c r="G141" s="224" t="n"/>
-      <c r="H141" s="224" t="n"/>
-      <c r="I141" s="224" t="n"/>
-      <c r="J141" s="224" t="n"/>
-      <c r="K141" s="224" t="n"/>
+      <c r="E141" s="223" t="n"/>
+      <c r="F141" s="223" t="n"/>
+      <c r="G141" s="223" t="n"/>
+      <c r="H141" s="223" t="n"/>
+      <c r="I141" s="223" t="n"/>
+      <c r="J141" s="223" t="n"/>
+      <c r="K141" s="223" t="n"/>
       <c r="L141" s="17" t="n"/>
       <c r="M141" s="18" t="n"/>
     </row>
@@ -13490,16 +13470,16 @@
       <c r="J142" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K142" s="225" t="n">
+      <c r="K142" s="224" t="n">
         <v>44745</v>
       </c>
       <c r="L142" s="17" t="n"/>
       <c r="M142" s="18" t="n"/>
     </row>
     <row r="143" ht="24.75" customHeight="1" s="70">
-      <c r="A143" s="224" t="n"/>
-      <c r="B143" s="224" t="n"/>
-      <c r="C143" s="224" t="n"/>
+      <c r="A143" s="223" t="n"/>
+      <c r="B143" s="223" t="n"/>
+      <c r="C143" s="223" t="n"/>
       <c r="D143" s="12" t="inlineStr">
         <is>
           <t>武汉大学</t>
@@ -13510,8 +13490,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F143" s="224" t="n"/>
-      <c r="G143" s="224" t="n"/>
+      <c r="F143" s="223" t="n"/>
+      <c r="G143" s="223" t="n"/>
       <c r="H143" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13525,7 +13505,7 @@
       <c r="J143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K143" s="225" t="n">
+      <c r="K143" s="224" t="n">
         <v>44675</v>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -13578,7 +13558,7 @@
       <c r="J144" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K144" s="225" t="n">
+      <c r="K144" s="224" t="n">
         <v>44826</v>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -13631,16 +13611,16 @@
       <c r="J145" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K145" s="225" t="n">
+      <c r="K145" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L145" s="17" t="n"/>
       <c r="M145" s="18" t="n"/>
     </row>
     <row r="146" ht="24.75" customHeight="1" s="70">
-      <c r="A146" s="224" t="n"/>
-      <c r="B146" s="224" t="n"/>
-      <c r="C146" s="224" t="n"/>
+      <c r="A146" s="223" t="n"/>
+      <c r="B146" s="223" t="n"/>
+      <c r="C146" s="223" t="n"/>
       <c r="D146" s="12" t="inlineStr">
         <is>
           <t>华南农业大学</t>
@@ -13651,8 +13631,8 @@
           <t>广东省科技厅</t>
         </is>
       </c>
-      <c r="F146" s="224" t="n"/>
-      <c r="G146" s="224" t="n"/>
+      <c r="F146" s="223" t="n"/>
+      <c r="G146" s="223" t="n"/>
       <c r="H146" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13666,7 +13646,7 @@
       <c r="J146" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K146" s="225" t="n">
+      <c r="K146" s="224" t="n">
         <v>44876</v>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -13719,7 +13699,7 @@
       <c r="J147" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K147" s="225" t="n">
+      <c r="K147" s="224" t="n">
         <v>44870</v>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -13772,7 +13752,7 @@
       <c r="J148" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K148" s="225" t="n">
+      <c r="K148" s="224" t="n">
         <v>44653</v>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -13825,7 +13805,7 @@
       <c r="J149" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K149" s="225" t="n">
+      <c r="K149" s="224" t="n">
         <v>44844</v>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -13878,7 +13858,7 @@
       <c r="J150" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K150" s="225" t="n">
+      <c r="K150" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L150" s="17" t="n"/>
@@ -13931,7 +13911,7 @@
       <c r="J151" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K151" s="225" t="n">
+      <c r="K151" s="224" t="n">
         <v>44737</v>
       </c>
       <c r="L151" s="17" t="n"/>
@@ -13984,7 +13964,7 @@
       <c r="J152" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K152" s="225" t="n">
+      <c r="K152" s="224" t="n">
         <v>44761</v>
       </c>
       <c r="L152" s="17" t="n"/>
@@ -14037,7 +14017,7 @@
       <c r="J153" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K153" s="225" t="n">
+      <c r="K153" s="224" t="n">
         <v>44590</v>
       </c>
       <c r="L153" s="17" t="n"/>
@@ -14090,7 +14070,7 @@
       <c r="J154" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K154" s="225" t="n">
+      <c r="K154" s="224" t="n">
         <v>44597</v>
       </c>
       <c r="L154" s="17" t="n"/>
@@ -14145,7 +14125,7 @@
           <t>4、5</t>
         </is>
       </c>
-      <c r="K155" s="225" t="n">
+      <c r="K155" s="224" t="n">
         <v>44701</v>
       </c>
       <c r="L155" s="17" t="n"/>
@@ -14198,7 +14178,7 @@
       <c r="J156" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K156" s="225" t="n">
+      <c r="K156" s="224" t="n">
         <v>44924</v>
       </c>
       <c r="L156" s="17" t="n"/>
@@ -14251,7 +14231,7 @@
       <c r="J157" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K157" s="225" t="n">
+      <c r="K157" s="224" t="n">
         <v>44657</v>
       </c>
       <c r="L157" s="17" t="n"/>
@@ -14304,7 +14284,7 @@
       <c r="J158" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K158" s="225" t="n">
+      <c r="K158" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L158" s="17" t="n"/>
@@ -14357,7 +14337,7 @@
       <c r="J159" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K159" s="225" t="n">
+      <c r="K159" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L159" s="59" t="n"/>
@@ -14410,7 +14390,7 @@
       <c r="J160" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K160" s="225" t="n">
+      <c r="K160" s="224" t="n">
         <v>44649</v>
       </c>
       <c r="L160" s="17" t="n"/>
@@ -14463,24 +14443,24 @@
       <c r="J161" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K161" s="225" t="n">
+      <c r="K161" s="224" t="n">
         <v>44789</v>
       </c>
       <c r="L161" s="17" t="n"/>
       <c r="M161" s="18" t="n"/>
     </row>
     <row r="162" ht="24.75" customHeight="1" s="70">
-      <c r="A162" s="224" t="n"/>
-      <c r="B162" s="224" t="n"/>
-      <c r="C162" s="224" t="n"/>
+      <c r="A162" s="223" t="n"/>
+      <c r="B162" s="223" t="n"/>
+      <c r="C162" s="223" t="n"/>
       <c r="D162" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E162" s="224" t="n"/>
-      <c r="F162" s="224" t="n"/>
-      <c r="G162" s="224" t="n"/>
+      <c r="E162" s="223" t="n"/>
+      <c r="F162" s="223" t="n"/>
+      <c r="G162" s="223" t="n"/>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -14488,7 +14468,7 @@
       </c>
       <c r="I162" s="28" t="n"/>
       <c r="J162" s="15" t="n"/>
-      <c r="K162" s="222" t="n"/>
+      <c r="K162" s="221" t="n"/>
       <c r="L162" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知</t>
@@ -14537,7 +14517,7 @@
       </c>
       <c r="I163" s="28" t="n"/>
       <c r="J163" s="15" t="n"/>
-      <c r="K163" s="222" t="n"/>
+      <c r="K163" s="221" t="n"/>
       <c r="L163" s="17" t="n"/>
       <c r="M163" s="18" t="n"/>
     </row>
@@ -14588,7 +14568,7 @@
       <c r="J164" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="225" t="n">
+      <c r="K164" s="224" t="n">
         <v>44668</v>
       </c>
       <c r="L164" s="17" t="n"/>
@@ -14637,7 +14617,7 @@
       <c r="J165" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K165" s="225" t="n">
+      <c r="K165" s="224" t="n">
         <v>44660</v>
       </c>
       <c r="L165" s="60" t="inlineStr">
@@ -14698,7 +14678,7 @@
       <c r="J166" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K166" s="225" t="n">
+      <c r="K166" s="224" t="n">
         <v>44649</v>
       </c>
       <c r="L166" s="40" t="n"/>
@@ -14751,28 +14731,28 @@
       <c r="J167" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K167" s="226" t="n">
+      <c r="K167" s="225" t="n">
         <v>44709</v>
       </c>
       <c r="L167" s="17" t="n"/>
       <c r="M167" s="18" t="n"/>
     </row>
     <row r="168" ht="24.75" customHeight="1" s="70">
-      <c r="A168" s="224" t="n"/>
-      <c r="B168" s="224" t="n"/>
-      <c r="C168" s="224" t="n"/>
+      <c r="A168" s="223" t="n"/>
+      <c r="B168" s="223" t="n"/>
+      <c r="C168" s="223" t="n"/>
       <c r="D168" s="12" t="inlineStr">
         <is>
           <t>中国科学院半导体研究所</t>
         </is>
       </c>
-      <c r="E168" s="224" t="n"/>
-      <c r="F168" s="224" t="n"/>
-      <c r="G168" s="224" t="n"/>
-      <c r="H168" s="224" t="n"/>
-      <c r="I168" s="224" t="n"/>
-      <c r="J168" s="224" t="n"/>
-      <c r="K168" s="224" t="n"/>
+      <c r="E168" s="223" t="n"/>
+      <c r="F168" s="223" t="n"/>
+      <c r="G168" s="223" t="n"/>
+      <c r="H168" s="223" t="n"/>
+      <c r="I168" s="223" t="n"/>
+      <c r="J168" s="223" t="n"/>
+      <c r="K168" s="223" t="n"/>
       <c r="L168" s="17" t="n"/>
       <c r="M168" s="18" t="n"/>
     </row>
@@ -14823,7 +14803,7 @@
       <c r="J169" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K169" s="225" t="n">
+      <c r="K169" s="224" t="n">
         <v>44821</v>
       </c>
       <c r="L169" s="17" t="n"/>
@@ -14876,28 +14856,28 @@
       <c r="J170" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K170" s="226" t="n">
+      <c r="K170" s="225" t="n">
         <v>44819</v>
       </c>
       <c r="L170" s="17" t="n"/>
       <c r="M170" s="18" t="n"/>
     </row>
     <row r="171" ht="24.75" customHeight="1" s="70">
-      <c r="A171" s="224" t="n"/>
-      <c r="B171" s="224" t="n"/>
-      <c r="C171" s="224" t="n"/>
+      <c r="A171" s="223" t="n"/>
+      <c r="B171" s="223" t="n"/>
+      <c r="C171" s="223" t="n"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
           <t>中国科学院电子学研究所</t>
         </is>
       </c>
-      <c r="E171" s="224" t="n"/>
-      <c r="F171" s="224" t="n"/>
-      <c r="G171" s="224" t="n"/>
-      <c r="H171" s="224" t="n"/>
-      <c r="I171" s="224" t="n"/>
-      <c r="J171" s="224" t="n"/>
-      <c r="K171" s="224" t="n"/>
+      <c r="E171" s="223" t="n"/>
+      <c r="F171" s="223" t="n"/>
+      <c r="G171" s="223" t="n"/>
+      <c r="H171" s="223" t="n"/>
+      <c r="I171" s="223" t="n"/>
+      <c r="J171" s="223" t="n"/>
+      <c r="K171" s="223" t="n"/>
       <c r="L171" s="17" t="n"/>
       <c r="M171" s="18" t="n"/>
     </row>
@@ -14946,7 +14926,7 @@
         </is>
       </c>
       <c r="J172" s="15" t="n"/>
-      <c r="K172" s="222" t="n"/>
+      <c r="K172" s="221" t="n"/>
       <c r="L172" s="26" t="inlineStr">
         <is>
           <t>网站时常故障</t>
@@ -15001,28 +14981,28 @@
       <c r="J173" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K173" s="226" t="n">
+      <c r="K173" s="225" t="n">
         <v>44881</v>
       </c>
       <c r="L173" s="17" t="n"/>
       <c r="M173" s="18" t="n"/>
     </row>
     <row r="174" ht="24.75" customHeight="1" s="70">
-      <c r="A174" s="224" t="n"/>
-      <c r="B174" s="224" t="n"/>
-      <c r="C174" s="224" t="n"/>
+      <c r="A174" s="223" t="n"/>
+      <c r="B174" s="223" t="n"/>
+      <c r="C174" s="223" t="n"/>
       <c r="D174" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E174" s="224" t="n"/>
-      <c r="F174" s="224" t="n"/>
-      <c r="G174" s="224" t="n"/>
-      <c r="H174" s="224" t="n"/>
-      <c r="I174" s="224" t="n"/>
-      <c r="J174" s="224" t="n"/>
-      <c r="K174" s="224" t="n"/>
+      <c r="E174" s="223" t="n"/>
+      <c r="F174" s="223" t="n"/>
+      <c r="G174" s="223" t="n"/>
+      <c r="H174" s="223" t="n"/>
+      <c r="I174" s="223" t="n"/>
+      <c r="J174" s="223" t="n"/>
+      <c r="K174" s="223" t="n"/>
       <c r="L174" s="17" t="n"/>
       <c r="M174" s="18" t="n"/>
     </row>
@@ -15073,7 +15053,7 @@
       <c r="J175" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K175" s="225" t="n">
+      <c r="K175" s="224" t="n">
         <v>44666</v>
       </c>
       <c r="L175" s="26" t="inlineStr">
@@ -15130,7 +15110,7 @@
       <c r="J176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K176" s="225" t="n">
+      <c r="K176" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L176" s="26" t="inlineStr">
@@ -15187,7 +15167,7 @@
       <c r="J177" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K177" s="225" t="n">
+      <c r="K177" s="224" t="n">
         <v>44671</v>
       </c>
       <c r="L177" s="17" t="n"/>
@@ -15240,7 +15220,7 @@
       <c r="J178" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K178" s="225" t="n">
+      <c r="K178" s="224" t="n">
         <v>44648</v>
       </c>
       <c r="L178" s="17" t="n"/>
@@ -15293,7 +15273,7 @@
       <c r="J179" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K179" s="225" t="n">
+      <c r="K179" s="224" t="n">
         <v>44812</v>
       </c>
       <c r="L179" s="17" t="n"/>
@@ -15346,7 +15326,7 @@
       <c r="J180" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K180" s="225" t="n">
+      <c r="K180" s="224" t="n">
         <v>44831</v>
       </c>
       <c r="L180" s="17" t="n"/>
@@ -15399,7 +15379,7 @@
       <c r="J181" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K181" s="225" t="n">
+      <c r="K181" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L181" s="17" t="n"/>
@@ -15452,7 +15432,7 @@
       <c r="J182" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K182" s="225" t="n">
+      <c r="K182" s="224" t="n">
         <v>44926</v>
       </c>
       <c r="L182" s="17" t="n"/>
@@ -15499,7 +15479,7 @@
       </c>
       <c r="I183" s="28" t="n"/>
       <c r="J183" s="15" t="n"/>
-      <c r="K183" s="222" t="n"/>
+      <c r="K183" s="221" t="n"/>
       <c r="L183" s="17" t="n"/>
       <c r="M183" s="18" t="n"/>
     </row>
@@ -15550,7 +15530,7 @@
       <c r="J184" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K184" s="225" t="n">
+      <c r="K184" s="224" t="n">
         <v>44718</v>
       </c>
       <c r="L184" s="17" t="n"/>
@@ -15603,7 +15583,7 @@
       <c r="J185" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K185" s="225" t="n">
+      <c r="K185" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L185" s="17" t="n"/>
@@ -15656,7 +15636,7 @@
       <c r="J186" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K186" s="225" t="n">
+      <c r="K186" s="224" t="n">
         <v>44800</v>
       </c>
       <c r="L186" s="17" t="n"/>
@@ -15709,7 +15689,7 @@
       <c r="J187" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K187" s="225" t="n">
+      <c r="K187" s="224" t="n">
         <v>44737</v>
       </c>
       <c r="L187" s="17" t="n"/>
@@ -15762,7 +15742,7 @@
       <c r="J188" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="225" t="n">
+      <c r="K188" s="224" t="n">
         <v>44573</v>
       </c>
       <c r="L188" s="17" t="n"/>
@@ -15815,7 +15795,7 @@
       <c r="J189" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K189" s="225" t="n">
+      <c r="K189" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L189" s="17" t="n"/>
@@ -15862,7 +15842,7 @@
       </c>
       <c r="I190" s="28" t="n"/>
       <c r="J190" s="15" t="n"/>
-      <c r="K190" s="222" t="n"/>
+      <c r="K190" s="221" t="n"/>
       <c r="L190" s="17" t="n"/>
       <c r="M190" s="18" t="n"/>
     </row>
@@ -15913,7 +15893,7 @@
       <c r="J191" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K191" s="225" t="n">
+      <c r="K191" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L191" s="63" t="inlineStr">
@@ -15964,7 +15944,7 @@
       </c>
       <c r="I192" s="28" t="n"/>
       <c r="J192" s="15" t="n"/>
-      <c r="K192" s="222" t="n"/>
+      <c r="K192" s="221" t="n"/>
       <c r="L192" s="40" t="n"/>
       <c r="M192" s="18" t="n"/>
     </row>
@@ -16015,7 +15995,7 @@
       <c r="J193" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K193" s="225" t="n">
+      <c r="K193" s="224" t="n">
         <v>44694</v>
       </c>
       <c r="L193" s="17" t="n"/>
@@ -16068,7 +16048,7 @@
       <c r="J194" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K194" s="225" t="n">
+      <c r="K194" s="224" t="n">
         <v>44904</v>
       </c>
       <c r="L194" s="17" t="n"/>
@@ -16115,7 +16095,7 @@
       </c>
       <c r="I195" s="28" t="n"/>
       <c r="J195" s="15" t="n"/>
-      <c r="K195" s="222" t="n"/>
+      <c r="K195" s="221" t="n"/>
       <c r="L195" s="17" t="n"/>
       <c r="M195" s="18" t="n"/>
     </row>
@@ -16166,7 +16146,7 @@
       <c r="J196" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K196" s="225" t="n">
+      <c r="K196" s="224" t="n">
         <v>44632</v>
       </c>
       <c r="L196" s="17" t="n"/>
@@ -16219,7 +16199,7 @@
       <c r="J197" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K197" s="225" t="n">
+      <c r="K197" s="224" t="n">
         <v>44764</v>
       </c>
       <c r="L197" s="17" t="n"/>
@@ -16272,7 +16252,7 @@
       <c r="J198" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K198" s="225" t="n">
+      <c r="K198" s="224" t="n">
         <v>44813</v>
       </c>
       <c r="L198" s="17" t="n"/>
@@ -16325,7 +16305,7 @@
       <c r="J199" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K199" s="225" t="n">
+      <c r="K199" s="224" t="n">
         <v>44856</v>
       </c>
       <c r="L199" s="17" t="n"/>
@@ -16378,7 +16358,7 @@
       <c r="J200" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K200" s="225" t="n">
+      <c r="K200" s="224" t="n">
         <v>44730</v>
       </c>
       <c r="L200" s="17" t="n"/>
@@ -16425,7 +16405,7 @@
       </c>
       <c r="I201" s="28" t="n"/>
       <c r="J201" s="15" t="n"/>
-      <c r="K201" s="222" t="n"/>
+      <c r="K201" s="221" t="n"/>
       <c r="L201" s="17" t="n"/>
       <c r="M201" s="18" t="n"/>
     </row>
@@ -16476,7 +16456,7 @@
       <c r="J202" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K202" s="225" t="n">
+      <c r="K202" s="224" t="n">
         <v>44872</v>
       </c>
       <c r="L202" s="17" t="n"/>
@@ -16529,7 +16509,7 @@
       <c r="J203" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K203" s="225" t="n">
+      <c r="K203" s="224" t="n">
         <v>44845</v>
       </c>
       <c r="L203" s="17" t="n"/>
@@ -16582,7 +16562,7 @@
       <c r="J204" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K204" s="225" t="n">
+      <c r="K204" s="224" t="n">
         <v>44688</v>
       </c>
       <c r="L204" s="17" t="n"/>
@@ -16635,7 +16615,7 @@
       <c r="J205" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K205" s="225" t="n">
+      <c r="K205" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L205" s="17" t="n"/>
@@ -16688,7 +16668,7 @@
       <c r="J206" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K206" s="225" t="n">
+      <c r="K206" s="224" t="n">
         <v>44593</v>
       </c>
       <c r="L206" s="17" t="n"/>
@@ -16735,7 +16715,7 @@
       </c>
       <c r="I207" s="28" t="n"/>
       <c r="J207" s="15" t="n"/>
-      <c r="K207" s="222" t="n"/>
+      <c r="K207" s="221" t="n"/>
       <c r="L207" s="26" t="inlineStr">
         <is>
           <t>未找到往年申请通知</t>
@@ -16794,7 +16774,7 @@
       <c r="J208" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K208" s="225" t="n">
+      <c r="K208" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L208" s="26" t="inlineStr">
@@ -16845,7 +16825,7 @@
       </c>
       <c r="I209" s="28" t="n"/>
       <c r="J209" s="15" t="n"/>
-      <c r="K209" s="222" t="n"/>
+      <c r="K209" s="221" t="n"/>
       <c r="L209" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -16900,7 +16880,7 @@
       <c r="J210" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K210" s="225" t="n">
+      <c r="K210" s="224" t="n">
         <v>44831</v>
       </c>
       <c r="L210" s="17" t="n"/>
@@ -16953,7 +16933,7 @@
       <c r="J211" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K211" s="225" t="n">
+      <c r="K211" s="224" t="n">
         <v>44815</v>
       </c>
       <c r="L211" s="17" t="n"/>
@@ -17006,7 +16986,7 @@
       <c r="J212" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K212" s="225" t="n">
+      <c r="K212" s="224" t="n">
         <v>44850</v>
       </c>
       <c r="L212" s="17" t="n"/>
@@ -17059,7 +17039,7 @@
       <c r="J213" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K213" s="225" t="n">
+      <c r="K213" s="224" t="n">
         <v>44845</v>
       </c>
       <c r="L213" s="17" t="n"/>
@@ -17112,7 +17092,7 @@
       <c r="J214" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K214" s="225" t="n">
+      <c r="K214" s="224" t="n">
         <v>44772</v>
       </c>
       <c r="L214" s="26" t="inlineStr">
@@ -17169,7 +17149,7 @@
       <c r="J215" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K215" s="225" t="n">
+      <c r="K215" s="224" t="n">
         <v>44896</v>
       </c>
       <c r="L215" s="17" t="n"/>
@@ -17222,7 +17202,7 @@
       <c r="J216" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K216" s="225" t="n">
+      <c r="K216" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L216" s="17" t="n"/>
@@ -17269,7 +17249,7 @@
       </c>
       <c r="I217" s="34" t="n"/>
       <c r="J217" s="15" t="n"/>
-      <c r="K217" s="222" t="n"/>
+      <c r="K217" s="221" t="n"/>
       <c r="L217" s="17" t="n"/>
       <c r="M217" s="18" t="n"/>
     </row>
@@ -17320,7 +17300,7 @@
       <c r="J218" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K218" s="225" t="n">
+      <c r="K218" s="224" t="n">
         <v>44843</v>
       </c>
       <c r="L218" s="17" t="n"/>
@@ -17373,7 +17353,7 @@
       <c r="J219" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K219" s="225" t="n">
+      <c r="K219" s="224" t="n">
         <v>44680</v>
       </c>
       <c r="L219" s="17" t="n"/>
@@ -17426,7 +17406,7 @@
       <c r="J220" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K220" s="225" t="n">
+      <c r="K220" s="224" t="n">
         <v>44722</v>
       </c>
       <c r="L220" s="17" t="n"/>
@@ -17479,7 +17459,7 @@
       <c r="J221" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K221" s="225" t="n">
+      <c r="K221" s="224" t="n">
         <v>44646</v>
       </c>
       <c r="L221" s="17" t="n"/>
@@ -17532,7 +17512,7 @@
       <c r="J222" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K222" s="225" t="n">
+      <c r="K222" s="224" t="n">
         <v>44637</v>
       </c>
       <c r="L222" s="17" t="n"/>
@@ -17585,7 +17565,7 @@
       <c r="J223" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K223" s="225" t="n">
+      <c r="K223" s="224" t="n">
         <v>44847</v>
       </c>
       <c r="L223" s="17" t="n"/>
@@ -17638,7 +17618,7 @@
       <c r="J224" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K224" s="225" t="n">
+      <c r="K224" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L224" s="17" t="n"/>
@@ -17691,7 +17671,7 @@
       <c r="J225" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K225" s="225" t="n">
+      <c r="K225" s="224" t="n">
         <v>44811</v>
       </c>
       <c r="L225" s="17" t="n"/>
@@ -17744,7 +17724,7 @@
       <c r="J226" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K226" s="225" t="n">
+      <c r="K226" s="224" t="n">
         <v>44857</v>
       </c>
       <c r="L226" s="17" t="n"/>
@@ -17797,28 +17777,28 @@
       <c r="J227" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K227" s="226" t="n">
+      <c r="K227" s="225" t="n">
         <v>44808</v>
       </c>
       <c r="L227" s="17" t="n"/>
       <c r="M227" s="18" t="n"/>
     </row>
     <row r="228" ht="24.75" customHeight="1" s="70">
-      <c r="A228" s="224" t="n"/>
-      <c r="B228" s="224" t="n"/>
-      <c r="C228" s="224" t="n"/>
+      <c r="A228" s="223" t="n"/>
+      <c r="B228" s="223" t="n"/>
+      <c r="C228" s="223" t="n"/>
       <c r="D228" s="12" t="inlineStr">
         <is>
           <t>南京水利科学研究院</t>
         </is>
       </c>
-      <c r="E228" s="224" t="n"/>
-      <c r="F228" s="224" t="n"/>
-      <c r="G228" s="224" t="n"/>
-      <c r="H228" s="224" t="n"/>
-      <c r="I228" s="224" t="n"/>
-      <c r="J228" s="224" t="n"/>
-      <c r="K228" s="224" t="n"/>
+      <c r="E228" s="223" t="n"/>
+      <c r="F228" s="223" t="n"/>
+      <c r="G228" s="223" t="n"/>
+      <c r="H228" s="223" t="n"/>
+      <c r="I228" s="223" t="n"/>
+      <c r="J228" s="223" t="n"/>
+      <c r="K228" s="223" t="n"/>
       <c r="L228" s="17" t="n"/>
       <c r="M228" s="18" t="n"/>
     </row>
@@ -17869,7 +17849,7 @@
       <c r="J229" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K229" s="225" t="n">
+      <c r="K229" s="224" t="n">
         <v>44846</v>
       </c>
       <c r="L229" s="17" t="n"/>
@@ -17909,7 +17889,7 @@
           <t>2008DA105277</t>
         </is>
       </c>
-      <c r="H230" s="236" t="inlineStr">
+      <c r="H230" s="235" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17922,28 +17902,28 @@
       <c r="J230" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K230" s="226" t="n">
+      <c r="K230" s="225" t="n">
         <v>44724</v>
       </c>
       <c r="L230" s="17" t="n"/>
       <c r="M230" s="18" t="n"/>
     </row>
     <row r="231" ht="24.75" customHeight="1" s="70">
-      <c r="A231" s="224" t="n"/>
-      <c r="B231" s="224" t="n"/>
-      <c r="C231" s="224" t="n"/>
+      <c r="A231" s="223" t="n"/>
+      <c r="B231" s="223" t="n"/>
+      <c r="C231" s="223" t="n"/>
       <c r="D231" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学（北京）</t>
         </is>
       </c>
-      <c r="E231" s="224" t="n"/>
-      <c r="F231" s="224" t="n"/>
-      <c r="G231" s="224" t="n"/>
-      <c r="H231" s="224" t="n"/>
-      <c r="I231" s="224" t="n"/>
-      <c r="J231" s="224" t="n"/>
-      <c r="K231" s="224" t="n"/>
+      <c r="E231" s="223" t="n"/>
+      <c r="F231" s="223" t="n"/>
+      <c r="G231" s="223" t="n"/>
+      <c r="H231" s="223" t="n"/>
+      <c r="I231" s="223" t="n"/>
+      <c r="J231" s="223" t="n"/>
+      <c r="K231" s="223" t="n"/>
       <c r="L231" s="17" t="n"/>
       <c r="M231" s="18" t="n"/>
     </row>
@@ -17994,7 +17974,7 @@
       <c r="J232" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K232" s="225" t="n">
+      <c r="K232" s="224" t="n">
         <v>44828</v>
       </c>
       <c r="L232" s="17" t="n"/>
@@ -18047,7 +18027,7 @@
       <c r="J233" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K233" s="225" t="n">
+      <c r="K233" s="224" t="n">
         <v>44833</v>
       </c>
       <c r="L233" s="17" t="n"/>
@@ -18094,7 +18074,7 @@
       </c>
       <c r="I234" s="34" t="n"/>
       <c r="J234" s="15" t="n"/>
-      <c r="K234" s="222" t="n"/>
+      <c r="K234" s="221" t="n"/>
       <c r="L234" s="17" t="n"/>
       <c r="M234" s="18" t="n"/>
     </row>
@@ -18145,7 +18125,7 @@
       <c r="J235" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K235" s="225" t="n">
+      <c r="K235" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L235" s="26" t="inlineStr">
@@ -18202,7 +18182,7 @@
       <c r="J236" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K236" s="225" t="n">
+      <c r="K236" s="224" t="n">
         <v>44622</v>
       </c>
       <c r="L236" s="17" t="n"/>
@@ -18255,7 +18235,7 @@
       <c r="J237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K237" s="225" t="n">
+      <c r="K237" s="224" t="n">
         <v>44689</v>
       </c>
       <c r="L237" s="17" t="n"/>
@@ -18308,7 +18288,7 @@
       <c r="J238" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K238" s="225" t="n">
+      <c r="K238" s="224" t="n">
         <v>44861</v>
       </c>
       <c r="L238" s="17" t="n"/>
@@ -18361,7 +18341,7 @@
       <c r="J239" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K239" s="225" t="n">
+      <c r="K239" s="224" t="n">
         <v>44826</v>
       </c>
       <c r="L239" s="17" t="n"/>
@@ -18408,7 +18388,7 @@
       </c>
       <c r="I240" s="28" t="n"/>
       <c r="J240" s="15" t="n"/>
-      <c r="K240" s="222" t="n"/>
+      <c r="K240" s="221" t="n"/>
       <c r="L240" s="26" t="inlineStr">
         <is>
           <t>未找到相关往年通知</t>
@@ -18467,7 +18447,7 @@
       <c r="J241" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K241" s="225" t="n">
+      <c r="K241" s="224" t="n">
         <v>44848</v>
       </c>
       <c r="L241" s="17" t="n"/>
@@ -18520,7 +18500,7 @@
       <c r="J242" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K242" s="225" t="n">
+      <c r="K242" s="224" t="n">
         <v>44820</v>
       </c>
       <c r="L242" s="17" t="n"/>
@@ -18573,7 +18553,7 @@
       <c r="J243" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K243" s="225" t="n">
+      <c r="K243" s="224" t="n">
         <v>44699</v>
       </c>
       <c r="L243" s="17" t="n"/>
@@ -18626,7 +18606,7 @@
       <c r="J244" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="225" t="n">
+      <c r="K244" s="224" t="n">
         <v>44743</v>
       </c>
       <c r="L244" s="26" t="inlineStr">
@@ -18683,7 +18663,7 @@
       <c r="J245" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K245" s="225" t="n">
+      <c r="K245" s="224" t="n">
         <v>44741</v>
       </c>
       <c r="L245" s="17" t="n"/>
@@ -18736,7 +18716,7 @@
       <c r="J246" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K246" s="225" t="n">
+      <c r="K246" s="224" t="n">
         <v>44771</v>
       </c>
       <c r="L246" s="17" t="n"/>
@@ -18789,7 +18769,7 @@
       <c r="J247" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K247" s="225" t="n">
+      <c r="K247" s="224" t="n">
         <v>44859</v>
       </c>
       <c r="L247" s="17" t="n"/>
@@ -18842,7 +18822,7 @@
       <c r="J248" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K248" s="225" t="n">
+      <c r="K248" s="224" t="n">
         <v>44815</v>
       </c>
       <c r="L248" s="17" t="n"/>
@@ -18895,7 +18875,7 @@
       <c r="J249" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K249" s="225" t="n">
+      <c r="K249" s="224" t="n">
         <v>44742</v>
       </c>
       <c r="L249" s="26" t="inlineStr">
@@ -18946,7 +18926,7 @@
       </c>
       <c r="I250" s="28" t="n"/>
       <c r="J250" s="15" t="n"/>
-      <c r="K250" s="222" t="n"/>
+      <c r="K250" s="221" t="n"/>
       <c r="L250" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -19001,7 +18981,7 @@
       <c r="J251" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K251" s="225" t="n">
+      <c r="K251" s="224" t="n">
         <v>44805</v>
       </c>
       <c r="L251" s="26" t="inlineStr">
@@ -19056,7 +19036,7 @@
       </c>
       <c r="I252" s="28" t="n"/>
       <c r="J252" s="15" t="n"/>
-      <c r="K252" s="222" t="n"/>
+      <c r="K252" s="221" t="n"/>
       <c r="L252" s="17" t="n"/>
       <c r="M252" s="18" t="n"/>
     </row>
@@ -19107,7 +19087,7 @@
       <c r="J253" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K253" s="225" t="n">
+      <c r="K253" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L253" s="17" t="n"/>
@@ -19154,7 +19134,7 @@
       </c>
       <c r="I254" s="28" t="n"/>
       <c r="J254" s="15" t="n"/>
-      <c r="K254" s="222" t="n"/>
+      <c r="K254" s="221" t="n"/>
       <c r="L254" s="17" t="n"/>
       <c r="M254" s="18" t="n"/>
     </row>
@@ -19199,7 +19179,7 @@
       </c>
       <c r="I255" s="28" t="n"/>
       <c r="J255" s="15" t="n"/>
-      <c r="K255" s="222" t="n"/>
+      <c r="K255" s="221" t="n"/>
       <c r="L255" s="17" t="n"/>
       <c r="M255" s="18" t="n"/>
     </row>
@@ -19244,7 +19224,7 @@
       </c>
       <c r="I256" s="28" t="n"/>
       <c r="J256" s="15" t="n"/>
-      <c r="K256" s="222" t="n"/>
+      <c r="K256" s="221" t="n"/>
       <c r="L256" s="17" t="n"/>
       <c r="M256" s="18" t="n"/>
     </row>
@@ -19295,7 +19275,7 @@
       <c r="J257" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K257" s="225" t="n">
+      <c r="K257" s="224" t="n">
         <v>44562</v>
       </c>
       <c r="L257" s="17" t="n"/>
@@ -19348,7 +19328,7 @@
       <c r="J258" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K258" s="225" t="n">
+      <c r="K258" s="224" t="n">
         <v>44665</v>
       </c>
       <c r="L258" s="17" t="n"/>
@@ -19401,7 +19381,7 @@
       <c r="J259" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K259" s="225" t="n">
+      <c r="K259" s="224" t="n">
         <v>44882</v>
       </c>
       <c r="L259" s="17" t="n"/>
@@ -19448,7 +19428,7 @@
       </c>
       <c r="I260" s="28" t="n"/>
       <c r="J260" s="15" t="n"/>
-      <c r="K260" s="222" t="n"/>
+      <c r="K260" s="221" t="n"/>
       <c r="L260" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -19497,7 +19477,7 @@
       </c>
       <c r="I261" s="34" t="n"/>
       <c r="J261" s="15" t="n"/>
-      <c r="K261" s="222" t="n"/>
+      <c r="K261" s="221" t="n"/>
       <c r="L261" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -19546,7 +19526,7 @@
       </c>
       <c r="I262" s="28" t="n"/>
       <c r="J262" s="15" t="n"/>
-      <c r="K262" s="222" t="n"/>
+      <c r="K262" s="221" t="n"/>
       <c r="L262" s="17" t="n"/>
       <c r="M262" s="18" t="n"/>
     </row>
@@ -19591,7 +19571,7 @@
       </c>
       <c r="I263" s="28" t="n"/>
       <c r="J263" s="15" t="n"/>
-      <c r="K263" s="222" t="n"/>
+      <c r="K263" s="221" t="n"/>
       <c r="L263" s="17" t="n"/>
       <c r="M263" s="18" t="n"/>
     </row>
@@ -19642,7 +19622,7 @@
       <c r="J264" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K264" s="225" t="n">
+      <c r="K264" s="224" t="n">
         <v>44667</v>
       </c>
       <c r="L264" s="26" t="n">
@@ -19697,7 +19677,7 @@
       <c r="J265" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K265" s="225" t="n">
+      <c r="K265" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L265" s="17" t="n"/>
@@ -19748,7 +19728,7 @@
         </is>
       </c>
       <c r="J266" s="15" t="n"/>
-      <c r="K266" s="222" t="n"/>
+      <c r="K266" s="221" t="n"/>
       <c r="L266" s="26" t="inlineStr">
         <is>
           <t>相关通知最近的是2014年的</t>
@@ -19803,7 +19783,7 @@
       <c r="J267" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K267" s="225" t="n">
+      <c r="K267" s="224" t="n">
         <v>44731</v>
       </c>
       <c r="L267" s="17" t="n"/>
@@ -19850,7 +19830,7 @@
       </c>
       <c r="I268" s="28" t="n"/>
       <c r="J268" s="15" t="n"/>
-      <c r="K268" s="222" t="n"/>
+      <c r="K268" s="221" t="n"/>
       <c r="L268" s="17" t="n"/>
       <c r="M268" s="18" t="n"/>
     </row>
@@ -19901,7 +19881,7 @@
       <c r="J269" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K269" s="225" t="n">
+      <c r="K269" s="224" t="n">
         <v>44905</v>
       </c>
       <c r="L269" s="17" t="n"/>
@@ -19954,7 +19934,7 @@
       <c r="J270" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K270" s="225" t="n">
+      <c r="K270" s="224" t="n">
         <v>44721</v>
       </c>
       <c r="L270" s="26" t="inlineStr">
@@ -20005,7 +19985,7 @@
       </c>
       <c r="I271" s="28" t="n"/>
       <c r="J271" s="15" t="n"/>
-      <c r="K271" s="222" t="n"/>
+      <c r="K271" s="221" t="n"/>
       <c r="L271" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20054,7 +20034,7 @@
       </c>
       <c r="I272" s="28" t="n"/>
       <c r="J272" s="15" t="n"/>
-      <c r="K272" s="222" t="n"/>
+      <c r="K272" s="221" t="n"/>
       <c r="L272" s="17" t="n"/>
       <c r="M272" s="18" t="n"/>
     </row>
@@ -20099,7 +20079,7 @@
       </c>
       <c r="I273" s="28" t="n"/>
       <c r="J273" s="15" t="n"/>
-      <c r="K273" s="222" t="n"/>
+      <c r="K273" s="221" t="n"/>
       <c r="L273" s="17" t="n"/>
       <c r="M273" s="18" t="n"/>
     </row>
@@ -20144,7 +20124,7 @@
       </c>
       <c r="I274" s="28" t="n"/>
       <c r="J274" s="15" t="n"/>
-      <c r="K274" s="222" t="n"/>
+      <c r="K274" s="221" t="n"/>
       <c r="L274" s="17" t="n"/>
       <c r="M274" s="18" t="n"/>
     </row>
@@ -20195,7 +20175,7 @@
       <c r="J275" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K275" s="225" t="n">
+      <c r="K275" s="224" t="n">
         <v>44746</v>
       </c>
       <c r="L275" s="26" t="inlineStr">
@@ -20252,7 +20232,7 @@
       <c r="J276" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K276" s="225" t="n">
+      <c r="K276" s="224" t="n">
         <v>44866</v>
       </c>
       <c r="L276" s="17" t="n"/>
@@ -20299,7 +20279,7 @@
       </c>
       <c r="I277" s="28" t="n"/>
       <c r="J277" s="15" t="n"/>
-      <c r="K277" s="222" t="n"/>
+      <c r="K277" s="221" t="n"/>
       <c r="L277" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20354,7 +20334,7 @@
       <c r="J278" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K278" s="225" t="n">
+      <c r="K278" s="224" t="n">
         <v>44652</v>
       </c>
       <c r="L278" s="17" t="n"/>
@@ -20403,7 +20383,7 @@
       <c r="J279" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K279" s="225" t="n">
+      <c r="K279" s="224" t="n">
         <v>44599</v>
       </c>
       <c r="L279" s="26" t="inlineStr">
@@ -20458,7 +20438,7 @@
       </c>
       <c r="I280" s="34" t="n"/>
       <c r="J280" s="15" t="n"/>
-      <c r="K280" s="222" t="n"/>
+      <c r="K280" s="221" t="n"/>
       <c r="L280" s="17" t="n"/>
       <c r="M280" s="18" t="n"/>
     </row>
@@ -20509,7 +20489,7 @@
       <c r="J281" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K281" s="225" t="n">
+      <c r="K281" s="224" t="n">
         <v>44855</v>
       </c>
       <c r="L281" s="17" t="n"/>
@@ -20562,7 +20542,7 @@
       <c r="J282" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K282" s="225" t="n">
+      <c r="K282" s="224" t="n">
         <v>44569</v>
       </c>
       <c r="L282" s="26" t="inlineStr">
@@ -20613,7 +20593,7 @@
       </c>
       <c r="I283" s="28" t="n"/>
       <c r="J283" s="15" t="n"/>
-      <c r="K283" s="222" t="n"/>
+      <c r="K283" s="221" t="n"/>
       <c r="L283" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -20668,7 +20648,7 @@
       <c r="J284" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K284" s="225" t="n">
+      <c r="K284" s="224" t="n">
         <v>44581</v>
       </c>
       <c r="L284" s="17" t="n"/>
@@ -20715,7 +20695,7 @@
       </c>
       <c r="I285" s="28" t="n"/>
       <c r="J285" s="15" t="n"/>
-      <c r="K285" s="222" t="n"/>
+      <c r="K285" s="221" t="n"/>
       <c r="L285" s="17" t="n"/>
       <c r="M285" s="18" t="n"/>
     </row>
@@ -20760,7 +20740,7 @@
       </c>
       <c r="I286" s="28" t="n"/>
       <c r="J286" s="15" t="n"/>
-      <c r="K286" s="222" t="n"/>
+      <c r="K286" s="221" t="n"/>
       <c r="L286" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20811,7 +20791,7 @@
       <c r="J287" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K287" s="225" t="n">
+      <c r="K287" s="224" t="n">
         <v>44923</v>
       </c>
       <c r="L287" s="58" t="n"/>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -1063,7 +1063,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1630,29 +1630,35 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1660,9 +1666,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2678,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-17）</t>
+          <t>最新更新（2026-10-18）</t>
         </is>
       </c>
     </row>
@@ -2731,96 +2734,130 @@
       <c r="J3" s="148" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="190" t="n">
+      <c r="A4" s="194" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="189" t="inlineStr">
+      <c r="B4" s="195" t="n"/>
+      <c r="C4" s="196" t="inlineStr">
         <is>
           <t>国自然面上项目</t>
         </is>
       </c>
-      <c r="D4" s="175" t="inlineStr">
+      <c r="D4" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E4" s="152" t="inlineStr">
+      <c r="E4" s="198" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（主申/参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F4" s="189" t="inlineStr">
+      <c r="F4" s="196" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为4年</t>
         </is>
       </c>
-      <c r="G4" s="189" t="inlineStr">
+      <c r="G4" s="196" t="inlineStr">
         <is>
           <t>平均资助强度
 约50万</t>
         </is>
       </c>
-      <c r="H4" s="190" t="inlineStr">
+      <c r="H4" s="194" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I4" s="155" t="inlineStr">
+      <c r="I4" s="199" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3976/msxm22.html</t>
         </is>
       </c>
-      <c r="J4" s="148" t="n"/>
+      <c r="J4" s="200" t="n"/>
+      <c r="K4" s="195" t="n"/>
+      <c r="L4" s="195" t="n"/>
+      <c r="M4" s="195" t="n"/>
+      <c r="N4" s="195" t="n"/>
+      <c r="O4" s="195" t="n"/>
+      <c r="P4" s="195" t="n"/>
+      <c r="Q4" s="195" t="n"/>
+      <c r="R4" s="195" t="n"/>
+      <c r="S4" s="195" t="n"/>
+      <c r="T4" s="195" t="n"/>
+      <c r="U4" s="195" t="n"/>
+      <c r="V4" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：关于发布2026年度国家自然科学基金“面向低空经济前沿的基础研究”专项项目申请指南...（2026-09-30）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="190" t="n">
+      <c r="A5" s="194" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="189" t="inlineStr">
+      <c r="B5" s="195" t="n"/>
+      <c r="C5" s="196" t="inlineStr">
         <is>
           <t>国自然重点项目</t>
         </is>
       </c>
-      <c r="D5" s="175" t="inlineStr">
+      <c r="D5" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="152" t="inlineStr">
+      <c r="E5" s="198" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F5" s="189" t="inlineStr">
+      <c r="F5" s="196" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为5年</t>
         </is>
       </c>
-      <c r="G5" s="189" t="inlineStr">
+      <c r="G5" s="196" t="inlineStr">
         <is>
           <t>平均资助强度
 约220万</t>
         </is>
       </c>
-      <c r="H5" s="190" t="inlineStr">
+      <c r="H5" s="194" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I5" s="155" t="inlineStr">
+      <c r="I5" s="199" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3979/zdxm222.html</t>
         </is>
       </c>
-      <c r="J5" s="148" t="n"/>
+      <c r="J5" s="200" t="n"/>
+      <c r="K5" s="195" t="n"/>
+      <c r="L5" s="195" t="n"/>
+      <c r="M5" s="195" t="n"/>
+      <c r="N5" s="195" t="n"/>
+      <c r="O5" s="195" t="n"/>
+      <c r="P5" s="195" t="n"/>
+      <c r="Q5" s="195" t="n"/>
+      <c r="R5" s="195" t="n"/>
+      <c r="S5" s="195" t="n"/>
+      <c r="T5" s="195" t="n"/>
+      <c r="U5" s="195" t="n"/>
+      <c r="V5" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：关于征集2028年度自治区自然科学基金重点项目指南建议的通知（2026-10-14）</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="76" customHeight="1" s="70">
       <c r="A6" s="190" t="n">
@@ -2966,7 +3003,7 @@
       <c r="A9" s="190" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="194" t="n"/>
+      <c r="B9" s="202" t="n"/>
       <c r="C9" s="161" t="inlineStr">
         <is>
           <t>国家科技部重大研发计划</t>
@@ -3156,49 +3193,66 @@
       <c r="J12" s="148" t="n"/>
     </row>
     <row r="13" ht="111" customHeight="1" s="70">
-      <c r="A13" s="190" t="n">
+      <c r="A13" s="194" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="189" t="inlineStr">
+      <c r="B13" s="195" t="n"/>
+      <c r="C13" s="196" t="inlineStr">
         <is>
           <t>广东省量子科学战略专项项目申报指南</t>
         </is>
       </c>
-      <c r="D13" s="175" t="inlineStr">
+      <c r="D13" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E13" s="152" t="inlineStr">
+      <c r="E13" s="198" t="inlineStr">
         <is>
           <t>澳大教授（主申）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F13" s="189" t="inlineStr">
+      <c r="F13" s="196" t="inlineStr">
         <is>
           <t>重大和重点项目的申报材料应围绕相应指南内容，合理设置课题分工并突出重点，无须覆盖全部研究内容及考核指标。一般类项目以研究领域为导向，资助探索性强、选题新颖、前期研究基础较好的申请项目，优先支持但不限于指南提出的科学问题。项目负责人须全职来自依托单位。</t>
         </is>
       </c>
-      <c r="G13" s="189" t="inlineStr">
+      <c r="G13" s="196" t="inlineStr">
         <is>
           <t>1.重大类项目资助强度约为800万-1000万元/项，项目执行期为5年
 2.重点类项目资助强度约为200万元/项，项目执行期均为3年
 3.一般类项目资助强度不超过50万元/项，项目执行期均为3年</t>
         </is>
       </c>
-      <c r="H13" s="190" t="inlineStr">
+      <c r="H13" s="194" t="inlineStr">
         <is>
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I13" s="169" t="inlineStr">
+      <c r="I13" s="203" t="inlineStr">
         <is>
           <t>https://www.qscgba.org.cn/#/declare/view?alias=48fc5053-c7c2-40b0-b3c7-37e7d5e60ce0</t>
         </is>
       </c>
-      <c r="J13" s="148" t="n"/>
+      <c r="J13" s="200" t="n"/>
+      <c r="K13" s="195" t="n"/>
+      <c r="L13" s="195" t="n"/>
+      <c r="M13" s="195" t="n"/>
+      <c r="N13" s="195" t="n"/>
+      <c r="O13" s="195" t="n"/>
+      <c r="P13" s="195" t="n"/>
+      <c r="Q13" s="195" t="n"/>
+      <c r="R13" s="195" t="n"/>
+      <c r="S13" s="195" t="n"/>
+      <c r="T13" s="195" t="n"/>
+      <c r="U13" s="195" t="n"/>
+      <c r="V13" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：广东省科学技术厅关于转发2027年度广东省量子科学战略专项项目申报指南的通知（2026-10-15）</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="128" customFormat="1" customHeight="1" s="141">
       <c r="A14" s="190" t="n">
@@ -3391,16 +3445,16 @@
       <c r="J17" s="148" t="n"/>
     </row>
     <row r="18" ht="66" customHeight="1" s="70">
-      <c r="A18" s="195" t="n">
+      <c r="A18" s="194" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="196" t="n"/>
-      <c r="C18" s="197" t="inlineStr">
+      <c r="B18" s="197" t="n"/>
+      <c r="C18" s="196" t="inlineStr">
         <is>
           <t>国家重点研发计划“战略性科技创新合作”重点专项</t>
         </is>
       </c>
-      <c r="D18" s="196" t="inlineStr">
+      <c r="D18" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3410,39 +3464,39 @@
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F18" s="197" t="inlineStr">
+      <c r="F18" s="196" t="inlineStr">
         <is>
           <t>国家重点研发计划、国家科技重大专项、国家自然科学基金委有关类型项目实施联合限项，按照要求，对项目（课题）负责人等人员进行联合审查，科研人员同期申请和承担的项目（课题）数原则上不得超过2项。</t>
         </is>
       </c>
-      <c r="G18" s="197" t="inlineStr">
+      <c r="G18" s="196" t="inlineStr">
         <is>
           <t>200万元—400万元</t>
         </is>
       </c>
-      <c r="H18" s="196" t="inlineStr">
+      <c r="H18" s="197" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I18" s="199" t="inlineStr">
+      <c r="I18" s="204" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/20260828/5864.html</t>
         </is>
       </c>
       <c r="J18" s="200" t="n"/>
-      <c r="K18" s="201" t="n"/>
-      <c r="L18" s="201" t="n"/>
-      <c r="M18" s="201" t="n"/>
-      <c r="N18" s="201" t="n"/>
-      <c r="O18" s="201" t="n"/>
-      <c r="P18" s="201" t="n"/>
-      <c r="Q18" s="201" t="n"/>
-      <c r="R18" s="201" t="n"/>
-      <c r="S18" s="201" t="n"/>
-      <c r="T18" s="201" t="n"/>
-      <c r="U18" s="201" t="n"/>
-      <c r="V18" s="202" t="inlineStr">
+      <c r="K18" s="195" t="n"/>
+      <c r="L18" s="195" t="n"/>
+      <c r="M18" s="195" t="n"/>
+      <c r="N18" s="195" t="n"/>
+      <c r="O18" s="195" t="n"/>
+      <c r="P18" s="195" t="n"/>
+      <c r="Q18" s="195" t="n"/>
+      <c r="R18" s="195" t="n"/>
+      <c r="S18" s="195" t="n"/>
+      <c r="T18" s="195" t="n"/>
+      <c r="U18" s="195" t="n"/>
+      <c r="V18" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度联合研发与示范项目指南2026-09-01发布，港澳单位可承担课题，受聘内地单位的港澳科学家可作负责人</t>
         </is>
@@ -3495,58 +3549,58 @@
       <c r="J19" s="148" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1" s="70">
-      <c r="A20" s="195" t="n">
+      <c r="A20" s="194" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="201" t="n"/>
-      <c r="C20" s="197" t="inlineStr">
+      <c r="B20" s="195" t="n"/>
+      <c r="C20" s="196" t="inlineStr">
         <is>
           <t>粤澳科技创新联合资助专题-粤澳联合资助项目</t>
         </is>
       </c>
-      <c r="D20" s="196" t="inlineStr">
+      <c r="D20" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E20" s="196" t="inlineStr">
+      <c r="E20" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F20" s="203" t="inlineStr">
+      <c r="F20" s="205" t="inlineStr">
         <is>
           <t>由广东省科学技术厅和澳门科学技术发展基金联合征集、联合评审、联合资助。支持广东省创新主体联合澳门合作伙伴，在生物医药、新一代信息技术、节能环保、海洋科技、新材料、新能源、智能制造等涉及两地民生发展和前沿科技的领域开展联合技术研发及成果产业化合作。本专题优先支持在横琴、南沙等重大合作平台实施或落地转化的项目。</t>
         </is>
       </c>
-      <c r="G20" s="204" t="inlineStr">
+      <c r="G20" s="206" t="inlineStr">
         <is>
           <t>100万/项</t>
         </is>
       </c>
-      <c r="H20" s="195" t="inlineStr">
+      <c r="H20" s="194" t="inlineStr">
         <is>
           <t>11月-次年1月</t>
         </is>
       </c>
-      <c r="I20" s="205" t="inlineStr">
+      <c r="I20" s="207" t="inlineStr">
         <is>
           <t>https://gdstc.gd.gov.cn/zwgk_n/tzgg/content/post_4806341.html</t>
         </is>
       </c>
       <c r="J20" s="200" t="n"/>
-      <c r="K20" s="201" t="n"/>
-      <c r="L20" s="201" t="n"/>
-      <c r="M20" s="201" t="n"/>
-      <c r="N20" s="201" t="n"/>
-      <c r="O20" s="201" t="n"/>
-      <c r="P20" s="201" t="n"/>
-      <c r="Q20" s="201" t="n"/>
-      <c r="R20" s="201" t="n"/>
-      <c r="S20" s="201" t="n"/>
-      <c r="T20" s="201" t="n"/>
-      <c r="U20" s="201" t="n"/>
-      <c r="V20" s="202" t="inlineStr">
+      <c r="K20" s="195" t="n"/>
+      <c r="L20" s="195" t="n"/>
+      <c r="M20" s="195" t="n"/>
+      <c r="N20" s="195" t="n"/>
+      <c r="O20" s="195" t="n"/>
+      <c r="P20" s="195" t="n"/>
+      <c r="Q20" s="195" t="n"/>
+      <c r="R20" s="195" t="n"/>
+      <c r="S20" s="195" t="n"/>
+      <c r="T20" s="195" t="n"/>
+      <c r="U20" s="195" t="n"/>
+      <c r="V20" s="201" t="inlineStr">
         <is>
           <t>● 更新：2027年度申报指南已发布（2026-09-18），网上申报至2026-11-17 17:00，主管部门推荐截止11-24；粤科函资字〔2026〕1587号</t>
         </is>
@@ -3596,59 +3650,59 @@
       <c r="J21" s="148" t="n"/>
     </row>
     <row r="22" ht="148" customHeight="1" s="70">
-      <c r="A22" s="195" t="n">
+      <c r="A22" s="194" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="201" t="n"/>
-      <c r="C22" s="197" t="inlineStr">
+      <c r="B22" s="195" t="n"/>
+      <c r="C22" s="196" t="inlineStr">
         <is>
           <t>深圳市深港澳科技计划项目（C类项目）</t>
         </is>
       </c>
-      <c r="D22" s="196" t="inlineStr">
+      <c r="D22" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E22" s="196" t="inlineStr">
+      <c r="E22" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F22" s="197" t="inlineStr">
+      <c r="F22" s="196" t="inlineStr">
         <is>
           <t>深港澳科技计划C类项目由香港、澳门申请单位提出申请，深圳市科技创新局进行评审和资助，深圳市财政资助资金直接拨付至香港、澳门申请单位账户。
 重点支持领域（2025）：网络与通信、半导体与集成电路、软件与信息服务、人工智能、高端装备与仪器、低空经济与空天、机器人、高性能材料、生物医药、海洋、合成生物、智能机器人、脑科学与脑机工程等。</t>
         </is>
       </c>
-      <c r="G22" s="204" t="inlineStr">
+      <c r="G22" s="206" t="inlineStr">
         <is>
           <t>资助强度300万</t>
         </is>
       </c>
-      <c r="H22" s="195" t="inlineStr">
+      <c r="H22" s="194" t="inlineStr">
         <is>
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I22" s="206" t="inlineStr">
+      <c r="I22" s="203" t="inlineStr">
         <is>
           <t>https://stic.sz.gov.cn/xxgk/tzgg/content/post_12116696.html?sessionid=</t>
         </is>
       </c>
       <c r="J22" s="200" t="n"/>
-      <c r="K22" s="201" t="n"/>
-      <c r="L22" s="201" t="n"/>
-      <c r="M22" s="201" t="n"/>
-      <c r="N22" s="201" t="n"/>
-      <c r="O22" s="201" t="n"/>
-      <c r="P22" s="201" t="n"/>
-      <c r="Q22" s="201" t="n"/>
-      <c r="R22" s="201" t="n"/>
-      <c r="S22" s="201" t="n"/>
-      <c r="T22" s="201" t="n"/>
-      <c r="U22" s="201" t="n"/>
-      <c r="V22" s="202" t="inlineStr">
+      <c r="K22" s="195" t="n"/>
+      <c r="L22" s="195" t="n"/>
+      <c r="M22" s="195" t="n"/>
+      <c r="N22" s="195" t="n"/>
+      <c r="O22" s="195" t="n"/>
+      <c r="P22" s="195" t="n"/>
+      <c r="Q22" s="195" t="n"/>
+      <c r="R22" s="195" t="n"/>
+      <c r="S22" s="195" t="n"/>
+      <c r="T22" s="195" t="n"/>
+      <c r="U22" s="195" t="n"/>
+      <c r="V22" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026-06-05印发《深港澳科技计划项目管理办法》，A类须获香港ITC或澳门FDCT评审通过方可立项</t>
         </is>
@@ -3700,121 +3754,121 @@
       </c>
     </row>
     <row r="24" ht="70.5" customHeight="1" s="70">
-      <c r="A24" s="195" t="n">
+      <c r="A24" s="194" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="201" t="n"/>
-      <c r="C24" s="197" t="inlineStr">
+      <c r="B24" s="195" t="n"/>
+      <c r="C24" s="196" t="inlineStr">
         <is>
           <t>四川省国际科技创新/港澳台科技创新合作项目</t>
         </is>
       </c>
-      <c r="D24" s="196" t="inlineStr">
+      <c r="D24" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E24" s="196" t="inlineStr">
+      <c r="E24" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F24" s="197" t="inlineStr">
+      <c r="F24" s="196" t="inlineStr">
         <is>
           <t>支持省内高校、科研机构及企业与香港特区、澳门特区、台湾地区开展科技创新合作，结合基础研究和应用技术战略性发展需求，开展联合研发。</t>
         </is>
       </c>
-      <c r="G24" s="204" t="inlineStr">
+      <c r="G24" s="206" t="inlineStr">
         <is>
           <t>30万元-100万元</t>
         </is>
       </c>
-      <c r="H24" s="195" t="inlineStr">
+      <c r="H24" s="194" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I24" s="206" t="inlineStr">
+      <c r="I24" s="203" t="inlineStr">
         <is>
           <t>https://kjt.sc.gov.cn/kjt/gstz/2025/9/17/1959a2ee35844389a80b43eb99950708.shtml</t>
         </is>
       </c>
       <c r="J24" s="200" t="n"/>
-      <c r="K24" s="201" t="n"/>
-      <c r="L24" s="201" t="n"/>
-      <c r="M24" s="201" t="n"/>
-      <c r="N24" s="201" t="n"/>
-      <c r="O24" s="201" t="n"/>
-      <c r="P24" s="201" t="n"/>
-      <c r="Q24" s="201" t="n"/>
-      <c r="R24" s="201" t="n"/>
-      <c r="S24" s="201" t="n"/>
-      <c r="T24" s="201" t="n"/>
-      <c r="U24" s="201" t="n"/>
-      <c r="V24" s="202" t="inlineStr">
+      <c r="K24" s="195" t="n"/>
+      <c r="L24" s="195" t="n"/>
+      <c r="M24" s="195" t="n"/>
+      <c r="N24" s="195" t="n"/>
+      <c r="O24" s="195" t="n"/>
+      <c r="P24" s="195" t="n"/>
+      <c r="Q24" s="195" t="n"/>
+      <c r="R24" s="195" t="n"/>
+      <c r="S24" s="195" t="n"/>
+      <c r="T24" s="195" t="n"/>
+      <c r="U24" s="195" t="n"/>
+      <c r="V24" s="201" t="inlineStr">
         <is>
           <t>● 更新：2027年度需求征集已完成，指南适时发布；2026年度项目2025-09已发布</t>
         </is>
       </c>
     </row>
     <row r="25" ht="63.75" customHeight="1" s="70">
-      <c r="A25" s="195" t="n">
+      <c r="A25" s="194" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="201" t="n"/>
-      <c r="C25" s="197" t="inlineStr">
+      <c r="B25" s="195" t="n"/>
+      <c r="C25" s="196" t="inlineStr">
         <is>
           <t>江苏省国际科技合作/ 港澳台科技合作计划项目</t>
         </is>
       </c>
-      <c r="D25" s="196" t="inlineStr">
+      <c r="D25" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E25" s="196" t="inlineStr">
+      <c r="E25" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F25" s="197" t="inlineStr">
+      <c r="F25" s="196" t="inlineStr">
         <is>
           <t>专题五：港澳台科技合作项目
 重点支持的技术领域：生命健康、人工智能、先进材料等。</t>
         </is>
       </c>
-      <c r="G25" s="197" t="inlineStr">
+      <c r="G25" s="196" t="inlineStr">
         <is>
           <t>省资助经费每项原则上不超过80万元，且不超过项目江苏方总预算的50%。</t>
         </is>
       </c>
-      <c r="H25" s="195" t="inlineStr">
+      <c r="H25" s="194" t="inlineStr">
         <is>
           <t>3-4月</t>
         </is>
       </c>
-      <c r="I25" s="206" t="inlineStr">
+      <c r="I25" s="203" t="inlineStr">
         <is>
           <t>https://kxjst.jiangsu.gov.cn/art/2026/4/1/art_82568_11752538.html</t>
         </is>
       </c>
-      <c r="J25" s="207" t="n"/>
-      <c r="K25" s="201" t="inlineStr">
+      <c r="J25" s="208" t="n"/>
+      <c r="K25" s="195" t="inlineStr">
         <is>
           <t>这个不要了？</t>
         </is>
       </c>
-      <c r="L25" s="201" t="n"/>
-      <c r="M25" s="201" t="n"/>
-      <c r="N25" s="201" t="n"/>
-      <c r="O25" s="201" t="n"/>
-      <c r="P25" s="201" t="n"/>
-      <c r="Q25" s="201" t="n"/>
-      <c r="R25" s="201" t="n"/>
-      <c r="S25" s="201" t="n"/>
-      <c r="T25" s="201" t="n"/>
-      <c r="U25" s="201" t="n"/>
-      <c r="V25" s="202" t="inlineStr">
+      <c r="L25" s="195" t="n"/>
+      <c r="M25" s="195" t="n"/>
+      <c r="N25" s="195" t="n"/>
+      <c r="O25" s="195" t="n"/>
+      <c r="P25" s="195" t="n"/>
+      <c r="Q25" s="195" t="n"/>
+      <c r="R25" s="195" t="n"/>
+      <c r="S25" s="195" t="n"/>
+      <c r="T25" s="195" t="n"/>
+      <c r="U25" s="195" t="n"/>
+      <c r="V25" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度申报中（苏科资发〔2026〕26号），长三角—新加坡第五轮网上填报截止2026-10-12 17:30</t>
         </is>
@@ -3907,21 +3961,21 @@
       <c r="J27" s="85" t="n"/>
     </row>
     <row r="28" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A28" s="195" t="n">
+      <c r="A28" s="194" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="201" t="n"/>
-      <c r="C28" s="197" t="inlineStr">
+      <c r="B28" s="195" t="n"/>
+      <c r="C28" s="196" t="inlineStr">
         <is>
           <t>山西省科技合作交流专项项目</t>
         </is>
       </c>
-      <c r="D28" s="196" t="inlineStr">
+      <c r="D28" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E28" s="196" t="inlineStr">
+      <c r="E28" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -3931,34 +3985,34 @@
           <t>与香港、澳门科技合作交流项目</t>
         </is>
       </c>
-      <c r="G28" s="197" t="inlineStr">
+      <c r="G28" s="196" t="inlineStr">
         <is>
           <t>30万</t>
         </is>
       </c>
-      <c r="H28" s="195" t="inlineStr">
+      <c r="H28" s="194" t="inlineStr">
         <is>
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I28" s="208" t="inlineStr">
+      <c r="I28" s="209" t="inlineStr">
         <is>
           <t>https://kjt.shanxi.gov.cn/xxgk/zfxxgkml/acs_11737/gjyqykjhzc/202608/t20260831_10210987.shtml</t>
         </is>
       </c>
-      <c r="J28" s="209" t="n"/>
-      <c r="K28" s="201" t="n"/>
-      <c r="L28" s="201" t="n"/>
-      <c r="M28" s="201" t="n"/>
-      <c r="N28" s="201" t="n"/>
-      <c r="O28" s="201" t="n"/>
-      <c r="P28" s="201" t="n"/>
-      <c r="Q28" s="201" t="n"/>
-      <c r="R28" s="201" t="n"/>
-      <c r="S28" s="201" t="n"/>
-      <c r="T28" s="201" t="n"/>
-      <c r="U28" s="201" t="n"/>
-      <c r="V28" s="202" t="inlineStr">
+      <c r="J28" s="210" t="n"/>
+      <c r="K28" s="195" t="n"/>
+      <c r="L28" s="195" t="n"/>
+      <c r="M28" s="195" t="n"/>
+      <c r="N28" s="195" t="n"/>
+      <c r="O28" s="195" t="n"/>
+      <c r="P28" s="195" t="n"/>
+      <c r="Q28" s="195" t="n"/>
+      <c r="R28" s="195" t="n"/>
+      <c r="S28" s="195" t="n"/>
+      <c r="T28" s="195" t="n"/>
+      <c r="U28" s="195" t="n"/>
+      <c r="V28" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度设「与香港、澳门科技合作交流项目」，港澳方向不超过50万/项，2026年9月申报中</t>
         </is>
@@ -4006,21 +4060,21 @@
       <c r="J29" s="85" t="n"/>
     </row>
     <row r="30" ht="69" customFormat="1" customHeight="1" s="141">
-      <c r="A30" s="195" t="n">
+      <c r="A30" s="194" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="201" t="n"/>
-      <c r="C30" s="197" t="inlineStr">
+      <c r="B30" s="195" t="n"/>
+      <c r="C30" s="196" t="inlineStr">
         <is>
           <t>浙江省“尖兵”“领雁”科技计划科技合作项目</t>
         </is>
       </c>
-      <c r="D30" s="196" t="inlineStr">
+      <c r="D30" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E30" s="196" t="inlineStr">
+      <c r="E30" s="197" t="inlineStr">
         <is>
           <t>澳大教授（参与）</t>
         </is>
@@ -4030,34 +4084,34 @@
           <t>国际（含港澳台）科技合作项目。围绕支持元首外交合作平台、“一带一路”联合实验室、深化拓展政府间合作网络以及支撑撬动培育国际大科学计划、国际科技组织等重点任务，部署重点国家（地区）和关键领域合作项目。中国澳门：优先支持生物医药（中医药）、电子信息、空间科学、人工智能、海洋科技等领域。</t>
         </is>
       </c>
-      <c r="G30" s="197" t="inlineStr">
+      <c r="G30" s="196" t="inlineStr">
         <is>
           <t>120万元以内</t>
         </is>
       </c>
-      <c r="H30" s="195" t="inlineStr">
+      <c r="H30" s="194" t="inlineStr">
         <is>
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I30" s="210" t="inlineStr">
+      <c r="I30" s="211" t="inlineStr">
         <is>
           <t>https://kjt.zj.gov.cn/col/col1229225203/art/2026/art_e495d70575a44848947646e93ca2948c.html</t>
         </is>
       </c>
-      <c r="J30" s="209" t="n"/>
-      <c r="K30" s="201" t="n"/>
-      <c r="L30" s="201" t="n"/>
-      <c r="M30" s="201" t="n"/>
-      <c r="N30" s="201" t="n"/>
-      <c r="O30" s="201" t="n"/>
-      <c r="P30" s="201" t="n"/>
-      <c r="Q30" s="201" t="n"/>
-      <c r="R30" s="201" t="n"/>
-      <c r="S30" s="201" t="n"/>
-      <c r="T30" s="201" t="n"/>
-      <c r="U30" s="201" t="n"/>
-      <c r="V30" s="202" t="inlineStr">
+      <c r="J30" s="210" t="n"/>
+      <c r="K30" s="195" t="n"/>
+      <c r="L30" s="195" t="n"/>
+      <c r="M30" s="195" t="n"/>
+      <c r="N30" s="195" t="n"/>
+      <c r="O30" s="195" t="n"/>
+      <c r="P30" s="195" t="n"/>
+      <c r="Q30" s="195" t="n"/>
+      <c r="R30" s="195" t="n"/>
+      <c r="S30" s="195" t="n"/>
+      <c r="T30" s="195" t="n"/>
+      <c r="U30" s="195" t="n"/>
+      <c r="V30" s="201" t="inlineStr">
         <is>
           <t>● 更新：2026年度科技合作项目启动申报（2026-09），含国际（含港澳台）科技合作项目</t>
         </is>
@@ -4480,92 +4534,92 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="70">
-      <c r="A41" s="211" t="n">
+      <c r="A41" s="212" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="212" t="inlineStr">
+      <c r="B41" s="213" t="inlineStr">
         <is>
           <t>国家科技部</t>
         </is>
       </c>
-      <c r="C41" s="212" t="inlineStr">
+      <c r="C41" s="213" t="inlineStr">
         <is>
           <t>新一代人工智能国家科技重大专项2026年度公开项目</t>
         </is>
       </c>
-      <c r="D41" s="212" t="inlineStr"/>
-      <c r="E41" s="212" t="inlineStr">
+      <c r="D41" s="213" t="inlineStr"/>
+      <c r="E41" s="213" t="inlineStr">
         <is>
           <t>教授（参与，名单内港澳单位可参与）</t>
         </is>
       </c>
-      <c r="F41" s="212" t="inlineStr">
+      <c r="F41" s="213" t="inlineStr">
         <is>
           <t>申报附件含内地与香港、内地与澳门科技合作委员会协商确定的港澳科研单位名单</t>
         </is>
       </c>
-      <c r="G41" s="212" t="inlineStr">
+      <c r="G41" s="213" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H41" s="212" t="inlineStr">
+      <c r="H41" s="213" t="inlineStr">
         <is>
           <t>2026年度第一批申报中</t>
         </is>
       </c>
-      <c r="I41" s="213" t="inlineStr">
+      <c r="I41" s="214" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/</t>
         </is>
       </c>
-      <c r="V41" s="214" t="inlineStr">
+      <c r="V41" s="215" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度第一批公开项目申报启动，名单内港澳单位可参与</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="211" t="n">
+      <c r="A42" s="212" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="212" t="inlineStr">
+      <c r="B42" s="213" t="inlineStr">
         <is>
           <t>国家自然科学基金</t>
         </is>
       </c>
-      <c r="C42" s="212" t="inlineStr">
+      <c r="C42" s="213" t="inlineStr">
         <is>
           <t>NSFC民营企业创新发展联合基金（术理创新）</t>
         </is>
       </c>
-      <c r="D42" s="212" t="inlineStr"/>
-      <c r="E42" s="212" t="inlineStr">
+      <c r="D42" s="213" t="inlineStr"/>
+      <c r="E42" s="213" t="inlineStr">
         <is>
           <t>教授（主申/参与）</t>
         </is>
       </c>
-      <c r="F42" s="212" t="inlineStr">
+      <c r="F42" s="213" t="inlineStr">
         <is>
           <t>企业出资的NSFC联合基金，按国自然流程申报；脑机接口与神经调控方向</t>
         </is>
       </c>
-      <c r="G42" s="212" t="inlineStr">
+      <c r="G42" s="213" t="inlineStr">
         <is>
           <t>按指南</t>
         </is>
       </c>
-      <c r="H42" s="212" t="inlineStr">
+      <c r="H42" s="213" t="inlineStr">
         <is>
           <t>2026-06发布</t>
         </is>
       </c>
-      <c r="I42" s="213" t="inlineStr">
+      <c r="I42" s="214" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/</t>
         </is>
       </c>
-      <c r="V42" s="214" t="inlineStr">
+      <c r="V42" s="215" t="inlineStr">
         <is>
           <t>🆕 新增：2026年度项目申报中（脑机接口与神经调控方向）</t>
         </is>
@@ -4698,7 +4752,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-17）</t>
+          <t>最新更新（2026-10-18）</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4760,7 @@
       <c r="A3" s="190" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="215" t="inlineStr">
+      <c r="B3" s="216" t="inlineStr">
         <is>
           <t>社科项目</t>
         </is>
@@ -5010,7 +5064,7 @@
       <c r="A11" s="190" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="194" t="n"/>
+      <c r="B11" s="202" t="n"/>
       <c r="C11" s="134" t="inlineStr">
         <is>
           <t>珠海市哲学社会科学规划年度课题</t>
@@ -5132,7 +5186,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-17）</t>
+          <t>最新更新（2026-10-18）</t>
         </is>
       </c>
     </row>
@@ -5193,20 +5247,20 @@
       <c r="S3" s="82" t="n"/>
     </row>
     <row r="4" ht="148.5" customFormat="1" customHeight="1" s="141">
-      <c r="A4" s="195" t="n">
+      <c r="A4" s="194" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="197" t="inlineStr">
+      <c r="B4" s="196" t="inlineStr">
         <is>
           <t>何享健青年科学家项目</t>
         </is>
       </c>
-      <c r="C4" s="216" t="inlineStr">
+      <c r="C4" s="217" t="inlineStr">
         <is>
           <t>研究院全职研究人员</t>
         </is>
       </c>
-      <c r="D4" s="197" t="inlineStr">
+      <c r="D4" s="196" t="inlineStr">
         <is>
           <t>面向医学与生命科学、能源环境与气候变化领域，每年评选总数不超过20人。
 学位要求：已取得博士学位。
@@ -5214,39 +5268,39 @@
 年龄要求：被提名当年，参评人年龄在35周岁及以下，女性候选人放宽至38周岁。临床医学专业背景的被提名人统一放宽至40周岁，女性候选人放宽至43周岁。</t>
         </is>
       </c>
-      <c r="E4" s="197" t="inlineStr">
+      <c r="E4" s="196" t="inlineStr">
         <is>
           <t>200万元/3年</t>
         </is>
       </c>
-      <c r="F4" s="195" t="inlineStr">
+      <c r="F4" s="194" t="inlineStr">
         <is>
           <t>11月-次年2月</t>
         </is>
       </c>
-      <c r="G4" s="206" t="inlineStr">
+      <c r="G4" s="203" t="inlineStr">
         <is>
           <t>https://www.heprize.org/Home</t>
         </is>
       </c>
-      <c r="H4" s="209" t="inlineStr">
+      <c r="H4" s="210" t="inlineStr">
         <is>
           <t xml:space="preserve">评审流程按照“提名机构提交材料-秘书处形式审查-同行评审专家评审-评审委员会评审-理事会审批-获资助人名单公布”严格执行。
 </t>
         </is>
       </c>
-      <c r="I4" s="201" t="n"/>
-      <c r="J4" s="201" t="n"/>
-      <c r="K4" s="201" t="n"/>
-      <c r="L4" s="201" t="n"/>
-      <c r="M4" s="201" t="n"/>
-      <c r="N4" s="201" t="n"/>
-      <c r="O4" s="201" t="n"/>
-      <c r="P4" s="201" t="n"/>
-      <c r="Q4" s="201" t="n"/>
-      <c r="R4" s="201" t="n"/>
-      <c r="S4" s="201" t="n"/>
-      <c r="T4" s="202" t="inlineStr">
+      <c r="I4" s="195" t="n"/>
+      <c r="J4" s="195" t="n"/>
+      <c r="K4" s="195" t="n"/>
+      <c r="L4" s="195" t="n"/>
+      <c r="M4" s="195" t="n"/>
+      <c r="N4" s="195" t="n"/>
+      <c r="O4" s="195" t="n"/>
+      <c r="P4" s="195" t="n"/>
+      <c r="Q4" s="195" t="n"/>
+      <c r="R4" s="195" t="n"/>
+      <c r="S4" s="195" t="n"/>
+      <c r="T4" s="201" t="inlineStr">
         <is>
           <t>● 更新：第二期已启动（2025-11-03正式启动），200万元/3年，研究院全职研究人员可申</t>
         </is>
@@ -6614,18 +6668,18 @@
           <t>重点实验室开放课题清单</t>
         </is>
       </c>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="217" t="n"/>
-      <c r="L1" s="217" t="n"/>
-      <c r="M1" s="217" t="n"/>
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
     </row>
     <row r="2" ht="41.25" customHeight="1" s="70">
       <c r="A2" s="5" t="inlineStr">
@@ -6678,7 +6732,7 @@
           <t>公告月份</t>
         </is>
       </c>
-      <c r="K2" s="218" t="inlineStr">
+      <c r="K2" s="219" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -6700,9 +6754,9 @@
       <c r="R2" s="10" t="n"/>
       <c r="S2" s="10" t="n"/>
       <c r="T2" s="10" t="n"/>
-      <c r="U2" s="219" t="inlineStr">
-        <is>
-          <t>最新更新（2026-10-17）</t>
+      <c r="U2" s="220" t="inlineStr">
+        <is>
+          <t>最新更新（2026-10-18）</t>
         </is>
       </c>
     </row>
@@ -6745,84 +6799,84 @@
           <t>否</t>
         </is>
       </c>
-      <c r="I3" s="220" t="inlineStr">
+      <c r="I3" s="221" t="inlineStr">
         <is>
           <t>http://sklpre.zju.edu.cn/redir.php?catalog_id=60520&amp;object_id=63561</t>
         </is>
       </c>
       <c r="J3" s="15" t="n"/>
-      <c r="K3" s="221" t="n"/>
+      <c r="K3" s="222" t="n"/>
       <c r="L3" s="17" t="n"/>
       <c r="M3" s="18" t="n"/>
     </row>
     <row r="4" ht="63" customHeight="1" s="70">
-      <c r="A4" s="222" t="n"/>
-      <c r="B4" s="222" t="n"/>
-      <c r="C4" s="222" t="n"/>
+      <c r="A4" s="223" t="n"/>
+      <c r="B4" s="223" t="n"/>
+      <c r="C4" s="223" t="n"/>
       <c r="D4" s="12" t="inlineStr">
         <is>
           <t>天津大学</t>
         </is>
       </c>
-      <c r="E4" s="222" t="n"/>
-      <c r="F4" s="222" t="n"/>
-      <c r="G4" s="222" t="n"/>
+      <c r="E4" s="223" t="n"/>
+      <c r="F4" s="223" t="n"/>
+      <c r="G4" s="223" t="n"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I4" s="222" t="n"/>
+      <c r="I4" s="223" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="221" t="n"/>
+      <c r="K4" s="222" t="n"/>
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="18" t="n"/>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="222" t="n"/>
-      <c r="B5" s="222" t="n"/>
-      <c r="C5" s="222" t="n"/>
+      <c r="A5" s="223" t="n"/>
+      <c r="B5" s="223" t="n"/>
+      <c r="C5" s="223" t="n"/>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>华东理工大学</t>
         </is>
       </c>
-      <c r="E5" s="222" t="n"/>
-      <c r="F5" s="222" t="n"/>
-      <c r="G5" s="222" t="n"/>
+      <c r="E5" s="223" t="n"/>
+      <c r="F5" s="223" t="n"/>
+      <c r="G5" s="223" t="n"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I5" s="222" t="n"/>
+      <c r="I5" s="223" t="n"/>
       <c r="J5" s="15" t="n"/>
-      <c r="K5" s="221" t="n"/>
+      <c r="K5" s="222" t="n"/>
       <c r="L5" s="17" t="n"/>
       <c r="M5" s="18" t="n"/>
     </row>
     <row r="6" ht="55.5" customHeight="1" s="70">
-      <c r="A6" s="223" t="n"/>
-      <c r="B6" s="223" t="n"/>
-      <c r="C6" s="223" t="n"/>
+      <c r="A6" s="224" t="n"/>
+      <c r="B6" s="224" t="n"/>
+      <c r="C6" s="224" t="n"/>
       <c r="D6" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E6" s="223" t="n"/>
-      <c r="F6" s="223" t="n"/>
-      <c r="G6" s="223" t="n"/>
+      <c r="E6" s="224" t="n"/>
+      <c r="F6" s="224" t="n"/>
+      <c r="G6" s="224" t="n"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I6" s="223" t="n"/>
+      <c r="I6" s="224" t="n"/>
       <c r="J6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="224" t="n">
+      <c r="K6" s="225" t="n">
         <v>44679</v>
       </c>
       <c r="L6" s="17" t="n"/>
@@ -6875,30 +6929,30 @@
       <c r="J7" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="225" t="n">
+      <c r="K7" s="226" t="n">
         <v>44677</v>
       </c>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" s="70">
-      <c r="A8" s="223" t="n"/>
-      <c r="B8" s="223" t="n"/>
-      <c r="C8" s="223" t="n"/>
+      <c r="A8" s="224" t="n"/>
+      <c r="B8" s="224" t="n"/>
+      <c r="C8" s="224" t="n"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
           <t>中国石油大学（华东）</t>
         </is>
       </c>
-      <c r="E8" s="223" t="n"/>
-      <c r="F8" s="223" t="n"/>
-      <c r="G8" s="223" t="n"/>
-      <c r="H8" s="223" t="n"/>
-      <c r="I8" s="223" t="n"/>
-      <c r="J8" s="223" t="n"/>
-      <c r="K8" s="223" t="n"/>
-      <c r="L8" s="223" t="n"/>
-      <c r="M8" s="223" t="n"/>
+      <c r="E8" s="224" t="n"/>
+      <c r="F8" s="224" t="n"/>
+      <c r="G8" s="224" t="n"/>
+      <c r="H8" s="224" t="n"/>
+      <c r="I8" s="224" t="n"/>
+      <c r="J8" s="224" t="n"/>
+      <c r="K8" s="224" t="n"/>
+      <c r="L8" s="224" t="n"/>
+      <c r="M8" s="224" t="n"/>
     </row>
     <row r="9" ht="44.25" customHeight="1" s="70">
       <c r="A9" s="11" t="n">
@@ -6945,7 +6999,7 @@
         </is>
       </c>
       <c r="J9" s="15" t="n"/>
-      <c r="K9" s="221" t="n"/>
+      <c r="K9" s="222" t="n"/>
       <c r="L9" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -6998,7 +7052,7 @@
         </is>
       </c>
       <c r="J10" s="15" t="n"/>
-      <c r="K10" s="221" t="n"/>
+      <c r="K10" s="222" t="n"/>
       <c r="L10" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7057,7 +7111,7 @@
       <c r="J11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="224" t="n">
+      <c r="K11" s="225" t="n">
         <v>44727</v>
       </c>
       <c r="L11" s="26" t="inlineStr">
@@ -7104,7 +7158,7 @@
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="15" t="n"/>
-      <c r="K12" s="221" t="n"/>
+      <c r="K12" s="222" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="29" t="inlineStr">
         <is>
@@ -7157,7 +7211,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n"/>
-      <c r="K13" s="221" t="n"/>
+      <c r="K13" s="222" t="n"/>
       <c r="L13" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7214,7 +7268,7 @@
         </is>
       </c>
       <c r="J14" s="31" t="n"/>
-      <c r="K14" s="221" t="n"/>
+      <c r="K14" s="222" t="n"/>
       <c r="L14" s="26" t="inlineStr">
         <is>
           <t>暂无往年相关信息</t>
@@ -7273,7 +7327,7 @@
       <c r="J15" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="224" t="n">
+      <c r="K15" s="225" t="n">
         <v>44774</v>
       </c>
       <c r="L15" s="26" t="inlineStr">
@@ -7330,7 +7384,7 @@
       <c r="J16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="224" t="n">
+      <c r="K16" s="225" t="n">
         <v>44731</v>
       </c>
       <c r="L16" s="26" t="inlineStr">
@@ -7387,7 +7441,7 @@
       <c r="J17" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="224" t="n">
+      <c r="K17" s="225" t="n">
         <v>44696</v>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -7436,7 +7490,7 @@
       <c r="J18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="224" t="n">
+      <c r="K18" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L18" s="26" t="inlineStr">
@@ -7497,7 +7551,7 @@
       <c r="J19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K19" s="224" t="n">
+      <c r="K19" s="225" t="n">
         <v>44866</v>
       </c>
       <c r="L19" s="26" t="inlineStr">
@@ -7558,7 +7612,7 @@
       <c r="J20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="224" t="n">
+      <c r="K20" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L20" s="26" t="inlineStr">
@@ -7613,7 +7667,7 @@
       </c>
       <c r="I21" s="34" t="n"/>
       <c r="J21" s="15" t="n"/>
-      <c r="K21" s="221" t="n"/>
+      <c r="K21" s="222" t="n"/>
       <c r="L21" s="26" t="inlineStr">
         <is>
           <t>最近几年未有相关的课题申请消息</t>
@@ -7672,7 +7726,7 @@
       <c r="J22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="226" t="n">
+      <c r="K22" s="227" t="n">
         <v>44694</v>
       </c>
       <c r="L22" s="36" t="n"/>
@@ -7715,7 +7769,7 @@
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="28" t="n"/>
       <c r="J23" s="15" t="n"/>
-      <c r="K23" s="227" t="n"/>
+      <c r="K23" s="228" t="n"/>
       <c r="L23" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7760,7 +7814,7 @@
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="28" t="n"/>
       <c r="J24" s="15" t="n"/>
-      <c r="K24" s="221" t="n"/>
+      <c r="K24" s="222" t="n"/>
       <c r="L24" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -7815,7 +7869,7 @@
       <c r="J25" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K25" s="224" t="n">
+      <c r="K25" s="225" t="n">
         <v>44822</v>
       </c>
       <c r="L25" s="17" t="n"/>
@@ -7868,7 +7922,7 @@
       <c r="J26" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="224" t="n">
+      <c r="K26" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L26" s="39" t="inlineStr">
@@ -7929,7 +7983,7 @@
       <c r="J27" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="224" t="n">
+      <c r="K27" s="225" t="n">
         <v>44804</v>
       </c>
       <c r="L27" s="40" t="n"/>
@@ -7982,7 +8036,7 @@
       <c r="J28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="224" t="n">
+      <c r="K28" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L28" s="26" t="inlineStr">
@@ -8043,7 +8097,7 @@
       <c r="J29" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="224" t="n">
+      <c r="K29" s="225" t="n">
         <v>44835</v>
       </c>
       <c r="L29" s="17" t="n"/>
@@ -8096,7 +8150,7 @@
       <c r="J30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="224" t="n">
+      <c r="K30" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L30" s="26" t="inlineStr">
@@ -8151,7 +8205,7 @@
         </is>
       </c>
       <c r="J31" s="15" t="n"/>
-      <c r="K31" s="221" t="n"/>
+      <c r="K31" s="222" t="n"/>
       <c r="L31" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关消息</t>
@@ -8206,7 +8260,7 @@
       <c r="J32" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="224" t="n">
+      <c r="K32" s="225" t="n">
         <v>44631</v>
       </c>
       <c r="L32" s="17" t="n"/>
@@ -8257,7 +8311,7 @@
       </c>
       <c r="I33" s="28" t="n"/>
       <c r="J33" s="15" t="n"/>
-      <c r="K33" s="221" t="n"/>
+      <c r="K33" s="222" t="n"/>
       <c r="L33" s="17" t="n"/>
       <c r="M33" s="18" t="n"/>
     </row>
@@ -8308,7 +8362,7 @@
       <c r="J34" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="224" t="n">
+      <c r="K34" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L34" s="17" t="n"/>
@@ -8355,7 +8409,7 @@
       </c>
       <c r="I35" s="28" t="n"/>
       <c r="J35" s="15" t="n"/>
-      <c r="K35" s="221" t="n"/>
+      <c r="K35" s="222" t="n"/>
       <c r="L35" s="17" t="n"/>
       <c r="M35" s="18" t="n"/>
     </row>
@@ -8400,7 +8454,7 @@
       </c>
       <c r="I36" s="28" t="n"/>
       <c r="J36" s="15" t="n"/>
-      <c r="K36" s="221" t="n"/>
+      <c r="K36" s="222" t="n"/>
       <c r="L36" s="17" t="n"/>
       <c r="M36" s="18" t="n"/>
     </row>
@@ -8451,7 +8505,7 @@
       <c r="J37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="224" t="n">
+      <c r="K37" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L37" s="26" t="inlineStr">
@@ -8508,7 +8562,7 @@
       <c r="J38" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K38" s="224" t="n">
+      <c r="K38" s="225" t="n">
         <v>44835</v>
       </c>
       <c r="L38" s="26" t="inlineStr">
@@ -8565,7 +8619,7 @@
       <c r="J39" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K39" s="224" t="n">
+      <c r="K39" s="225" t="n">
         <v>44690</v>
       </c>
       <c r="L39" s="17" t="n"/>
@@ -8618,30 +8672,30 @@
       <c r="J40" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K40" s="225" t="n">
+      <c r="K40" s="226" t="n">
         <v>44657</v>
       </c>
       <c r="L40" s="36" t="n"/>
       <c r="M40" s="18" t="n"/>
     </row>
     <row r="41" ht="24.75" customHeight="1" s="70">
-      <c r="A41" s="223" t="n"/>
-      <c r="B41" s="223" t="n"/>
-      <c r="C41" s="223" t="n"/>
+      <c r="A41" s="224" t="n"/>
+      <c r="B41" s="224" t="n"/>
+      <c r="C41" s="224" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>中国科学技术大学</t>
         </is>
       </c>
-      <c r="E41" s="223" t="n"/>
-      <c r="F41" s="223" t="n"/>
-      <c r="G41" s="223" t="n"/>
-      <c r="H41" s="223" t="n"/>
-      <c r="I41" s="223" t="n"/>
-      <c r="J41" s="223" t="n"/>
-      <c r="K41" s="223" t="n"/>
-      <c r="L41" s="228" t="n"/>
-      <c r="M41" s="223" t="n"/>
+      <c r="E41" s="224" t="n"/>
+      <c r="F41" s="224" t="n"/>
+      <c r="G41" s="224" t="n"/>
+      <c r="H41" s="224" t="n"/>
+      <c r="I41" s="224" t="n"/>
+      <c r="J41" s="224" t="n"/>
+      <c r="K41" s="224" t="n"/>
+      <c r="L41" s="229" t="n"/>
+      <c r="M41" s="224" t="n"/>
     </row>
     <row r="42" ht="24.75" customHeight="1" s="70">
       <c r="A42" s="11" t="n">
@@ -8684,7 +8738,7 @@
       </c>
       <c r="I42" s="28" t="n"/>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="221" t="n"/>
+      <c r="K42" s="222" t="n"/>
       <c r="L42" s="17" t="n"/>
       <c r="M42" s="18" t="n"/>
     </row>
@@ -8729,7 +8783,7 @@
       </c>
       <c r="I43" s="28" t="n"/>
       <c r="J43" s="15" t="n"/>
-      <c r="K43" s="221" t="n"/>
+      <c r="K43" s="222" t="n"/>
       <c r="L43" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -8782,7 +8836,7 @@
       </c>
       <c r="I44" s="28" t="n"/>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="221" t="n"/>
+      <c r="K44" s="222" t="n"/>
       <c r="L44" s="17" t="n"/>
       <c r="M44" s="18" t="n"/>
     </row>
@@ -8833,7 +8887,7 @@
       <c r="J45" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="224" t="n">
+      <c r="K45" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L45" s="26" t="inlineStr">
@@ -8894,7 +8948,7 @@
       <c r="J46" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="224" t="n">
+      <c r="K46" s="225" t="n">
         <v>44642</v>
       </c>
       <c r="L46" s="26" t="inlineStr">
@@ -8945,7 +8999,7 @@
       </c>
       <c r="I47" s="28" t="n"/>
       <c r="J47" s="15" t="n"/>
-      <c r="K47" s="221" t="n"/>
+      <c r="K47" s="222" t="n"/>
       <c r="L47" s="17" t="n"/>
       <c r="M47" s="18" t="n"/>
     </row>
@@ -8996,7 +9050,7 @@
       <c r="J48" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K48" s="224" t="n">
+      <c r="K48" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L48" s="17" t="n"/>
@@ -9043,7 +9097,7 @@
       </c>
       <c r="I49" s="28" t="n"/>
       <c r="J49" s="15" t="n"/>
-      <c r="K49" s="221" t="n"/>
+      <c r="K49" s="222" t="n"/>
       <c r="L49" s="26" t="inlineStr">
         <is>
           <t>官网信息不全</t>
@@ -9102,68 +9156,68 @@
       <c r="J50" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="K50" s="225" t="n">
+      <c r="K50" s="226" t="n">
         <v>44652</v>
       </c>
       <c r="L50" s="18" t="n"/>
       <c r="M50" s="18" t="n"/>
     </row>
     <row r="51" ht="24.75" customHeight="1" s="70">
-      <c r="A51" s="222" t="n"/>
-      <c r="B51" s="222" t="n"/>
-      <c r="C51" s="222" t="n"/>
+      <c r="A51" s="223" t="n"/>
+      <c r="B51" s="223" t="n"/>
+      <c r="C51" s="223" t="n"/>
       <c r="D51" s="12" t="inlineStr">
         <is>
           <t>中国科学院生态环境研究中心</t>
         </is>
       </c>
-      <c r="E51" s="222" t="n"/>
-      <c r="F51" s="222" t="n"/>
-      <c r="G51" s="222" t="n"/>
-      <c r="H51" s="222" t="n"/>
-      <c r="I51" s="222" t="n"/>
-      <c r="J51" s="222" t="n"/>
-      <c r="K51" s="222" t="n"/>
-      <c r="L51" s="222" t="n"/>
-      <c r="M51" s="222" t="n"/>
+      <c r="E51" s="223" t="n"/>
+      <c r="F51" s="223" t="n"/>
+      <c r="G51" s="223" t="n"/>
+      <c r="H51" s="223" t="n"/>
+      <c r="I51" s="223" t="n"/>
+      <c r="J51" s="223" t="n"/>
+      <c r="K51" s="223" t="n"/>
+      <c r="L51" s="223" t="n"/>
+      <c r="M51" s="223" t="n"/>
     </row>
     <row r="52" ht="24.75" customHeight="1" s="70">
-      <c r="A52" s="222" t="n"/>
-      <c r="B52" s="222" t="n"/>
-      <c r="C52" s="222" t="n"/>
+      <c r="A52" s="223" t="n"/>
+      <c r="B52" s="223" t="n"/>
+      <c r="C52" s="223" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E52" s="222" t="n"/>
-      <c r="F52" s="222" t="n"/>
-      <c r="G52" s="222" t="n"/>
-      <c r="H52" s="222" t="n"/>
-      <c r="I52" s="222" t="n"/>
-      <c r="J52" s="222" t="n"/>
-      <c r="K52" s="222" t="n"/>
-      <c r="L52" s="222" t="n"/>
-      <c r="M52" s="222" t="n"/>
+      <c r="E52" s="223" t="n"/>
+      <c r="F52" s="223" t="n"/>
+      <c r="G52" s="223" t="n"/>
+      <c r="H52" s="223" t="n"/>
+      <c r="I52" s="223" t="n"/>
+      <c r="J52" s="223" t="n"/>
+      <c r="K52" s="223" t="n"/>
+      <c r="L52" s="223" t="n"/>
+      <c r="M52" s="223" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1" s="70">
-      <c r="A53" s="223" t="n"/>
-      <c r="B53" s="223" t="n"/>
-      <c r="C53" s="223" t="n"/>
+      <c r="A53" s="224" t="n"/>
+      <c r="B53" s="224" t="n"/>
+      <c r="C53" s="224" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E53" s="223" t="n"/>
-      <c r="F53" s="223" t="n"/>
-      <c r="G53" s="223" t="n"/>
-      <c r="H53" s="223" t="n"/>
-      <c r="I53" s="223" t="n"/>
-      <c r="J53" s="223" t="n"/>
-      <c r="K53" s="223" t="n"/>
-      <c r="L53" s="223" t="n"/>
-      <c r="M53" s="223" t="n"/>
+      <c r="E53" s="224" t="n"/>
+      <c r="F53" s="224" t="n"/>
+      <c r="G53" s="224" t="n"/>
+      <c r="H53" s="224" t="n"/>
+      <c r="I53" s="224" t="n"/>
+      <c r="J53" s="224" t="n"/>
+      <c r="K53" s="224" t="n"/>
+      <c r="L53" s="224" t="n"/>
+      <c r="M53" s="224" t="n"/>
     </row>
     <row r="54" ht="24.75" customHeight="1" s="70">
       <c r="A54" s="11" t="n">
@@ -9206,7 +9260,7 @@
       </c>
       <c r="I54" s="28" t="n"/>
       <c r="J54" s="15" t="n"/>
-      <c r="K54" s="221" t="n"/>
+      <c r="K54" s="222" t="n"/>
       <c r="L54" s="17" t="n"/>
       <c r="M54" s="18" t="n"/>
     </row>
@@ -9257,30 +9311,30 @@
       <c r="J55" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="225" t="n">
+      <c r="K55" s="226" t="n">
         <v>44599</v>
       </c>
       <c r="L55" s="18" t="n"/>
       <c r="M55" s="18" t="n"/>
     </row>
     <row r="56" ht="24.75" customHeight="1" s="70">
-      <c r="A56" s="223" t="n"/>
-      <c r="B56" s="223" t="n"/>
-      <c r="C56" s="223" t="n"/>
+      <c r="A56" s="224" t="n"/>
+      <c r="B56" s="224" t="n"/>
+      <c r="C56" s="224" t="n"/>
       <c r="D56" s="12" t="inlineStr">
         <is>
           <t>北京师范大学</t>
         </is>
       </c>
-      <c r="E56" s="223" t="n"/>
-      <c r="F56" s="223" t="n"/>
-      <c r="G56" s="223" t="n"/>
-      <c r="H56" s="223" t="n"/>
-      <c r="I56" s="223" t="n"/>
-      <c r="J56" s="223" t="n"/>
-      <c r="K56" s="223" t="n"/>
-      <c r="L56" s="223" t="n"/>
-      <c r="M56" s="223" t="n"/>
+      <c r="E56" s="224" t="n"/>
+      <c r="F56" s="224" t="n"/>
+      <c r="G56" s="224" t="n"/>
+      <c r="H56" s="224" t="n"/>
+      <c r="I56" s="224" t="n"/>
+      <c r="J56" s="224" t="n"/>
+      <c r="K56" s="224" t="n"/>
+      <c r="L56" s="224" t="n"/>
+      <c r="M56" s="224" t="n"/>
     </row>
     <row r="57" ht="24.75" customHeight="1" s="70">
       <c r="A57" s="11" t="n">
@@ -9329,7 +9383,7 @@
       <c r="J57" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K57" s="224" t="n">
+      <c r="K57" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L57" s="26" t="inlineStr">
@@ -9386,7 +9440,7 @@
       <c r="J58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="224" t="n">
+      <c r="K58" s="225" t="n">
         <v>44658</v>
       </c>
       <c r="L58" s="26" t="inlineStr">
@@ -9443,7 +9497,7 @@
       <c r="J59" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K59" s="229" t="n">
+      <c r="K59" s="230" t="n">
         <v>44615</v>
       </c>
       <c r="L59" s="36" t="n"/>
@@ -9496,7 +9550,7 @@
       <c r="J60" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K60" s="230" t="n">
+      <c r="K60" s="231" t="n">
         <v>44667</v>
       </c>
       <c r="L60" s="17" t="n"/>
@@ -9549,7 +9603,7 @@
       <c r="J61" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K61" s="224" t="n">
+      <c r="K61" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L61" s="17" t="n"/>
@@ -9602,30 +9656,30 @@
       <c r="J62" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K62" s="225" t="n">
+      <c r="K62" s="226" t="n">
         <v>44877</v>
       </c>
       <c r="L62" s="18" t="n"/>
       <c r="M62" s="18" t="n"/>
     </row>
     <row r="63" ht="24.75" customHeight="1" s="70">
-      <c r="A63" s="223" t="n"/>
-      <c r="B63" s="223" t="n"/>
-      <c r="C63" s="223" t="n"/>
+      <c r="A63" s="224" t="n"/>
+      <c r="B63" s="224" t="n"/>
+      <c r="C63" s="224" t="n"/>
       <c r="D63" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学</t>
         </is>
       </c>
-      <c r="E63" s="223" t="n"/>
-      <c r="F63" s="223" t="n"/>
-      <c r="G63" s="223" t="n"/>
-      <c r="H63" s="223" t="n"/>
-      <c r="I63" s="223" t="n"/>
-      <c r="J63" s="223" t="n"/>
-      <c r="K63" s="223" t="n"/>
-      <c r="L63" s="223" t="n"/>
-      <c r="M63" s="223" t="n"/>
+      <c r="E63" s="224" t="n"/>
+      <c r="F63" s="224" t="n"/>
+      <c r="G63" s="224" t="n"/>
+      <c r="H63" s="224" t="n"/>
+      <c r="I63" s="224" t="n"/>
+      <c r="J63" s="224" t="n"/>
+      <c r="K63" s="224" t="n"/>
+      <c r="L63" s="224" t="n"/>
+      <c r="M63" s="224" t="n"/>
     </row>
     <row r="64" ht="24.75" customHeight="1" s="70">
       <c r="A64" s="11" t="n">
@@ -9674,7 +9728,7 @@
       <c r="J64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="224" t="n">
+      <c r="K64" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L64" s="26" t="inlineStr">
@@ -9729,7 +9783,7 @@
       </c>
       <c r="I65" s="28" t="n"/>
       <c r="J65" s="15" t="n"/>
-      <c r="K65" s="221" t="n"/>
+      <c r="K65" s="222" t="n"/>
       <c r="L65" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -9784,7 +9838,7 @@
       <c r="J66" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K66" s="224" t="n">
+      <c r="K66" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L66" s="26" t="inlineStr">
@@ -9839,7 +9893,7 @@
       </c>
       <c r="I67" s="28" t="n"/>
       <c r="J67" s="15" t="n"/>
-      <c r="K67" s="221" t="n"/>
+      <c r="K67" s="222" t="n"/>
       <c r="L67" s="26" t="inlineStr">
         <is>
           <t>未找到往年信息</t>
@@ -9892,7 +9946,7 @@
       </c>
       <c r="I68" s="28" t="n"/>
       <c r="J68" s="15" t="n"/>
-      <c r="K68" s="221" t="n"/>
+      <c r="K68" s="222" t="n"/>
       <c r="L68" s="17" t="n"/>
       <c r="M68" s="18" t="n"/>
     </row>
@@ -9943,7 +9997,7 @@
       <c r="J69" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K69" s="224" t="n">
+      <c r="K69" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L69" s="26" t="inlineStr">
@@ -10000,7 +10054,7 @@
       <c r="J70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K70" s="224" t="n">
+      <c r="K70" s="225" t="n">
         <v>44565</v>
       </c>
       <c r="L70" s="26" t="inlineStr">
@@ -10057,30 +10111,30 @@
       <c r="J71" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K71" s="225" t="n">
+      <c r="K71" s="226" t="n">
         <v>44882</v>
       </c>
       <c r="L71" s="36" t="n"/>
       <c r="M71" s="18" t="n"/>
     </row>
     <row r="72" ht="24.75" customHeight="1" s="70">
-      <c r="A72" s="223" t="n"/>
-      <c r="B72" s="223" t="n"/>
-      <c r="C72" s="223" t="n"/>
+      <c r="A72" s="224" t="n"/>
+      <c r="B72" s="224" t="n"/>
+      <c r="C72" s="224" t="n"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
           <t>南京大学</t>
         </is>
       </c>
-      <c r="E72" s="223" t="n"/>
-      <c r="F72" s="223" t="n"/>
-      <c r="G72" s="223" t="n"/>
-      <c r="H72" s="223" t="n"/>
-      <c r="I72" s="223" t="n"/>
-      <c r="J72" s="223" t="n"/>
-      <c r="K72" s="223" t="n"/>
-      <c r="L72" s="228" t="n"/>
-      <c r="M72" s="223" t="n"/>
+      <c r="E72" s="224" t="n"/>
+      <c r="F72" s="224" t="n"/>
+      <c r="G72" s="224" t="n"/>
+      <c r="H72" s="224" t="n"/>
+      <c r="I72" s="224" t="n"/>
+      <c r="J72" s="224" t="n"/>
+      <c r="K72" s="224" t="n"/>
+      <c r="L72" s="229" t="n"/>
+      <c r="M72" s="224" t="n"/>
     </row>
     <row r="73" ht="24.75" customHeight="1" s="70">
       <c r="A73" s="11" t="n">
@@ -10129,7 +10183,7 @@
       <c r="J73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K73" s="224" t="n">
+      <c r="K73" s="225" t="n">
         <v>44670</v>
       </c>
       <c r="L73" s="26" t="inlineStr">
@@ -10186,7 +10240,7 @@
       <c r="J74" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K74" s="224" t="n">
+      <c r="K74" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L74" s="26" t="inlineStr">
@@ -10243,7 +10297,7 @@
       <c r="J75" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="224" t="n">
+      <c r="K75" s="225" t="n">
         <v>44588</v>
       </c>
       <c r="L75" s="26" t="inlineStr">
@@ -10300,7 +10354,7 @@
       <c r="J76" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="224" t="n">
+      <c r="K76" s="225" t="n">
         <v>44667</v>
       </c>
       <c r="L76" s="26" t="inlineStr">
@@ -10357,7 +10411,7 @@
       <c r="J77" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="224" t="n">
+      <c r="K77" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L77" s="26" t="inlineStr">
@@ -10414,7 +10468,7 @@
       <c r="J78" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K78" s="224" t="n">
+      <c r="K78" s="225" t="n">
         <v>44741</v>
       </c>
       <c r="L78" s="26" t="inlineStr">
@@ -10471,7 +10525,7 @@
       <c r="J79" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K79" s="224" t="n">
+      <c r="K79" s="225" t="n">
         <v>44825</v>
       </c>
       <c r="L79" s="17" t="n"/>
@@ -10524,7 +10578,7 @@
       <c r="J80" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K80" s="231" t="n">
+      <c r="K80" s="232" t="n">
         <v>44709</v>
       </c>
       <c r="L80" s="36" t="n"/>
@@ -10577,7 +10631,7 @@
       <c r="J81" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K81" s="232" t="n">
+      <c r="K81" s="233" t="n">
         <v>44670</v>
       </c>
       <c r="L81" s="17" t="n"/>
@@ -10620,7 +10674,7 @@
       <c r="H82" s="31" t="n"/>
       <c r="I82" s="48" t="n"/>
       <c r="J82" s="31" t="n"/>
-      <c r="K82" s="233" t="n"/>
+      <c r="K82" s="234" t="n"/>
       <c r="L82" s="29" t="inlineStr">
         <is>
           <t>不是专用连接，进不了官网</t>
@@ -10629,23 +10683,23 @@
       <c r="M82" s="18" t="n"/>
     </row>
     <row r="83" ht="24.75" customHeight="1" s="70">
-      <c r="A83" s="223" t="n"/>
-      <c r="B83" s="223" t="n"/>
-      <c r="C83" s="223" t="n"/>
+      <c r="A83" s="224" t="n"/>
+      <c r="B83" s="224" t="n"/>
+      <c r="C83" s="224" t="n"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
           <t>中国地质大学（北京）</t>
         </is>
       </c>
-      <c r="E83" s="223" t="n"/>
-      <c r="F83" s="223" t="n"/>
-      <c r="G83" s="223" t="n"/>
-      <c r="H83" s="223" t="n"/>
-      <c r="I83" s="223" t="n"/>
-      <c r="J83" s="223" t="n"/>
-      <c r="K83" s="223" t="n"/>
-      <c r="L83" s="223" t="n"/>
-      <c r="M83" s="223" t="n"/>
+      <c r="E83" s="224" t="n"/>
+      <c r="F83" s="224" t="n"/>
+      <c r="G83" s="224" t="n"/>
+      <c r="H83" s="224" t="n"/>
+      <c r="I83" s="224" t="n"/>
+      <c r="J83" s="224" t="n"/>
+      <c r="K83" s="224" t="n"/>
+      <c r="L83" s="224" t="n"/>
+      <c r="M83" s="224" t="n"/>
     </row>
     <row r="84" ht="24.75" customHeight="1" s="70">
       <c r="A84" s="11" t="n">
@@ -10694,7 +10748,7 @@
       <c r="J84" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K84" s="224" t="n">
+      <c r="K84" s="225" t="n">
         <v>44813</v>
       </c>
       <c r="L84" s="17" t="n"/>
@@ -10747,7 +10801,7 @@
       <c r="J85" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K85" s="224" t="n">
+      <c r="K85" s="225" t="n">
         <v>44881</v>
       </c>
       <c r="L85" s="26" t="inlineStr">
@@ -10804,7 +10858,7 @@
       <c r="J86" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="224" t="n">
+      <c r="K86" s="225" t="n">
         <v>44635</v>
       </c>
       <c r="L86" s="26" t="inlineStr">
@@ -10861,7 +10915,7 @@
       <c r="J87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K87" s="224" t="n">
+      <c r="K87" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L87" s="26" t="inlineStr">
@@ -10922,7 +10976,7 @@
       <c r="J88" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K88" s="224" t="n">
+      <c r="K88" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L88" s="26" t="inlineStr">
@@ -10979,7 +11033,7 @@
       <c r="J89" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K89" s="224" t="n">
+      <c r="K89" s="225" t="n">
         <v>44592</v>
       </c>
       <c r="L89" s="26" t="inlineStr">
@@ -10990,17 +11044,17 @@
       <c r="M89" s="18" t="n"/>
     </row>
     <row r="90" ht="24.75" customHeight="1" s="70">
-      <c r="A90" s="223" t="n"/>
-      <c r="B90" s="223" t="n"/>
-      <c r="C90" s="223" t="n"/>
+      <c r="A90" s="224" t="n"/>
+      <c r="B90" s="224" t="n"/>
+      <c r="C90" s="224" t="n"/>
       <c r="D90" s="12" t="inlineStr">
         <is>
           <t>成都理工大学</t>
         </is>
       </c>
-      <c r="E90" s="223" t="n"/>
-      <c r="F90" s="223" t="n"/>
-      <c r="G90" s="223" t="n"/>
+      <c r="E90" s="224" t="n"/>
+      <c r="F90" s="224" t="n"/>
+      <c r="G90" s="224" t="n"/>
       <c r="H90" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11014,7 +11068,7 @@
       <c r="J90" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K90" s="224" t="n">
+      <c r="K90" s="225" t="n">
         <v>44871</v>
       </c>
       <c r="L90" s="26" t="inlineStr">
@@ -11071,7 +11125,7 @@
       <c r="J91" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K91" s="224" t="n">
+      <c r="K91" s="225" t="n">
         <v>44806</v>
       </c>
       <c r="L91" s="26" t="inlineStr">
@@ -11128,7 +11182,7 @@
       <c r="J92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="224" t="n">
+      <c r="K92" s="225" t="n">
         <v>44576</v>
       </c>
       <c r="L92" s="26" t="inlineStr">
@@ -11179,7 +11233,7 @@
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="50" t="n"/>
-      <c r="K93" s="234" t="n"/>
+      <c r="K93" s="235" t="n"/>
       <c r="L93" s="17" t="n"/>
       <c r="M93" s="18" t="n"/>
     </row>
@@ -11230,7 +11284,7 @@
       <c r="J94" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K94" s="224" t="n">
+      <c r="K94" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L94" s="17" t="n"/>
@@ -11283,7 +11337,7 @@
       <c r="J95" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K95" s="224" t="n">
+      <c r="K95" s="225" t="n">
         <v>44679</v>
       </c>
       <c r="L95" s="17" t="n"/>
@@ -11336,7 +11390,7 @@
       <c r="J96" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K96" s="224" t="n">
+      <c r="K96" s="225" t="n">
         <v>44840</v>
       </c>
       <c r="L96" s="17" t="n"/>
@@ -11389,7 +11443,7 @@
       <c r="J97" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="K97" s="224" t="n">
+      <c r="K97" s="225" t="n">
         <v>44848</v>
       </c>
       <c r="L97" s="17" t="n"/>
@@ -11442,7 +11496,7 @@
       <c r="J98" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K98" s="224" t="n">
+      <c r="K98" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L98" s="17" t="n"/>
@@ -11495,7 +11549,7 @@
       <c r="J99" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="224" t="n">
+      <c r="K99" s="225" t="n">
         <v>44644</v>
       </c>
       <c r="L99" s="17" t="n"/>
@@ -11548,7 +11602,7 @@
       <c r="J100" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K100" s="224" t="n">
+      <c r="K100" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L100" s="26" t="inlineStr">
@@ -11609,7 +11663,7 @@
       <c r="J101" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K101" s="224" t="n">
+      <c r="K101" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L101" s="26" t="inlineStr">
@@ -11666,7 +11720,7 @@
       <c r="J102" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K102" s="224" t="n">
+      <c r="K102" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L102" s="26" t="inlineStr">
@@ -11717,22 +11771,22 @@
       </c>
       <c r="I103" s="28" t="n"/>
       <c r="J103" s="15" t="n"/>
-      <c r="K103" s="221" t="n"/>
+      <c r="K103" s="222" t="n"/>
       <c r="L103" s="17" t="n"/>
       <c r="M103" s="18" t="n"/>
     </row>
     <row r="104" ht="24.75" customHeight="1" s="70">
-      <c r="A104" s="222" t="n"/>
-      <c r="B104" s="222" t="n"/>
-      <c r="C104" s="222" t="n"/>
+      <c r="A104" s="223" t="n"/>
+      <c r="B104" s="223" t="n"/>
+      <c r="C104" s="223" t="n"/>
       <c r="D104" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E104" s="222" t="n"/>
-      <c r="F104" s="222" t="n"/>
-      <c r="G104" s="222" t="n"/>
+      <c r="E104" s="223" t="n"/>
+      <c r="F104" s="223" t="n"/>
+      <c r="G104" s="223" t="n"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -11746,7 +11800,7 @@
       <c r="J104" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K104" s="224" t="n">
+      <c r="K104" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L104" s="26" t="inlineStr">
@@ -11757,17 +11811,17 @@
       <c r="M104" s="18" t="n"/>
     </row>
     <row r="105" ht="24.75" customHeight="1" s="70">
-      <c r="A105" s="223" t="n"/>
-      <c r="B105" s="223" t="n"/>
-      <c r="C105" s="223" t="n"/>
+      <c r="A105" s="224" t="n"/>
+      <c r="B105" s="224" t="n"/>
+      <c r="C105" s="224" t="n"/>
       <c r="D105" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E105" s="223" t="n"/>
-      <c r="F105" s="223" t="n"/>
-      <c r="G105" s="223" t="n"/>
+      <c r="E105" s="224" t="n"/>
+      <c r="F105" s="224" t="n"/>
+      <c r="G105" s="224" t="n"/>
       <c r="H105" s="52" t="inlineStr">
         <is>
           <t>否</t>
@@ -11826,7 +11880,7 @@
       <c r="J106" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="K106" s="232" t="n">
+      <c r="K106" s="233" t="n">
         <v>44814</v>
       </c>
       <c r="L106" s="40" t="n"/>
@@ -11873,7 +11927,7 @@
       </c>
       <c r="I107" s="56" t="n"/>
       <c r="J107" s="15" t="n"/>
-      <c r="K107" s="221" t="n"/>
+      <c r="K107" s="222" t="n"/>
       <c r="L107" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11930,7 +11984,7 @@
         </is>
       </c>
       <c r="J108" s="15" t="n"/>
-      <c r="K108" s="221" t="n"/>
+      <c r="K108" s="222" t="n"/>
       <c r="L108" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关内容</t>
@@ -11979,7 +12033,7 @@
       </c>
       <c r="I109" s="28" t="n"/>
       <c r="J109" s="15" t="n"/>
-      <c r="K109" s="221" t="n"/>
+      <c r="K109" s="222" t="n"/>
       <c r="L109" s="26" t="inlineStr">
         <is>
           <t>网址打不开</t>
@@ -12032,7 +12086,7 @@
         </is>
       </c>
       <c r="J110" s="15" t="n"/>
-      <c r="K110" s="221" t="n"/>
+      <c r="K110" s="222" t="n"/>
       <c r="L110" s="26" t="inlineStr">
         <is>
           <t>未找到往年相关信息</t>
@@ -12041,17 +12095,17 @@
       <c r="M110" s="18" t="n"/>
     </row>
     <row r="111" ht="24.75" customHeight="1" s="70">
-      <c r="A111" s="223" t="n"/>
-      <c r="B111" s="223" t="n"/>
-      <c r="C111" s="223" t="n"/>
+      <c r="A111" s="224" t="n"/>
+      <c r="B111" s="224" t="n"/>
+      <c r="C111" s="224" t="n"/>
       <c r="D111" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E111" s="223" t="n"/>
-      <c r="F111" s="223" t="n"/>
-      <c r="G111" s="223" t="n"/>
+      <c r="E111" s="224" t="n"/>
+      <c r="F111" s="224" t="n"/>
+      <c r="G111" s="224" t="n"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
           <t>否</t>
@@ -12059,7 +12113,7 @@
       </c>
       <c r="I111" s="28" t="n"/>
       <c r="J111" s="15" t="n"/>
-      <c r="K111" s="221" t="n"/>
+      <c r="K111" s="222" t="n"/>
       <c r="L111" s="17" t="n"/>
       <c r="M111" s="18" t="n"/>
     </row>
@@ -12108,7 +12162,7 @@
         </is>
       </c>
       <c r="J112" s="31" t="n"/>
-      <c r="K112" s="233" t="n"/>
+      <c r="K112" s="234" t="n"/>
       <c r="L112" s="29" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -12117,23 +12171,23 @@
       <c r="M112" s="18" t="n"/>
     </row>
     <row r="113" ht="24.75" customHeight="1" s="70">
-      <c r="A113" s="223" t="n"/>
-      <c r="B113" s="223" t="n"/>
-      <c r="C113" s="223" t="n"/>
+      <c r="A113" s="224" t="n"/>
+      <c r="B113" s="224" t="n"/>
+      <c r="C113" s="224" t="n"/>
       <c r="D113" s="12" t="inlineStr">
         <is>
           <t>中国科学院微生物研究所</t>
         </is>
       </c>
-      <c r="E113" s="223" t="n"/>
-      <c r="F113" s="223" t="n"/>
-      <c r="G113" s="223" t="n"/>
-      <c r="H113" s="223" t="n"/>
-      <c r="I113" s="223" t="n"/>
-      <c r="J113" s="223" t="n"/>
-      <c r="K113" s="223" t="n"/>
-      <c r="L113" s="223" t="n"/>
-      <c r="M113" s="223" t="n"/>
+      <c r="E113" s="224" t="n"/>
+      <c r="F113" s="224" t="n"/>
+      <c r="G113" s="224" t="n"/>
+      <c r="H113" s="224" t="n"/>
+      <c r="I113" s="224" t="n"/>
+      <c r="J113" s="224" t="n"/>
+      <c r="K113" s="224" t="n"/>
+      <c r="L113" s="224" t="n"/>
+      <c r="M113" s="224" t="n"/>
     </row>
     <row r="114" ht="24.75" customHeight="1" s="70">
       <c r="A114" s="11" t="n">
@@ -12176,7 +12230,7 @@
       </c>
       <c r="I114" s="28" t="n"/>
       <c r="J114" s="15" t="n"/>
-      <c r="K114" s="221" t="n"/>
+      <c r="K114" s="222" t="n"/>
       <c r="L114" s="17" t="n"/>
       <c r="M114" s="18" t="n"/>
     </row>
@@ -12227,7 +12281,7 @@
       <c r="J115" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K115" s="225" t="n">
+      <c r="K115" s="226" t="n">
         <v>44690</v>
       </c>
       <c r="L115" s="27" t="inlineStr">
@@ -12238,23 +12292,23 @@
       <c r="M115" s="18" t="n"/>
     </row>
     <row r="116" ht="24.75" customHeight="1" s="70">
-      <c r="A116" s="223" t="n"/>
-      <c r="B116" s="223" t="n"/>
-      <c r="C116" s="223" t="n"/>
+      <c r="A116" s="224" t="n"/>
+      <c r="B116" s="224" t="n"/>
+      <c r="C116" s="224" t="n"/>
       <c r="D116" s="12" t="inlineStr">
         <is>
           <t>中国农业大学</t>
         </is>
       </c>
-      <c r="E116" s="223" t="n"/>
-      <c r="F116" s="223" t="n"/>
-      <c r="G116" s="223" t="n"/>
-      <c r="H116" s="223" t="n"/>
-      <c r="I116" s="223" t="n"/>
-      <c r="J116" s="223" t="n"/>
-      <c r="K116" s="223" t="n"/>
-      <c r="L116" s="223" t="n"/>
-      <c r="M116" s="223" t="n"/>
+      <c r="E116" s="224" t="n"/>
+      <c r="F116" s="224" t="n"/>
+      <c r="G116" s="224" t="n"/>
+      <c r="H116" s="224" t="n"/>
+      <c r="I116" s="224" t="n"/>
+      <c r="J116" s="224" t="n"/>
+      <c r="K116" s="224" t="n"/>
+      <c r="L116" s="224" t="n"/>
+      <c r="M116" s="224" t="n"/>
     </row>
     <row r="117" ht="24.75" customHeight="1" s="70">
       <c r="A117" s="11" t="n">
@@ -12303,16 +12357,16 @@
       <c r="J117" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K117" s="224" t="n">
+      <c r="K117" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L117" s="17" t="n"/>
       <c r="M117" s="18" t="n"/>
     </row>
     <row r="118" ht="24.75" customHeight="1" s="70">
-      <c r="A118" s="223" t="n"/>
-      <c r="B118" s="223" t="n"/>
-      <c r="C118" s="223" t="n"/>
+      <c r="A118" s="224" t="n"/>
+      <c r="B118" s="224" t="n"/>
+      <c r="C118" s="224" t="n"/>
       <c r="D118" s="12" t="inlineStr">
         <is>
           <t>东北林业大学</t>
@@ -12323,8 +12377,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F118" s="223" t="n"/>
-      <c r="G118" s="223" t="n"/>
+      <c r="F118" s="224" t="n"/>
+      <c r="G118" s="224" t="n"/>
       <c r="H118" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12338,7 +12392,7 @@
       <c r="J118" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K118" s="224" t="n">
+      <c r="K118" s="225" t="n">
         <v>44834</v>
       </c>
       <c r="L118" s="17" t="n"/>
@@ -12389,7 +12443,7 @@
         </is>
       </c>
       <c r="J119" s="15" t="n"/>
-      <c r="K119" s="221" t="n"/>
+      <c r="K119" s="222" t="n"/>
       <c r="L119" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知页</t>
@@ -12442,7 +12496,7 @@
       </c>
       <c r="I120" s="28" t="n"/>
       <c r="J120" s="15" t="n"/>
-      <c r="K120" s="221" t="n"/>
+      <c r="K120" s="222" t="n"/>
       <c r="L120" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -12497,7 +12551,7 @@
       <c r="J121" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K121" s="224" t="n">
+      <c r="K121" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L121" s="17" t="n"/>
@@ -12550,7 +12604,7 @@
       <c r="J122" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K122" s="224" t="n">
+      <c r="K122" s="225" t="n">
         <v>44621</v>
       </c>
       <c r="L122" s="17" t="n"/>
@@ -12597,7 +12651,7 @@
       </c>
       <c r="I123" s="28" t="n"/>
       <c r="J123" s="15" t="n"/>
-      <c r="K123" s="221" t="n"/>
+      <c r="K123" s="222" t="n"/>
       <c r="L123" s="17" t="n"/>
       <c r="M123" s="18" t="n"/>
     </row>
@@ -12648,7 +12702,7 @@
       <c r="J124" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K124" s="224" t="n">
+      <c r="K124" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L124" s="17" t="n"/>
@@ -12701,7 +12755,7 @@
       <c r="J125" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K125" s="224" t="n">
+      <c r="K125" s="225" t="n">
         <v>44809</v>
       </c>
       <c r="L125" s="17" t="n"/>
@@ -12748,7 +12802,7 @@
       </c>
       <c r="I126" s="28" t="n"/>
       <c r="J126" s="15" t="n"/>
-      <c r="K126" s="221" t="n"/>
+      <c r="K126" s="222" t="n"/>
       <c r="L126" s="26" t="inlineStr">
         <is>
           <t>未找到相应的官网</t>
@@ -12803,7 +12857,7 @@
       <c r="J127" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K127" s="224" t="n">
+      <c r="K127" s="225" t="n">
         <v>44589</v>
       </c>
       <c r="L127" s="17" t="n"/>
@@ -12856,7 +12910,7 @@
       <c r="J128" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K128" s="224" t="n">
+      <c r="K128" s="225" t="n">
         <v>44917</v>
       </c>
       <c r="L128" s="17" t="n"/>
@@ -12909,24 +12963,24 @@
       <c r="J129" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K129" s="224" t="n">
+      <c r="K129" s="225" t="n">
         <v>44586</v>
       </c>
       <c r="L129" s="17" t="n"/>
       <c r="M129" s="18" t="n"/>
     </row>
     <row r="130" ht="24.75" customHeight="1" s="70">
-      <c r="A130" s="223" t="n"/>
-      <c r="B130" s="223" t="n"/>
-      <c r="C130" s="223" t="n"/>
+      <c r="A130" s="224" t="n"/>
+      <c r="B130" s="224" t="n"/>
+      <c r="C130" s="224" t="n"/>
       <c r="D130" s="12" t="inlineStr">
         <is>
           <t>南昌大学</t>
         </is>
       </c>
-      <c r="E130" s="223" t="n"/>
-      <c r="F130" s="223" t="n"/>
-      <c r="G130" s="223" t="n"/>
+      <c r="E130" s="224" t="n"/>
+      <c r="F130" s="224" t="n"/>
+      <c r="G130" s="224" t="n"/>
       <c r="H130" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -12940,7 +12994,7 @@
       <c r="J130" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K130" s="224" t="n">
+      <c r="K130" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L130" s="26" t="inlineStr">
@@ -12991,26 +13045,26 @@
       </c>
       <c r="I131" s="28" t="n"/>
       <c r="J131" s="15" t="n"/>
-      <c r="K131" s="221" t="n"/>
+      <c r="K131" s="222" t="n"/>
       <c r="L131" s="17" t="n"/>
       <c r="M131" s="18" t="n"/>
     </row>
     <row r="132" ht="24.75" customHeight="1" s="70">
-      <c r="A132" s="223" t="n"/>
-      <c r="B132" s="223" t="n"/>
-      <c r="C132" s="223" t="n"/>
+      <c r="A132" s="224" t="n"/>
+      <c r="B132" s="224" t="n"/>
+      <c r="C132" s="224" t="n"/>
       <c r="D132" s="12" t="inlineStr">
         <is>
           <t>浙江大学</t>
         </is>
       </c>
-      <c r="E132" s="223" t="n"/>
-      <c r="F132" s="223" t="n"/>
-      <c r="G132" s="223" t="n"/>
-      <c r="H132" s="223" t="n"/>
+      <c r="E132" s="224" t="n"/>
+      <c r="F132" s="224" t="n"/>
+      <c r="G132" s="224" t="n"/>
+      <c r="H132" s="224" t="n"/>
       <c r="I132" s="28" t="n"/>
       <c r="J132" s="15" t="n"/>
-      <c r="K132" s="221" t="n"/>
+      <c r="K132" s="222" t="n"/>
       <c r="L132" s="17" t="n"/>
       <c r="M132" s="18" t="n"/>
     </row>
@@ -13061,7 +13115,7 @@
       <c r="J133" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K133" s="224" t="n">
+      <c r="K133" s="225" t="n">
         <v>44713</v>
       </c>
       <c r="L133" s="17" t="n"/>
@@ -13108,7 +13162,7 @@
       </c>
       <c r="I134" s="28" t="n"/>
       <c r="J134" s="15" t="n"/>
-      <c r="K134" s="221" t="n"/>
+      <c r="K134" s="222" t="n"/>
       <c r="L134" s="26" t="inlineStr">
         <is>
           <t>开放课题基金的申请每年受理一次，申请截止日期为每年的3月15日。</t>
@@ -13167,16 +13221,16 @@
       <c r="J135" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K135" s="225" t="n">
+      <c r="K135" s="226" t="n">
         <v>44878</v>
       </c>
       <c r="L135" s="18" t="n"/>
       <c r="M135" s="58" t="n"/>
     </row>
     <row r="136" ht="24.75" customHeight="1" s="70">
-      <c r="A136" s="223" t="n"/>
-      <c r="B136" s="223" t="n"/>
-      <c r="C136" s="223" t="n"/>
+      <c r="A136" s="224" t="n"/>
+      <c r="B136" s="224" t="n"/>
+      <c r="C136" s="224" t="n"/>
       <c r="D136" s="12" t="inlineStr">
         <is>
           <t>河南大学</t>
@@ -13187,13 +13241,13 @@
           <t>河南省科技厅</t>
         </is>
       </c>
-      <c r="F136" s="223" t="n"/>
-      <c r="G136" s="223" t="n"/>
-      <c r="H136" s="223" t="n"/>
-      <c r="I136" s="223" t="n"/>
-      <c r="J136" s="223" t="n"/>
-      <c r="K136" s="223" t="n"/>
-      <c r="L136" s="223" t="n"/>
+      <c r="F136" s="224" t="n"/>
+      <c r="G136" s="224" t="n"/>
+      <c r="H136" s="224" t="n"/>
+      <c r="I136" s="224" t="n"/>
+      <c r="J136" s="224" t="n"/>
+      <c r="K136" s="224" t="n"/>
+      <c r="L136" s="224" t="n"/>
       <c r="M136" s="58" t="n"/>
     </row>
     <row r="137" ht="24.75" customHeight="1" s="70">
@@ -13243,7 +13297,7 @@
       <c r="J137" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K137" s="224" t="n">
+      <c r="K137" s="225" t="n">
         <v>44624</v>
       </c>
       <c r="L137" s="17" t="n"/>
@@ -13296,7 +13350,7 @@
       <c r="J138" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K138" s="224" t="n">
+      <c r="K138" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L138" s="26" t="inlineStr">
@@ -13353,7 +13407,7 @@
       <c r="J139" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K139" s="224" t="n">
+      <c r="K139" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L139" s="17" t="n"/>
@@ -13400,26 +13454,26 @@
       </c>
       <c r="I140" s="48" t="n"/>
       <c r="J140" s="31" t="n"/>
-      <c r="K140" s="233" t="n"/>
+      <c r="K140" s="234" t="n"/>
       <c r="L140" s="17" t="n"/>
       <c r="M140" s="18" t="n"/>
     </row>
     <row r="141" ht="24.75" customHeight="1" s="70">
-      <c r="A141" s="223" t="n"/>
-      <c r="B141" s="223" t="n"/>
-      <c r="C141" s="223" t="n"/>
+      <c r="A141" s="224" t="n"/>
+      <c r="B141" s="224" t="n"/>
+      <c r="C141" s="224" t="n"/>
       <c r="D141" s="12" t="inlineStr">
         <is>
           <t>中国科学院武汉病毒研究所</t>
         </is>
       </c>
-      <c r="E141" s="223" t="n"/>
-      <c r="F141" s="223" t="n"/>
-      <c r="G141" s="223" t="n"/>
-      <c r="H141" s="223" t="n"/>
-      <c r="I141" s="223" t="n"/>
-      <c r="J141" s="223" t="n"/>
-      <c r="K141" s="223" t="n"/>
+      <c r="E141" s="224" t="n"/>
+      <c r="F141" s="224" t="n"/>
+      <c r="G141" s="224" t="n"/>
+      <c r="H141" s="224" t="n"/>
+      <c r="I141" s="224" t="n"/>
+      <c r="J141" s="224" t="n"/>
+      <c r="K141" s="224" t="n"/>
       <c r="L141" s="17" t="n"/>
       <c r="M141" s="18" t="n"/>
     </row>
@@ -13470,16 +13524,16 @@
       <c r="J142" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K142" s="224" t="n">
+      <c r="K142" s="225" t="n">
         <v>44745</v>
       </c>
       <c r="L142" s="17" t="n"/>
       <c r="M142" s="18" t="n"/>
     </row>
     <row r="143" ht="24.75" customHeight="1" s="70">
-      <c r="A143" s="223" t="n"/>
-      <c r="B143" s="223" t="n"/>
-      <c r="C143" s="223" t="n"/>
+      <c r="A143" s="224" t="n"/>
+      <c r="B143" s="224" t="n"/>
+      <c r="C143" s="224" t="n"/>
       <c r="D143" s="12" t="inlineStr">
         <is>
           <t>武汉大学</t>
@@ -13490,8 +13544,8 @@
           <t>教育部</t>
         </is>
       </c>
-      <c r="F143" s="223" t="n"/>
-      <c r="G143" s="223" t="n"/>
+      <c r="F143" s="224" t="n"/>
+      <c r="G143" s="224" t="n"/>
       <c r="H143" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13505,7 +13559,7 @@
       <c r="J143" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K143" s="224" t="n">
+      <c r="K143" s="225" t="n">
         <v>44675</v>
       </c>
       <c r="L143" s="17" t="n"/>
@@ -13558,7 +13612,7 @@
       <c r="J144" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K144" s="224" t="n">
+      <c r="K144" s="225" t="n">
         <v>44826</v>
       </c>
       <c r="L144" s="17" t="n"/>
@@ -13611,16 +13665,16 @@
       <c r="J145" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K145" s="224" t="n">
+      <c r="K145" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L145" s="17" t="n"/>
       <c r="M145" s="18" t="n"/>
     </row>
     <row r="146" ht="24.75" customHeight="1" s="70">
-      <c r="A146" s="223" t="n"/>
-      <c r="B146" s="223" t="n"/>
-      <c r="C146" s="223" t="n"/>
+      <c r="A146" s="224" t="n"/>
+      <c r="B146" s="224" t="n"/>
+      <c r="C146" s="224" t="n"/>
       <c r="D146" s="12" t="inlineStr">
         <is>
           <t>华南农业大学</t>
@@ -13631,8 +13685,8 @@
           <t>广东省科技厅</t>
         </is>
       </c>
-      <c r="F146" s="223" t="n"/>
-      <c r="G146" s="223" t="n"/>
+      <c r="F146" s="224" t="n"/>
+      <c r="G146" s="224" t="n"/>
       <c r="H146" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -13646,7 +13700,7 @@
       <c r="J146" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K146" s="224" t="n">
+      <c r="K146" s="225" t="n">
         <v>44876</v>
       </c>
       <c r="L146" s="17" t="n"/>
@@ -13699,7 +13753,7 @@
       <c r="J147" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K147" s="224" t="n">
+      <c r="K147" s="225" t="n">
         <v>44870</v>
       </c>
       <c r="L147" s="17" t="n"/>
@@ -13752,7 +13806,7 @@
       <c r="J148" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K148" s="224" t="n">
+      <c r="K148" s="225" t="n">
         <v>44653</v>
       </c>
       <c r="L148" s="17" t="n"/>
@@ -13805,7 +13859,7 @@
       <c r="J149" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K149" s="224" t="n">
+      <c r="K149" s="225" t="n">
         <v>44844</v>
       </c>
       <c r="L149" s="17" t="n"/>
@@ -13858,7 +13912,7 @@
       <c r="J150" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K150" s="224" t="n">
+      <c r="K150" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L150" s="17" t="n"/>
@@ -13911,7 +13965,7 @@
       <c r="J151" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K151" s="224" t="n">
+      <c r="K151" s="225" t="n">
         <v>44737</v>
       </c>
       <c r="L151" s="17" t="n"/>
@@ -13964,7 +14018,7 @@
       <c r="J152" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K152" s="224" t="n">
+      <c r="K152" s="225" t="n">
         <v>44761</v>
       </c>
       <c r="L152" s="17" t="n"/>
@@ -14017,7 +14071,7 @@
       <c r="J153" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K153" s="224" t="n">
+      <c r="K153" s="225" t="n">
         <v>44590</v>
       </c>
       <c r="L153" s="17" t="n"/>
@@ -14070,7 +14124,7 @@
       <c r="J154" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K154" s="224" t="n">
+      <c r="K154" s="225" t="n">
         <v>44597</v>
       </c>
       <c r="L154" s="17" t="n"/>
@@ -14125,7 +14179,7 @@
           <t>4、5</t>
         </is>
       </c>
-      <c r="K155" s="224" t="n">
+      <c r="K155" s="225" t="n">
         <v>44701</v>
       </c>
       <c r="L155" s="17" t="n"/>
@@ -14178,7 +14232,7 @@
       <c r="J156" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K156" s="224" t="n">
+      <c r="K156" s="225" t="n">
         <v>44924</v>
       </c>
       <c r="L156" s="17" t="n"/>
@@ -14231,7 +14285,7 @@
       <c r="J157" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K157" s="224" t="n">
+      <c r="K157" s="225" t="n">
         <v>44657</v>
       </c>
       <c r="L157" s="17" t="n"/>
@@ -14284,7 +14338,7 @@
       <c r="J158" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K158" s="224" t="n">
+      <c r="K158" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L158" s="17" t="n"/>
@@ -14337,7 +14391,7 @@
       <c r="J159" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K159" s="224" t="n">
+      <c r="K159" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L159" s="59" t="n"/>
@@ -14390,7 +14444,7 @@
       <c r="J160" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K160" s="224" t="n">
+      <c r="K160" s="225" t="n">
         <v>44649</v>
       </c>
       <c r="L160" s="17" t="n"/>
@@ -14443,24 +14497,24 @@
       <c r="J161" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K161" s="224" t="n">
+      <c r="K161" s="225" t="n">
         <v>44789</v>
       </c>
       <c r="L161" s="17" t="n"/>
       <c r="M161" s="18" t="n"/>
     </row>
     <row r="162" ht="24.75" customHeight="1" s="70">
-      <c r="A162" s="223" t="n"/>
-      <c r="B162" s="223" t="n"/>
-      <c r="C162" s="223" t="n"/>
+      <c r="A162" s="224" t="n"/>
+      <c r="B162" s="224" t="n"/>
+      <c r="C162" s="224" t="n"/>
       <c r="D162" s="12" t="inlineStr">
         <is>
           <t>清华大学</t>
         </is>
       </c>
-      <c r="E162" s="223" t="n"/>
-      <c r="F162" s="223" t="n"/>
-      <c r="G162" s="223" t="n"/>
+      <c r="E162" s="224" t="n"/>
+      <c r="F162" s="224" t="n"/>
+      <c r="G162" s="224" t="n"/>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t>是</t>
@@ -14468,7 +14522,7 @@
       </c>
       <c r="I162" s="28" t="n"/>
       <c r="J162" s="15" t="n"/>
-      <c r="K162" s="221" t="n"/>
+      <c r="K162" s="222" t="n"/>
       <c r="L162" s="26" t="inlineStr">
         <is>
           <t>未找到相关通知</t>
@@ -14517,7 +14571,7 @@
       </c>
       <c r="I163" s="28" t="n"/>
       <c r="J163" s="15" t="n"/>
-      <c r="K163" s="221" t="n"/>
+      <c r="K163" s="222" t="n"/>
       <c r="L163" s="17" t="n"/>
       <c r="M163" s="18" t="n"/>
     </row>
@@ -14568,7 +14622,7 @@
       <c r="J164" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K164" s="224" t="n">
+      <c r="K164" s="225" t="n">
         <v>44668</v>
       </c>
       <c r="L164" s="17" t="n"/>
@@ -14617,7 +14671,7 @@
       <c r="J165" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K165" s="224" t="n">
+      <c r="K165" s="225" t="n">
         <v>44660</v>
       </c>
       <c r="L165" s="60" t="inlineStr">
@@ -14678,7 +14732,7 @@
       <c r="J166" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="K166" s="224" t="n">
+      <c r="K166" s="225" t="n">
         <v>44649</v>
       </c>
       <c r="L166" s="40" t="n"/>
@@ -14731,28 +14785,28 @@
       <c r="J167" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="K167" s="225" t="n">
+      <c r="K167" s="226" t="n">
         <v>44709</v>
       </c>
       <c r="L167" s="17" t="n"/>
       <c r="M167" s="18" t="n"/>
     </row>
     <row r="168" ht="24.75" customHeight="1" s="70">
-      <c r="A168" s="223" t="n"/>
-      <c r="B168" s="223" t="n"/>
-      <c r="C168" s="223" t="n"/>
+      <c r="A168" s="224" t="n"/>
+      <c r="B168" s="224" t="n"/>
+      <c r="C168" s="224" t="n"/>
       <c r="D168" s="12" t="inlineStr">
         <is>
           <t>中国科学院半导体研究所</t>
         </is>
       </c>
-      <c r="E168" s="223" t="n"/>
-      <c r="F168" s="223" t="n"/>
-      <c r="G168" s="223" t="n"/>
-      <c r="H168" s="223" t="n"/>
-      <c r="I168" s="223" t="n"/>
-      <c r="J168" s="223" t="n"/>
-      <c r="K168" s="223" t="n"/>
+      <c r="E168" s="224" t="n"/>
+      <c r="F168" s="224" t="n"/>
+      <c r="G168" s="224" t="n"/>
+      <c r="H168" s="224" t="n"/>
+      <c r="I168" s="224" t="n"/>
+      <c r="J168" s="224" t="n"/>
+      <c r="K168" s="224" t="n"/>
       <c r="L168" s="17" t="n"/>
       <c r="M168" s="18" t="n"/>
     </row>
@@ -14803,7 +14857,7 @@
       <c r="J169" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K169" s="224" t="n">
+      <c r="K169" s="225" t="n">
         <v>44821</v>
       </c>
       <c r="L169" s="17" t="n"/>
@@ -14856,28 +14910,28 @@
       <c r="J170" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K170" s="225" t="n">
+      <c r="K170" s="226" t="n">
         <v>44819</v>
       </c>
       <c r="L170" s="17" t="n"/>
       <c r="M170" s="18" t="n"/>
     </row>
     <row r="171" ht="24.75" customHeight="1" s="70">
-      <c r="A171" s="223" t="n"/>
-      <c r="B171" s="223" t="n"/>
-      <c r="C171" s="223" t="n"/>
+      <c r="A171" s="224" t="n"/>
+      <c r="B171" s="224" t="n"/>
+      <c r="C171" s="224" t="n"/>
       <c r="D171" s="12" t="inlineStr">
         <is>
           <t>中国科学院电子学研究所</t>
         </is>
       </c>
-      <c r="E171" s="223" t="n"/>
-      <c r="F171" s="223" t="n"/>
-      <c r="G171" s="223" t="n"/>
-      <c r="H171" s="223" t="n"/>
-      <c r="I171" s="223" t="n"/>
-      <c r="J171" s="223" t="n"/>
-      <c r="K171" s="223" t="n"/>
+      <c r="E171" s="224" t="n"/>
+      <c r="F171" s="224" t="n"/>
+      <c r="G171" s="224" t="n"/>
+      <c r="H171" s="224" t="n"/>
+      <c r="I171" s="224" t="n"/>
+      <c r="J171" s="224" t="n"/>
+      <c r="K171" s="224" t="n"/>
       <c r="L171" s="17" t="n"/>
       <c r="M171" s="18" t="n"/>
     </row>
@@ -14926,7 +14980,7 @@
         </is>
       </c>
       <c r="J172" s="15" t="n"/>
-      <c r="K172" s="221" t="n"/>
+      <c r="K172" s="222" t="n"/>
       <c r="L172" s="26" t="inlineStr">
         <is>
           <t>网站时常故障</t>
@@ -14981,28 +15035,28 @@
       <c r="J173" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="K173" s="225" t="n">
+      <c r="K173" s="226" t="n">
         <v>44881</v>
       </c>
       <c r="L173" s="17" t="n"/>
       <c r="M173" s="18" t="n"/>
     </row>
     <row r="174" ht="24.75" customHeight="1" s="70">
-      <c r="A174" s="223" t="n"/>
-      <c r="B174" s="223" t="n"/>
-      <c r="C174" s="223" t="n"/>
+      <c r="A174" s="224" t="n"/>
+      <c r="B174" s="224" t="n"/>
+      <c r="C174" s="224" t="n"/>
       <c r="D174" s="12" t="inlineStr">
         <is>
           <t>北京大学</t>
         </is>
       </c>
-      <c r="E174" s="223" t="n"/>
-      <c r="F174" s="223" t="n"/>
-      <c r="G174" s="223" t="n"/>
-      <c r="H174" s="223" t="n"/>
-      <c r="I174" s="223" t="n"/>
-      <c r="J174" s="223" t="n"/>
-      <c r="K174" s="223" t="n"/>
+      <c r="E174" s="224" t="n"/>
+      <c r="F174" s="224" t="n"/>
+      <c r="G174" s="224" t="n"/>
+      <c r="H174" s="224" t="n"/>
+      <c r="I174" s="224" t="n"/>
+      <c r="J174" s="224" t="n"/>
+      <c r="K174" s="224" t="n"/>
       <c r="L174" s="17" t="n"/>
       <c r="M174" s="18" t="n"/>
     </row>
@@ -15053,7 +15107,7 @@
       <c r="J175" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K175" s="224" t="n">
+      <c r="K175" s="225" t="n">
         <v>44666</v>
       </c>
       <c r="L175" s="26" t="inlineStr">
@@ -15110,7 +15164,7 @@
       <c r="J176" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K176" s="224" t="n">
+      <c r="K176" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L176" s="26" t="inlineStr">
@@ -15167,7 +15221,7 @@
       <c r="J177" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K177" s="224" t="n">
+      <c r="K177" s="225" t="n">
         <v>44671</v>
       </c>
       <c r="L177" s="17" t="n"/>
@@ -15220,7 +15274,7 @@
       <c r="J178" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K178" s="224" t="n">
+      <c r="K178" s="225" t="n">
         <v>44648</v>
       </c>
       <c r="L178" s="17" t="n"/>
@@ -15273,7 +15327,7 @@
       <c r="J179" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K179" s="224" t="n">
+      <c r="K179" s="225" t="n">
         <v>44812</v>
       </c>
       <c r="L179" s="17" t="n"/>
@@ -15326,7 +15380,7 @@
       <c r="J180" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K180" s="224" t="n">
+      <c r="K180" s="225" t="n">
         <v>44831</v>
       </c>
       <c r="L180" s="17" t="n"/>
@@ -15379,7 +15433,7 @@
       <c r="J181" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K181" s="224" t="n">
+      <c r="K181" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L181" s="17" t="n"/>
@@ -15432,7 +15486,7 @@
       <c r="J182" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K182" s="224" t="n">
+      <c r="K182" s="225" t="n">
         <v>44926</v>
       </c>
       <c r="L182" s="17" t="n"/>
@@ -15479,7 +15533,7 @@
       </c>
       <c r="I183" s="28" t="n"/>
       <c r="J183" s="15" t="n"/>
-      <c r="K183" s="221" t="n"/>
+      <c r="K183" s="222" t="n"/>
       <c r="L183" s="17" t="n"/>
       <c r="M183" s="18" t="n"/>
     </row>
@@ -15530,7 +15584,7 @@
       <c r="J184" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K184" s="224" t="n">
+      <c r="K184" s="225" t="n">
         <v>44718</v>
       </c>
       <c r="L184" s="17" t="n"/>
@@ -15583,7 +15637,7 @@
       <c r="J185" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K185" s="224" t="n">
+      <c r="K185" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L185" s="17" t="n"/>
@@ -15636,7 +15690,7 @@
       <c r="J186" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K186" s="224" t="n">
+      <c r="K186" s="225" t="n">
         <v>44800</v>
       </c>
       <c r="L186" s="17" t="n"/>
@@ -15689,7 +15743,7 @@
       <c r="J187" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K187" s="224" t="n">
+      <c r="K187" s="225" t="n">
         <v>44737</v>
       </c>
       <c r="L187" s="17" t="n"/>
@@ -15742,7 +15796,7 @@
       <c r="J188" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K188" s="224" t="n">
+      <c r="K188" s="225" t="n">
         <v>44573</v>
       </c>
       <c r="L188" s="17" t="n"/>
@@ -15795,7 +15849,7 @@
       <c r="J189" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K189" s="224" t="n">
+      <c r="K189" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L189" s="17" t="n"/>
@@ -15842,7 +15896,7 @@
       </c>
       <c r="I190" s="28" t="n"/>
       <c r="J190" s="15" t="n"/>
-      <c r="K190" s="221" t="n"/>
+      <c r="K190" s="222" t="n"/>
       <c r="L190" s="17" t="n"/>
       <c r="M190" s="18" t="n"/>
     </row>
@@ -15893,7 +15947,7 @@
       <c r="J191" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K191" s="224" t="n">
+      <c r="K191" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L191" s="63" t="inlineStr">
@@ -15944,7 +15998,7 @@
       </c>
       <c r="I192" s="28" t="n"/>
       <c r="J192" s="15" t="n"/>
-      <c r="K192" s="221" t="n"/>
+      <c r="K192" s="222" t="n"/>
       <c r="L192" s="40" t="n"/>
       <c r="M192" s="18" t="n"/>
     </row>
@@ -15995,7 +16049,7 @@
       <c r="J193" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K193" s="224" t="n">
+      <c r="K193" s="225" t="n">
         <v>44694</v>
       </c>
       <c r="L193" s="17" t="n"/>
@@ -16048,7 +16102,7 @@
       <c r="J194" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K194" s="224" t="n">
+      <c r="K194" s="225" t="n">
         <v>44904</v>
       </c>
       <c r="L194" s="17" t="n"/>
@@ -16095,7 +16149,7 @@
       </c>
       <c r="I195" s="28" t="n"/>
       <c r="J195" s="15" t="n"/>
-      <c r="K195" s="221" t="n"/>
+      <c r="K195" s="222" t="n"/>
       <c r="L195" s="17" t="n"/>
       <c r="M195" s="18" t="n"/>
     </row>
@@ -16146,7 +16200,7 @@
       <c r="J196" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K196" s="224" t="n">
+      <c r="K196" s="225" t="n">
         <v>44632</v>
       </c>
       <c r="L196" s="17" t="n"/>
@@ -16199,7 +16253,7 @@
       <c r="J197" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K197" s="224" t="n">
+      <c r="K197" s="225" t="n">
         <v>44764</v>
       </c>
       <c r="L197" s="17" t="n"/>
@@ -16252,7 +16306,7 @@
       <c r="J198" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K198" s="224" t="n">
+      <c r="K198" s="225" t="n">
         <v>44813</v>
       </c>
       <c r="L198" s="17" t="n"/>
@@ -16305,7 +16359,7 @@
       <c r="J199" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K199" s="224" t="n">
+      <c r="K199" s="225" t="n">
         <v>44856</v>
       </c>
       <c r="L199" s="17" t="n"/>
@@ -16358,7 +16412,7 @@
       <c r="J200" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K200" s="224" t="n">
+      <c r="K200" s="225" t="n">
         <v>44730</v>
       </c>
       <c r="L200" s="17" t="n"/>
@@ -16405,7 +16459,7 @@
       </c>
       <c r="I201" s="28" t="n"/>
       <c r="J201" s="15" t="n"/>
-      <c r="K201" s="221" t="n"/>
+      <c r="K201" s="222" t="n"/>
       <c r="L201" s="17" t="n"/>
       <c r="M201" s="18" t="n"/>
     </row>
@@ -16456,7 +16510,7 @@
       <c r="J202" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K202" s="224" t="n">
+      <c r="K202" s="225" t="n">
         <v>44872</v>
       </c>
       <c r="L202" s="17" t="n"/>
@@ -16509,7 +16563,7 @@
       <c r="J203" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K203" s="224" t="n">
+      <c r="K203" s="225" t="n">
         <v>44845</v>
       </c>
       <c r="L203" s="17" t="n"/>
@@ -16562,7 +16616,7 @@
       <c r="J204" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K204" s="224" t="n">
+      <c r="K204" s="225" t="n">
         <v>44688</v>
       </c>
       <c r="L204" s="17" t="n"/>
@@ -16615,7 +16669,7 @@
       <c r="J205" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K205" s="224" t="n">
+      <c r="K205" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L205" s="17" t="n"/>
@@ -16668,7 +16722,7 @@
       <c r="J206" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K206" s="224" t="n">
+      <c r="K206" s="225" t="n">
         <v>44593</v>
       </c>
       <c r="L206" s="17" t="n"/>
@@ -16715,7 +16769,7 @@
       </c>
       <c r="I207" s="28" t="n"/>
       <c r="J207" s="15" t="n"/>
-      <c r="K207" s="221" t="n"/>
+      <c r="K207" s="222" t="n"/>
       <c r="L207" s="26" t="inlineStr">
         <is>
           <t>未找到往年申请通知</t>
@@ -16774,7 +16828,7 @@
       <c r="J208" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K208" s="224" t="n">
+      <c r="K208" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L208" s="26" t="inlineStr">
@@ -16825,7 +16879,7 @@
       </c>
       <c r="I209" s="28" t="n"/>
       <c r="J209" s="15" t="n"/>
-      <c r="K209" s="221" t="n"/>
+      <c r="K209" s="222" t="n"/>
       <c r="L209" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -16880,7 +16934,7 @@
       <c r="J210" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K210" s="224" t="n">
+      <c r="K210" s="225" t="n">
         <v>44831</v>
       </c>
       <c r="L210" s="17" t="n"/>
@@ -16933,7 +16987,7 @@
       <c r="J211" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K211" s="224" t="n">
+      <c r="K211" s="225" t="n">
         <v>44815</v>
       </c>
       <c r="L211" s="17" t="n"/>
@@ -16986,7 +17040,7 @@
       <c r="J212" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K212" s="224" t="n">
+      <c r="K212" s="225" t="n">
         <v>44850</v>
       </c>
       <c r="L212" s="17" t="n"/>
@@ -17039,7 +17093,7 @@
       <c r="J213" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K213" s="224" t="n">
+      <c r="K213" s="225" t="n">
         <v>44845</v>
       </c>
       <c r="L213" s="17" t="n"/>
@@ -17092,7 +17146,7 @@
       <c r="J214" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K214" s="224" t="n">
+      <c r="K214" s="225" t="n">
         <v>44772</v>
       </c>
       <c r="L214" s="26" t="inlineStr">
@@ -17149,7 +17203,7 @@
       <c r="J215" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K215" s="224" t="n">
+      <c r="K215" s="225" t="n">
         <v>44896</v>
       </c>
       <c r="L215" s="17" t="n"/>
@@ -17202,7 +17256,7 @@
       <c r="J216" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K216" s="224" t="n">
+      <c r="K216" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L216" s="17" t="n"/>
@@ -17249,7 +17303,7 @@
       </c>
       <c r="I217" s="34" t="n"/>
       <c r="J217" s="15" t="n"/>
-      <c r="K217" s="221" t="n"/>
+      <c r="K217" s="222" t="n"/>
       <c r="L217" s="17" t="n"/>
       <c r="M217" s="18" t="n"/>
     </row>
@@ -17300,7 +17354,7 @@
       <c r="J218" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K218" s="224" t="n">
+      <c r="K218" s="225" t="n">
         <v>44843</v>
       </c>
       <c r="L218" s="17" t="n"/>
@@ -17353,7 +17407,7 @@
       <c r="J219" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K219" s="224" t="n">
+      <c r="K219" s="225" t="n">
         <v>44680</v>
       </c>
       <c r="L219" s="17" t="n"/>
@@ -17406,7 +17460,7 @@
       <c r="J220" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K220" s="224" t="n">
+      <c r="K220" s="225" t="n">
         <v>44722</v>
       </c>
       <c r="L220" s="17" t="n"/>
@@ -17459,7 +17513,7 @@
       <c r="J221" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K221" s="224" t="n">
+      <c r="K221" s="225" t="n">
         <v>44646</v>
       </c>
       <c r="L221" s="17" t="n"/>
@@ -17512,7 +17566,7 @@
       <c r="J222" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K222" s="224" t="n">
+      <c r="K222" s="225" t="n">
         <v>44637</v>
       </c>
       <c r="L222" s="17" t="n"/>
@@ -17565,7 +17619,7 @@
       <c r="J223" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K223" s="224" t="n">
+      <c r="K223" s="225" t="n">
         <v>44847</v>
       </c>
       <c r="L223" s="17" t="n"/>
@@ -17618,7 +17672,7 @@
       <c r="J224" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K224" s="224" t="n">
+      <c r="K224" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L224" s="17" t="n"/>
@@ -17671,7 +17725,7 @@
       <c r="J225" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K225" s="224" t="n">
+      <c r="K225" s="225" t="n">
         <v>44811</v>
       </c>
       <c r="L225" s="17" t="n"/>
@@ -17724,7 +17778,7 @@
       <c r="J226" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K226" s="224" t="n">
+      <c r="K226" s="225" t="n">
         <v>44857</v>
       </c>
       <c r="L226" s="17" t="n"/>
@@ -17777,28 +17831,28 @@
       <c r="J227" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="K227" s="225" t="n">
+      <c r="K227" s="226" t="n">
         <v>44808</v>
       </c>
       <c r="L227" s="17" t="n"/>
       <c r="M227" s="18" t="n"/>
     </row>
     <row r="228" ht="24.75" customHeight="1" s="70">
-      <c r="A228" s="223" t="n"/>
-      <c r="B228" s="223" t="n"/>
-      <c r="C228" s="223" t="n"/>
+      <c r="A228" s="224" t="n"/>
+      <c r="B228" s="224" t="n"/>
+      <c r="C228" s="224" t="n"/>
       <c r="D228" s="12" t="inlineStr">
         <is>
           <t>南京水利科学研究院</t>
         </is>
       </c>
-      <c r="E228" s="223" t="n"/>
-      <c r="F228" s="223" t="n"/>
-      <c r="G228" s="223" t="n"/>
-      <c r="H228" s="223" t="n"/>
-      <c r="I228" s="223" t="n"/>
-      <c r="J228" s="223" t="n"/>
-      <c r="K228" s="223" t="n"/>
+      <c r="E228" s="224" t="n"/>
+      <c r="F228" s="224" t="n"/>
+      <c r="G228" s="224" t="n"/>
+      <c r="H228" s="224" t="n"/>
+      <c r="I228" s="224" t="n"/>
+      <c r="J228" s="224" t="n"/>
+      <c r="K228" s="224" t="n"/>
       <c r="L228" s="17" t="n"/>
       <c r="M228" s="18" t="n"/>
     </row>
@@ -17849,7 +17903,7 @@
       <c r="J229" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K229" s="224" t="n">
+      <c r="K229" s="225" t="n">
         <v>44846</v>
       </c>
       <c r="L229" s="17" t="n"/>
@@ -17889,7 +17943,7 @@
           <t>2008DA105277</t>
         </is>
       </c>
-      <c r="H230" s="235" t="inlineStr">
+      <c r="H230" s="236" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17902,28 +17956,28 @@
       <c r="J230" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="K230" s="225" t="n">
+      <c r="K230" s="226" t="n">
         <v>44724</v>
       </c>
       <c r="L230" s="17" t="n"/>
       <c r="M230" s="18" t="n"/>
     </row>
     <row r="231" ht="24.75" customHeight="1" s="70">
-      <c r="A231" s="223" t="n"/>
-      <c r="B231" s="223" t="n"/>
-      <c r="C231" s="223" t="n"/>
+      <c r="A231" s="224" t="n"/>
+      <c r="B231" s="224" t="n"/>
+      <c r="C231" s="224" t="n"/>
       <c r="D231" s="12" t="inlineStr">
         <is>
           <t>中国矿业大学（北京）</t>
         </is>
       </c>
-      <c r="E231" s="223" t="n"/>
-      <c r="F231" s="223" t="n"/>
-      <c r="G231" s="223" t="n"/>
-      <c r="H231" s="223" t="n"/>
-      <c r="I231" s="223" t="n"/>
-      <c r="J231" s="223" t="n"/>
-      <c r="K231" s="223" t="n"/>
+      <c r="E231" s="224" t="n"/>
+      <c r="F231" s="224" t="n"/>
+      <c r="G231" s="224" t="n"/>
+      <c r="H231" s="224" t="n"/>
+      <c r="I231" s="224" t="n"/>
+      <c r="J231" s="224" t="n"/>
+      <c r="K231" s="224" t="n"/>
       <c r="L231" s="17" t="n"/>
       <c r="M231" s="18" t="n"/>
     </row>
@@ -17974,7 +18028,7 @@
       <c r="J232" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K232" s="224" t="n">
+      <c r="K232" s="225" t="n">
         <v>44828</v>
       </c>
       <c r="L232" s="17" t="n"/>
@@ -18027,7 +18081,7 @@
       <c r="J233" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K233" s="224" t="n">
+      <c r="K233" s="225" t="n">
         <v>44833</v>
       </c>
       <c r="L233" s="17" t="n"/>
@@ -18074,7 +18128,7 @@
       </c>
       <c r="I234" s="34" t="n"/>
       <c r="J234" s="15" t="n"/>
-      <c r="K234" s="221" t="n"/>
+      <c r="K234" s="222" t="n"/>
       <c r="L234" s="17" t="n"/>
       <c r="M234" s="18" t="n"/>
     </row>
@@ -18125,7 +18179,7 @@
       <c r="J235" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K235" s="224" t="n">
+      <c r="K235" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L235" s="26" t="inlineStr">
@@ -18182,7 +18236,7 @@
       <c r="J236" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K236" s="224" t="n">
+      <c r="K236" s="225" t="n">
         <v>44622</v>
       </c>
       <c r="L236" s="17" t="n"/>
@@ -18235,7 +18289,7 @@
       <c r="J237" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K237" s="224" t="n">
+      <c r="K237" s="225" t="n">
         <v>44689</v>
       </c>
       <c r="L237" s="17" t="n"/>
@@ -18288,7 +18342,7 @@
       <c r="J238" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K238" s="224" t="n">
+      <c r="K238" s="225" t="n">
         <v>44861</v>
       </c>
       <c r="L238" s="17" t="n"/>
@@ -18341,7 +18395,7 @@
       <c r="J239" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K239" s="224" t="n">
+      <c r="K239" s="225" t="n">
         <v>44826</v>
       </c>
       <c r="L239" s="17" t="n"/>
@@ -18388,7 +18442,7 @@
       </c>
       <c r="I240" s="28" t="n"/>
       <c r="J240" s="15" t="n"/>
-      <c r="K240" s="221" t="n"/>
+      <c r="K240" s="222" t="n"/>
       <c r="L240" s="26" t="inlineStr">
         <is>
           <t>未找到相关往年通知</t>
@@ -18447,7 +18501,7 @@
       <c r="J241" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K241" s="224" t="n">
+      <c r="K241" s="225" t="n">
         <v>44848</v>
       </c>
       <c r="L241" s="17" t="n"/>
@@ -18500,7 +18554,7 @@
       <c r="J242" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K242" s="224" t="n">
+      <c r="K242" s="225" t="n">
         <v>44820</v>
       </c>
       <c r="L242" s="17" t="n"/>
@@ -18553,7 +18607,7 @@
       <c r="J243" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="K243" s="224" t="n">
+      <c r="K243" s="225" t="n">
         <v>44699</v>
       </c>
       <c r="L243" s="17" t="n"/>
@@ -18606,7 +18660,7 @@
       <c r="J244" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K244" s="224" t="n">
+      <c r="K244" s="225" t="n">
         <v>44743</v>
       </c>
       <c r="L244" s="26" t="inlineStr">
@@ -18663,7 +18717,7 @@
       <c r="J245" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K245" s="224" t="n">
+      <c r="K245" s="225" t="n">
         <v>44741</v>
       </c>
       <c r="L245" s="17" t="n"/>
@@ -18716,7 +18770,7 @@
       <c r="J246" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K246" s="224" t="n">
+      <c r="K246" s="225" t="n">
         <v>44771</v>
       </c>
       <c r="L246" s="17" t="n"/>
@@ -18769,7 +18823,7 @@
       <c r="J247" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K247" s="224" t="n">
+      <c r="K247" s="225" t="n">
         <v>44859</v>
       </c>
       <c r="L247" s="17" t="n"/>
@@ -18822,7 +18876,7 @@
       <c r="J248" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K248" s="224" t="n">
+      <c r="K248" s="225" t="n">
         <v>44815</v>
       </c>
       <c r="L248" s="17" t="n"/>
@@ -18875,7 +18929,7 @@
       <c r="J249" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K249" s="224" t="n">
+      <c r="K249" s="225" t="n">
         <v>44742</v>
       </c>
       <c r="L249" s="26" t="inlineStr">
@@ -18926,7 +18980,7 @@
       </c>
       <c r="I250" s="28" t="n"/>
       <c r="J250" s="15" t="n"/>
-      <c r="K250" s="221" t="n"/>
+      <c r="K250" s="222" t="n"/>
       <c r="L250" s="26" t="inlineStr">
         <is>
           <t>未找到相关官网</t>
@@ -18981,7 +19035,7 @@
       <c r="J251" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="K251" s="224" t="n">
+      <c r="K251" s="225" t="n">
         <v>44805</v>
       </c>
       <c r="L251" s="26" t="inlineStr">
@@ -19036,7 +19090,7 @@
       </c>
       <c r="I252" s="28" t="n"/>
       <c r="J252" s="15" t="n"/>
-      <c r="K252" s="221" t="n"/>
+      <c r="K252" s="222" t="n"/>
       <c r="L252" s="17" t="n"/>
       <c r="M252" s="18" t="n"/>
     </row>
@@ -19087,7 +19141,7 @@
       <c r="J253" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K253" s="224" t="n">
+      <c r="K253" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L253" s="17" t="n"/>
@@ -19134,7 +19188,7 @@
       </c>
       <c r="I254" s="28" t="n"/>
       <c r="J254" s="15" t="n"/>
-      <c r="K254" s="221" t="n"/>
+      <c r="K254" s="222" t="n"/>
       <c r="L254" s="17" t="n"/>
       <c r="M254" s="18" t="n"/>
     </row>
@@ -19179,7 +19233,7 @@
       </c>
       <c r="I255" s="28" t="n"/>
       <c r="J255" s="15" t="n"/>
-      <c r="K255" s="221" t="n"/>
+      <c r="K255" s="222" t="n"/>
       <c r="L255" s="17" t="n"/>
       <c r="M255" s="18" t="n"/>
     </row>
@@ -19224,7 +19278,7 @@
       </c>
       <c r="I256" s="28" t="n"/>
       <c r="J256" s="15" t="n"/>
-      <c r="K256" s="221" t="n"/>
+      <c r="K256" s="222" t="n"/>
       <c r="L256" s="17" t="n"/>
       <c r="M256" s="18" t="n"/>
     </row>
@@ -19275,7 +19329,7 @@
       <c r="J257" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K257" s="224" t="n">
+      <c r="K257" s="225" t="n">
         <v>44562</v>
       </c>
       <c r="L257" s="17" t="n"/>
@@ -19328,7 +19382,7 @@
       <c r="J258" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K258" s="224" t="n">
+      <c r="K258" s="225" t="n">
         <v>44665</v>
       </c>
       <c r="L258" s="17" t="n"/>
@@ -19381,7 +19435,7 @@
       <c r="J259" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K259" s="224" t="n">
+      <c r="K259" s="225" t="n">
         <v>44882</v>
       </c>
       <c r="L259" s="17" t="n"/>
@@ -19428,7 +19482,7 @@
       </c>
       <c r="I260" s="28" t="n"/>
       <c r="J260" s="15" t="n"/>
-      <c r="K260" s="221" t="n"/>
+      <c r="K260" s="222" t="n"/>
       <c r="L260" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -19477,7 +19531,7 @@
       </c>
       <c r="I261" s="34" t="n"/>
       <c r="J261" s="15" t="n"/>
-      <c r="K261" s="221" t="n"/>
+      <c r="K261" s="222" t="n"/>
       <c r="L261" s="26" t="inlineStr">
         <is>
           <t>未找到往年的相关通知</t>
@@ -19526,7 +19580,7 @@
       </c>
       <c r="I262" s="28" t="n"/>
       <c r="J262" s="15" t="n"/>
-      <c r="K262" s="221" t="n"/>
+      <c r="K262" s="222" t="n"/>
       <c r="L262" s="17" t="n"/>
       <c r="M262" s="18" t="n"/>
     </row>
@@ -19571,7 +19625,7 @@
       </c>
       <c r="I263" s="28" t="n"/>
       <c r="J263" s="15" t="n"/>
-      <c r="K263" s="221" t="n"/>
+      <c r="K263" s="222" t="n"/>
       <c r="L263" s="17" t="n"/>
       <c r="M263" s="18" t="n"/>
     </row>
@@ -19622,7 +19676,7 @@
       <c r="J264" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K264" s="224" t="n">
+      <c r="K264" s="225" t="n">
         <v>44667</v>
       </c>
       <c r="L264" s="26" t="n">
@@ -19677,7 +19731,7 @@
       <c r="J265" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K265" s="224" t="n">
+      <c r="K265" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L265" s="17" t="n"/>
@@ -19728,7 +19782,7 @@
         </is>
       </c>
       <c r="J266" s="15" t="n"/>
-      <c r="K266" s="221" t="n"/>
+      <c r="K266" s="222" t="n"/>
       <c r="L266" s="26" t="inlineStr">
         <is>
           <t>相关通知最近的是2014年的</t>
@@ -19783,7 +19837,7 @@
       <c r="J267" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K267" s="224" t="n">
+      <c r="K267" s="225" t="n">
         <v>44731</v>
       </c>
       <c r="L267" s="17" t="n"/>
@@ -19830,7 +19884,7 @@
       </c>
       <c r="I268" s="28" t="n"/>
       <c r="J268" s="15" t="n"/>
-      <c r="K268" s="221" t="n"/>
+      <c r="K268" s="222" t="n"/>
       <c r="L268" s="17" t="n"/>
       <c r="M268" s="18" t="n"/>
     </row>
@@ -19881,7 +19935,7 @@
       <c r="J269" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K269" s="224" t="n">
+      <c r="K269" s="225" t="n">
         <v>44905</v>
       </c>
       <c r="L269" s="17" t="n"/>
@@ -19934,7 +19988,7 @@
       <c r="J270" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K270" s="224" t="n">
+      <c r="K270" s="225" t="n">
         <v>44721</v>
       </c>
       <c r="L270" s="26" t="inlineStr">
@@ -19985,7 +20039,7 @@
       </c>
       <c r="I271" s="28" t="n"/>
       <c r="J271" s="15" t="n"/>
-      <c r="K271" s="221" t="n"/>
+      <c r="K271" s="222" t="n"/>
       <c r="L271" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20034,7 +20088,7 @@
       </c>
       <c r="I272" s="28" t="n"/>
       <c r="J272" s="15" t="n"/>
-      <c r="K272" s="221" t="n"/>
+      <c r="K272" s="222" t="n"/>
       <c r="L272" s="17" t="n"/>
       <c r="M272" s="18" t="n"/>
     </row>
@@ -20079,7 +20133,7 @@
       </c>
       <c r="I273" s="28" t="n"/>
       <c r="J273" s="15" t="n"/>
-      <c r="K273" s="221" t="n"/>
+      <c r="K273" s="222" t="n"/>
       <c r="L273" s="17" t="n"/>
       <c r="M273" s="18" t="n"/>
     </row>
@@ -20124,7 +20178,7 @@
       </c>
       <c r="I274" s="28" t="n"/>
       <c r="J274" s="15" t="n"/>
-      <c r="K274" s="221" t="n"/>
+      <c r="K274" s="222" t="n"/>
       <c r="L274" s="17" t="n"/>
       <c r="M274" s="18" t="n"/>
     </row>
@@ -20175,7 +20229,7 @@
       <c r="J275" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K275" s="224" t="n">
+      <c r="K275" s="225" t="n">
         <v>44746</v>
       </c>
       <c r="L275" s="26" t="inlineStr">
@@ -20232,7 +20286,7 @@
       <c r="J276" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="K276" s="224" t="n">
+      <c r="K276" s="225" t="n">
         <v>44866</v>
       </c>
       <c r="L276" s="17" t="n"/>
@@ -20279,7 +20333,7 @@
       </c>
       <c r="I277" s="28" t="n"/>
       <c r="J277" s="15" t="n"/>
-      <c r="K277" s="221" t="n"/>
+      <c r="K277" s="222" t="n"/>
       <c r="L277" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20334,7 +20388,7 @@
       <c r="J278" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="K278" s="224" t="n">
+      <c r="K278" s="225" t="n">
         <v>44652</v>
       </c>
       <c r="L278" s="17" t="n"/>
@@ -20383,7 +20437,7 @@
       <c r="J279" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K279" s="224" t="n">
+      <c r="K279" s="225" t="n">
         <v>44599</v>
       </c>
       <c r="L279" s="26" t="inlineStr">
@@ -20438,7 +20492,7 @@
       </c>
       <c r="I280" s="34" t="n"/>
       <c r="J280" s="15" t="n"/>
-      <c r="K280" s="221" t="n"/>
+      <c r="K280" s="222" t="n"/>
       <c r="L280" s="17" t="n"/>
       <c r="M280" s="18" t="n"/>
     </row>
@@ -20489,7 +20543,7 @@
       <c r="J281" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="K281" s="224" t="n">
+      <c r="K281" s="225" t="n">
         <v>44855</v>
       </c>
       <c r="L281" s="17" t="n"/>
@@ -20542,7 +20596,7 @@
       <c r="J282" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K282" s="224" t="n">
+      <c r="K282" s="225" t="n">
         <v>44569</v>
       </c>
       <c r="L282" s="26" t="inlineStr">
@@ -20593,7 +20647,7 @@
       </c>
       <c r="I283" s="28" t="n"/>
       <c r="J283" s="15" t="n"/>
-      <c r="K283" s="221" t="n"/>
+      <c r="K283" s="222" t="n"/>
       <c r="L283" s="26" t="inlineStr">
         <is>
           <t>官网打不开</t>
@@ -20648,7 +20702,7 @@
       <c r="J284" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K284" s="224" t="n">
+      <c r="K284" s="225" t="n">
         <v>44581</v>
       </c>
       <c r="L284" s="17" t="n"/>
@@ -20695,7 +20749,7 @@
       </c>
       <c r="I285" s="28" t="n"/>
       <c r="J285" s="15" t="n"/>
-      <c r="K285" s="221" t="n"/>
+      <c r="K285" s="222" t="n"/>
       <c r="L285" s="17" t="n"/>
       <c r="M285" s="18" t="n"/>
     </row>
@@ -20740,7 +20794,7 @@
       </c>
       <c r="I286" s="28" t="n"/>
       <c r="J286" s="15" t="n"/>
-      <c r="K286" s="221" t="n"/>
+      <c r="K286" s="222" t="n"/>
       <c r="L286" s="26" t="inlineStr">
         <is>
           <t>未找到官网</t>
@@ -20791,7 +20845,7 @@
       <c r="J287" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="K287" s="224" t="n">
+      <c r="K287" s="225" t="n">
         <v>44923</v>
       </c>
       <c r="L287" s="58" t="n"/>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-18）</t>
+          <t>最新更新（2026-10-19）</t>
         </is>
       </c>
     </row>
@@ -2860,51 +2860,68 @@
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" s="70">
-      <c r="A6" s="190" t="n">
+      <c r="A6" s="194" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="189" t="inlineStr">
+      <c r="B6" s="195" t="n"/>
+      <c r="C6" s="196" t="inlineStr">
         <is>
           <t>国自然重大研究计划项目</t>
         </is>
       </c>
-      <c r="D6" s="175" t="inlineStr">
+      <c r="D6" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E6" s="152" t="inlineStr">
+      <c r="E6" s="198" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F6" s="189" t="inlineStr">
+      <c r="F6" s="196" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.培育项目-3年，重点支持项目-4年，集成项目根据实际确定。</t>
         </is>
       </c>
-      <c r="G6" s="189" t="inlineStr">
+      <c r="G6" s="196" t="inlineStr">
         <is>
           <t>培育项目-60万/项
 重点支持项目-250万/项
 （具体资助金额视指南通知）</t>
         </is>
       </c>
-      <c r="H6" s="190" t="inlineStr">
+      <c r="H6" s="194" t="inlineStr">
         <is>
           <t>1-10月</t>
         </is>
       </c>
-      <c r="I6" s="155" t="inlineStr">
+      <c r="I6" s="199" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3981/zdyjjhxm22.html</t>
         </is>
       </c>
-      <c r="J6" s="148" t="n"/>
+      <c r="J6" s="200" t="n"/>
+      <c r="K6" s="195" t="n"/>
+      <c r="L6" s="195" t="n"/>
+      <c r="M6" s="195" t="n"/>
+      <c r="N6" s="195" t="n"/>
+      <c r="O6" s="195" t="n"/>
+      <c r="P6" s="195" t="n"/>
+      <c r="Q6" s="195" t="n"/>
+      <c r="R6" s="195" t="n"/>
+      <c r="S6" s="195" t="n"/>
+      <c r="T6" s="195" t="n"/>
+      <c r="U6" s="195" t="n"/>
+      <c r="V6" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：转发国家自然科学基金委员会“脑科学与类脑研究”国家科技重大专项2027年度第一批项目申报指南的通知（2026-10-19）</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="52.5" customFormat="1" customHeight="1" s="141">
       <c r="A7" s="190" t="n">
@@ -4752,7 +4769,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-18）</t>
+          <t>最新更新（2026-10-19）</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5203,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-18）</t>
+          <t>最新更新（2026-10-19）</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6773,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-18）</t>
+          <t>最新更新（2026-10-19）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-19）</t>
+          <t>最新更新（2026-10-20）</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-19）</t>
+          <t>最新更新（2026-10-20）</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-19）</t>
+          <t>最新更新（2026-10-20）</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-19）</t>
+          <t>最新更新（2026-10-20）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-20）</t>
+          <t>最新更新（2026-10-21）</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-20）</t>
+          <t>最新更新（2026-10-21）</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-20）</t>
+          <t>最新更新（2026-10-21）</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-20）</t>
+          <t>最新更新（2026-10-21）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-21）</t>
+          <t>最新更新（2026-10-23）</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-21）</t>
+          <t>最新更新（2026-10-23）</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-21）</t>
+          <t>最新更新（2026-10-23）</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-21）</t>
+          <t>最新更新（2026-10-23）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -1653,9 +1653,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1666,6 +1663,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-23）</t>
+          <t>最新更新（2026-10-28）</t>
         </is>
       </c>
     </row>
@@ -3210,66 +3210,49 @@
       <c r="J12" s="148" t="n"/>
     </row>
     <row r="13" ht="111" customHeight="1" s="70">
-      <c r="A13" s="194" t="n">
+      <c r="A13" s="190" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="195" t="n"/>
-      <c r="C13" s="196" t="inlineStr">
+      <c r="C13" s="189" t="inlineStr">
         <is>
           <t>广东省量子科学战略专项项目申报指南</t>
         </is>
       </c>
-      <c r="D13" s="197" t="inlineStr">
+      <c r="D13" s="175" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E13" s="198" t="inlineStr">
+      <c r="E13" s="152" t="inlineStr">
         <is>
           <t>澳大教授（主申）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F13" s="196" t="inlineStr">
+      <c r="F13" s="189" t="inlineStr">
         <is>
           <t>重大和重点项目的申报材料应围绕相应指南内容，合理设置课题分工并突出重点，无须覆盖全部研究内容及考核指标。一般类项目以研究领域为导向，资助探索性强、选题新颖、前期研究基础较好的申请项目，优先支持但不限于指南提出的科学问题。项目负责人须全职来自依托单位。</t>
         </is>
       </c>
-      <c r="G13" s="196" t="inlineStr">
+      <c r="G13" s="189" t="inlineStr">
         <is>
           <t>1.重大类项目资助强度约为800万-1000万元/项，项目执行期为5年
 2.重点类项目资助强度约为200万元/项，项目执行期均为3年
 3.一般类项目资助强度不超过50万元/项，项目执行期均为3年</t>
         </is>
       </c>
-      <c r="H13" s="194" t="inlineStr">
+      <c r="H13" s="190" t="inlineStr">
         <is>
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I13" s="203" t="inlineStr">
+      <c r="I13" s="169" t="inlineStr">
         <is>
           <t>https://www.qscgba.org.cn/#/declare/view?alias=48fc5053-c7c2-40b0-b3c7-37e7d5e60ce0</t>
         </is>
       </c>
-      <c r="J13" s="200" t="n"/>
-      <c r="K13" s="195" t="n"/>
-      <c r="L13" s="195" t="n"/>
-      <c r="M13" s="195" t="n"/>
-      <c r="N13" s="195" t="n"/>
-      <c r="O13" s="195" t="n"/>
-      <c r="P13" s="195" t="n"/>
-      <c r="Q13" s="195" t="n"/>
-      <c r="R13" s="195" t="n"/>
-      <c r="S13" s="195" t="n"/>
-      <c r="T13" s="195" t="n"/>
-      <c r="U13" s="195" t="n"/>
-      <c r="V13" s="201" t="inlineStr">
-        <is>
-          <t>● 更新：广东省科学技术厅关于转发2027年度广东省量子科学战略专项项目申报指南的通知（2026-10-15）</t>
-        </is>
-      </c>
+      <c r="J13" s="148" t="n"/>
     </row>
     <row r="14" ht="128" customFormat="1" customHeight="1" s="141">
       <c r="A14" s="190" t="n">
@@ -3496,7 +3479,7 @@
           <t>8-10月</t>
         </is>
       </c>
-      <c r="I18" s="204" t="inlineStr">
+      <c r="I18" s="203" t="inlineStr">
         <is>
           <t>https://service.most.gov.cn/kjjh_tztg_all/20260828/5864.html</t>
         </is>
@@ -3585,12 +3568,12 @@
           <t>澳大教授（参与）</t>
         </is>
       </c>
-      <c r="F20" s="205" t="inlineStr">
+      <c r="F20" s="204" t="inlineStr">
         <is>
           <t>由广东省科学技术厅和澳门科学技术发展基金联合征集、联合评审、联合资助。支持广东省创新主体联合澳门合作伙伴，在生物医药、新一代信息技术、节能环保、海洋科技、新材料、新能源、智能制造等涉及两地民生发展和前沿科技的领域开展联合技术研发及成果产业化合作。本专题优先支持在横琴、南沙等重大合作平台实施或落地转化的项目。</t>
         </is>
       </c>
-      <c r="G20" s="206" t="inlineStr">
+      <c r="G20" s="205" t="inlineStr">
         <is>
           <t>100万/项</t>
         </is>
@@ -3600,7 +3583,7 @@
           <t>11月-次年1月</t>
         </is>
       </c>
-      <c r="I20" s="207" t="inlineStr">
+      <c r="I20" s="206" t="inlineStr">
         <is>
           <t>https://gdstc.gd.gov.cn/zwgk_n/tzgg/content/post_4806341.html</t>
         </is>
@@ -3692,7 +3675,7 @@
 重点支持领域（2025）：网络与通信、半导体与集成电路、软件与信息服务、人工智能、高端装备与仪器、低空经济与空天、机器人、高性能材料、生物医药、海洋、合成生物、智能机器人、脑科学与脑机工程等。</t>
         </is>
       </c>
-      <c r="G22" s="206" t="inlineStr">
+      <c r="G22" s="205" t="inlineStr">
         <is>
           <t>资助强度300万</t>
         </is>
@@ -3702,7 +3685,7 @@
           <t>4-5月</t>
         </is>
       </c>
-      <c r="I22" s="203" t="inlineStr">
+      <c r="I22" s="207" t="inlineStr">
         <is>
           <t>https://stic.sz.gov.cn/xxgk/tzgg/content/post_12116696.html?sessionid=</t>
         </is>
@@ -3795,7 +3778,7 @@
           <t>支持省内高校、科研机构及企业与香港特区、澳门特区、台湾地区开展科技创新合作，结合基础研究和应用技术战略性发展需求，开展联合研发。</t>
         </is>
       </c>
-      <c r="G24" s="206" t="inlineStr">
+      <c r="G24" s="205" t="inlineStr">
         <is>
           <t>30万元-100万元</t>
         </is>
@@ -3805,7 +3788,7 @@
           <t>9-10月</t>
         </is>
       </c>
-      <c r="I24" s="203" t="inlineStr">
+      <c r="I24" s="207" t="inlineStr">
         <is>
           <t>https://kjt.sc.gov.cn/kjt/gstz/2025/9/17/1959a2ee35844389a80b43eb99950708.shtml</t>
         </is>
@@ -3864,7 +3847,7 @@
           <t>3-4月</t>
         </is>
       </c>
-      <c r="I25" s="203" t="inlineStr">
+      <c r="I25" s="207" t="inlineStr">
         <is>
           <t>https://kxjst.jiangsu.gov.cn/art/2026/4/1/art_82568_11752538.html</t>
         </is>
@@ -4769,7 +4752,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-23）</t>
+          <t>最新更新（2026-10-28）</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5186,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-23）</t>
+          <t>最新更新（2026-10-28）</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5278,7 @@
           <t>11月-次年2月</t>
         </is>
       </c>
-      <c r="G4" s="203" t="inlineStr">
+      <c r="G4" s="207" t="inlineStr">
         <is>
           <t>https://www.heprize.org/Home</t>
         </is>
@@ -6773,7 +6756,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-23）</t>
+          <t>最新更新（2026-10-28）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-28）</t>
+          <t>最新更新（2026-10-29）</t>
         </is>
       </c>
     </row>
@@ -2797,67 +2797,50 @@
       </c>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="194" t="n">
+      <c r="A5" s="190" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="195" t="n"/>
-      <c r="C5" s="196" t="inlineStr">
+      <c r="C5" s="189" t="inlineStr">
         <is>
           <t>国自然重点项目</t>
         </is>
       </c>
-      <c r="D5" s="197" t="inlineStr">
+      <c r="D5" s="175" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="198" t="inlineStr">
+      <c r="E5" s="152" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F5" s="196" t="inlineStr">
+      <c r="F5" s="189" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为5年</t>
         </is>
       </c>
-      <c r="G5" s="196" t="inlineStr">
+      <c r="G5" s="189" t="inlineStr">
         <is>
           <t>平均资助强度
 约220万</t>
         </is>
       </c>
-      <c r="H5" s="194" t="inlineStr">
+      <c r="H5" s="190" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I5" s="199" t="inlineStr">
+      <c r="I5" s="155" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3979/zdxm222.html</t>
         </is>
       </c>
-      <c r="J5" s="200" t="n"/>
-      <c r="K5" s="195" t="n"/>
-      <c r="L5" s="195" t="n"/>
-      <c r="M5" s="195" t="n"/>
-      <c r="N5" s="195" t="n"/>
-      <c r="O5" s="195" t="n"/>
-      <c r="P5" s="195" t="n"/>
-      <c r="Q5" s="195" t="n"/>
-      <c r="R5" s="195" t="n"/>
-      <c r="S5" s="195" t="n"/>
-      <c r="T5" s="195" t="n"/>
-      <c r="U5" s="195" t="n"/>
-      <c r="V5" s="201" t="inlineStr">
-        <is>
-          <t>● 更新：关于征集2028年度自治区自然科学基金重点项目指南建议的通知（2026-10-14）</t>
-        </is>
-      </c>
+      <c r="J5" s="148" t="n"/>
     </row>
     <row r="6" ht="76" customHeight="1" s="70">
       <c r="A6" s="194" t="n">
@@ -4752,7 +4735,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-28）</t>
+          <t>最新更新（2026-10-29）</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5169,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-28）</t>
+          <t>最新更新（2026-10-29）</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6739,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-28）</t>
+          <t>最新更新（2026-10-29）</t>
         </is>
       </c>
     </row>

--- a/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
+++ b/export/澳大科研人员依托研究院可申报或参与的科技项目清单-含最新更新标注.xlsx
@@ -2681,7 +2681,7 @@
       <c r="U2" s="151" t="n"/>
       <c r="V2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-29）</t>
+          <t>最新更新（2026-10-30）</t>
         </is>
       </c>
     </row>
@@ -2797,50 +2797,67 @@
       </c>
     </row>
     <row r="5" ht="56.25" customHeight="1" s="70">
-      <c r="A5" s="190" t="n">
+      <c r="A5" s="194" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="189" t="inlineStr">
+      <c r="B5" s="195" t="n"/>
+      <c r="C5" s="196" t="inlineStr">
         <is>
           <t>国自然重点项目</t>
         </is>
       </c>
-      <c r="D5" s="175" t="inlineStr">
+      <c r="D5" s="197" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="E5" s="152" t="inlineStr">
+      <c r="E5" s="198" t="inlineStr">
         <is>
           <t>教授（主申/参与）
 澳大博后（参与）
 研究院全职人员（主申/参与）</t>
         </is>
       </c>
-      <c r="F5" s="189" t="inlineStr">
+      <c r="F5" s="196" t="inlineStr">
         <is>
           <t>1.具有承担基础课题研究的经历
 2.具有高级职称或博士学位
 3.项目执行期为5年</t>
         </is>
       </c>
-      <c r="G5" s="189" t="inlineStr">
+      <c r="G5" s="196" t="inlineStr">
         <is>
           <t>平均资助强度
 约220万</t>
         </is>
       </c>
-      <c r="H5" s="190" t="inlineStr">
+      <c r="H5" s="194" t="inlineStr">
         <is>
           <t>1-3月</t>
         </is>
       </c>
-      <c r="I5" s="155" t="inlineStr">
+      <c r="I5" s="199" t="inlineStr">
         <is>
           <t>https://www.nsfc.gov.cn/p1/2931/3971/3979/zdxm222.html</t>
         </is>
       </c>
-      <c r="J5" s="148" t="n"/>
+      <c r="J5" s="200" t="n"/>
+      <c r="K5" s="195" t="n"/>
+      <c r="L5" s="195" t="n"/>
+      <c r="M5" s="195" t="n"/>
+      <c r="N5" s="195" t="n"/>
+      <c r="O5" s="195" t="n"/>
+      <c r="P5" s="195" t="n"/>
+      <c r="Q5" s="195" t="n"/>
+      <c r="R5" s="195" t="n"/>
+      <c r="S5" s="195" t="n"/>
+      <c r="T5" s="195" t="n"/>
+      <c r="U5" s="195" t="n"/>
+      <c r="V5" s="201" t="inlineStr">
+        <is>
+          <t>● 更新：关于征集2028年度自治区自然科学基金重点项目指南建议的通知（2026-10-14）</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="76" customHeight="1" s="70">
       <c r="A6" s="194" t="n">
@@ -4735,7 +4752,7 @@
       <c r="I2" s="118" t="n"/>
       <c r="U2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-29）</t>
+          <t>最新更新（2026-10-30）</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5186,7 @@
       <c r="H2" s="118" t="n"/>
       <c r="T2" s="193" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-29）</t>
+          <t>最新更新（2026-10-30）</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6756,7 @@
       <c r="T2" s="10" t="n"/>
       <c r="U2" s="220" t="inlineStr">
         <is>
-          <t>最新更新（2026-10-29）</t>
+          <t>最新更新（2026-10-30）</t>
         </is>
       </c>
     </row>
